--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053889870644</t>
+    <t xml:space="preserve">0.158053904771805</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.158481389284134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155000299215317</t>
+    <t xml:space="preserve">0.155000284314156</t>
   </si>
   <si>
     <t xml:space="preserve">0.153229206800461</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.148099184036255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150297775864601</t>
+    <t xml:space="preserve">0.150297746062279</t>
   </si>
   <si>
     <t xml:space="preserve">0.151580274105072</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">0.147366315126419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142358422279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132831245660782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134541243314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125319391489029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131121203303337</t>
+    <t xml:space="preserve">0.142358437180519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132831215858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134541228413582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12531940639019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131121218204498</t>
   </si>
   <si>
     <t xml:space="preserve">0.134358018636703</t>
@@ -92,58 +92,58 @@
     <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13802233338356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778043746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140465199947357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139854475855827</t>
+    <t xml:space="preserve">0.138022348284721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778028845787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140465214848518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
     <t xml:space="preserve">0.136190190911293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792992353439</t>
+    <t xml:space="preserve">0.131793007254601</t>
   </si>
   <si>
     <t xml:space="preserve">0.129166916012764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12928906083107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967950344086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754380106926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116158626973629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118479363620281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125807955861092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125197231769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960864782333</t>
+    <t xml:space="preserve">0.129289075732231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967935442924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754372656345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116158619523048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479356169701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125807970762253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125197246670723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960849881172</t>
   </si>
   <si>
     <t xml:space="preserve">0.127029404044151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125014036893845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999088287354</t>
+    <t xml:space="preserve">0.125014021992683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999073386192</t>
   </si>
   <si>
     <t xml:space="preserve">0.12910583615303</t>
@@ -155,121 +155,121 @@
     <t xml:space="preserve">0.130205124616623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130510494112968</t>
+    <t xml:space="preserve">0.130510479211807</t>
   </si>
   <si>
     <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133808389306068</t>
+    <t xml:space="preserve">0.133808374404907</t>
   </si>
   <si>
     <t xml:space="preserve">0.138755202293396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139671295881271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13673985004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136495545506477</t>
+    <t xml:space="preserve">0.139671251177788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136739835143089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136495515704155</t>
   </si>
   <si>
     <t xml:space="preserve">0.140159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141747713088989</t>
+    <t xml:space="preserve">0.14174772799015</t>
   </si>
   <si>
     <t xml:space="preserve">0.147122040390968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149015262722969</t>
+    <t xml:space="preserve">0.14901527762413</t>
   </si>
   <si>
     <t xml:space="preserve">0.146572396159172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14571738243103</t>
+    <t xml:space="preserve">0.145717397332191</t>
   </si>
   <si>
     <t xml:space="preserve">0.1432134360075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144129514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892714262009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139793410897255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968757629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068031191826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13594588637352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135823741555214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133136570453644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130693688988686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128861546516418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125258296728134</t>
+    <t xml:space="preserve">0.144129529595375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140892699360847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139793395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968742728233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068016290665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135945871472359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135823756456375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133136585354805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130693703889847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12886156141758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125258341431618</t>
   </si>
   <si>
     <t xml:space="preserve">0.133930519223213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137472704052925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142480567097664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142114162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141320198774338</t>
+    <t xml:space="preserve">0.137472674250603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142480581998825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142114147543907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141320213675499</t>
   </si>
   <si>
     <t xml:space="preserve">0.142175227403641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138327717781067</t>
+    <t xml:space="preserve">0.138327687978745</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236277461052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1382055580616</t>
+    <t xml:space="preserve">0.138205528259277</t>
   </si>
   <si>
     <t xml:space="preserve">0.140526756644249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139899417757988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136135265231133</t>
+    <t xml:space="preserve">0.139899402856827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
     <t xml:space="preserve">0.136637166142464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133876800537109</t>
+    <t xml:space="preserve">0.133876830339432</t>
   </si>
   <si>
     <t xml:space="preserve">0.133814096450806</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">0.132998526096344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129234418272972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128732547163963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125156626105309</t>
+    <t xml:space="preserve">0.129234433174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128732532262802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125156611204147</t>
   </si>
   <si>
     <t xml:space="preserve">0.126662269234657</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">0.126725032925606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127352371811867</t>
+    <t xml:space="preserve">0.127352356910706</t>
   </si>
   <si>
     <t xml:space="preserve">0.127979725599289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12659952044487</t>
+    <t xml:space="preserve">0.126599535346031</t>
   </si>
   <si>
     <t xml:space="preserve">0.127916976809502</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131743833422661</t>
+    <t xml:space="preserve">0.1317438185215</t>
   </si>
   <si>
     <t xml:space="preserve">0.131116464734077</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">0.134065017104149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131179213523865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133688598871231</t>
+    <t xml:space="preserve">0.131179183721542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133688628673553</t>
   </si>
   <si>
     <t xml:space="preserve">0.134880587458611</t>
@@ -335,73 +335,73 @@
     <t xml:space="preserve">0.130614593625069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132873058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128481596708298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121078871190548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12020055949688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831655502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413886606693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233206629753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366173744202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794039607048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052504301071</t>
+    <t xml:space="preserve">0.132873073220253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128481581807137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121078863739967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120200574398041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1218316629529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413864254951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233199179173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366196095943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794047057629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114052496850491</t>
   </si>
   <si>
     <t xml:space="preserve">0.105395063757896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104893177747726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041232943535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904471457005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354894936085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727533698082</t>
+    <t xml:space="preserve">0.104893192648888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041218042374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904478907585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354880034924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727541148663</t>
   </si>
   <si>
     <t xml:space="preserve">0.107277125120163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102822914719582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501708686352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716277241707</t>
+    <t xml:space="preserve">0.102822929620743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501716136932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
   </si>
   <si>
     <t xml:space="preserve">0.110790275037289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11455437541008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923286855221</t>
+    <t xml:space="preserve">0.114554382860661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11292327940464</t>
   </si>
   <si>
     <t xml:space="preserve">0.114303462207317</t>
@@ -410,34 +410,34 @@
     <t xml:space="preserve">0.118632160127163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11656192690134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116373710334301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746349096298</t>
+    <t xml:space="preserve">0.116561904549599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116373717784882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746356546879</t>
   </si>
   <si>
     <t xml:space="preserve">0.115432687103748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114805318415165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185508668423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569441139698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820384144783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934565663338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159141778946</t>
+    <t xml:space="preserve">0.114805325865746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185501217842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569448590279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820376694202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934558212757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159164130688</t>
   </si>
   <si>
     <t xml:space="preserve">0.107088901102543</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.106147885322571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104140348732471</t>
+    <t xml:space="preserve">0.104140363633633</t>
   </si>
   <si>
     <t xml:space="preserve">0.105645999312401</t>
@@ -455,40 +455,40 @@
     <t xml:space="preserve">0.107465304434299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108531802892685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590787112713</t>
+    <t xml:space="preserve">0.108531810343266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590779662132</t>
   </si>
   <si>
     <t xml:space="preserve">0.109535589814186</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104830428957939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092673122883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029916882515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849251806736</t>
+    <t xml:space="preserve">0.104830421507359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092665672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029931783676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10765352845192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849259257317</t>
   </si>
   <si>
     <t xml:space="preserve">0.110978491604328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11160583794117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738849759102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864317536354</t>
+    <t xml:space="preserve">0.11160584539175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113738834857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864310085773</t>
   </si>
   <si>
     <t xml:space="preserve">0.11028840392828</t>
@@ -497,85 +497,85 @@
     <t xml:space="preserve">0.110225655138493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108845509588718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723791480064</t>
+    <t xml:space="preserve">0.108845494687557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723784029484</t>
   </si>
   <si>
     <t xml:space="preserve">0.107339844107628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108406357467175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104516766965389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10501866042614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10664975643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10583420842886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085143983364</t>
+    <t xml:space="preserve">0.108406350016594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10451678186655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105018638074398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10664976388216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105834200978279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085136532784</t>
   </si>
   <si>
     <t xml:space="preserve">0.109786532819271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104391291737556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107778981328011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214376330376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116060025990009</t>
+    <t xml:space="preserve">0.104391299188137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107778996229172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214391231537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060055792332</t>
   </si>
   <si>
     <t xml:space="preserve">0.114742591977119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11242138594389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11342515796423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295910716057</t>
+    <t xml:space="preserve">0.112421400845051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113425150513649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295925617218</t>
   </si>
   <si>
     <t xml:space="preserve">0.106022410094738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106712490320206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10683798789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520516633987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265823960304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760203182697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003609597683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579515755177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885656058788</t>
+    <t xml:space="preserve">0.106712475419044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520524084568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265831410885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760180830956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003579795361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579508304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885648608208</t>
   </si>
   <si>
     <t xml:space="preserve">0.103889420628548</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">0.100564457476139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101066336035728</t>
+    <t xml:space="preserve">0.101066321134567</t>
   </si>
   <si>
     <t xml:space="preserve">0.101630948483944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106524288654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109911985695362</t>
+    <t xml:space="preserve">0.106524281203747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109912000596523</t>
   </si>
   <si>
     <t xml:space="preserve">0.110539346933365</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">0.108657285571098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11260960996151</t>
+    <t xml:space="preserve">0.112609587609768</t>
   </si>
   <si>
     <t xml:space="preserve">0.111292161047459</t>
@@ -617,25 +617,25 @@
     <t xml:space="preserve">0.109410099685192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108343616127968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108280874788761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033703804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351137816906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153701141476631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144918203353882</t>
+    <t xml:space="preserve">0.108343623578548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108280882239342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033711254597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351122915745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544315695763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153701156377792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144918218255043</t>
   </si>
   <si>
     <t xml:space="preserve">0.142408803105354</t>
@@ -644,133 +644,133 @@
     <t xml:space="preserve">0.132371172308922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132684841752052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13425324857235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304681301117</t>
+    <t xml:space="preserve">0.132684856653214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134253218770027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304696202278</t>
   </si>
   <si>
     <t xml:space="preserve">0.134692385792732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135821610689163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836668968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855469465256</t>
+    <t xml:space="preserve">0.135821625590324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836654067039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855454564095</t>
   </si>
   <si>
     <t xml:space="preserve">0.143161624670029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141781434416771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133500412106514</t>
+    <t xml:space="preserve">0.141781464219093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133500397205353</t>
   </si>
   <si>
     <t xml:space="preserve">0.129861772060394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130175456404686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131681084632874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130112692713737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13074004650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842964112759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097664237022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975938677788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289623022079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226904034615</t>
+    <t xml:space="preserve">0.130175441503525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131681069731712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130112707614899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130740061402321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842949211597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097649335861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975953578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289637923241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226889133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.126411318778992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125470295548439</t>
+    <t xml:space="preserve">0.125470325350761</t>
   </si>
   <si>
     <t xml:space="preserve">0.126536816358566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215595424175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125972181558609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551859736443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182970643044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171684384346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132245689630508</t>
+    <t xml:space="preserve">0.124215617775917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12597219645977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551874637604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677342414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182985544205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171669483185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13224570453167</t>
   </si>
   <si>
     <t xml:space="preserve">0.135006040334702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133939549326897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127750992775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136260777711868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943336248398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766405940056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13801734149456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777692198753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145733758807182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144165396690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143977180123329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14115409553051</t>
+    <t xml:space="preserve">0.133939564228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127765893936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136260747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943321347237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766420841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138017326593399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777677297592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145733773708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165381789207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141154110431671</t>
   </si>
   <si>
     <t xml:space="preserve">0.137640923261642</t>
@@ -779,58 +779,58 @@
     <t xml:space="preserve">0.136762633919716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134629622101784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002298116684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133437663316727</t>
+    <t xml:space="preserve">0.134629637002945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002283215523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133437678217888</t>
   </si>
   <si>
     <t xml:space="preserve">0.129673570394516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356128931046</t>
+    <t xml:space="preserve">0.128356143832207</t>
   </si>
   <si>
     <t xml:space="preserve">0.132496654987335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135633394122124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137891888618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13770367205143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433906197548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132057502865791</t>
+    <t xml:space="preserve">0.135633379220963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137891873717308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137703642249107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433891296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13205748796463</t>
   </si>
   <si>
     <t xml:space="preserve">0.134504169225693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134502410888672</t>
+    <t xml:space="preserve">0.134502425789833</t>
   </si>
   <si>
     <t xml:space="preserve">0.13298973441124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131729155778885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13072070479393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133178800344467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565427899361</t>
+    <t xml:space="preserve">0.131729170680046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130720719695091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13317883014679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565457701683</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943619370461</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">0.131477057933807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132359459996223</t>
+    <t xml:space="preserve">0.132359445095062</t>
   </si>
   <si>
     <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468592047691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129964396357536</t>
+    <t xml:space="preserve">0.130468621850014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129964351654053</t>
   </si>
   <si>
     <t xml:space="preserve">0.127506271004677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129586204886436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002030611038</t>
+    <t xml:space="preserve">0.129586189985275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002045512199</t>
   </si>
   <si>
     <t xml:space="preserve">0.127947464585304</t>
@@ -881,16 +881,16 @@
     <t xml:space="preserve">0.127128109335899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126056611537933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479605525732</t>
+    <t xml:space="preserve">0.126056626439095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124796032905579</t>
   </si>
   <si>
     <t xml:space="preserve">0.124669998884201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124165765941143</t>
+    <t xml:space="preserve">0.124165773391724</t>
   </si>
   <si>
     <t xml:space="preserve">0.125174224376678</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">0.127380207180977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128451690077782</t>
+    <t xml:space="preserve">0.128451704978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.128136560320854</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">0.127884447574615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127443224191666</t>
+    <t xml:space="preserve">0.127443253993988</t>
   </si>
   <si>
     <t xml:space="preserve">0.126939013600349</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">0.128262609243393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126875996589661</t>
+    <t xml:space="preserve">0.126876011490822</t>
   </si>
   <si>
     <t xml:space="preserve">0.126497820019722</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">0.136456295847893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135636925697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134061217308044</t>
+    <t xml:space="preserve">0.135636940598488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134061202406883</t>
   </si>
   <si>
     <t xml:space="preserve">0.132485508918762</t>
@@ -956,13 +956,13 @@
     <t xml:space="preserve">0.133556991815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135195717215538</t>
+    <t xml:space="preserve">0.135195732116699</t>
   </si>
   <si>
     <t xml:space="preserve">0.136141151189804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134439393877983</t>
+    <t xml:space="preserve">0.134439408779144</t>
   </si>
   <si>
     <t xml:space="preserve">0.137464731931686</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">0.138221085071564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137842923402786</t>
+    <t xml:space="preserve">0.137842908501625</t>
   </si>
   <si>
     <t xml:space="preserve">0.136330232024193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13708658516407</t>
+    <t xml:space="preserve">0.137086570262909</t>
   </si>
   <si>
     <t xml:space="preserve">0.13677142560482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136204168200493</t>
+    <t xml:space="preserve">0.136204198002815</t>
   </si>
   <si>
     <t xml:space="preserve">0.13500665128231</t>
@@ -995,52 +995,52 @@
     <t xml:space="preserve">0.134754523634911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13506968319416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137401700019836</t>
+    <t xml:space="preserve">0.135069668292999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
     <t xml:space="preserve">0.15114189684391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153789073228836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152780637145042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15126796066761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145280256867409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147045060992241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444715499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15939861536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156625360250473</t>
+    <t xml:space="preserve">0.153789088129997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152780622243881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267930865288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145280227065086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14704504609108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444730401039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159398600459099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
     <t xml:space="preserve">0.157570779323578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152843654155731</t>
+    <t xml:space="preserve">0.15284363925457</t>
   </si>
   <si>
     <t xml:space="preserve">0.152654573321342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151898220181465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153095781803131</t>
+    <t xml:space="preserve">0.151898235082626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15309576690197</t>
   </si>
   <si>
     <t xml:space="preserve">0.150259494781494</t>
@@ -1052,31 +1052,31 @@
     <t xml:space="preserve">0.153347879648209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155805975198746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419362545013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156940504908562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159146502614021</t>
+    <t xml:space="preserve">0.155805990099907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419377446175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156940475106239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15914648771286</t>
   </si>
   <si>
     <t xml:space="preserve">0.167655318975449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170050367712975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167214125394821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067299485207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945826530457</t>
+    <t xml:space="preserve">0.170050397515297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167214095592499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067284584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945811629295</t>
   </si>
   <si>
     <t xml:space="preserve">0.178811311721802</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">0.174336314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170176431536674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479294896126</t>
+    <t xml:space="preserve">0.170176446437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479265093803</t>
   </si>
   <si>
     <t xml:space="preserve">0.173643007874489</t>
@@ -1100,31 +1100,31 @@
     <t xml:space="preserve">0.170365527272224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166205674409866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222561478615</t>
+    <t xml:space="preserve">0.166205689311028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222546577454</t>
   </si>
   <si>
     <t xml:space="preserve">0.168600738048553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166520804166794</t>
+    <t xml:space="preserve">0.166520789265633</t>
   </si>
   <si>
     <t xml:space="preserve">0.166394755244255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161730647087097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160091891884804</t>
+    <t xml:space="preserve">0.161730632185936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160091906785965</t>
   </si>
   <si>
     <t xml:space="preserve">0.156688377261162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161226406693459</t>
+    <t xml:space="preserve">0.161226436495781</t>
   </si>
   <si>
     <t xml:space="preserve">0.162487000226974</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">0.163747534155846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163873627781868</t>
+    <t xml:space="preserve">0.163873597979546</t>
   </si>
   <si>
     <t xml:space="preserve">0.16103732585907</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">0.158011972904205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157759845256805</t>
+    <t xml:space="preserve">0.157759860157967</t>
   </si>
   <si>
     <t xml:space="preserve">0.167970433831215</t>
@@ -1151,91 +1151,91 @@
     <t xml:space="preserve">0.167718321084976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165260255336761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163117259740829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163810595870018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159461617469788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147675350308418</t>
+    <t xml:space="preserve">0.165260225534439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163117274641991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163810580968857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159461632370949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147675320506096</t>
   </si>
   <si>
     <t xml:space="preserve">0.147486254572868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150007382035255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150448560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511607527733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15107886493206</t>
+    <t xml:space="preserve">0.150007396936417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150448575615883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511622428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151078879833221</t>
   </si>
   <si>
     <t xml:space="preserve">0.151646107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150322511792183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494705557823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150826767086983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151772186160088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881333112717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583075523376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149629220366478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709139347076</t>
+    <t xml:space="preserve">0.150322526693344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494690656662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150826752185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151772156357765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881318211555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583090424538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149629205465317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709169149399</t>
   </si>
   <si>
     <t xml:space="preserve">0.15101583302021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148935899138451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148116528987885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15076370537281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150637671351433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15120492875576</t>
+    <t xml:space="preserve">0.148935914039612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148116543889046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150763720273972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150637686252594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151204913854599</t>
   </si>
   <si>
     <t xml:space="preserve">0.149944365024567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152213379740715</t>
+    <t xml:space="preserve">0.152213364839554</t>
   </si>
   <si>
     <t xml:space="preserve">0.152528524398804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149377107620239</t>
+    <t xml:space="preserve">0.149377092719078</t>
   </si>
   <si>
     <t xml:space="preserve">0.157255634665489</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">0.156310215592384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164503902196884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243323564529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613034248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982774734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163558468222618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165764451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16544933617115</t>
+    <t xml:space="preserve">0.164503887295723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243338465691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162613049149513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982759833336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163558453321457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165764465928078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165449321269989</t>
   </si>
   <si>
     <t xml:space="preserve">0.166079625487328</t>
@@ -1271,28 +1271,28 @@
     <t xml:space="preserve">0.160722196102142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162297889590263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061948060989</t>
+    <t xml:space="preserve">0.162297904491425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061933159828</t>
   </si>
   <si>
     <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146540835499763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146225675940514</t>
+    <t xml:space="preserve">0.146540850400925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146225690841675</t>
   </si>
   <si>
     <t xml:space="preserve">0.142759129405022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144334837794304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140237972140312</t>
+    <t xml:space="preserve">0.144334852695465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140237987041473</t>
   </si>
   <si>
     <t xml:space="preserve">0.139607712626457</t>
@@ -1301,70 +1301,64 @@
     <t xml:space="preserve">0.138032004237175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139922842383385</t>
+    <t xml:space="preserve">0.139922857284546</t>
   </si>
   <si>
     <t xml:space="preserve">0.135826006531715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138347148895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498550772667</t>
+    <t xml:space="preserve">0.138347163796425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498535871506</t>
   </si>
   <si>
     <t xml:space="preserve">0.141813695430756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140553146600723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141183435916901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138662278652191</t>
+    <t xml:space="preserve">0.140553161501884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141183406114578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138662293553352</t>
   </si>
   <si>
     <t xml:space="preserve">0.135510876774788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134880572557449</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.134250313043594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133935153484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132674589753151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143074259161949</t>
+    <t xml:space="preserve">0.133935168385506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13267457485199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14307427406311</t>
   </si>
   <si>
     <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575853228569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864431142807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146253690123558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14560940861702</t>
+    <t xml:space="preserve">0.143389403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443999648094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575823426247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864401340485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146253705024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145609423518181</t>
   </si>
   <si>
     <t xml:space="preserve">0.140455082058907</t>
@@ -1376,22 +1370,22 @@
     <t xml:space="preserve">0.141421526670456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139166504144669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139488637447357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135622918605804</t>
+    <t xml:space="preserve">0.13916651904583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777245163918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139488652348518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135622903704643</t>
   </si>
   <si>
     <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132723599672318</t>
+    <t xml:space="preserve">0.13272362947464</t>
   </si>
   <si>
     <t xml:space="preserve">0.132079318165779</t>
@@ -1403,19 +1397,19 @@
     <t xml:space="preserve">0.125765278935432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12499213963747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126796156167984</t>
+    <t xml:space="preserve">0.124992154538631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126796141266823</t>
   </si>
   <si>
     <t xml:space="preserve">0.129180029034615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133367910981178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131757184863091</t>
+    <t xml:space="preserve">0.133367925882339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131757169961929</t>
   </si>
   <si>
     <t xml:space="preserve">0.125894144177437</t>
@@ -1427,7 +1421,10 @@
     <t xml:space="preserve">0.125378727912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128600150346756</t>
+    <t xml:space="preserve">0.128600165247917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130468606948853</t>
   </si>
   <si>
     <t xml:space="preserve">0.127440437674522</t>
@@ -1436,31 +1433,31 @@
     <t xml:space="preserve">0.127955883741379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127827033400536</t>
+    <t xml:space="preserve">0.127827018499374</t>
   </si>
   <si>
     <t xml:space="preserve">0.126023009419441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124347865581512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703561723232</t>
+    <t xml:space="preserve">0.124347858130932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703554272652</t>
   </si>
   <si>
     <t xml:space="preserve">0.127311587333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127569273114204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126667320728302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126538455486298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12872901558876</t>
+    <t xml:space="preserve">0.127569288015366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126667305827141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126538440585136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128729030489922</t>
   </si>
   <si>
     <t xml:space="preserve">0.12834244966507</t>
@@ -1469,7 +1466,7 @@
     <t xml:space="preserve">0.129502177238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130146458745003</t>
+    <t xml:space="preserve">0.130146473646164</t>
   </si>
   <si>
     <t xml:space="preserve">0.134012192487717</t>
@@ -1478,16 +1475,16 @@
     <t xml:space="preserve">0.134656488895416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138522237539291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138200044631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300755500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130790755152702</t>
+    <t xml:space="preserve">0.13852222263813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13820007443428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300770401955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130790740251541</t>
   </si>
   <si>
     <t xml:space="preserve">0.128084734082222</t>
@@ -1496,19 +1493,19 @@
     <t xml:space="preserve">0.128857880830765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125249862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122157268226147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123317003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125507593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128213584423065</t>
+    <t xml:space="preserve">0.125249847769737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122157275676727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123316988348961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125507563352585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128213599324226</t>
   </si>
   <si>
     <t xml:space="preserve">0.126151874661446</t>
@@ -1520,19 +1517,19 @@
     <t xml:space="preserve">0.125636428594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120482102036476</t>
+    <t xml:space="preserve">0.120482131838799</t>
   </si>
   <si>
     <t xml:space="preserve">0.12228611856699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122414983808994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260657250881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266073167324</t>
+    <t xml:space="preserve">0.122414991259575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260679602623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266065716743</t>
   </si>
   <si>
     <t xml:space="preserve">0.113394938409328</t>
@@ -1544,34 +1541,34 @@
     <t xml:space="preserve">0.11210635304451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114425800740719</t>
+    <t xml:space="preserve">0.114425793290138</t>
   </si>
   <si>
     <t xml:space="preserve">0.114683508872986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112235218286514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110817782580853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108240604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565453112125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921171605587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101926580071449</t>
+    <t xml:space="preserve">0.112235210835934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110817775130272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108240626752377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921164155006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101926572620869</t>
   </si>
   <si>
     <t xml:space="preserve">0.105019174516201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103086292743683</t>
+    <t xml:space="preserve">0.103086307644844</t>
   </si>
   <si>
     <t xml:space="preserve">0.104374878108501</t>
@@ -1580,25 +1577,25 @@
     <t xml:space="preserve">0.104117169976234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105663478374481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107982903718948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108627185225487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108111754059792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111462064087391</t>
+    <t xml:space="preserve">0.10566346347332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107982911169529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108627192676067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108111768960953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11146204918623</t>
   </si>
   <si>
     <t xml:space="preserve">0.112750649452209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108756050467491</t>
+    <t xml:space="preserve">0.108756028115749</t>
   </si>
   <si>
     <t xml:space="preserve">0.110173493623734</t>
@@ -1607,10 +1604,10 @@
     <t xml:space="preserve">0.109529197216034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106952033936977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153440773487</t>
+    <t xml:space="preserve">0.106952041387558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153433322906</t>
   </si>
   <si>
     <t xml:space="preserve">0.103988312184811</t>
@@ -1619,67 +1616,67 @@
     <t xml:space="preserve">0.102699726819992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105276882648468</t>
+    <t xml:space="preserve">0.105276875197887</t>
   </si>
   <si>
     <t xml:space="preserve">0.111204348504543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115585520863533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1158432289958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327805280685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113008365035057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10940033942461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11043119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107854038476944</t>
+    <t xml:space="preserve">0.115585528314114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843243896961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327812731266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113008357584476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10940033197403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110431201756001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107854053378105</t>
   </si>
   <si>
     <t xml:space="preserve">0.103730589151382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106307744979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103859461843967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554658532143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109142623841763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013758599758</t>
+    <t xml:space="preserve">0.106307752430439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103859446942806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554643630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109142616391182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013773500919</t>
   </si>
   <si>
     <t xml:space="preserve">0.108884900808334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109271489083767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107338614761829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442003786564</t>
+    <t xml:space="preserve">0.109271481633186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107338629662991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442011237144</t>
   </si>
   <si>
     <t xml:space="preserve">0.101411141455173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102055445313454</t>
+    <t xml:space="preserve">0.102055437862873</t>
   </si>
   <si>
     <t xml:space="preserve">0.10025142878294</t>
@@ -1688,55 +1685,55 @@
     <t xml:space="preserve">0.0999937132000923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10128228366375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797722280025</t>
+    <t xml:space="preserve">0.101282298564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797729730606</t>
   </si>
   <si>
     <t xml:space="preserve">0.100766852498055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105148047208786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915778040886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111075505614281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112621791660786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302351415157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110688924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761458933353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534613132477</t>
+    <t xml:space="preserve">0.105148032307625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915770590305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111075483262539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112621784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302358865738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688909888268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761466383934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534598231316</t>
   </si>
   <si>
     <t xml:space="preserve">0.107467480003834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108498334884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080899178982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503735899925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792321264744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436602771282</t>
+    <t xml:space="preserve">0.108498342335224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080906629562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503743350506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792328715324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">0.10534131526947</t>
@@ -1745,67 +1742,67 @@
     <t xml:space="preserve">0.107596330344677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108562760055065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207049012184</t>
+    <t xml:space="preserve">0.108562767505646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207056462765</t>
   </si>
   <si>
     <t xml:space="preserve">0.110185071825981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109857127070427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11116885393858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110512994229794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889540493488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106905743479729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10592196136713</t>
+    <t xml:space="preserve">0.109857134521008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11116886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110513001680374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889547944069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106905750930309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921968817711</t>
   </si>
   <si>
     <t xml:space="preserve">0.10395435988903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104282297194004</t>
+    <t xml:space="preserve">0.104282289743423</t>
   </si>
   <si>
     <t xml:space="preserve">0.105594016611576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108217485249043</t>
+    <t xml:space="preserve">0.108217477798462</t>
   </si>
   <si>
     <t xml:space="preserve">0.105266094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104938164353371</t>
+    <t xml:space="preserve">0.10493815690279</t>
   </si>
   <si>
     <t xml:space="preserve">0.102970562875271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103626422584057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103298492729664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101658836007118</t>
+    <t xml:space="preserve">0.103626437485218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103298500180244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101658843457699</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347109138966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330898702145</t>
+    <t xml:space="preserve">0.101330906152725</t>
   </si>
   <si>
     <t xml:space="preserve">0.0970677956938744</t>
@@ -1820,37 +1817,37 @@
     <t xml:space="preserve">0.0951002016663551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0980516001582146</t>
+    <t xml:space="preserve">0.098051592707634</t>
   </si>
   <si>
     <t xml:space="preserve">0.0964119359850883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.09870745241642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099363312125206</t>
+    <t xml:space="preserve">0.0987074598670006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0993633195757866</t>
   </si>
   <si>
     <t xml:space="preserve">0.100019194185734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101002976298332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100675038993359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102642625570297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0983795300126076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0996912494301796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099035382270813</t>
+    <t xml:space="preserve">0.101002968847752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100675046443939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102642647922039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098379522562027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099691241979599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0990353748202324</t>
   </si>
   <si>
     <t xml:space="preserve">0.104610234498978</t>
@@ -1859,40 +1856,43 @@
     <t xml:space="preserve">0.107561610639095</t>
   </si>
   <si>
+    <t xml:space="preserve">0.109529204666615</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.108873337507248</t>
   </si>
   <si>
     <t xml:space="preserve">0.108545407652855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109201267361641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107233673334122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249891221523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1121526658535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114448182284832</t>
+    <t xml:space="preserve">0.109201274812222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107233680784702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249876320362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11215265840292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11444815993309</t>
   </si>
   <si>
     <t xml:space="preserve">0.111824721097946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112808525562286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11313646286726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480588257313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496776342392</t>
+    <t xml:space="preserve">0.112808518111706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113136455416679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480573356152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
     <t xml:space="preserve">0.130516842007637</t>
@@ -1901,13 +1901,13 @@
     <t xml:space="preserve">0.139698937535286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132484421133995</t>
+    <t xml:space="preserve">0.132484436035156</t>
   </si>
   <si>
     <t xml:space="preserve">0.141010656952858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160686552524567</t>
+    <t xml:space="preserve">0.160686567425728</t>
   </si>
   <si>
     <t xml:space="preserve">0.173803806304932</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">0.157407224178314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156751379370689</t>
+    <t xml:space="preserve">0.156751394271851</t>
   </si>
   <si>
     <t xml:space="preserve">0.15281617641449</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">0.148881018161774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145601689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146257564425468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146913439035416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150192737579346</t>
+    <t xml:space="preserve">0.145601704716682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14625757932663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146913409233093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150192752480507</t>
   </si>
   <si>
     <t xml:space="preserve">0.14953687787056</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">0.14756928384304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148225143551826</t>
+    <t xml:space="preserve">0.148225158452988</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654146552086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161342412233353</t>
+    <t xml:space="preserve">0.161342427134514</t>
   </si>
   <si>
     <t xml:space="preserve">0.141666516661644</t>
@@ -1973,13 +1973,13 @@
     <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1351078748703</t>
+    <t xml:space="preserve">0.135107889771461</t>
   </si>
   <si>
     <t xml:space="preserve">0.133140280842781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137731343507767</t>
+    <t xml:space="preserve">0.137731328606606</t>
   </si>
   <si>
     <t xml:space="preserve">0.154783770442009</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">0.131828561425209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135763749480247</t>
+    <t xml:space="preserve">0.135763764381409</t>
   </si>
   <si>
     <t xml:space="preserve">0.13707546889782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12559786438942</t>
+    <t xml:space="preserve">0.125597849488258</t>
   </si>
   <si>
     <t xml:space="preserve">0.126581653952599</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">0.118711292743683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110840924084187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0967398434877396</t>
+    <t xml:space="preserve">0.110840916633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0967398583889008</t>
   </si>
   <si>
     <t xml:space="preserve">0.0826388001441956</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">0.0911650210618973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0918208956718445</t>
+    <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
     <t xml:space="preserve">0.0928046777844429</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">0.0957560613751411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0937884896993637</t>
+    <t xml:space="preserve">0.0937884822487831</t>
   </si>
   <si>
     <t xml:space="preserve">0.0965431109070778</t>
@@ -2060,13 +2060,13 @@
     <t xml:space="preserve">0.0969366282224655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0978548303246498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0971989780664444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0924767404794693</t>
+    <t xml:space="preserve">0.0978548377752304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.097198985517025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0924767553806305</t>
   </si>
   <si>
     <t xml:space="preserve">0.0940508171916008</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">0.0954937264323235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0982483401894569</t>
+    <t xml:space="preserve">0.0982483476400375</t>
   </si>
   <si>
     <t xml:space="preserve">0.100740641355515</t>
@@ -2093,25 +2093,25 @@
     <t xml:space="preserve">0.0968054458498955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0966742783784866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709756612778</t>
+    <t xml:space="preserve">0.096674270927906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709734261036</t>
   </si>
   <si>
     <t xml:space="preserve">0.0979860052466393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0991665571928024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0936573073267937</t>
+    <t xml:space="preserve">0.099166564643383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0936572998762131</t>
   </si>
   <si>
     <t xml:space="preserve">0.0948378518223763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100084759294987</t>
+    <t xml:space="preserve">0.100084774196148</t>
   </si>
   <si>
     <t xml:space="preserve">0.102183528244495</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">0.0999535992741585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10323291271925</t>
+    <t xml:space="preserve">0.103232905268669</t>
   </si>
   <si>
     <t xml:space="preserve">0.104806981980801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14035476744175</t>
+    <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
     <t xml:space="preserve">0.125925779342651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13838717341423</t>
+    <t xml:space="preserve">0.138387188315392</t>
   </si>
   <si>
     <t xml:space="preserve">0.142322361469269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137403398752213</t>
+    <t xml:space="preserve">0.137403413653374</t>
   </si>
   <si>
     <t xml:space="preserve">0.135435804724693</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">0.134452000260353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134124085307121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131041511893272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127893358469009</t>
+    <t xml:space="preserve">0.13412407040596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131041526794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127893373370171</t>
   </si>
   <si>
     <t xml:space="preserve">0.134779945015907</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">0.131172701716423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130779162049294</t>
+    <t xml:space="preserve">0.130779191851616</t>
   </si>
   <si>
     <t xml:space="preserve">0.130123317241669</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">0.129992142319679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975178718567</t>
+    <t xml:space="preserve">0.126975163817406</t>
   </si>
   <si>
     <t xml:space="preserve">0.127631038427353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128549247980118</t>
+    <t xml:space="preserve">0.128549233078957</t>
   </si>
   <si>
     <t xml:space="preserve">0.133796155452728</t>
@@ -2222,31 +2222,31 @@
     <t xml:space="preserve">0.129860952496529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130254477262497</t>
+    <t xml:space="preserve">0.130254492163658</t>
   </si>
   <si>
     <t xml:space="preserve">0.129073917865753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125138744711876</t>
+    <t xml:space="preserve">0.125138759613037</t>
   </si>
   <si>
     <t xml:space="preserve">0.12461406737566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143634095788002</t>
+    <t xml:space="preserve">0.143634110689163</t>
   </si>
   <si>
     <t xml:space="preserve">0.143962040543556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370992779732</t>
+    <t xml:space="preserve">0.139371007680893</t>
   </si>
   <si>
     <t xml:space="preserve">0.136091664433479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138059258460999</t>
+    <t xml:space="preserve">0.138059243559837</t>
   </si>
   <si>
     <t xml:space="preserve">0.136747524142265</t>
@@ -2264,31 +2264,31 @@
     <t xml:space="preserve">0.141994446516037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144289955496788</t>
+    <t xml:space="preserve">0.144289970397949</t>
   </si>
   <si>
     <t xml:space="preserve">0.15379998087883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152488261461258</t>
+    <t xml:space="preserve">0.152488276362419</t>
   </si>
   <si>
     <t xml:space="preserve">0.157079309225082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152160316705704</t>
+    <t xml:space="preserve">0.152160331606865</t>
   </si>
   <si>
     <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155111715197563</t>
+    <t xml:space="preserve">0.155111700296402</t>
   </si>
   <si>
     <t xml:space="preserve">0.155767574906349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160358622670174</t>
+    <t xml:space="preserve">0.160358637571335</t>
   </si>
   <si>
     <t xml:space="preserve">0.159702748060226</t>
@@ -2297,31 +2297,31 @@
     <t xml:space="preserve">0.162982076406479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166917264461517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163310006260872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162326231598854</t>
+    <t xml:space="preserve">0.166917249560356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163309991359711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162326216697693</t>
   </si>
   <si>
     <t xml:space="preserve">0.161014467477798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159046903252602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159374818205833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158718958497047</t>
+    <t xml:space="preserve">0.15904688835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159374833106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158718973398209</t>
   </si>
   <si>
     <t xml:space="preserve">0.158391028642654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160030677914619</t>
+    <t xml:space="preserve">0.160030692815781</t>
   </si>
   <si>
     <t xml:space="preserve">0.158063098788261</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">0.162863075733185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162509009242058</t>
+    <t xml:space="preserve">0.162509024143219</t>
   </si>
   <si>
     <t xml:space="preserve">0.161092847585678</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157198294997215</t>
+    <t xml:space="preserve">0.157198309898376</t>
   </si>
   <si>
     <t xml:space="preserve">0.158260434865952</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">0.158968538045883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160384729504585</t>
+    <t xml:space="preserve">0.160384744405746</t>
   </si>
   <si>
     <t xml:space="preserve">0.159322589635849</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">0.153303727507591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15578205883503</t>
+    <t xml:space="preserve">0.155782073736191</t>
   </si>
   <si>
     <t xml:space="preserve">0.151533469557762</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">0.155428037047386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156844243407249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156490162014961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153657764196396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154011830687523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156136125326157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152241572737694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154365867376328</t>
+    <t xml:space="preserve">0.156844228506088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156490176916122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153657779097557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154011845588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156136140227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152241587638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154365882277489</t>
   </si>
   <si>
     <t xml:space="preserve">0.151887521147728</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150471344590187</t>
+    <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
     <t xml:space="preserve">0.149055123329163</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">0.145514622330666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148347035050392</t>
+    <t xml:space="preserve">0.148347020149231</t>
   </si>
   <si>
     <t xml:space="preserve">0.149409160017967</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">0.1451605707407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147638916969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148701086640358</t>
+    <t xml:space="preserve">0.147638931870461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148701071739197</t>
   </si>
   <si>
     <t xml:space="preserve">0.146576792001724</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">0.144806519150734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144098445773125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14586865901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147992968559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165695488452911</t>
+    <t xml:space="preserve">0.144098430871964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145868673920631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147992983460426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16569547355175</t>
   </si>
   <si>
     <t xml:space="preserve">0.168527901172638</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16746574640274</t>
+    <t xml:space="preserve">0.167465731501579</t>
   </si>
   <si>
     <t xml:space="preserve">0.164987370371819</t>
@@ -2504,7 +2504,7 @@
     <t xml:space="preserve">0.163217127323151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164358526468277</t>
+    <t xml:space="preserve">0.164358541369438</t>
   </si>
   <si>
     <t xml:space="preserve">0.162075757980347</t>
@@ -2516,19 +2516,19 @@
     <t xml:space="preserve">0.167021736502647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161695286631584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161314845085144</t>
+    <t xml:space="preserve">0.161695301532745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161314830183983</t>
   </si>
   <si>
     <t xml:space="preserve">0.159793004393578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163978055119514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16055391728878</t>
+    <t xml:space="preserve">0.163978040218353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160553902387619</t>
   </si>
   <si>
     <t xml:space="preserve">0.158271163702011</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">0.160934388637543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162836670875549</t>
+    <t xml:space="preserve">0.162836685776711</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">0.162456214427948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159032076597214</t>
+    <t xml:space="preserve">0.159032091498375</t>
   </si>
   <si>
     <t xml:space="preserve">0.159412547945976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160173445940018</t>
+    <t xml:space="preserve">0.160173460841179</t>
   </si>
   <si>
     <t xml:space="preserve">0.165880352258682</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">0.157129779458046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15789070725441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153705641627312</t>
+    <t xml:space="preserve">0.157890692353249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153705656528473</t>
   </si>
   <si>
     <t xml:space="preserve">0.14427025616169</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">0.14777047932148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155227482318878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155988410115242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157510235905647</t>
+    <t xml:space="preserve">0.155227467417717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155988395214081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157510250806808</t>
   </si>
   <si>
     <t xml:space="preserve">0.164738968014717</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166641265153885</t>
+    <t xml:space="preserve">0.166641250252724</t>
   </si>
   <si>
     <t xml:space="preserve">0.168163105845451</t>
@@ -18485,7 +18485,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G571" t="s">
-        <v>438</v>
+        <v>104</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18511,7 +18511,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G572" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18537,7 +18537,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G573" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18563,7 +18563,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G574" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18589,7 +18589,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G575" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18615,7 +18615,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18849,7 +18849,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18875,7 +18875,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G586" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18927,7 +18927,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G588" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19031,7 +19031,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G592" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19057,7 +19057,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G593" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19083,7 +19083,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G594" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19109,7 +19109,7 @@
         <v>0.229499995708466</v>
       </c>
       <c r="G595" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19135,7 +19135,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19161,7 +19161,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G597" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19187,7 +19187,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G598" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19213,7 +19213,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G599" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G600" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19265,7 +19265,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G601" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G602" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G603" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G604" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19369,7 +19369,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G605" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G606" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G608" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G609" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G610" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G611" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G612" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G613" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G615" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G616" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G617" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G618" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G619" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G620" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G621" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G622" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G623" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G624" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G625" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G626" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G627" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G628" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G629" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>0.198599994182587</v>
       </c>
       <c r="G630" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G631" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G632" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>0.195600003004074</v>
       </c>
       <c r="G633" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G634" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G635" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G636" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G637" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>0.196600005030632</v>
       </c>
       <c r="G638" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>0.196400001645088</v>
       </c>
       <c r="G639" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G640" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G641" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G642" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G643" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G644" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G645" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G646" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G647" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G648" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G649" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G650" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G651" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G652" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G653" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G654" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G655" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G656" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G657" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G658" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G659" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G660" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G661" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G662" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G663" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G664" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G665" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G666" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G667" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>0.19879999756813</v>
       </c>
       <c r="G668" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G669" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G670" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G671" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G672" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G673" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G674" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G675" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G676" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G677" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G678" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G679" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>0.194399997591972</v>
       </c>
       <c r="G680" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>0.189600005745888</v>
       </c>
       <c r="G681" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>0.19140000641346</v>
       </c>
       <c r="G682" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>0.19480000436306</v>
       </c>
       <c r="G683" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G684" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G685" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G686" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G687" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G688" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G689" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G690" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>0.195800006389618</v>
       </c>
       <c r="G691" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G692" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G693" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G694" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G695" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>0.197400003671646</v>
       </c>
       <c r="G696" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G697" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G698" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G699" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G700" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G701" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>0.18979999423027</v>
       </c>
       <c r="G702" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>0.18979999423027</v>
       </c>
       <c r="G703" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>0.189600005745888</v>
       </c>
       <c r="G704" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G705" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G706" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G707" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>0.175799995660782</v>
       </c>
       <c r="G708" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G709" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>0.173600003123283</v>
       </c>
       <c r="G710" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>0.17399999499321</v>
       </c>
       <c r="G711" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>0.177599996328354</v>
       </c>
       <c r="G712" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G713" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>0.174199998378754</v>
       </c>
       <c r="G714" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G715" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G716" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>0.165399998426437</v>
       </c>
       <c r="G717" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>0.164399996399879</v>
       </c>
       <c r="G718" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>0.158199995756149</v>
       </c>
       <c r="G719" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G720" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G721" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G722" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>0.16159999370575</v>
       </c>
       <c r="G723" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G724" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G725" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>0.167600005865097</v>
       </c>
       <c r="G726" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>0.168599992990494</v>
       </c>
       <c r="G727" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>0.16779999434948</v>
       </c>
       <c r="G728" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>0.172999992966652</v>
       </c>
       <c r="G729" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>0.174999997019768</v>
       </c>
       <c r="G730" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>0.168599992990494</v>
       </c>
       <c r="G731" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>0.168799996376038</v>
       </c>
       <c r="G732" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G733" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G734" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G735" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>0.168599992990494</v>
       </c>
       <c r="G736" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G737" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>0.157000005245209</v>
       </c>
       <c r="G738" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>0.161400005221367</v>
       </c>
       <c r="G739" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>0.159400001168251</v>
       </c>
       <c r="G740" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>0.163399994373322</v>
       </c>
       <c r="G741" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>0.16779999434948</v>
       </c>
       <c r="G742" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G743" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G744" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>0.172600001096725</v>
       </c>
       <c r="G745" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>0.173600003123283</v>
       </c>
       <c r="G746" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>0.179399996995926</v>
       </c>
       <c r="G747" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>0.179800003767014</v>
       </c>
       <c r="G748" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G749" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>0.175799995660782</v>
       </c>
       <c r="G750" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>0.175400003790855</v>
       </c>
       <c r="G751" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>0.169799998402596</v>
       </c>
       <c r="G752" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>0.171399995684624</v>
       </c>
       <c r="G753" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G754" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>0.168799996376038</v>
       </c>
       <c r="G755" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>0.167400002479553</v>
       </c>
       <c r="G756" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G757" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G758" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>0.164399996399879</v>
       </c>
       <c r="G759" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G760" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G761" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>0.161200001835823</v>
       </c>
       <c r="G762" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>0.177799999713898</v>
       </c>
       <c r="G763" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>0.169400006532669</v>
       </c>
       <c r="G764" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>0.167400002479553</v>
       </c>
       <c r="G765" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>0.168799996376038</v>
       </c>
       <c r="G766" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>0.169200003147125</v>
       </c>
       <c r="G767" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G768" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>0.168799996376038</v>
       </c>
       <c r="G769" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G770" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>0.168799996376038</v>
       </c>
       <c r="G771" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>0.172600001096725</v>
       </c>
       <c r="G772" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>0.169400006532669</v>
       </c>
       <c r="G773" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G774" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G775" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G776" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>0.169599995017052</v>
       </c>
       <c r="G777" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>0.166600003838539</v>
       </c>
       <c r="G778" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G779" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G780" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G781" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>0.157399997115135</v>
       </c>
       <c r="G782" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G783" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>0.158399999141693</v>
       </c>
       <c r="G784" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G785" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>0.158199995756149</v>
       </c>
       <c r="G786" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G787" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>0.155599996447563</v>
       </c>
       <c r="G788" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G789" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>0.155200004577637</v>
       </c>
       <c r="G790" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>0.157199993729591</v>
       </c>
       <c r="G791" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G792" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>0.156399995088577</v>
       </c>
       <c r="G793" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G794" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>0.163200005888939</v>
       </c>
       <c r="G795" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>0.17059999704361</v>
       </c>
       <c r="G796" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>0.17399999499321</v>
       </c>
       <c r="G797" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>0.172399997711182</v>
       </c>
       <c r="G798" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>0.174799993634224</v>
       </c>
       <c r="G799" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>0.17059999704361</v>
       </c>
       <c r="G800" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>0.169400006532669</v>
       </c>
       <c r="G801" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G802" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>0.17399999499321</v>
       </c>
       <c r="G803" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>0.172600001096725</v>
       </c>
       <c r="G804" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>0.171200007200241</v>
       </c>
       <c r="G805" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>0.171800002455711</v>
       </c>
       <c r="G806" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>0.168599992990494</v>
       </c>
       <c r="G807" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>0.169400006532669</v>
       </c>
       <c r="G808" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>0.168599992990494</v>
       </c>
       <c r="G809" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>0.164399996399879</v>
       </c>
       <c r="G810" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>0.162599995732307</v>
       </c>
       <c r="G811" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>0.163800001144409</v>
       </c>
       <c r="G812" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>0.166800007224083</v>
       </c>
       <c r="G813" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>0.166600003838539</v>
       </c>
       <c r="G814" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>0.167600005865097</v>
       </c>
       <c r="G815" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>0.168400004506111</v>
       </c>
       <c r="G816" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>0.169200003147125</v>
       </c>
       <c r="G817" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G818" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G819" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>0.168799996376038</v>
       </c>
       <c r="G820" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>0.166199997067451</v>
       </c>
       <c r="G821" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G822" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>0.162200003862381</v>
       </c>
       <c r="G823" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>0.164199993014336</v>
       </c>
       <c r="G824" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G825" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>0.165199995040894</v>
       </c>
       <c r="G826" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>0.163499996066093</v>
       </c>
       <c r="G827" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G828" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G829" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G830" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G831" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G832" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G833" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G834" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G835" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G836" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G837" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G838" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G839" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G840" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G841" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G842" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G843" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G844" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G845" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G846" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G847" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G848" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G849" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G850" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25765,7 +25765,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G851" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25791,7 +25791,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G852" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G853" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25843,7 +25843,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G854" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25869,7 +25869,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G855" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25895,7 +25895,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G856" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25921,7 +25921,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G857" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25947,7 +25947,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G858" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25973,7 +25973,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G859" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G860" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -26025,7 +26025,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G861" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -26051,7 +26051,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G862" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -26077,7 +26077,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G863" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -26103,7 +26103,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G864" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -26129,7 +26129,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G865" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26155,7 +26155,7 @@
         <v>0.157000005245209</v>
       </c>
       <c r="G866" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G867" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>0.157499998807907</v>
       </c>
       <c r="G868" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>0.155000001192093</v>
       </c>
       <c r="G869" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26259,7 +26259,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G870" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26285,7 +26285,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G871" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26311,7 +26311,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G872" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26337,7 +26337,7 @@
         <v>0.154499992728233</v>
       </c>
       <c r="G873" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26363,7 +26363,7 @@
         <v>0.148000001907349</v>
       </c>
       <c r="G874" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26389,7 +26389,7 @@
         <v>0.149000003933907</v>
       </c>
       <c r="G875" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26415,7 +26415,7 @@
         <v>0.148499995470047</v>
       </c>
       <c r="G876" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26441,7 +26441,7 @@
         <v>0.144999995827675</v>
       </c>
       <c r="G877" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26467,7 +26467,7 @@
         <v>0.149499997496605</v>
       </c>
       <c r="G878" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26493,7 +26493,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G879" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26519,7 +26519,7 @@
         <v>0.148000001907349</v>
       </c>
       <c r="G880" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26545,7 +26545,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G881" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -26571,7 +26571,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G882" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26597,7 +26597,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G883" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26623,7 +26623,7 @@
         <v>0.152500003576279</v>
       </c>
       <c r="G884" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26649,7 +26649,7 @@
         <v>0.153999999165535</v>
       </c>
       <c r="G885" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26675,7 +26675,7 @@
         <v>0.152500003576279</v>
       </c>
       <c r="G886" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26701,7 +26701,7 @@
         <v>0.153500005602837</v>
       </c>
       <c r="G887" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26727,7 +26727,7 @@
         <v>0.153500005602837</v>
       </c>
       <c r="G888" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26753,7 +26753,7 @@
         <v>0.153999999165535</v>
       </c>
       <c r="G889" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26779,7 +26779,7 @@
         <v>0.152500003576279</v>
       </c>
       <c r="G890" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26805,7 +26805,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G891" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26831,7 +26831,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G892" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26857,7 +26857,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G893" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26883,7 +26883,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G894" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26909,7 +26909,7 @@
         <v>0.157499998807907</v>
       </c>
       <c r="G895" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26935,7 +26935,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G896" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26961,7 +26961,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G897" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26987,7 +26987,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G898" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -27013,7 +27013,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G899" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -27039,7 +27039,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G900" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -27065,7 +27065,7 @@
         <v>0.157000005245209</v>
       </c>
       <c r="G901" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -27091,7 +27091,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G902" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -27117,7 +27117,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G903" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -27143,7 +27143,7 @@
         <v>0.157499998807907</v>
       </c>
       <c r="G904" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -27169,7 +27169,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G905" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -27195,7 +27195,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G906" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -27221,7 +27221,7 @@
         <v>0.153999999165535</v>
       </c>
       <c r="G907" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27247,7 +27247,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G908" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27273,7 +27273,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G909" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27299,7 +27299,7 @@
         <v>0.153999999165535</v>
       </c>
       <c r="G910" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27325,7 +27325,7 @@
         <v>0.155000001192093</v>
       </c>
       <c r="G911" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27351,7 +27351,7 @@
         <v>0.150000005960464</v>
       </c>
       <c r="G912" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27377,7 +27377,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G913" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27403,7 +27403,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G914" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27429,7 +27429,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G915" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27455,7 +27455,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G916" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27481,7 +27481,7 @@
         <v>0.152500003576279</v>
       </c>
       <c r="G917" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27507,7 +27507,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G918" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27533,7 +27533,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G919" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27559,7 +27559,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G920" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27585,7 +27585,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G921" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27611,7 +27611,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G922" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27637,7 +27637,7 @@
         <v>0.149499997496605</v>
       </c>
       <c r="G923" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27663,7 +27663,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G924" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27689,7 +27689,7 @@
         <v>0.148499995470047</v>
       </c>
       <c r="G925" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27715,7 +27715,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G926" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27741,7 +27741,7 @@
         <v>0.150999993085861</v>
       </c>
       <c r="G927" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27767,7 +27767,7 @@
         <v>0.150999993085861</v>
       </c>
       <c r="G928" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27793,7 +27793,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G929" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27819,7 +27819,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G930" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27845,7 +27845,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G931" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27871,7 +27871,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G932" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27897,7 +27897,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G933" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27923,7 +27923,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G934" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27949,7 +27949,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G935" t="s">
-        <v>530</v>
+        <v>614</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -28079,7 +28079,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G940" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -28157,7 +28157,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G943" t="s">
-        <v>530</v>
+        <v>614</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -28183,7 +28183,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G944" t="s">
-        <v>530</v>
+        <v>614</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -28261,7 +28261,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G947" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28339,7 +28339,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G950" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28365,7 +28365,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G951" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28391,7 +28391,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G952" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28469,7 +28469,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G955" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28521,7 +28521,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G957" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28599,7 +28599,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G960" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28625,7 +28625,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G961" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28651,7 +28651,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G962" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28729,7 +28729,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G965" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28755,7 +28755,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G966" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28833,7 +28833,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G969" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28885,7 +28885,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G971" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28911,7 +28911,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G972" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28937,7 +28937,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G973" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28963,7 +28963,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G974" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28989,7 +28989,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G975" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -29015,7 +29015,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G976" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -29093,7 +29093,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G979" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -29119,7 +29119,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G980" t="s">
-        <v>530</v>
+        <v>614</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -29249,7 +29249,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G985" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29275,7 +29275,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G986" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29301,7 +29301,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G987" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -31277,7 +31277,7 @@
         <v>0.149000003933907</v>
       </c>
       <c r="G1063" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31329,7 +31329,7 @@
         <v>0.148499995470047</v>
       </c>
       <c r="G1065" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31589,7 +31589,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G1075" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31615,7 +31615,7 @@
         <v>0.153999999165535</v>
       </c>
       <c r="G1076" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31641,7 +31641,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G1077" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31667,7 +31667,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G1078" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31849,7 +31849,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G1085" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32317,7 +32317,7 @@
         <v>0.155000001192093</v>
       </c>
       <c r="G1103" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32343,7 +32343,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G1104" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32421,7 +32421,7 @@
         <v>0.149000003933907</v>
       </c>
       <c r="G1107" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32447,7 +32447,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G1108" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32473,7 +32473,7 @@
         <v>0.146999999880791</v>
       </c>
       <c r="G1109" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32499,7 +32499,7 @@
         <v>0.149000003933907</v>
       </c>
       <c r="G1110" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32759,7 +32759,7 @@
         <v>0.153999999165535</v>
       </c>
       <c r="G1120" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32811,7 +32811,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G1122" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -68387,7 +68387,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6495717593</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>1061492</v>
@@ -68408,6 +68408,32 @@
         <v>1092</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.649525463</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>1722259</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>0.164000004529953</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>0.160999998450279</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="1098">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053874969482</t>
+    <t xml:space="preserve">0.158053889870644</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481404185295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155000299215317</t>
+    <t xml:space="preserve">0.158481359481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155000314116478</t>
   </si>
   <si>
     <t xml:space="preserve">0.153229206800461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150542065501213</t>
+    <t xml:space="preserve">0.150542035698891</t>
   </si>
   <si>
     <t xml:space="preserve">0.148099198937416</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">0.150297775864601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151580274105072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147366315126419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358422279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132831200957298</t>
+    <t xml:space="preserve">0.151580259203911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147366344928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142358437180519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132831230759621</t>
   </si>
   <si>
     <t xml:space="preserve">0.134541243314743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125319391489029</t>
+    <t xml:space="preserve">0.12531940639019</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121218204498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134358048439026</t>
+    <t xml:space="preserve">0.134358033537865</t>
   </si>
   <si>
     <t xml:space="preserve">0.134419098496437</t>
@@ -92,40 +92,40 @@
     <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13802233338356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778058648109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140465214848518</t>
+    <t xml:space="preserve">0.138022348284721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778028845787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140465199947357</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854475855827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136190161108971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131792992353439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129166916012764</t>
+    <t xml:space="preserve">0.136190176010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131793007254601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129166901111603</t>
   </si>
   <si>
     <t xml:space="preserve">0.12928906083107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118967905640602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754365205765</t>
+    <t xml:space="preserve">0.118967920541763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754380106926</t>
   </si>
   <si>
     <t xml:space="preserve">0.116158612072468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118479333817959</t>
+    <t xml:space="preserve">0.118479363620281</t>
   </si>
   <si>
     <t xml:space="preserve">0.125807970762253</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">0.130999058485031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129105851054192</t>
+    <t xml:space="preserve">0.12910583615303</t>
   </si>
   <si>
     <t xml:space="preserve">0.128617271780968</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">0.130205139517784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130510494112968</t>
+    <t xml:space="preserve">0.13051050901413</t>
   </si>
   <si>
     <t xml:space="preserve">0.129533350467682</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">0.133808359503746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138755187392235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139671295881271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13673985004425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136495515704155</t>
+    <t xml:space="preserve">0.138755202293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139671266078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136739835143089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136495530605316</t>
   </si>
   <si>
     <t xml:space="preserve">0.140159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14174772799015</t>
+    <t xml:space="preserve">0.141747713088989</t>
   </si>
   <si>
     <t xml:space="preserve">0.147122040390968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14901527762413</t>
+    <t xml:space="preserve">0.149015262722969</t>
   </si>
   <si>
     <t xml:space="preserve">0.146572381258011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145717367529869</t>
+    <t xml:space="preserve">0.14571738243103</t>
   </si>
   <si>
     <t xml:space="preserve">0.1432134360075</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">0.140892699360847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139793410897255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968727827072</t>
+    <t xml:space="preserve">0.139793425798416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968742728233</t>
   </si>
   <si>
     <t xml:space="preserve">0.136068031191826</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">0.135823726654053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133136570453644</t>
+    <t xml:space="preserve">0.133136555552483</t>
   </si>
   <si>
     <t xml:space="preserve">0.130693718791008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12886156141758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125258311629295</t>
+    <t xml:space="preserve">0.128861546516418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125258326530457</t>
   </si>
   <si>
     <t xml:space="preserve">0.133930519223213</t>
@@ -242,28 +242,28 @@
     <t xml:space="preserve">0.142114147543907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141320198774338</t>
+    <t xml:space="preserve">0.14132022857666</t>
   </si>
   <si>
     <t xml:space="preserve">0.142175227403641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138327687978745</t>
+    <t xml:space="preserve">0.138327702879906</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236277461052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138205543160439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140526741743088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139899387955666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136135280132294</t>
+    <t xml:space="preserve">0.1382055580616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140526756644249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139899402856827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136135250329971</t>
   </si>
   <si>
     <t xml:space="preserve">0.136637181043625</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.133814081549644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132998540997505</t>
+    <t xml:space="preserve">0.132998526096344</t>
   </si>
   <si>
     <t xml:space="preserve">0.129234418272972</t>
@@ -302,25 +302,25 @@
     <t xml:space="preserve">0.126599565148354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127916991710663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130489140748978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131743803620338</t>
+    <t xml:space="preserve">0.127916976809502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130489125847816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1317438185215</t>
   </si>
   <si>
     <t xml:space="preserve">0.131116479635239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131555616855621</t>
+    <t xml:space="preserve">0.131555631756783</t>
   </si>
   <si>
     <t xml:space="preserve">0.134065017104149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131179213523865</t>
+    <t xml:space="preserve">0.131179198622704</t>
   </si>
   <si>
     <t xml:space="preserve">0.133688613772392</t>
@@ -329,133 +329,133 @@
     <t xml:space="preserve">0.134880572557449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134190514683723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130614578723907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132873043417931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128481581807137</t>
+    <t xml:space="preserve">0.134190499782562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130614593625069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132873058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
     <t xml:space="preserve">0.121078856289387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12020055949688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831655502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413886606693</t>
+    <t xml:space="preserve">0.120200544595718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831670403481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413864254951</t>
   </si>
   <si>
     <t xml:space="preserve">0.112233191728592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114366173744202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794039607048</t>
+    <t xml:space="preserve">0.114366188645363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794047057629</t>
   </si>
   <si>
     <t xml:space="preserve">0.114052511751652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105395063757896</t>
+    <t xml:space="preserve">0.105395056307316</t>
   </si>
   <si>
     <t xml:space="preserve">0.104893177747726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111041225492954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904471457005</t>
+    <t xml:space="preserve">0.111041210591793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904478907585</t>
   </si>
   <si>
     <t xml:space="preserve">0.111354894936085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110727548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277117669582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102822922170162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501723587513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716262340546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110790282487869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554382860661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923294305801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303439855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632175028324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116561934351921</t>
+    <t xml:space="preserve">0.110727533698082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277125120163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102822929620743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501731038094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716269791126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110790260136127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923286855221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303462207317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632160127163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116561912000179</t>
   </si>
   <si>
     <t xml:space="preserve">0.116373710334301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115746363997459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432694554329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805333316326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185508668423</t>
+    <t xml:space="preserve">0.115746349096298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432679653168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805340766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185501217842</t>
   </si>
   <si>
     <t xml:space="preserve">0.118569441139698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118820391595364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934565663338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159179031849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088908553123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106147885322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104140371084213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105645999312401</t>
+    <t xml:space="preserve">0.118820384144783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934558212757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159164130688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088916003704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106147892773151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104140356183052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10564599186182</t>
   </si>
   <si>
     <t xml:space="preserve">0.107465304434299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108531802892685</t>
+    <t xml:space="preserve">0.108531810343266</t>
   </si>
   <si>
     <t xml:space="preserve">0.107590794563293</t>
@@ -464,133 +464,133 @@
     <t xml:space="preserve">0.109535574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104830451309681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092673122883</t>
+    <t xml:space="preserve">0.1048304438591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092658221722</t>
   </si>
   <si>
     <t xml:space="preserve">0.108029931783676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849259257317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978484153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11160583794117</t>
+    <t xml:space="preserve">0.10765352845192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849251806736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978491604328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11160584539175</t>
   </si>
   <si>
     <t xml:space="preserve">0.11373882740736</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113864324986935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11028840392828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225670039654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845509588718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723776578903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339851558208</t>
+    <t xml:space="preserve">0.113864302635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110288389027119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225662589073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845494687557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723791480064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339859008789</t>
   </si>
   <si>
     <t xml:space="preserve">0.108406350016594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104516759514809</t>
+    <t xml:space="preserve">0.104516766965389</t>
   </si>
   <si>
     <t xml:space="preserve">0.10501866042614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10664975643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105834186077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085158884525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10978652536869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104391299188137</t>
+    <t xml:space="preserve">0.10664976388216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10583420842886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085151433945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109786532819271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104391306638718</t>
   </si>
   <si>
     <t xml:space="preserve">0.107778996229172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107214391231537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116060040891171</t>
+    <t xml:space="preserve">0.107214368879795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060048341751</t>
   </si>
   <si>
     <t xml:space="preserve">0.1147425994277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11242139339447</t>
+    <t xml:space="preserve">0.11242138594389</t>
   </si>
   <si>
     <t xml:space="preserve">0.11342515796423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112295918166637</t>
+    <t xml:space="preserve">0.112295925617218</t>
   </si>
   <si>
     <t xml:space="preserve">0.106022410094738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106712497770786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837965548038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520516633987</t>
+    <t xml:space="preserve">0.106712505221367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10552054643631</t>
   </si>
   <si>
     <t xml:space="preserve">0.104265823960304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102760188281536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003602147102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579508304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885663509369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889435529709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254537701607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100564442574978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101066328585148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101630948483944</t>
+    <t xml:space="preserve">0.102760173380375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003594696522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579500854015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885670959949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889413177967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254545152187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10056446492672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101066336035728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101630941033363</t>
   </si>
   <si>
     <t xml:space="preserve">0.106524296104908</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">0.109911993145943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110539332032204</t>
+    <t xml:space="preserve">0.110539346933365</t>
   </si>
   <si>
     <t xml:space="preserve">0.110915750265121</t>
@@ -611,46 +611,46 @@
     <t xml:space="preserve">0.112609602510929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111292146146297</t>
+    <t xml:space="preserve">0.11129217594862</t>
   </si>
   <si>
     <t xml:space="preserve">0.109410099685192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108343608677387</t>
+    <t xml:space="preserve">0.108343601226807</t>
   </si>
   <si>
     <t xml:space="preserve">0.108280867338181</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109033696353436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351137816906</t>
+    <t xml:space="preserve">0.109033703804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351130366325</t>
   </si>
   <si>
     <t xml:space="preserve">0.128544315695763</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153701111674309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144918203353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142408788204193</t>
+    <t xml:space="preserve">0.15370112657547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144918218255043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142408803105354</t>
   </si>
   <si>
     <t xml:space="preserve">0.132371172308922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132684856653214</t>
+    <t xml:space="preserve">0.132684841752052</t>
   </si>
   <si>
     <t xml:space="preserve">0.134253233671188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131304681301117</t>
+    <t xml:space="preserve">0.131304666399956</t>
   </si>
   <si>
     <t xml:space="preserve">0.134692370891571</t>
@@ -659,28 +659,28 @@
     <t xml:space="preserve">0.135821610689163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139836668968201</t>
+    <t xml:space="preserve">0.139836654067039</t>
   </si>
   <si>
     <t xml:space="preserve">0.14265975356102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144855454564095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14316163957119</t>
+    <t xml:space="preserve">0.144855484366417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143161624670029</t>
   </si>
   <si>
     <t xml:space="preserve">0.141781449317932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133500412106514</t>
+    <t xml:space="preserve">0.133500397205353</t>
   </si>
   <si>
     <t xml:space="preserve">0.129861772060394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130175441503525</t>
+    <t xml:space="preserve">0.130175456404686</t>
   </si>
   <si>
     <t xml:space="preserve">0.131681084632874</t>
@@ -692,31 +692,31 @@
     <t xml:space="preserve">0.130740061402321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124842949211597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097664237022</t>
+    <t xml:space="preserve">0.124842964112759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097679138184</t>
   </si>
   <si>
     <t xml:space="preserve">0.126975938677788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127289623022079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226889133453</t>
+    <t xml:space="preserve">0.127289637923241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226904034615</t>
   </si>
   <si>
     <t xml:space="preserve">0.126411333680153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125470340251923</t>
+    <t xml:space="preserve">0.1254703104496</t>
   </si>
   <si>
     <t xml:space="preserve">0.126536816358566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215625226498</t>
+    <t xml:space="preserve">0.124215610325336</t>
   </si>
   <si>
     <t xml:space="preserve">0.125972181558609</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">0.130551844835281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182970643044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171699285507</t>
+    <t xml:space="preserve">0.130677312612534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182985544205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171669483185</t>
   </si>
   <si>
     <t xml:space="preserve">0.13224570453167</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">0.135006055235863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133939564228058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127765893936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136260762810707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943321347237</t>
+    <t xml:space="preserve">0.133939549326897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127750992775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136260733008385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943336248398</t>
   </si>
   <si>
     <t xml:space="preserve">0.137766405940056</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">0.13801734149456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140777692198753</t>
+    <t xml:space="preserve">0.140777677297592</t>
   </si>
   <si>
     <t xml:space="preserve">0.145733773708344</t>
@@ -767,52 +767,52 @@
     <t xml:space="preserve">0.144165381789207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14397719502449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14115409553051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137640938162804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136762633919716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629637002945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002283215523</t>
+    <t xml:space="preserve">0.143977180123329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141154110431671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137640923261642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136762619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629666805267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002298116684</t>
   </si>
   <si>
     <t xml:space="preserve">0.133437678217888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129673570394516</t>
+    <t xml:space="preserve">0.129673555493355</t>
   </si>
   <si>
     <t xml:space="preserve">0.128356128931046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132496640086174</t>
+    <t xml:space="preserve">0.132496654987335</t>
   </si>
   <si>
     <t xml:space="preserve">0.135633394122124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137891873717308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137703686952591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433906197548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132057517766953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134504154324532</t>
+    <t xml:space="preserve">0.137891888618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13770367205143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433921098709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13205748796463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134504169225693</t>
   </si>
   <si>
     <t xml:space="preserve">0.134502425789833</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">0.134943619370461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792202591896</t>
+    <t xml:space="preserve">0.131792187690735</t>
   </si>
   <si>
     <t xml:space="preserve">0.131477043032646</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">0.132359445095062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130909815430641</t>
+    <t xml:space="preserve">0.130909785628319</t>
   </si>
   <si>
     <t xml:space="preserve">0.130468606948853</t>
@@ -854,85 +854,85 @@
     <t xml:space="preserve">0.129964396357536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129586189985275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002030611038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127947464585304</t>
+    <t xml:space="preserve">0.127506271004677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129586204886436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002060413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127947479486465</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199592232704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128703817725182</t>
+    <t xml:space="preserve">0.12870380282402</t>
   </si>
   <si>
     <t xml:space="preserve">0.126371756196022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125930577516556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127128109335899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056656241417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124796070158482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12466999143362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124165780842304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125174209475517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125237256288528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12901896238327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127380222082138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12845167517662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136545419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884447574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443239092827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126939013600349</t>
+    <t xml:space="preserve">0.125930562615395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127128094434738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056626439095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12479605525732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124669998884201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124165765941143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125174224376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125237241387367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129018947482109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127380207180977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128451690077782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136560320854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884462475777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443224191666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126938998699188</t>
   </si>
   <si>
     <t xml:space="preserve">0.128262624144554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126875996589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126308724284172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133430927991867</t>
+    <t xml:space="preserve">0.126875981688499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126497820019722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126308709383011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133430942893028</t>
   </si>
   <si>
     <t xml:space="preserve">0.135573908686638</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">0.135762974619865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136456295847893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135636940598488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134061217308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132485508918762</t>
+    <t xml:space="preserve">0.136456310749054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135636925697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134061232209206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132485494017601</t>
   </si>
   <si>
     <t xml:space="preserve">0.133556991815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135195702314377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136141151189804</t>
+    <t xml:space="preserve">0.135195717215538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136141180992126</t>
   </si>
   <si>
     <t xml:space="preserve">0.134439393877983</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">0.138221070170403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137842923402786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136330232024193</t>
+    <t xml:space="preserve">0.137842938303947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136330217123032</t>
   </si>
   <si>
     <t xml:space="preserve">0.137086570262909</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">0.13500665128231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134754523634911</t>
+    <t xml:space="preserve">0.134754538536072</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137401714920998</t>
+    <t xml:space="preserve">0.137401700019836</t>
   </si>
   <si>
     <t xml:space="preserve">0.15114189684391</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">0.153789088129997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152780622243881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15126796066761</t>
+    <t xml:space="preserve">0.152780637145042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267945766449</t>
   </si>
   <si>
     <t xml:space="preserve">0.145280256867409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14704504609108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444715499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159398600459099</t>
+    <t xml:space="preserve">0.147045060992241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444730401039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159398570656776</t>
   </si>
   <si>
     <t xml:space="preserve">0.156625360250473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570779323578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152843654155731</t>
+    <t xml:space="preserve">0.157570764422417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15284363925457</t>
   </si>
   <si>
     <t xml:space="preserve">0.152654573321342</t>
@@ -1052,22 +1052,22 @@
     <t xml:space="preserve">0.153347864747047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155805990099907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419347643852</t>
+    <t xml:space="preserve">0.155805975198746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419362545013</t>
   </si>
   <si>
     <t xml:space="preserve">0.156940504908562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159146472811699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167655318975449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050382614136</t>
+    <t xml:space="preserve">0.159146502614021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167655304074287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050397515297</t>
   </si>
   <si>
     <t xml:space="preserve">0.16721411049366</t>
@@ -1076,43 +1076,43 @@
     <t xml:space="preserve">0.172067299485207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179945811629295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811296820641</t>
+    <t xml:space="preserve">0.179945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811326622963</t>
   </si>
   <si>
     <t xml:space="preserve">0.17521870136261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174336329102516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176446437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479279994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173643007874489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170365542173386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166205674409866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168600752949715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166520804166794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166394755244255</t>
+    <t xml:space="preserve">0.174336299300194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176431536674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479265093803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173642978072166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170365527272224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166205659508705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222591280937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168600738048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166520833969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166394740343094</t>
   </si>
   <si>
     <t xml:space="preserve">0.161730647087097</t>
@@ -1121,31 +1121,31 @@
     <t xml:space="preserve">0.160091906785965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156688377261162</t>
+    <t xml:space="preserve">0.156688392162323</t>
   </si>
   <si>
     <t xml:space="preserve">0.16122642159462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162487015128136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163747549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873612880707</t>
+    <t xml:space="preserve">0.162487000226974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163747534155846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873597979546</t>
   </si>
   <si>
     <t xml:space="preserve">0.16103732585907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158011987805367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157759845256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970448732376</t>
+    <t xml:space="preserve">0.158011958003044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157759860157967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970433831215</t>
   </si>
   <si>
     <t xml:space="preserve">0.167718335986137</t>
@@ -1157,34 +1157,34 @@
     <t xml:space="preserve">0.163117274641991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163810595870018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159461602568626</t>
+    <t xml:space="preserve">0.163810580968857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159461617469788</t>
   </si>
   <si>
     <t xml:space="preserve">0.147675335407257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147486239671707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150007382035255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150448560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511592626572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151078879833221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151646092534065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150322511792183</t>
+    <t xml:space="preserve">0.147486224770546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150007352232933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150448590517044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511607527733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15107886493206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151646122336388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150322526693344</t>
   </si>
   <si>
     <t xml:space="preserve">0.148494705557823</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">0.151583090424538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149629205465317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709124445915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15101583302021</t>
+    <t xml:space="preserve">0.149629190564156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709154248238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151015818119049</t>
   </si>
   <si>
     <t xml:space="preserve">0.148935899138451</t>
@@ -1220,34 +1220,34 @@
     <t xml:space="preserve">0.150763720273972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150637656450272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15120492875576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149944365024567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213379740715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528509497643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377077817917</t>
+    <t xml:space="preserve">0.150637671351433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151204913854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149944350123405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213364839554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149377107620239</t>
   </si>
   <si>
     <t xml:space="preserve">0.157255619764328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156310200691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164503872394562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243323564529</t>
+    <t xml:space="preserve">0.156310215592384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164503887295723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243338465691</t>
   </si>
   <si>
     <t xml:space="preserve">0.162613034248352</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">0.163558468222618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165764451026917</t>
+    <t xml:space="preserve">0.165764465928078</t>
   </si>
   <si>
     <t xml:space="preserve">0.165449321269989</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">0.162297889590263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149061933159828</t>
+    <t xml:space="preserve">0.149061962962151</t>
   </si>
   <si>
     <t xml:space="preserve">0.14717110991478</t>
@@ -1286,25 +1286,25 @@
     <t xml:space="preserve">0.146225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14275911450386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334822893143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140237987041473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139607727527618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138032004237175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139922857284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135826006531715</t>
+    <t xml:space="preserve">0.142759129405022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334837794304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140237972140312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139607712626457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138031989336014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139922842383385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135825991630554</t>
   </si>
   <si>
     <t xml:space="preserve">0.138347163796425</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">0.141813695430756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140553131699562</t>
+    <t xml:space="preserve">0.140553146600723</t>
   </si>
   <si>
     <t xml:space="preserve">0.141183421015739</t>
@@ -1328,22 +1328,22 @@
     <t xml:space="preserve">0.135510876774788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134250283241272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935138583183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132674604654312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143074259161949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14496511220932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14338943362236</t>
+    <t xml:space="preserve">0.134250298142433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935153484344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132674589753151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14307427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144965097308159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
   </si>
   <si>
     <t xml:space="preserve">0.142443984746933</t>
@@ -1355,55 +1355,52 @@
     <t xml:space="preserve">0.147864431142807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145609393715858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455082058907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142710119485855</t>
+    <t xml:space="preserve">0.14560940861702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455067157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142710104584694</t>
   </si>
   <si>
     <t xml:space="preserve">0.141421541571617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139166504144669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
+    <t xml:space="preserve">0.139166533946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777215361595</t>
   </si>
   <si>
     <t xml:space="preserve">0.13948866724968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135622933506966</t>
+    <t xml:space="preserve">0.135622903704643</t>
   </si>
   <si>
     <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132723614573479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132079318165779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129824310541153</t>
+    <t xml:space="preserve">0.132723599672318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13207933306694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129824325442314</t>
   </si>
   <si>
     <t xml:space="preserve">0.125765278935432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124992124736309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126796156167984</t>
+    <t xml:space="preserve">0.12499213963747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126796141266823</t>
   </si>
   <si>
     <t xml:space="preserve">0.129180029034615</t>
@@ -1418,16 +1415,19 @@
     <t xml:space="preserve">0.125894159078598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126925021409988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125378713011742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128600165247917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127440422773361</t>
+    <t xml:space="preserve">0.126925006508827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125378727912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128600150346756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130468592047691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127440437674522</t>
   </si>
   <si>
     <t xml:space="preserve">0.127955883741379</t>
@@ -1439,40 +1439,40 @@
     <t xml:space="preserve">0.12602299451828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124347850680351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703576624393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127311572432518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127569302916527</t>
+    <t xml:space="preserve">0.124347865581512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703561723232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127311587333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127569288015366</t>
   </si>
   <si>
     <t xml:space="preserve">0.126667305827141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126538425683975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128729030489922</t>
+    <t xml:space="preserve">0.126538440585136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12872901558876</t>
   </si>
   <si>
     <t xml:space="preserve">0.12834244966507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129502177238464</t>
+    <t xml:space="preserve">0.129502192139626</t>
   </si>
   <si>
     <t xml:space="preserve">0.130146443843842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134012207388878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134656503796577</t>
+    <t xml:space="preserve">0.134012192487717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134656488895416</t>
   </si>
   <si>
     <t xml:space="preserve">0.13852222263813</t>
@@ -1481,25 +1481,25 @@
     <t xml:space="preserve">0.138200059533119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135300770401955</t>
+    <t xml:space="preserve">0.135300755500793</t>
   </si>
   <si>
     <t xml:space="preserve">0.130790755152702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128084719181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128857895731926</t>
+    <t xml:space="preserve">0.128084734082222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128857880830765</t>
   </si>
   <si>
     <t xml:space="preserve">0.125249862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122157268226147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123317003250122</t>
+    <t xml:space="preserve">0.122157283127308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123316988348961</t>
   </si>
   <si>
     <t xml:space="preserve">0.125507578253746</t>
@@ -1511,52 +1511,52 @@
     <t xml:space="preserve">0.126151859760284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127182722091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12563644349575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120482131838799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12228611856699</t>
+    <t xml:space="preserve">0.127182707190514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125636428594589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120482116937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122286133468151</t>
   </si>
   <si>
     <t xml:space="preserve">0.122414983808994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.117260664701462</t>
+    <t xml:space="preserve">0.117260657250881</t>
   </si>
   <si>
     <t xml:space="preserve">0.113266073167324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113394945859909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848637461662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112106367945671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114425800740719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683508872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112235210835934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110817775130272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108240619301796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565460562706</t>
+    <t xml:space="preserve">0.113394938409328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848644912243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11210635304451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114425785839558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683516323566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112235203385353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110817782580853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108240626752377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565453112125</t>
   </si>
   <si>
     <t xml:space="preserve">0.105921171605587</t>
@@ -1565,67 +1565,67 @@
     <t xml:space="preserve">0.101926580071449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105019181966782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103086307644844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374885559082</t>
+    <t xml:space="preserve">0.10501916706562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103086285293102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374878108501</t>
   </si>
   <si>
     <t xml:space="preserve">0.104117169976234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10566346347332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107982911169529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108627192676067</t>
+    <t xml:space="preserve">0.105663456022739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107982903718948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108627185225487</t>
   </si>
   <si>
     <t xml:space="preserve">0.108111768960953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11146205663681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750642001629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756043016911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173486173153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109529189765453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106952041387558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103988312184811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699734270573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105276875197887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111204341053963</t>
+    <t xml:space="preserve">0.111462064087391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750649452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756057918072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173508524895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109529182314873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106952048838139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153425872326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10398830473423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699726819992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105276890099049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111204333603382</t>
   </si>
   <si>
     <t xml:space="preserve">0.115585520863533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1158432289958</t>
+    <t xml:space="preserve">0.115843214094639</t>
   </si>
   <si>
     <t xml:space="preserve">0.115327805280685</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">0.113008365035057</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109400346875191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110431201756001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107854053378105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730589151382</t>
+    <t xml:space="preserve">0.10940033942461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11043119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107854031026363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730604052544</t>
   </si>
   <si>
     <t xml:space="preserve">0.10630775988102</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">0.114554658532143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109142631292343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013773500919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884908258915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271481633186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107338614761829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102441996335983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411148905754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055452764034</t>
+    <t xml:space="preserve">0.109142638742924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013758599758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884915709496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271474182606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10733862221241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442011237144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411156356335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055445313454</t>
   </si>
   <si>
     <t xml:space="preserve">0.100251436233521</t>
@@ -1685,88 +1685,88 @@
     <t xml:space="preserve">0.0999937206506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10128229111433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797729730606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766852498055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105148039758205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915770590305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1110754981637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112621791660786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302343964577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110688917338848</t>
+    <t xml:space="preserve">0.101282298564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797737181187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766867399216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105148024857044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915778040886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11107549071312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112621776759624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302351415157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688924789429</t>
   </si>
   <si>
     <t xml:space="preserve">0.104761451482773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105534605681896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467487454414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108498334884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080899178982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503743350506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792306363583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436587870121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10534131526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596307992935</t>
+    <t xml:space="preserve">0.105534613132477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467480003834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108498342335224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080891728401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503735899925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792313814163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436602771282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10534130781889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596315443516</t>
   </si>
   <si>
     <t xml:space="preserve">0.108562767505646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109207049012184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11018505692482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857127070427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11116885393858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110513001680374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10788955539465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10690576583147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10592195391655</t>
+    <t xml:space="preserve">0.109207034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185071825981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857134521008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111168839037418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110513009130955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889540493488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10690575838089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921968817711</t>
   </si>
   <si>
     <t xml:space="preserve">0.10395435988903</t>
@@ -1775,22 +1775,22 @@
     <t xml:space="preserve">0.104282282292843</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105594024062157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217470347881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10493815690279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102970570325851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103626422584057</t>
+    <t xml:space="preserve">0.105594016611576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266086757183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104938149452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10297055542469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103626444935799</t>
   </si>
   <si>
     <t xml:space="preserve">0.103298500180244</t>
@@ -1802,43 +1802,43 @@
     <t xml:space="preserve">0.100347109138966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330906152725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0970677956938744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0977236554026604</t>
+    <t xml:space="preserve">0.101330913603306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.097067803144455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.097723662853241</t>
   </si>
   <si>
     <t xml:space="preserve">0.0973957180976868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0951001942157745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0980516001582146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0964119359850883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0987074598670006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0993633195757866</t>
+    <t xml:space="preserve">0.0951002016663551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098051592707634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0964119285345078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09870745241642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099363312125206</t>
   </si>
   <si>
     <t xml:space="preserve">0.100019186735153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101002983748913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10067505389452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102642625570297</t>
+    <t xml:space="preserve">0.101002968847752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100675046443939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102642633020878</t>
   </si>
   <si>
     <t xml:space="preserve">0.098379522562027</t>
@@ -1847,52 +1847,52 @@
     <t xml:space="preserve">0.0996912494301796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.099035382270813</t>
+    <t xml:space="preserve">0.0990353897213936</t>
   </si>
   <si>
     <t xml:space="preserve">0.104610219597816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107561618089676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108873337507248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545407652855</t>
+    <t xml:space="preserve">0.107561603188515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108873330056667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545415103436</t>
   </si>
   <si>
     <t xml:space="preserve">0.10920125991106</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107233665883541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249876320362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112152643501759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114448167383671</t>
+    <t xml:space="preserve">0.107233673334122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249883770943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1121526658535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114448182284832</t>
   </si>
   <si>
     <t xml:space="preserve">0.111824728548527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112808525562286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113136455416679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480580806732</t>
+    <t xml:space="preserve">0.112808518111706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11313646286726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480573356152</t>
   </si>
   <si>
     <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130516842007637</t>
+    <t xml:space="preserve">0.130516827106476</t>
   </si>
   <si>
     <t xml:space="preserve">0.139698922634125</t>
@@ -1919,31 +1919,31 @@
     <t xml:space="preserve">0.150848597288132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154127925634384</t>
+    <t xml:space="preserve">0.154127910733223</t>
   </si>
   <si>
     <t xml:space="preserve">0.157407239079475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156751349568367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152816191315651</t>
+    <t xml:space="preserve">0.156751379370689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15281617641449</t>
   </si>
   <si>
     <t xml:space="preserve">0.148881003260612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145601704716682</t>
+    <t xml:space="preserve">0.145601689815521</t>
   </si>
   <si>
     <t xml:space="preserve">0.146257564425468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146913424134254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150192752480507</t>
+    <t xml:space="preserve">0.146913439035416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150192737579346</t>
   </si>
   <si>
     <t xml:space="preserve">0.14953687787056</t>
@@ -1952,22 +1952,22 @@
     <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147569254040718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148225143551826</t>
+    <t xml:space="preserve">0.147569268941879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148225158452988</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654131650925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161342412233353</t>
+    <t xml:space="preserve">0.161342427134514</t>
   </si>
   <si>
     <t xml:space="preserve">0.141666516661644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139043048024178</t>
+    <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
     <t xml:space="preserve">0.1351078748703</t>
@@ -1997,7 +1997,7 @@
     <t xml:space="preserve">0.13707546889782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125597849488258</t>
+    <t xml:space="preserve">0.12559786438942</t>
   </si>
   <si>
     <t xml:space="preserve">0.126581653952599</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">0.110840924084187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0967398509383202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.082638792693615</t>
+    <t xml:space="preserve">0.0967398583889008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0826388001441956</t>
   </si>
   <si>
     <t xml:space="preserve">0.087885707616806</t>
@@ -2030,37 +2030,37 @@
     <t xml:space="preserve">0.0911650210618973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0918208956718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0928046852350235</t>
+    <t xml:space="preserve">0.0918208882212639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0928046926856041</t>
   </si>
   <si>
     <t xml:space="preserve">0.0944443345069885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0960839986801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0931326076388359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0957560688257217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0937884896993637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0965431034564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0969366282224655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.097854845225811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0971989706158638</t>
+    <t xml:space="preserve">0.0960840061306953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0931326150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0957560613751411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0937884822487831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0965431183576584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0969366133213043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0978548377752304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0971989780664444</t>
   </si>
   <si>
     <t xml:space="preserve">0.0924767479300499</t>
@@ -2075,49 +2075,49 @@
     <t xml:space="preserve">0.0941819921135902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0949690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937264323235</t>
+    <t xml:space="preserve">0.0949690267443657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937338829041</t>
   </si>
   <si>
     <t xml:space="preserve">0.0982483476400375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100740641355515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0968054533004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0966742858290672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709749162197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0979860052466393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0991665571928024</t>
+    <t xml:space="preserve">0.100740633904934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0968054458498955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0966742932796478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709756612778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0979859977960587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099166564643383</t>
   </si>
   <si>
     <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0948378667235374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084759294987</t>
+    <t xml:space="preserve">0.0948378592729568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084774196148</t>
   </si>
   <si>
     <t xml:space="preserve">0.102183528244495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0999535992741585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103232897818089</t>
+    <t xml:space="preserve">0.0999535918235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10323291271925</t>
   </si>
   <si>
     <t xml:space="preserve">0.104806981980801</t>
@@ -2138,31 +2138,31 @@
     <t xml:space="preserve">0.137403398752213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135435804724693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136419609189034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134452000260353</t>
+    <t xml:space="preserve">0.135435819625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136419594287872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134452015161514</t>
   </si>
   <si>
     <t xml:space="preserve">0.134124100208282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131041511893272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127893373370171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134779945015907</t>
+    <t xml:space="preserve">0.131041496992111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127893358469009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134779930114746</t>
   </si>
   <si>
     <t xml:space="preserve">0.131172701716423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130779176950455</t>
+    <t xml:space="preserve">0.130779162049294</t>
   </si>
   <si>
     <t xml:space="preserve">0.130123317241669</t>
@@ -2186,22 +2186,22 @@
     <t xml:space="preserve">0.129992127418518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975163817406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127631038427353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128549233078957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133796140551567</t>
+    <t xml:space="preserve">0.126975178718567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127631023526192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128549247980118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133796155452728</t>
   </si>
   <si>
     <t xml:space="preserve">0.132156491279602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130647987127304</t>
+    <t xml:space="preserve">0.130648016929626</t>
   </si>
   <si>
     <t xml:space="preserve">0.129205107688904</t>
@@ -2210,25 +2210,25 @@
     <t xml:space="preserve">0.129598617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140026837587357</t>
+    <t xml:space="preserve">0.140026867389679</t>
   </si>
   <si>
     <t xml:space="preserve">0.1297297924757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12986096739769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130254477262497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129073932766914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125138759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124614052474499</t>
+    <t xml:space="preserve">0.129860952496529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130254492163658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129073917865753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125138744711876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12461406737566</t>
   </si>
   <si>
     <t xml:space="preserve">0.143634095788002</t>
@@ -2237,40 +2237,40 @@
     <t xml:space="preserve">0.143962040543556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370992779732</t>
+    <t xml:space="preserve">0.139370977878571</t>
   </si>
   <si>
     <t xml:space="preserve">0.136091664433479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13805927336216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136747524142265</t>
+    <t xml:space="preserve">0.138059258460999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136747539043427</t>
   </si>
   <si>
     <t xml:space="preserve">0.140682712197304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144945830106735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142650306224823</t>
+    <t xml:space="preserve">0.144945845007896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142650321125984</t>
   </si>
   <si>
     <t xml:space="preserve">0.141994446516037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144289970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153799995779991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152488261461258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157079309225082</t>
+    <t xml:space="preserve">0.144289955496788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15379998087883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152488276362419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157079294323921</t>
   </si>
   <si>
     <t xml:space="preserve">0.152160316705704</t>
@@ -2288,13 +2288,13 @@
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702748060226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162982061505318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166917264461517</t>
+    <t xml:space="preserve">0.159702733159065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162982076406479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166917249560356</t>
   </si>
   <si>
     <t xml:space="preserve">0.163310006260872</t>
@@ -2303,37 +2303,37 @@
     <t xml:space="preserve">0.162326231598854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161014497280121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15904688835144</t>
+    <t xml:space="preserve">0.16101448237896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159046918153763</t>
   </si>
   <si>
     <t xml:space="preserve">0.159374833106995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158718973398209</t>
+    <t xml:space="preserve">0.158718958497047</t>
   </si>
   <si>
     <t xml:space="preserve">0.158391028642654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160030707716942</t>
+    <t xml:space="preserve">0.160030677914619</t>
   </si>
   <si>
     <t xml:space="preserve">0.1580630838871</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165341436862946</t>
+    <t xml:space="preserve">0.165341451764107</t>
   </si>
   <si>
     <t xml:space="preserve">0.163571178913116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16250903904438</t>
+    <t xml:space="preserve">0.162863090634346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162509024143219</t>
   </si>
   <si>
     <t xml:space="preserve">0.161092847585678</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">0.157198294997215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15826041996479</t>
+    <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
     <t xml:space="preserve">0.162154987454414</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">0.158968538045883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160384729504585</t>
+    <t xml:space="preserve">0.160384744405746</t>
   </si>
   <si>
     <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15755233168602</t>
+    <t xml:space="preserve">0.157552346587181</t>
   </si>
   <si>
     <t xml:space="preserve">0.161800920963287</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">0.156490176916122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153657793998718</t>
+    <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
     <t xml:space="preserve">0.154011845588684</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">0.152241572737694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154365882277489</t>
+    <t xml:space="preserve">0.154365867376328</t>
   </si>
   <si>
     <t xml:space="preserve">0.151887521147728</t>
@@ -2423,46 +2423,46 @@
     <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150471344590187</t>
+    <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
     <t xml:space="preserve">0.149055123329163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146222710609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147284895181656</t>
+    <t xml:space="preserve">0.146222725510597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147284880280495</t>
   </si>
   <si>
     <t xml:space="preserve">0.142682209610939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143390342593193</t>
+    <t xml:space="preserve">0.143390327692032</t>
   </si>
   <si>
     <t xml:space="preserve">0.145514622330666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148347020149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149409174919128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152949675917625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145160555839539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147638916969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148701071739197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146576777100563</t>
+    <t xml:space="preserve">0.148347035050392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149409160017967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152949690818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1451605707407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147638931870461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148701086640358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146576792001724</t>
   </si>
   <si>
     <t xml:space="preserve">0.144452482461929</t>
@@ -2471,16 +2471,16 @@
     <t xml:space="preserve">0.143744379281998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144806548953056</t>
+    <t xml:space="preserve">0.144806534051895</t>
   </si>
   <si>
     <t xml:space="preserve">0.144098430871964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145868673920631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147992983460426</t>
+    <t xml:space="preserve">0.14586865901947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147992968559265</t>
   </si>
   <si>
     <t xml:space="preserve">0.165695488452911</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167465731501579</t>
+    <t xml:space="preserve">0.16746574640274</t>
   </si>
   <si>
     <t xml:space="preserve">0.16498738527298</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">0.167021736502647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161695301532745</t>
+    <t xml:space="preserve">0.161695286631584</t>
   </si>
   <si>
     <t xml:space="preserve">0.161314845085144</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.160934388637543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162836685776711</t>
+    <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">0.159032076597214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159412533044815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160173460841179</t>
+    <t xml:space="preserve">0.159412547945976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160173445940018</t>
   </si>
   <si>
     <t xml:space="preserve">0.165880352258682</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">0.14427025616169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147770464420319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155227467417717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155988395214081</t>
+    <t xml:space="preserve">0.14777047932148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155227482318878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
     <t xml:space="preserve">0.157510235905647</t>
@@ -2633,28 +2633,28 @@
     <t xml:space="preserve">0.168983712792397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166133403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170612469315529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16816933453083</t>
+    <t xml:space="preserve">0.166133388876915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17061248421669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168169349431992</t>
   </si>
   <si>
     <t xml:space="preserve">0.167354971170425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165319010615349</t>
+    <t xml:space="preserve">0.16531902551651</t>
   </si>
   <si>
     <t xml:space="preserve">0.166540592908859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166947782039642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167762160301208</t>
+    <t xml:space="preserve">0.166947767138481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167762145400047</t>
   </si>
   <si>
     <t xml:space="preserve">0.168576538562775</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">0.169390916824341</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16287587583065</t>
+    <t xml:space="preserve">0.162875890731812</t>
   </si>
   <si>
     <t xml:space="preserve">0.15196318924427</t>
@@ -2678,43 +2678,43 @@
     <t xml:space="preserve">0.15636083483696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157338097691536</t>
+    <t xml:space="preserve">0.157338112592697</t>
   </si>
   <si>
     <t xml:space="preserve">0.155546456575394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15424345433712</t>
+    <t xml:space="preserve">0.154243469238281</t>
   </si>
   <si>
     <t xml:space="preserve">0.150660187005997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152451813220978</t>
+    <t xml:space="preserve">0.152451828122139</t>
   </si>
   <si>
     <t xml:space="preserve">0.152614697813988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163690254092216</t>
+    <t xml:space="preserve">0.163690268993378</t>
   </si>
   <si>
     <t xml:space="preserve">0.162387236952782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158478230237961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160432741045952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157012343406677</t>
+    <t xml:space="preserve">0.158478245139122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160432755947113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157012358307838</t>
   </si>
   <si>
     <t xml:space="preserve">0.161247119307518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161735728383064</t>
+    <t xml:space="preserve">0.161735743284225</t>
   </si>
   <si>
     <t xml:space="preserve">0.161572873592377</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">0.160269856452942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159129723906517</t>
+    <t xml:space="preserve">0.159129738807678</t>
   </si>
   <si>
     <t xml:space="preserve">0.160595625638962</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">0.157989606261253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155057832598686</t>
+    <t xml:space="preserve">0.155057847499847</t>
   </si>
   <si>
     <t xml:space="preserve">0.162061497569084</t>
@@ -2747,10 +2747,10 @@
     <t xml:space="preserve">0.161410003900528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159944102168083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154732078313828</t>
+    <t xml:space="preserve">0.159944117069244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154732093214989</t>
   </si>
   <si>
     <t xml:space="preserve">0.158966839313507</t>
@@ -2765,22 +2765,22 @@
     <t xml:space="preserve">0.155872225761414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156197965145111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156035080552101</t>
+    <t xml:space="preserve">0.156197980046272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156035095453262</t>
   </si>
   <si>
     <t xml:space="preserve">0.157663851976395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155383586883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157826736569405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158152461051941</t>
+    <t xml:space="preserve">0.155383601784706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157826721668243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158152475953102</t>
   </si>
   <si>
     <t xml:space="preserve">0.156686589121819</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">0.153103321790695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152288943529129</t>
+    <t xml:space="preserve">0.15228895843029</t>
   </si>
   <si>
     <t xml:space="preserve">0.154894962906837</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">0.160921365022659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159292608499527</t>
+    <t xml:space="preserve">0.159292623400688</t>
   </si>
   <si>
     <t xml:space="preserve">0.158641114830971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164911836385727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164504632353783</t>
+    <t xml:space="preserve">0.164911821484566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164504647254944</t>
   </si>
   <si>
     <t xml:space="preserve">0.163283064961433</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">0.164097443223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162224382162094</t>
+    <t xml:space="preserve">0.162224397063255</t>
   </si>
   <si>
     <t xml:space="preserve">0.162550121545792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161084234714508</t>
+    <t xml:space="preserve">0.161084249615669</t>
   </si>
   <si>
     <t xml:space="preserve">0.15880398452282</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">0.159455493092537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16271299123764</t>
+    <t xml:space="preserve">0.162713006138802</t>
   </si>
   <si>
     <t xml:space="preserve">0.165726214647293</t>
@@ -2849,16 +2849,16 @@
     <t xml:space="preserve">0.170205295085907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175905957818031</t>
+    <t xml:space="preserve">0.175905972719193</t>
   </si>
   <si>
     <t xml:space="preserve">0.17305563390255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176720336079597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177534714341164</t>
+    <t xml:space="preserve">0.176720321178436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177534699440002</t>
   </si>
   <si>
     <t xml:space="preserve">0.179163470864296</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">0.172241255640984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172648444771767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171834066510201</t>
+    <t xml:space="preserve">0.172648429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171834051609039</t>
   </si>
   <si>
     <t xml:space="preserve">0.169798091053963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183235362172127</t>
+    <t xml:space="preserve">0.183235347270966</t>
   </si>
   <si>
     <t xml:space="preserve">0.181606605648994</t>
@@ -2903,28 +2903,31 @@
     <t xml:space="preserve">0.188121646642685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182920128107071</t>
+    <t xml:space="preserve">0.18292011320591</t>
   </si>
   <si>
     <t xml:space="preserve">0.186387807130814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187254726886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189855486154556</t>
+    <t xml:space="preserve">0.18725474178791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189855471253395</t>
   </si>
   <si>
     <t xml:space="preserve">0.190722405910492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188988566398621</t>
+    <t xml:space="preserve">0.188988551497459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188121631741524</t>
   </si>
   <si>
     <t xml:space="preserve">0.185520887374878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183787047863007</t>
+    <t xml:space="preserve">0.183787032961845</t>
   </si>
   <si>
     <t xml:space="preserve">0.182053208351135</t>
@@ -2942,25 +2945,25 @@
     <t xml:space="preserve">0.179452449083328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177718609571457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176851689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175984755158424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175117835402489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174250915646553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173383995890617</t>
+    <t xml:space="preserve">0.178585514426231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177718594670296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17685167491436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175984770059586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17511785030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174250930547714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173384010791779</t>
   </si>
   <si>
     <t xml:space="preserve">0.191589325666428</t>
@@ -19129,7 +19132,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19155,7 +19158,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G597" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19181,7 +19184,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G598" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19207,7 +19210,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G599" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19233,7 +19236,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G600" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19259,7 +19262,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G601" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19285,7 +19288,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G602" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19311,7 +19314,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G603" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19337,7 +19340,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G604" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19363,7 +19366,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G605" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19389,7 +19392,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G606" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19415,7 +19418,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19441,7 +19444,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G608" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19467,7 +19470,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G609" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19493,7 +19496,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G610" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19519,7 +19522,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G611" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19545,7 +19548,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G612" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19571,7 +19574,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G613" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19597,7 +19600,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19623,7 +19626,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G615" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19649,7 +19652,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G616" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19675,7 +19678,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G617" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19701,7 +19704,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G618" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19727,7 +19730,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G619" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19753,7 +19756,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G620" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19779,7 +19782,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G621" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19805,7 +19808,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19831,7 +19834,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G623" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19857,7 +19860,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G624" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19883,7 +19886,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G625" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19909,7 +19912,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G626" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19935,7 +19938,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G627" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19987,7 +19990,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G629" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20039,7 +20042,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G631" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20273,7 +20276,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G640" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20403,7 +20406,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G645" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20585,7 +20588,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G652" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20637,7 +20640,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G654" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20689,7 +20692,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G656" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20845,7 +20848,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G662" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20897,7 +20900,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G664" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20923,7 +20926,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G665" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20949,7 +20952,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G666" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21131,7 +21134,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G673" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21183,7 +21186,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G675" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21209,7 +21212,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G676" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21495,7 +21498,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G687" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21547,7 +21550,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G689" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21651,7 +21654,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G693" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21677,7 +21680,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21781,7 +21784,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G698" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -52331,7 +52334,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1873" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52383,7 +52386,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1875" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52409,7 +52412,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1876" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52435,7 +52438,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1877" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52461,7 +52464,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1878" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52513,7 +52516,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1880" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52591,7 +52594,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1883" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52617,7 +52620,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1884" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52643,7 +52646,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1885" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52721,7 +52724,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1888" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52747,7 +52750,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1889" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52773,7 +52776,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1890" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52799,7 +52802,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1891" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52825,7 +52828,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1892" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52851,7 +52854,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1893" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52877,7 +52880,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1894" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52903,7 +52906,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1895" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52929,7 +52932,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1896" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52981,7 +52984,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1898" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53007,7 +53010,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1899" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53033,7 +53036,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1900" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53059,7 +53062,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1901" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53085,7 +53088,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1902" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53137,7 +53140,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1904" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53163,7 +53166,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1905" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53241,7 +53244,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1908" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53267,7 +53270,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1909" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53293,7 +53296,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1910" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53319,7 +53322,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1911" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53371,7 +53374,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1913" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53397,7 +53400,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1914" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53449,7 +53452,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1916" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53475,7 +53478,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1917" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53501,7 +53504,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1918" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53527,7 +53530,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1919" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53553,7 +53556,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1920" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53579,7 +53582,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1921" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53605,7 +53608,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1922" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53631,7 +53634,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1923" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53657,7 +53660,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1924" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53683,7 +53686,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1925" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53709,7 +53712,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1926" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53735,7 +53738,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1927" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53787,7 +53790,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1929" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53839,7 +53842,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1931" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53865,7 +53868,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1932" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53891,7 +53894,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1933" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53917,7 +53920,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1934" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53943,7 +53946,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1935" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53969,7 +53972,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1936" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53995,7 +53998,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54021,7 +54024,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1938" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54047,7 +54050,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1939" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54073,7 +54076,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1940" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54099,7 +54102,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1941" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54125,7 +54128,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1942" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54151,7 +54154,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54177,7 +54180,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54203,7 +54206,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1945" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54229,7 +54232,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1946" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54255,7 +54258,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54281,7 +54284,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1948" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54307,7 +54310,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54333,7 +54336,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1950" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54359,7 +54362,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54385,7 +54388,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1952" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54411,7 +54414,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1953" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54437,7 +54440,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1954" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54463,7 +54466,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1955" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54489,7 +54492,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1956" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54515,7 +54518,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1957" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54541,7 +54544,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1958" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54567,7 +54570,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1959" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54593,7 +54596,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1960" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54619,7 +54622,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1961" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54645,7 +54648,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1962" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54671,7 +54674,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54697,7 +54700,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54723,7 +54726,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1965" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54775,7 +54778,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1967" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54801,7 +54804,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1968" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54827,7 +54830,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1969" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54853,7 +54856,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1970" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54879,7 +54882,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1971" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54905,7 +54908,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1972" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54931,7 +54934,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1973" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54957,7 +54960,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1974" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54983,7 +54986,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1975" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55009,7 +55012,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55035,7 +55038,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1977" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55061,7 +55064,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1978" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55087,7 +55090,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55113,7 +55116,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1980" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55139,7 +55142,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1981" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55165,7 +55168,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1982" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55191,7 +55194,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1983" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55217,7 +55220,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1984" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55243,7 +55246,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1985" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55269,7 +55272,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1986" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55295,7 +55298,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1987" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55321,7 +55324,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55347,7 +55350,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1989" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55373,7 +55376,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55399,7 +55402,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1991" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55425,7 +55428,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1992" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55451,7 +55454,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1993" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55477,7 +55480,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1994" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55503,7 +55506,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1995" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55529,7 +55532,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1996" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55555,7 +55558,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1997" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55581,7 +55584,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1998" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55607,7 +55610,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1999" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55633,7 +55636,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2000" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55659,7 +55662,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55685,7 +55688,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2002" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55711,7 +55714,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2003" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55737,7 +55740,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2004" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55763,7 +55766,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55789,7 +55792,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2006" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55815,7 +55818,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2007" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55841,7 +55844,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2008" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55867,7 +55870,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2009" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55893,7 +55896,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2010" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55919,7 +55922,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2011" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55945,7 +55948,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2012" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55971,7 +55974,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2013" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55997,7 +56000,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2014" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56023,7 +56026,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2015" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56049,7 +56052,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2016" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56075,7 +56078,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2017" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56101,7 +56104,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2018" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56127,7 +56130,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2019" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56153,7 +56156,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2020" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56179,7 +56182,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2021" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56205,7 +56208,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56231,7 +56234,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2023" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56257,7 +56260,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2024" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56283,7 +56286,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2025" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56309,7 +56312,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56335,7 +56338,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2027" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56361,7 +56364,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56387,7 +56390,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2029" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56413,7 +56416,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2030" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56439,7 +56442,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2031" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56465,7 +56468,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2032" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56491,7 +56494,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56517,7 +56520,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2034" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56543,7 +56546,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2035" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56569,7 +56572,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2036" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56595,7 +56598,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2037" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56621,7 +56624,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2038" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56647,7 +56650,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2039" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56673,7 +56676,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56699,7 +56702,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2041" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56725,7 +56728,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2042" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56751,7 +56754,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2043" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56777,7 +56780,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2044" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56803,7 +56806,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2045" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56829,7 +56832,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2046" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56855,7 +56858,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2047" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56881,7 +56884,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2048" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56907,7 +56910,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2049" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56933,7 +56936,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2050" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56959,7 +56962,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2051" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56985,7 +56988,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2052" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57011,7 +57014,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2053" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57037,7 +57040,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2054" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57063,7 +57066,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2055" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57089,7 +57092,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2056" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57115,7 +57118,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2057" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57141,7 +57144,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2058" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57167,7 +57170,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2059" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57193,7 +57196,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2060" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57219,7 +57222,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2061" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57245,7 +57248,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2062" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57271,7 +57274,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2063" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57297,7 +57300,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2064" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57323,7 +57326,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2065" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57349,7 +57352,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57375,7 +57378,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57401,7 +57404,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2068" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57427,7 +57430,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57453,7 +57456,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57479,7 +57482,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57505,7 +57508,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57531,7 +57534,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57557,7 +57560,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2074" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57583,7 +57586,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2075" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57609,7 +57612,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2076" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57635,7 +57638,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2077" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57661,7 +57664,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2078" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57687,7 +57690,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2079" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57713,7 +57716,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2080" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57739,7 +57742,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2081" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57765,7 +57768,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2082" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57791,7 +57794,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2083" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57817,7 +57820,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2084" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57843,7 +57846,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2085" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57869,7 +57872,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2086" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57895,7 +57898,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2087" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57921,7 +57924,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2088" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57947,7 +57950,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2089" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57973,7 +57976,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2090" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57999,7 +58002,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2091" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58025,7 +58028,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2092" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58051,7 +58054,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2093" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58077,7 +58080,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2094" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58103,7 +58106,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2095" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58181,7 +58184,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2098" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58259,7 +58262,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2101" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58285,7 +58288,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2102" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58311,7 +58314,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2103" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58337,7 +58340,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2104" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58389,7 +58392,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2106" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58441,7 +58444,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2108" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58493,7 +58496,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2110" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58519,7 +58522,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2111" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58545,7 +58548,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2112" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58571,7 +58574,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2113" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58597,7 +58600,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2114" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58623,7 +58626,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2115" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58649,7 +58652,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2116" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58701,7 +58704,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2118" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58727,7 +58730,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2119" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58753,7 +58756,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2120" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58779,7 +58782,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2121" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58805,7 +58808,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2122" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58831,7 +58834,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2123" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58857,7 +58860,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2124" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58883,7 +58886,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2125" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58909,7 +58912,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2126" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58935,7 +58938,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2127" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58961,7 +58964,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2128" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58987,7 +58990,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2129" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59013,7 +59016,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2130" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59039,7 +59042,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2131" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59065,7 +59068,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2132" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59091,7 +59094,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2133" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59117,7 +59120,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2134" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59143,7 +59146,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2135" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59169,7 +59172,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2136" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59195,7 +59198,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2137" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59221,7 +59224,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2138" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59247,7 +59250,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2139" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59273,7 +59276,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2140" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59299,7 +59302,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2141" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59325,7 +59328,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2142" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59351,7 +59354,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2143" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59377,7 +59380,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2144" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59403,7 +59406,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2145" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59429,7 +59432,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2146" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59455,7 +59458,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2147" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59481,7 +59484,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2148" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59507,7 +59510,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2149" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59533,7 +59536,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2150" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59559,7 +59562,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2151" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59585,7 +59588,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2152" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59611,7 +59614,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2153" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59637,7 +59640,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2154" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59663,7 +59666,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2155" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59689,7 +59692,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2156" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59715,7 +59718,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2157" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59741,7 +59744,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2158" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59767,7 +59770,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2159" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59793,7 +59796,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2160" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59819,7 +59822,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2161" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59845,7 +59848,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2162" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59871,7 +59874,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2163" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59897,7 +59900,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2164" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59923,7 +59926,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2165" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59949,7 +59952,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G2166" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59975,7 +59978,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2167" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60001,7 +60004,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2168" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60027,7 +60030,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2169" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60053,7 +60056,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2170" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60079,7 +60082,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2171" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60105,7 +60108,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2172" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60131,7 +60134,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2173" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60157,7 +60160,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2174" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60183,7 +60186,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2175" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60209,7 +60212,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2176" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60235,7 +60238,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2177" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60261,7 +60264,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2178" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60287,7 +60290,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2179" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60313,7 +60316,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2180" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60339,7 +60342,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G2181" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60365,7 +60368,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2182" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60391,7 +60394,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2183" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60417,7 +60420,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2184" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60443,7 +60446,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2185" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60469,7 +60472,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2186" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60495,7 +60498,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2187" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60521,7 +60524,7 @@
         <v>0.195500001311302</v>
       </c>
       <c r="G2188" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60547,7 +60550,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2189" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60573,7 +60576,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2190" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60599,7 +60602,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2191" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60625,7 +60628,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2192" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60651,7 +60654,7 @@
         <v>0.194499999284744</v>
       </c>
       <c r="G2193" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60677,7 +60680,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2194" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60703,7 +60706,7 @@
         <v>0.195999994874001</v>
       </c>
       <c r="G2195" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60729,7 +60732,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2196" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60755,7 +60758,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2197" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60781,7 +60784,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2198" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60807,7 +60810,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2199" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60833,7 +60836,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2200" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60859,7 +60862,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2201" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60885,7 +60888,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2202" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60911,7 +60914,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2203" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60937,7 +60940,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2204" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60963,7 +60966,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2205" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60989,7 +60992,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2206" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61015,7 +61018,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2207" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61041,7 +61044,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2208" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61067,7 +61070,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2209" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61093,7 +61096,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2210" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61119,7 +61122,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2211" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61145,7 +61148,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2212" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61171,7 +61174,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2213" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61197,7 +61200,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2214" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61223,7 +61226,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2215" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61249,7 +61252,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2216" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61275,7 +61278,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2217" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61301,7 +61304,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2218" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61327,7 +61330,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2219" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61353,7 +61356,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2220" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61379,7 +61382,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2221" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61405,7 +61408,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2222" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61431,7 +61434,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2223" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61457,7 +61460,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2224" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61483,7 +61486,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2225" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61509,7 +61512,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2226" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61535,7 +61538,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2227" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61561,7 +61564,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2228" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61587,7 +61590,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2229" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61613,7 +61616,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2230" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61639,7 +61642,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2231" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61665,7 +61668,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2232" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61691,7 +61694,7 @@
         <v>0.197500005364418</v>
       </c>
       <c r="G2233" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61717,7 +61720,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2234" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61743,7 +61746,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2235" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61769,7 +61772,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2236" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61795,7 +61798,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2237" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61821,7 +61824,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2238" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61847,7 +61850,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2239" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61873,7 +61876,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2240" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61899,7 +61902,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2241" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61925,7 +61928,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2242" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61951,7 +61954,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2243" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61977,7 +61980,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2244" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62003,7 +62006,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2245" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62029,7 +62032,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2246" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62055,7 +62058,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2247" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62081,7 +62084,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2248" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62107,7 +62110,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62133,7 +62136,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G2250" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62159,7 +62162,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2251" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62185,7 +62188,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2252" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62211,7 +62214,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2253" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62237,7 +62240,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2254" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62263,7 +62266,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2255" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62289,7 +62292,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62315,7 +62318,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2257" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62341,7 +62344,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2258" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62367,7 +62370,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2259" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62393,7 +62396,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2260" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62419,7 +62422,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2261" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62445,7 +62448,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2262" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62471,7 +62474,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2263" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62497,7 +62500,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2264" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62523,7 +62526,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2265" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62549,7 +62552,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2266" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62575,7 +62578,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2267" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62601,7 +62604,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2268" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62627,7 +62630,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2269" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62653,7 +62656,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2270" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62679,7 +62682,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2271" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62705,7 +62708,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2272" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62731,7 +62734,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2273" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62757,7 +62760,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2274" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62783,7 +62786,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2275" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62809,7 +62812,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2276" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62835,7 +62838,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2277" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62861,7 +62864,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2278" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62887,7 +62890,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2279" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62913,7 +62916,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2280" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62939,7 +62942,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2281" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62965,7 +62968,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G2282" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62991,7 +62994,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2283" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63017,7 +63020,7 @@
         <v>0.19149999320507</v>
       </c>
       <c r="G2284" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63043,7 +63046,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2285" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63069,7 +63072,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2286" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63095,7 +63098,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2287" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63121,7 +63124,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2288" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63147,7 +63150,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2289" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63173,7 +63176,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2290" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63199,7 +63202,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G2291" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63225,7 +63228,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2292" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63251,7 +63254,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G2293" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63277,7 +63280,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2294" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63303,7 +63306,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2295" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63329,7 +63332,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2296" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63355,7 +63358,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2297" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63381,7 +63384,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2298" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63407,7 +63410,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2299" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63433,7 +63436,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2300" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63459,7 +63462,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2301" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63485,7 +63488,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2302" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63511,7 +63514,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2303" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63537,7 +63540,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2304" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63563,7 +63566,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2305" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63589,7 +63592,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2306" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63615,7 +63618,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2307" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63641,7 +63644,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2308" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63667,7 +63670,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2309" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63693,7 +63696,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2310" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63719,7 +63722,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2311" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63745,7 +63748,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2312" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63771,7 +63774,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2313" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63797,7 +63800,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2314" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63823,7 +63826,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2315" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63849,7 +63852,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2316" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63875,7 +63878,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2317" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63901,7 +63904,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2318" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63927,7 +63930,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2319" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63953,7 +63956,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2320" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63979,7 +63982,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2321" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64005,7 +64008,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2322" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64031,7 +64034,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2323" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64057,7 +64060,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2324" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64083,7 +64086,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2325" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64109,7 +64112,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2326" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64135,7 +64138,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2327" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64161,7 +64164,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2328" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64187,7 +64190,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2329" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64213,7 +64216,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2330" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64239,7 +64242,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2331" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64265,7 +64268,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2332" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64291,7 +64294,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2333" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64317,7 +64320,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2334" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64343,7 +64346,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2335" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64369,7 +64372,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2336" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64395,7 +64398,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2337" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64421,7 +64424,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2338" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64447,7 +64450,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64473,7 +64476,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2340" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64499,7 +64502,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2341" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64525,7 +64528,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2342" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64551,7 +64554,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2343" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64577,7 +64580,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2344" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64603,7 +64606,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2345" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64629,7 +64632,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2346" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64655,7 +64658,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2347" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64681,7 +64684,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64707,7 +64710,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2349" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64733,7 +64736,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2350" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64759,7 +64762,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2351" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64785,7 +64788,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2352" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64811,7 +64814,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2353" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64837,7 +64840,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G2354" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64863,7 +64866,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2355" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64889,7 +64892,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2356" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64915,7 +64918,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2357" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64941,7 +64944,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2358" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64967,7 +64970,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2359" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64993,7 +64996,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2360" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65019,7 +65022,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2361" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65045,7 +65048,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65071,7 +65074,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2363" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65097,7 +65100,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G2364" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65123,7 +65126,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2365" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65149,7 +65152,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2366" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65175,7 +65178,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2367" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65201,7 +65204,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2368" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65227,7 +65230,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2369" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65253,7 +65256,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2370" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65279,7 +65282,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2371" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65305,7 +65308,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2372" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65331,7 +65334,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2373" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65357,7 +65360,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2374" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65383,7 +65386,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2375" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65409,7 +65412,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2376" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65435,7 +65438,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2377" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65461,7 +65464,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2378" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65487,7 +65490,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2379" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65513,7 +65516,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2380" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65539,7 +65542,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2381" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65565,7 +65568,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2382" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65591,7 +65594,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2383" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65617,7 +65620,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65643,7 +65646,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2385" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65669,7 +65672,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2386" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65695,7 +65698,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2387" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65721,7 +65724,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2388" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65747,7 +65750,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2389" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65773,7 +65776,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2390" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65799,7 +65802,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2391" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65825,7 +65828,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2392" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65851,7 +65854,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2393" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65877,7 +65880,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2394" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65903,7 +65906,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2395" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65929,7 +65932,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2396" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65955,7 +65958,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2397" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65981,7 +65984,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2398" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66007,7 +66010,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2399" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66033,7 +66036,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2400" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66059,7 +66062,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2401" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66085,7 +66088,7 @@
         <v>0.172499999403954</v>
       </c>
       <c r="G2402" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66111,7 +66114,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2403" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66137,7 +66140,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2404" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66163,7 +66166,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2405" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66189,7 +66192,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2406" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66215,7 +66218,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2407" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66241,7 +66244,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2408" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66267,7 +66270,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2409" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66293,7 +66296,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2410" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66319,7 +66322,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2411" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66345,7 +66348,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2412" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66371,7 +66374,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2413" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66397,7 +66400,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2414" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66423,7 +66426,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2415" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66449,7 +66452,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2416" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66475,7 +66478,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2417" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66501,7 +66504,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2418" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66527,7 +66530,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2419" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66553,7 +66556,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2420" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66579,7 +66582,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2421" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66605,7 +66608,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2422" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66631,7 +66634,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2423" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66657,7 +66660,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2424" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66683,7 +66686,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2425" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66709,7 +66712,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2426" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66735,7 +66738,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66761,7 +66764,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2428" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66787,7 +66790,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2429" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66813,7 +66816,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2430" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66839,7 +66842,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2431" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66865,7 +66868,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2432" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66891,7 +66894,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2433" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66917,7 +66920,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66943,7 +66946,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2435" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66969,7 +66972,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2436" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66995,7 +66998,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2437" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67021,7 +67024,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2438" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67047,7 +67050,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2439" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67073,7 +67076,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2440" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67099,7 +67102,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2441" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67125,7 +67128,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2442" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67151,7 +67154,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2443" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67177,7 +67180,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67203,7 +67206,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2445" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67229,7 +67232,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2446" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67255,7 +67258,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2447" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67281,7 +67284,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2448" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67307,7 +67310,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2449" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67333,7 +67336,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2450" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67359,7 +67362,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67385,7 +67388,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2452" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67411,7 +67414,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2453" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67437,7 +67440,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2454" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67463,7 +67466,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2455" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67489,7 +67492,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2456" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67515,7 +67518,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2457" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67541,7 +67544,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2458" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67567,7 +67570,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67593,7 +67596,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2460" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67619,7 +67622,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2461" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67645,7 +67648,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2462" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67671,7 +67674,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2463" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67697,7 +67700,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2464" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67723,7 +67726,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2465" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67749,7 +67752,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2466" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67775,7 +67778,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2467" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67801,7 +67804,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2468" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67827,7 +67830,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67853,7 +67856,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2470" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67879,7 +67882,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2471" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67905,7 +67908,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2472" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67931,7 +67934,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2473" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67957,7 +67960,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2474" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67983,7 +67986,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2475" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68009,7 +68012,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2476" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68035,7 +68038,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2477" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68061,7 +68064,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2478" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68087,7 +68090,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2479" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68113,7 +68116,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2480" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68139,7 +68142,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68165,7 +68168,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2482" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68191,7 +68194,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2483" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68217,7 +68220,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2484" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68243,7 +68246,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2485" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68269,7 +68272,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2486" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68295,7 +68298,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2487" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68321,7 +68324,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68347,7 +68350,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2489" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68373,7 +68376,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2490" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68399,7 +68402,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2491" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68425,7 +68428,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2492" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68433,7 +68436,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495717593</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>920189</v>
@@ -68451,9 +68454,35 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2493" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.649525463</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>1283697</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.162000000476837</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.161500006914139</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053889870644</t>
+    <t xml:space="preserve">0.158053904771805</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481404185295</t>
+    <t xml:space="preserve">0.158481389284134</t>
   </si>
   <si>
     <t xml:space="preserve">0.155000299215317</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">0.153229221701622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150542065501213</t>
+    <t xml:space="preserve">0.150542050600052</t>
   </si>
   <si>
     <t xml:space="preserve">0.148099198937416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15029776096344</t>
+    <t xml:space="preserve">0.150297775864601</t>
   </si>
   <si>
     <t xml:space="preserve">0.151580274105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147366315126419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358422279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132831215858459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134541243314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12531940639019</t>
+    <t xml:space="preserve">0.14736633002758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14235845208168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132831230759621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134541258215904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121203303337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134358018636703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419098496437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143335580825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13802233338356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778043746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140465214848518</t>
+    <t xml:space="preserve">0.134358033537865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419113397598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143335595726967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138022348284721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778058648109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140465185046196</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
@@ -107,124 +107,124 @@
     <t xml:space="preserve">0.136190176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131793022155762</t>
+    <t xml:space="preserve">0.131792992353439</t>
   </si>
   <si>
     <t xml:space="preserve">0.129166916012764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129289075732231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967920541763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754380106926</t>
+    <t xml:space="preserve">0.12928906083107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967913091183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754372656345</t>
   </si>
   <si>
     <t xml:space="preserve">0.116158619523048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118479333817959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125807955861092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125197246670723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960849881172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12702938914299</t>
+    <t xml:space="preserve">0.11847934871912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125807970762253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125197231769562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960834980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127029433846474</t>
   </si>
   <si>
     <t xml:space="preserve">0.125014036893845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130999088287354</t>
+    <t xml:space="preserve">0.130999058485031</t>
   </si>
   <si>
     <t xml:space="preserve">0.129105851054192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128617271780968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130205139517784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130510494112968</t>
+    <t xml:space="preserve">0.128617256879807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130205124616623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13051050901413</t>
   </si>
   <si>
     <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133808374404907</t>
+    <t xml:space="preserve">0.13380840420723</t>
   </si>
   <si>
     <t xml:space="preserve">0.138755187392235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13967128098011</t>
+    <t xml:space="preserve">0.139671266078949</t>
   </si>
   <si>
     <t xml:space="preserve">0.136739835143089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136495545506477</t>
+    <t xml:space="preserve">0.136495530605316</t>
   </si>
   <si>
     <t xml:space="preserve">0.140159860253334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141747713088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147122040390968</t>
+    <t xml:space="preserve">0.14174772799015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147122025489807</t>
   </si>
   <si>
     <t xml:space="preserve">0.149015262722969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146572381258011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145717397332191</t>
+    <t xml:space="preserve">0.14657236635685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14571738243103</t>
   </si>
   <si>
     <t xml:space="preserve">0.143213450908661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144129499793053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892699360847</t>
+    <t xml:space="preserve">0.144129529595375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140892714262009</t>
   </si>
   <si>
     <t xml:space="preserve">0.139793425798416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134968727827072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068031191826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135945916175842</t>
+    <t xml:space="preserve">0.134968742728233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068046092987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13594588637352</t>
   </si>
   <si>
     <t xml:space="preserve">0.135823741555214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133136600255966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130693688988686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128861546516418</t>
+    <t xml:space="preserve">0.133136555552483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130693703889847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12886156141758</t>
   </si>
   <si>
     <t xml:space="preserve">0.125258311629295</t>
@@ -236,43 +236,43 @@
     <t xml:space="preserve">0.137472674250603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142480581998825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142114147543907</t>
+    <t xml:space="preserve">0.142480596899986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142114162445068</t>
   </si>
   <si>
     <t xml:space="preserve">0.141320198774338</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142175227403641</t>
+    <t xml:space="preserve">0.142175242304802</t>
   </si>
   <si>
     <t xml:space="preserve">0.138327687978745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142236277461052</t>
+    <t xml:space="preserve">0.142236292362213</t>
   </si>
   <si>
     <t xml:space="preserve">0.138205543160439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140526756644249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139899402856827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136135265231133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136637166142464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133876815438271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133814081549644</t>
+    <t xml:space="preserve">0.140526741743088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139899387955666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136135280132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136637181043625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133876800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133814066648483</t>
   </si>
   <si>
     <t xml:space="preserve">0.132998540997505</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">0.129234418272972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128732517361641</t>
+    <t xml:space="preserve">0.128732532262802</t>
   </si>
   <si>
     <t xml:space="preserve">0.125156626105309</t>
@@ -293,16 +293,16 @@
     <t xml:space="preserve">0.126725018024445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127352386713028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127979680895805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126599565148354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127916991710663</t>
+    <t xml:space="preserve">0.127352371811867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127979710698128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126599535346031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127916976809502</t>
   </si>
   <si>
     <t xml:space="preserve">0.130489140748978</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">0.131116464734077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13155560195446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134065017104149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131179213523865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133688613772392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134880572557449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134190499782562</t>
+    <t xml:space="preserve">0.131555616855621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13406503200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131179198622704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133688598871231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134880587458611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134190514683723</t>
   </si>
   <si>
     <t xml:space="preserve">0.130614578723907</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">0.132873058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128481581807137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121078863739967</t>
+    <t xml:space="preserve">0.128481596708298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121078848838806</t>
   </si>
   <si>
     <t xml:space="preserve">0.120200552046299</t>
@@ -350,214 +350,214 @@
     <t xml:space="preserve">0.1218316629529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110413864254951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233199179173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366196095943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794054508209</t>
+    <t xml:space="preserve">0.110413879156113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233176827431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366188645363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794039607048</t>
   </si>
   <si>
     <t xml:space="preserve">0.114052496850491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105395048856735</t>
+    <t xml:space="preserve">0.105395063757896</t>
   </si>
   <si>
     <t xml:space="preserve">0.104893177747726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111041225492954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904464006424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354887485504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277125120163</t>
+    <t xml:space="preserve">0.111041210591793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904471457005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354902386665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727563500404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277132570744</t>
   </si>
   <si>
     <t xml:space="preserve">0.102822914719582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100501716136932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716262340546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110790275037289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554397761822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923294305801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303454756737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632167577744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116561912000179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116373710334301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746356546879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432694554329</t>
+    <t xml:space="preserve">0.100501708686352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11079028993845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554390311241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923286855221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303462207317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632189929485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11656191945076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116373725235462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746363997459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432679653168</t>
   </si>
   <si>
     <t xml:space="preserve">0.114805333316326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116185508668423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569433689117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820384144783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934573113918</t>
+    <t xml:space="preserve">0.116185501217842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569448590279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820376694202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934558212757</t>
   </si>
   <si>
     <t xml:space="preserve">0.109159179031849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107088908553123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10614787787199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104140318930149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105646021664143</t>
+    <t xml:space="preserve">0.107088901102543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10614787042141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104140356183052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105645999312401</t>
   </si>
   <si>
     <t xml:space="preserve">0.107465319335461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108531817793846</t>
+    <t xml:space="preserve">0.108531802892685</t>
   </si>
   <si>
     <t xml:space="preserve">0.107590794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109535589814186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104830428957939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092650771141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029931783676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849236905575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978476703167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111605852842331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11373882740736</t>
+    <t xml:space="preserve">0.109535582363605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104830421507359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092673122883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029924333096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10765352845192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849244356155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978491604328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111605830490589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113738834857941</t>
   </si>
   <si>
     <t xml:space="preserve">0.113864310085773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110288389027119</t>
+    <t xml:space="preserve">0.11028840392828</t>
   </si>
   <si>
     <t xml:space="preserve">0.110225647687912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108845487236977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723776578903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10733986645937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406342566013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104516759514809</t>
+    <t xml:space="preserve">0.108845509588718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723769128323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339851558208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406350016594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104516789317131</t>
   </si>
   <si>
     <t xml:space="preserve">0.105018652975559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106649771332741</t>
+    <t xml:space="preserve">0.10664976388216</t>
   </si>
   <si>
     <t xml:space="preserve">0.10583420842886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106085151433945</t>
+    <t xml:space="preserve">0.106085158884525</t>
   </si>
   <si>
     <t xml:space="preserve">0.10978651791811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104391291737556</t>
+    <t xml:space="preserve">0.104391299188137</t>
   </si>
   <si>
     <t xml:space="preserve">0.107779003679752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107214368879795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11606003344059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114742606878281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11242139339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425187766552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295903265476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022402644157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712497770786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1068379804492</t>
+    <t xml:space="preserve">0.107214391231537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060040891171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114742584526539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112421400845051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113425143063068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295933067799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022410094738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712505221367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837958097458</t>
   </si>
   <si>
     <t xml:space="preserve">0.105520524084568</t>
@@ -566,25 +566,25 @@
     <t xml:space="preserve">0.104265816509724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102760180830956</t>
+    <t xml:space="preserve">0.102760203182697</t>
   </si>
   <si>
     <t xml:space="preserve">0.101003594696522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104579493403435</t>
+    <t xml:space="preserve">0.104579500854015</t>
   </si>
   <si>
     <t xml:space="preserve">0.102885663509369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103889405727386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254545152187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10056446492672</t>
+    <t xml:space="preserve">0.103889428079128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254537701607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100564457476139</t>
   </si>
   <si>
     <t xml:space="preserve">0.101066328585148</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">0.101630955934525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106524296104908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109912008047104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539339482784</t>
+    <t xml:space="preserve">0.106524288654327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109911985695362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539346933365</t>
   </si>
   <si>
     <t xml:space="preserve">0.110915750265121</t>
@@ -608,70 +608,70 @@
     <t xml:space="preserve">0.108657278120518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112609587609768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111292168498039</t>
+    <t xml:space="preserve">0.11260960996151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111292161047459</t>
   </si>
   <si>
     <t xml:space="preserve">0.109410114586353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108343608677387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108280897140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033688902855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351152718067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544300794601</t>
+    <t xml:space="preserve">0.108343616127968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108280874788761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033718705177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351130366325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544330596924</t>
   </si>
   <si>
     <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144918218255043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142408803105354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132371157407761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132684856653214</t>
+    <t xml:space="preserve">0.144918188452721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142408788204193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132371187210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132684841752052</t>
   </si>
   <si>
     <t xml:space="preserve">0.134253218770027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131304681301117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13469235599041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135821625590324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836654067039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855484366417</t>
+    <t xml:space="preserve">0.131304666399956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134692370891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135821610689163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836668968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855469465256</t>
   </si>
   <si>
     <t xml:space="preserve">0.143161624670029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141781464219093</t>
+    <t xml:space="preserve">0.141781434416771</t>
   </si>
   <si>
     <t xml:space="preserve">0.133500412106514</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">0.130175426602364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131681084632874</t>
+    <t xml:space="preserve">0.131681114435196</t>
   </si>
   <si>
     <t xml:space="preserve">0.130112707614899</t>
@@ -692,37 +692,37 @@
     <t xml:space="preserve">0.130740061402321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124842956662178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097664237022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12697596848011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289623022079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226889133453</t>
+    <t xml:space="preserve">0.124842964112759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097679138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975953578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289637923241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226904034615</t>
   </si>
   <si>
     <t xml:space="preserve">0.126411333680153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1254703104496</t>
+    <t xml:space="preserve">0.125470325350761</t>
   </si>
   <si>
     <t xml:space="preserve">0.126536816358566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125972181558609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551844835281</t>
+    <t xml:space="preserve">0.124215610325336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12597219645977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551859736443</t>
   </si>
   <si>
     <t xml:space="preserve">0.130677327513695</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">0.129171699285507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13224570453167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006055235863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133939534425735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127750992775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136260762810707</t>
+    <t xml:space="preserve">0.132245734333992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006040334702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133939549326897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127765893936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136260747909546</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943306446075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137766376137733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138017326593399</t>
+    <t xml:space="preserve">0.137766405940056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13801734149456</t>
   </si>
   <si>
     <t xml:space="preserve">0.140777692198753</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">0.134629637002945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134002283215523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133437663316727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129673570394516</t>
+    <t xml:space="preserve">0.134002268314362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133437678217888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129673555493355</t>
   </si>
   <si>
     <t xml:space="preserve">0.128356128931046</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">0.135633409023285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137891858816147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13770367205143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433921098709</t>
+    <t xml:space="preserve">0.137891873717308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137703657150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433906197548</t>
   </si>
   <si>
     <t xml:space="preserve">0.132057502865791</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">0.134504154324532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134502410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132989704608917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131729170680046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130720734596252</t>
+    <t xml:space="preserve">0.134502425789833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13298973441124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131729155778885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13072070479393</t>
   </si>
   <si>
     <t xml:space="preserve">0.133178815245628</t>
@@ -839,31 +839,31 @@
     <t xml:space="preserve">0.131792187690735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131477057933807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132359459996223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130909785628319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130468606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129964381456375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129586204886436</t>
+    <t xml:space="preserve">0.131477043032646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132359430193901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130909815430641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130468592047691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129964396357536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127506285905838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129586219787598</t>
   </si>
   <si>
     <t xml:space="preserve">0.127002045512199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127947464585304</t>
+    <t xml:space="preserve">0.127947479486465</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199592232704</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">0.128703817725182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126371741294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125930562615395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127128109335899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056611537933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124796077609062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124670013785362</t>
+    <t xml:space="preserve">0.126371771097183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125930592417717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127128094434738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056641340256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12479605525732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12466999143362</t>
   </si>
   <si>
     <t xml:space="preserve">0.124165765941143</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">0.125237256288528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12901896238327</t>
+    <t xml:space="preserve">0.129018932580948</t>
   </si>
   <si>
     <t xml:space="preserve">0.127380222082138</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">0.128136560320854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127884447574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443253993988</t>
+    <t xml:space="preserve">0.127884462475777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443239092827</t>
   </si>
   <si>
     <t xml:space="preserve">0.126939013600349</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">0.126308739185333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430942893028</t>
+    <t xml:space="preserve">0.133430927991867</t>
   </si>
   <si>
     <t xml:space="preserve">0.135573893785477</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">0.136456280946732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135636925697327</t>
+    <t xml:space="preserve">0.135636940598488</t>
   </si>
   <si>
     <t xml:space="preserve">0.134061217308044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132485523819923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133557006716728</t>
+    <t xml:space="preserve">0.132485508918762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133556976914406</t>
   </si>
   <si>
     <t xml:space="preserve">0.135195732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136141166090965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134439378976822</t>
+    <t xml:space="preserve">0.136141180992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134439393877983</t>
   </si>
   <si>
     <t xml:space="preserve">0.137464731931686</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">0.137842923402786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136330232024193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137086570262909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136771410703659</t>
+    <t xml:space="preserve">0.136330261826515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13708658516407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136771455407143</t>
   </si>
   <si>
     <t xml:space="preserve">0.136204183101654</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">0.13500665128231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134754508733749</t>
+    <t xml:space="preserve">0.134754538536072</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
@@ -1001,34 +1001,34 @@
     <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151141881942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153789073228836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152780637145042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151267930865288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145280241966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14704504609108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444715499878</t>
+    <t xml:space="preserve">0.15114189684391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153789088129997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152780622243881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267945766449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145280256867409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147045060992241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444700598717</t>
   </si>
   <si>
     <t xml:space="preserve">0.159398600459099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156625360250473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157570794224739</t>
+    <t xml:space="preserve">0.156625345349312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157570779323578</t>
   </si>
   <si>
     <t xml:space="preserve">0.152843654155731</t>
@@ -1046,46 +1046,46 @@
     <t xml:space="preserve">0.150259494781494</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148746818304062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15334789454937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805990099907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419362545013</t>
+    <t xml:space="preserve">0.148746803402901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153347864747047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805975198746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419377446175</t>
   </si>
   <si>
     <t xml:space="preserve">0.156940490007401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159146472811699</t>
+    <t xml:space="preserve">0.15914648771286</t>
   </si>
   <si>
     <t xml:space="preserve">0.167655304074287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170050397515297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167214095592499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067269682884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945811629295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17521870136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336299300194</t>
+    <t xml:space="preserve">0.170050382614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16721411049366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067299485207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811296820641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175218716263771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336329102516</t>
   </si>
   <si>
     <t xml:space="preserve">0.170176446437836</t>
@@ -1094,118 +1094,118 @@
     <t xml:space="preserve">0.176479265093803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173642992973328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170365542173386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166205659508705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222561478615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168600752949715</t>
+    <t xml:space="preserve">0.173643007874489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170365512371063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166205644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222546577454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168600723147392</t>
   </si>
   <si>
     <t xml:space="preserve">0.166520789265633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166394725441933</t>
+    <t xml:space="preserve">0.166394710540771</t>
   </si>
   <si>
     <t xml:space="preserve">0.161730632185936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160091906785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156688392162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161226436495781</t>
+    <t xml:space="preserve">0.160091921687126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156688377261162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16122642159462</t>
   </si>
   <si>
     <t xml:space="preserve">0.162487000226974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747563958168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873612880707</t>
+    <t xml:space="preserve">0.163747534155846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873597979546</t>
   </si>
   <si>
     <t xml:space="preserve">0.16103732585907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158011958003044</t>
+    <t xml:space="preserve">0.158011987805367</t>
   </si>
   <si>
     <t xml:space="preserve">0.157759860157967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167970463633537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167718306183815</t>
+    <t xml:space="preserve">0.167970448732376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167718321084976</t>
   </si>
   <si>
     <t xml:space="preserve">0.165260225534439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163117259740829</t>
+    <t xml:space="preserve">0.163117274641991</t>
   </si>
   <si>
     <t xml:space="preserve">0.163810580968857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159461632370949</t>
+    <t xml:space="preserve">0.159461617469788</t>
   </si>
   <si>
     <t xml:space="preserve">0.147675335407257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147486239671707</t>
+    <t xml:space="preserve">0.147486254572868</t>
   </si>
   <si>
     <t xml:space="preserve">0.150007382035255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150448560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511607527733</t>
+    <t xml:space="preserve">0.150448575615883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511622428894</t>
   </si>
   <si>
     <t xml:space="preserve">0.15107886493206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151646122336388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150322511792183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494705557823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150826752185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151772171258926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881318211555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583105325699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149629205465317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709154248238</t>
+    <t xml:space="preserve">0.151646137237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150322526693344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494690656662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15082673728466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151772156357765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881333112717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583090424538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149629220366478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709169149399</t>
   </si>
   <si>
     <t xml:space="preserve">0.15101583302021</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763720273972</t>
+    <t xml:space="preserve">0.150763735175133</t>
   </si>
   <si>
     <t xml:space="preserve">0.150637671351433</t>
@@ -1226,58 +1226,58 @@
     <t xml:space="preserve">0.151204913854599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149944379925728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213364839554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377092719078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15725564956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156310215592384</t>
+    <t xml:space="preserve">0.149944350123405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213379740715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528509497643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1493771225214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157255634665489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156310200691223</t>
   </si>
   <si>
     <t xml:space="preserve">0.164503902196884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163243323564529</t>
+    <t xml:space="preserve">0.163243308663368</t>
   </si>
   <si>
     <t xml:space="preserve">0.162613034248352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161982774734497</t>
+    <t xml:space="preserve">0.161982759833336</t>
   </si>
   <si>
     <t xml:space="preserve">0.163558468222618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165764480829239</t>
+    <t xml:space="preserve">0.165764451026917</t>
   </si>
   <si>
     <t xml:space="preserve">0.165449306368828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166079580783844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160722181200981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162297904491425</t>
+    <t xml:space="preserve">0.166079610586166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160722196102142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162297889590263</t>
   </si>
   <si>
     <t xml:space="preserve">0.149061962962151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14717110991478</t>
+    <t xml:space="preserve">0.147171124815941</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540835499763</t>
@@ -1286,37 +1286,37 @@
     <t xml:space="preserve">0.146225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142759129405022</t>
+    <t xml:space="preserve">0.14275911450386</t>
   </si>
   <si>
     <t xml:space="preserve">0.144334822893143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140238001942635</t>
+    <t xml:space="preserve">0.140237987041473</t>
   </si>
   <si>
     <t xml:space="preserve">0.139607697725296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138031989336014</t>
+    <t xml:space="preserve">0.138032004237175</t>
   </si>
   <si>
     <t xml:space="preserve">0.139922857284546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135826021432877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138347148895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813695430756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140553146600723</t>
+    <t xml:space="preserve">0.135826006531715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138347178697586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498550772667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813680529594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140553131699562</t>
   </si>
   <si>
     <t xml:space="preserve">0.141183421015739</t>
@@ -1337,82 +1337,82 @@
     <t xml:space="preserve">0.132674589753151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143074259161949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965127110481</t>
+    <t xml:space="preserve">0.14307427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
     <t xml:space="preserve">0.143389403820038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142443969845772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575853228569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864416241646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14496511220932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146253690123558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145609393715858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455096960068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142710104584694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141421526670456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139166504144669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777245163918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139488652348518</t>
+    <t xml:space="preserve">0.142443984746933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575838327408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864401340485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144965097308159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146253705024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14560940861702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455082058907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142710089683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141421556472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139166533946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777230262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139488637447357</t>
   </si>
   <si>
     <t xml:space="preserve">0.135622918605804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133690029382706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132723599672318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13207933306694</t>
+    <t xml:space="preserve">0.133690044283867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132723614573479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132079318165779</t>
   </si>
   <si>
     <t xml:space="preserve">0.129824310541153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125765293836594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12499213218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126796141266823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129180014133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133367910981178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131757169961929</t>
+    <t xml:space="preserve">0.125765278935432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12499213963747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126796156167984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129180029034615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133367896080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131757199764252</t>
   </si>
   <si>
     <t xml:space="preserve">0.125894144177437</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">0.128600165247917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468592047691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127440452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127955853939056</t>
+    <t xml:space="preserve">0.130468621850014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127440437674522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127955868840218</t>
   </si>
   <si>
     <t xml:space="preserve">0.127827018499374</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">0.124347865581512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123703561723232</t>
+    <t xml:space="preserve">0.123703569173813</t>
   </si>
   <si>
     <t xml:space="preserve">0.127311587333679</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">0.126667305827141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126538455486298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128729030489922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12834244966507</t>
+    <t xml:space="preserve">0.126538440585136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128729045391083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128342464566231</t>
   </si>
   <si>
     <t xml:space="preserve">0.129502162337303</t>
@@ -1478,25 +1478,25 @@
     <t xml:space="preserve">0.134656473994255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138522237539291</t>
+    <t xml:space="preserve">0.13852222263813</t>
   </si>
   <si>
     <t xml:space="preserve">0.13820007443428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135300770401955</t>
+    <t xml:space="preserve">0.135300755500793</t>
   </si>
   <si>
     <t xml:space="preserve">0.130790755152702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128084719181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128857880830765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125249862670898</t>
+    <t xml:space="preserve">0.128084748983383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128857895731926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12524987757206</t>
   </si>
   <si>
     <t xml:space="preserve">0.122157283127308</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">0.123316988348961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125507563352585</t>
+    <t xml:space="preserve">0.125507578253746</t>
   </si>
   <si>
     <t xml:space="preserve">0.128213584423065</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">0.126151859760284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127182736992836</t>
+    <t xml:space="preserve">0.127182722091675</t>
   </si>
   <si>
     <t xml:space="preserve">0.125636428594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120482116937637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12228612601757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122414991259575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260657250881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266050815582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113394930958748</t>
+    <t xml:space="preserve">0.120482131838799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122286133468151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122414983808994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260672152042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266080617905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113394938409328</t>
   </si>
   <si>
     <t xml:space="preserve">0.111848644912243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112106367945671</t>
+    <t xml:space="preserve">0.112106345593929</t>
   </si>
   <si>
     <t xml:space="preserve">0.114425800740719</t>
@@ -1550,37 +1550,37 @@
     <t xml:space="preserve">0.114683516323566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112235203385353</t>
+    <t xml:space="preserve">0.112235195934772</t>
   </si>
   <si>
     <t xml:space="preserve">0.110817790031433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108240611851215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921164155006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101926572620869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10501915961504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103086300194263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374893009663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105663470923901</t>
+    <t xml:space="preserve">0.108240626752377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565460562706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921186506748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101926580071449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105019174516201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103086292743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117169976234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105663456022739</t>
   </si>
   <si>
     <t xml:space="preserve">0.107982911169529</t>
@@ -1589,19 +1589,19 @@
     <t xml:space="preserve">0.108627177774906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108111761510372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111462064087391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11275065690279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756050467491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173501074314</t>
+    <t xml:space="preserve">0.108111754059792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11146205663681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750642001629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756057918072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173471271992</t>
   </si>
   <si>
     <t xml:space="preserve">0.109529189765453</t>
@@ -1613,46 +1613,46 @@
     <t xml:space="preserve">0.101153448224068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10398830473423</t>
+    <t xml:space="preserve">0.103988319635391</t>
   </si>
   <si>
     <t xml:space="preserve">0.102699734270573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105276875197887</t>
+    <t xml:space="preserve">0.105276890099049</t>
   </si>
   <si>
     <t xml:space="preserve">0.111204348504543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115585520863533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1158432289958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327805280685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113008379936218</t>
+    <t xml:space="preserve">0.115585513412952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843236446381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327797830105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113008357584476</t>
   </si>
   <si>
     <t xml:space="preserve">0.10940033942461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110431179404259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107854045927525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730596601963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10630775988102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103859454393387</t>
+    <t xml:space="preserve">0.110431201756001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107854038476944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730589151382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106307752430439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103859461843967</t>
   </si>
   <si>
     <t xml:space="preserve">0.114554651081562</t>
@@ -1661,25 +1661,25 @@
     <t xml:space="preserve">0.109142631292343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1090137809515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884915709496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271489083767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107338607311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442011237144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411156356335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055437862873</t>
+    <t xml:space="preserve">0.109013766050339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884900808334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271474182606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107338614761829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411163806915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055445313454</t>
   </si>
   <si>
     <t xml:space="preserve">0.100251421332359</t>
@@ -1688,46 +1688,46 @@
     <t xml:space="preserve">0.0999937206506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101282298564911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797729730606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766845047474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105148032307625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915755689144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111075505614281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112621776759624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302343964577</t>
+    <t xml:space="preserve">0.10128228366375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797737181187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766852498055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105148024857044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915770590305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1110754981637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112621799111366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302358865738</t>
   </si>
   <si>
     <t xml:space="preserve">0.110688924789429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104761466383934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534613132477</t>
+    <t xml:space="preserve">0.104761451482773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534598231316</t>
   </si>
   <si>
     <t xml:space="preserve">0.107467472553253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108498334884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080891728401</t>
+    <t xml:space="preserve">0.108498349785805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080884277821</t>
   </si>
   <si>
     <t xml:space="preserve">0.104503743350506</t>
@@ -1739,121 +1739,121 @@
     <t xml:space="preserve">0.106436610221863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105341322720051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596345245838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562774956226</t>
+    <t xml:space="preserve">0.10534130781889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596322894096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562767505646</t>
   </si>
   <si>
     <t xml:space="preserve">0.109207049012184</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110185049474239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857119619846</t>
+    <t xml:space="preserve">0.110185064375401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857127070427</t>
   </si>
   <si>
     <t xml:space="preserve">0.11116885393858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110513009130955</t>
+    <t xml:space="preserve">0.110512994229794</t>
   </si>
   <si>
     <t xml:space="preserve">0.107889533042908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106905743479729</t>
+    <t xml:space="preserve">0.10690575838089</t>
   </si>
   <si>
     <t xml:space="preserve">0.10592196136713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103954367339611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104282297194004</t>
+    <t xml:space="preserve">0.10395435243845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104282304644585</t>
   </si>
   <si>
     <t xml:space="preserve">0.105594016611576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108217462897301</t>
+    <t xml:space="preserve">0.108217470347881</t>
   </si>
   <si>
     <t xml:space="preserve">0.105266094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104938164353371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102970585227013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103626422584057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103298500180244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101658850908279</t>
+    <t xml:space="preserve">0.104938142001629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102970570325851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103626430034637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103298492729664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101658843457699</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347109138966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330898702145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0970677882432938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.097723662853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957255482674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951002165675163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.098051592707634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0964119359850883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09870745241642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099363312125206</t>
+    <t xml:space="preserve">0.101330906152725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0970677956938744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0977236703038216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957180976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951001942157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0980515852570534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0964119285345078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0987074598670006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0993633195757866</t>
   </si>
   <si>
     <t xml:space="preserve">0.100019179284573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101002968847752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100675038993359</t>
+    <t xml:space="preserve">0.101002991199493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100675046443939</t>
   </si>
   <si>
     <t xml:space="preserve">0.102642640471458</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0983795300126076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099691241979599</t>
+    <t xml:space="preserve">0.098379522562027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0996912494301796</t>
   </si>
   <si>
     <t xml:space="preserve">0.099035382270813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104610227048397</t>
+    <t xml:space="preserve">0.104610219597816</t>
   </si>
   <si>
     <t xml:space="preserve">0.107561610639095</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">0.108873322606087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108545392751694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109201274812222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107233673334122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249891221523</t>
+    <t xml:space="preserve">0.108545415103436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109201267361641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107233680784702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249883770943</t>
   </si>
   <si>
     <t xml:space="preserve">0.112152650952339</t>
@@ -1880,46 +1880,46 @@
     <t xml:space="preserve">0.114448182284832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111824721097946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808525562286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113136455416679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480595707893</t>
+    <t xml:space="preserve">0.111824728548527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808533012867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113136440515518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480580806732</t>
   </si>
   <si>
     <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130516827106476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139698922634125</t>
+    <t xml:space="preserve">0.130516812205315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139698937535286</t>
   </si>
   <si>
     <t xml:space="preserve">0.132484436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141010656952858</t>
+    <t xml:space="preserve">0.141010642051697</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686567425728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173803806304932</t>
+    <t xml:space="preserve">0.173803821206093</t>
   </si>
   <si>
     <t xml:space="preserve">0.167245179414749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155439630150795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150848597288132</t>
+    <t xml:space="preserve">0.155439659953117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150848612189293</t>
   </si>
   <si>
     <t xml:space="preserve">0.154127910733223</t>
@@ -1928,37 +1928,37 @@
     <t xml:space="preserve">0.157407239079475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156751349568367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152816191315651</t>
+    <t xml:space="preserve">0.156751379370689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152816161513329</t>
   </si>
   <si>
     <t xml:space="preserve">0.148881003260612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145601689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146257564425468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146913424134254</t>
+    <t xml:space="preserve">0.145601704716682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146257549524307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146913409233093</t>
   </si>
   <si>
     <t xml:space="preserve">0.150192737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14953687787056</t>
+    <t xml:space="preserve">0.149536862969398</t>
   </si>
   <si>
     <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147569268941879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148225158452988</t>
+    <t xml:space="preserve">0.147569254040718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148225143551826</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654146552086</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">0.141666516661644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139043048024178</t>
+    <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
     <t xml:space="preserve">0.135107859969139</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">0.133140295743942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137731328606606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15478378534317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156095519661903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153472051024437</t>
+    <t xml:space="preserve">0.137731313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154783770442009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156095504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153472036123276</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">0.126581653952599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123958185315132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118711270391941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110840924084187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0967398658394814</t>
+    <t xml:space="preserve">0.123958192765713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118711285293102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110840916633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0967398583889008</t>
   </si>
   <si>
     <t xml:space="preserve">0.0826388001441956</t>
@@ -2024,82 +2024,82 @@
     <t xml:space="preserve">0.087885707616806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0872298404574394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0885415822267532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0911650210618973</t>
+    <t xml:space="preserve">0.08722984790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.088541567325592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0911650285124779</t>
   </si>
   <si>
     <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0928046703338623</t>
+    <t xml:space="preserve">0.0928046852350235</t>
   </si>
   <si>
     <t xml:space="preserve">0.0944443345069885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0960839986801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0931326225399971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0957560613751411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0937884747982025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0965431034564972</t>
+    <t xml:space="preserve">0.0960840061306953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0931326150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0957560688257217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0937884822487831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0965431109070778</t>
   </si>
   <si>
     <t xml:space="preserve">0.0969366207718849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0978548377752304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0971989706158638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0924767479300499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0940508171916008</t>
+    <t xml:space="preserve">0.097854845225811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0971989631652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0924767553806305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0940508246421814</t>
   </si>
   <si>
     <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0941819995641708</t>
+    <t xml:space="preserve">0.0941819921135902</t>
   </si>
   <si>
     <t xml:space="preserve">0.0949690341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0954937189817429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483550906181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740641355515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0968054458498955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0966742932796478</t>
+    <t xml:space="preserve">0.0954937264323235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483476400375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740633904934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0968054533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0966742858290672</t>
   </si>
   <si>
     <t xml:space="preserve">0.110709756612778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0979859977960587</t>
+    <t xml:space="preserve">0.0979859903454781</t>
   </si>
   <si>
     <t xml:space="preserve">0.0991665497422218</t>
@@ -2108,22 +2108,22 @@
     <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0948378667235374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084781646729</t>
+    <t xml:space="preserve">0.0948378518223763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084766745567</t>
   </si>
   <si>
     <t xml:space="preserve">0.102183535695076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0999535992741585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10323291271925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104806989431381</t>
+    <t xml:space="preserve">0.0999536067247391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10323292016983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104806981980801</t>
   </si>
   <si>
     <t xml:space="preserve">0.140354782342911</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">0.125925794243813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138387188315392</t>
+    <t xml:space="preserve">0.138387203216553</t>
   </si>
   <si>
     <t xml:space="preserve">0.14232237637043</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">0.137403398752213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135435789823532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136419594287872</t>
+    <t xml:space="preserve">0.135435804724693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136419609189034</t>
   </si>
   <si>
     <t xml:space="preserve">0.134452015161514</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">0.130779176950455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130123302340508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129336282610893</t>
+    <t xml:space="preserve">0.130123317241669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129336267709732</t>
   </si>
   <si>
     <t xml:space="preserve">0.130385652184486</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">0.131500631570816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130910351872444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133468225598335</t>
+    <t xml:space="preserve">0.130910336971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133468210697174</t>
   </si>
   <si>
     <t xml:space="preserve">0.129992142319679</t>
@@ -2192,40 +2192,40 @@
     <t xml:space="preserve">0.126975163817406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127631038427353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128549218177795</t>
+    <t xml:space="preserve">0.127631023526192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128549247980118</t>
   </si>
   <si>
     <t xml:space="preserve">0.133796155452728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132156506180763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130648002028465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129205107688904</t>
+    <t xml:space="preserve">0.132156476378441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130648016929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129205092787743</t>
   </si>
   <si>
     <t xml:space="preserve">0.129598632454872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140026837587357</t>
+    <t xml:space="preserve">0.140026852488518</t>
   </si>
   <si>
     <t xml:space="preserve">0.1297297924757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129860982298851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130254492163658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129073917865753</t>
+    <t xml:space="preserve">0.12986096739769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130254477262497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129073932766914</t>
   </si>
   <si>
     <t xml:space="preserve">0.125138744711876</t>
@@ -2234,34 +2234,34 @@
     <t xml:space="preserve">0.124614059925079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143634095788002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143962040543556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139370977878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136091649532318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138059258460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136747524142265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140682727098465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144945830106735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142650291323662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141994461417198</t>
+    <t xml:space="preserve">0.143634110689163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143962055444717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139370992779732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136091664433479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13805927336216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136747539043427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140682712197304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144945845007896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142650321125984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141994431614876</t>
   </si>
   <si>
     <t xml:space="preserve">0.144289970397949</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">0.153799995779991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152488246560097</t>
+    <t xml:space="preserve">0.152488261461258</t>
   </si>
   <si>
     <t xml:space="preserve">0.157079309225082</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153144136071205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155111685395241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155767560005188</t>
+    <t xml:space="preserve">0.153144121170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155111700296402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155767574906349</t>
   </si>
   <si>
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702748060226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162982076406479</t>
+    <t xml:space="preserve">0.159702762961388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16298209130764</t>
   </si>
   <si>
     <t xml:space="preserve">0.166917249560356</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">0.162326216697693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161014497280121</t>
+    <t xml:space="preserve">0.16101448237896</t>
   </si>
   <si>
     <t xml:space="preserve">0.15904688835144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159374833106995</t>
+    <t xml:space="preserve">0.159374818205833</t>
   </si>
   <si>
     <t xml:space="preserve">0.158718958497047</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">0.165341451764107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163571193814278</t>
+    <t xml:space="preserve">0.163571178913116</t>
   </si>
   <si>
     <t xml:space="preserve">0.162863090634346</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">0.157198280096054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158260434865952</t>
+    <t xml:space="preserve">0.158260449767113</t>
   </si>
   <si>
     <t xml:space="preserve">0.162154987454414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158968538045883</t>
+    <t xml:space="preserve">0.158968523144722</t>
   </si>
   <si>
     <t xml:space="preserve">0.160384744405746</t>
@@ -2363,25 +2363,25 @@
     <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157552316784859</t>
+    <t xml:space="preserve">0.15755233168602</t>
   </si>
   <si>
     <t xml:space="preserve">0.161800935864449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155073970556259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153303742408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155782088637352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151533484458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15259562432766</t>
+    <t xml:space="preserve">0.155073955655098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153303727507591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155782073736191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151533469557762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152595639228821</t>
   </si>
   <si>
     <t xml:space="preserve">0.154719948768616</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">0.156844228506088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156490176916122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153657793998718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154011815786362</t>
+    <t xml:space="preserve">0.156490191817284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153657779097557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154011830687523</t>
   </si>
   <si>
     <t xml:space="preserve">0.156136125326157</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">0.154365882277489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151887536048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151179417967796</t>
+    <t xml:space="preserve">0.151887521147728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151179432868958</t>
   </si>
   <si>
     <t xml:space="preserve">0.15011727809906</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149055123329163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146222725510597</t>
+    <t xml:space="preserve">0.149055138230324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146222710609436</t>
   </si>
   <si>
     <t xml:space="preserve">0.147284880280495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142682239413261</t>
+    <t xml:space="preserve">0.1426822245121</t>
   </si>
   <si>
     <t xml:space="preserve">0.143390327692032</t>
@@ -2453,16 +2453,16 @@
     <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152949675917625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145160585641861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147638916969299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148701071739197</t>
+    <t xml:space="preserve">0.152949690818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1451605707407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147638931870461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148701086640358</t>
   </si>
   <si>
     <t xml:space="preserve">0.146576777100563</t>
@@ -2477,31 +2477,31 @@
     <t xml:space="preserve">0.144806534051895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144098415970802</t>
+    <t xml:space="preserve">0.144098430871964</t>
   </si>
   <si>
     <t xml:space="preserve">0.145868673920631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147992983460426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165695488452911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168527901172638</t>
+    <t xml:space="preserve">0.147992968559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16569547355175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168527871370316</t>
   </si>
   <si>
     <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167465716600418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16498738527298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163217142224312</t>
+    <t xml:space="preserve">0.16746574640274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164987370371819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163217127323151</t>
   </si>
   <si>
     <t xml:space="preserve">0.164358526468277</t>
@@ -2510,13 +2510,13 @@
     <t xml:space="preserve">0.162075757980347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167782664299011</t>
+    <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
     <t xml:space="preserve">0.167021736502647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161695286631584</t>
+    <t xml:space="preserve">0.161695301532745</t>
   </si>
   <si>
     <t xml:space="preserve">0.161314830183983</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">0.159793004393578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163978055119514</t>
+    <t xml:space="preserve">0.163978070020676</t>
   </si>
   <si>
     <t xml:space="preserve">0.16055391728878</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165119424462318</t>
+    <t xml:space="preserve">0.16511943936348</t>
   </si>
   <si>
     <t xml:space="preserve">0.163597598671913</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">0.162456214427948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159032091498375</t>
+    <t xml:space="preserve">0.159032076597214</t>
   </si>
   <si>
     <t xml:space="preserve">0.159412547945976</t>
@@ -2558,16 +2558,16 @@
     <t xml:space="preserve">0.16017347574234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165880337357521</t>
+    <t xml:space="preserve">0.165880352258682</t>
   </si>
   <si>
     <t xml:space="preserve">0.170445874333382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169684961438179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170826330780983</t>
+    <t xml:space="preserve">0.169684946537018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170826315879822</t>
   </si>
   <si>
     <t xml:space="preserve">0.171967700123787</t>
@@ -2576,19 +2576,19 @@
     <t xml:space="preserve">0.17006541788578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157129779458046</t>
+    <t xml:space="preserve">0.157129764556885</t>
   </si>
   <si>
     <t xml:space="preserve">0.157890692353249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153705641627312</t>
+    <t xml:space="preserve">0.153705656528473</t>
   </si>
   <si>
     <t xml:space="preserve">0.14427025616169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147770464420319</t>
+    <t xml:space="preserve">0.14777047932148</t>
   </si>
   <si>
     <t xml:space="preserve">0.155227482318878</t>
@@ -2597,25 +2597,25 @@
     <t xml:space="preserve">0.155988395214081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157510235905647</t>
+    <t xml:space="preserve">0.157510250806808</t>
   </si>
   <si>
     <t xml:space="preserve">0.164738968014717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166260808706284</t>
+    <t xml:space="preserve">0.166260823607445</t>
   </si>
   <si>
     <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166641265153885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168163105845451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167402192950249</t>
+    <t xml:space="preserve">0.166641250252724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168163120746613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167402178049088</t>
   </si>
   <si>
     <t xml:space="preserve">0.168543562293053</t>
@@ -68696,7 +68696,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6912847222</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>143258</v>
@@ -68717,6 +68717,32 @@
         <v>1095</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6910648148</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>612844</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>0.160500004887581</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>0.159999996423721</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481374382973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155000314116478</t>
+    <t xml:space="preserve">0.158481404185295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155000299215317</t>
   </si>
   <si>
     <t xml:space="preserve">0.153229221701622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150542080402374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148099198937416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150297746062279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151580289006233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147366315126419</t>
+    <t xml:space="preserve">0.150542065501213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148099184036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15029776096344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151580274105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14736633002758</t>
   </si>
   <si>
     <t xml:space="preserve">0.142358422279358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132831215858459</t>
+    <t xml:space="preserve">0.132831230759621</t>
   </si>
   <si>
     <t xml:space="preserve">0.134541243314743</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">0.12531940639019</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131121218204498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134358018636703</t>
+    <t xml:space="preserve">0.131121203303337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134358033537865</t>
   </si>
   <si>
     <t xml:space="preserve">0.134419083595276</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143335565924644</t>
+    <t xml:space="preserve">0.143335551023483</t>
   </si>
   <si>
     <t xml:space="preserve">0.138022348284721</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">0.137778058648109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140465214848518</t>
+    <t xml:space="preserve">0.140465199947357</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136190190911293</t>
+    <t xml:space="preserve">0.136190176010132</t>
   </si>
   <si>
     <t xml:space="preserve">0.131793007254601</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">0.129166916012764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129289075732231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967920541763</t>
+    <t xml:space="preserve">0.12928906083107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967935442924</t>
   </si>
   <si>
     <t xml:space="preserve">0.122754380106926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116158604621887</t>
+    <t xml:space="preserve">0.116158619523048</t>
   </si>
   <si>
     <t xml:space="preserve">0.11847934871912</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">0.125807970762253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125197231769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960864782333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127029404044151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125014051795006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13099904358387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129105851054192</t>
+    <t xml:space="preserve">0.125197261571884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960849881172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127029418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125014021992683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999058485031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12910583615303</t>
   </si>
   <si>
     <t xml:space="preserve">0.128617271780968</t>
@@ -161,25 +161,25 @@
     <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133808374404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138755187392235</t>
+    <t xml:space="preserve">0.133808389306068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138755202293396</t>
   </si>
   <si>
     <t xml:space="preserve">0.139671266078949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136739805340767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136495545506477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140159860253334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141747698187828</t>
+    <t xml:space="preserve">0.136739820241928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136495530605316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140159830451012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141747713088989</t>
   </si>
   <si>
     <t xml:space="preserve">0.147122040390968</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">0.14901527762413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146572411060333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14571738243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143213421106339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144129529595375</t>
+    <t xml:space="preserve">0.146572396159172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145717397332191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143213465809822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144129514694214</t>
   </si>
   <si>
     <t xml:space="preserve">0.140892699360847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139793410897255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968742728233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068046092987</t>
+    <t xml:space="preserve">0.139793425798416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068060994148</t>
   </si>
   <si>
     <t xml:space="preserve">0.13594588637352</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">0.135823741555214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133136585354805</t>
+    <t xml:space="preserve">0.133136570453644</t>
   </si>
   <si>
     <t xml:space="preserve">0.130693703889847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128861546516418</t>
+    <t xml:space="preserve">0.12886156141758</t>
   </si>
   <si>
     <t xml:space="preserve">0.125258311629295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133930504322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137472659349442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142480581998825</t>
+    <t xml:space="preserve">0.133930519223213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137472689151764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142480552196503</t>
   </si>
   <si>
     <t xml:space="preserve">0.142114147543907</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">0.14217521250248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138327702879906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142236277461052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138205528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140526756644249</t>
+    <t xml:space="preserve">0.138327687978745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142236292362213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138205543160439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140526741743088</t>
   </si>
   <si>
     <t xml:space="preserve">0.139899402856827</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136637195944786</t>
+    <t xml:space="preserve">0.136637166142464</t>
   </si>
   <si>
     <t xml:space="preserve">0.133876830339432</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">0.133814081549644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132998511195183</t>
+    <t xml:space="preserve">0.132998540997505</t>
   </si>
   <si>
     <t xml:space="preserve">0.129234418272972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128732562065125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12515664100647</t>
+    <t xml:space="preserve">0.128732547163963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125156655907631</t>
   </si>
   <si>
     <t xml:space="preserve">0.126662269234657</t>
@@ -293,70 +293,70 @@
     <t xml:space="preserve">0.126725018024445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127352371811867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12797974050045</t>
+    <t xml:space="preserve">0.127352356910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127979725599289</t>
   </si>
   <si>
     <t xml:space="preserve">0.126599550247192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127916976809502</t>
+    <t xml:space="preserve">0.12791696190834</t>
   </si>
   <si>
     <t xml:space="preserve">0.130489140748978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1317438185215</t>
+    <t xml:space="preserve">0.131743803620338</t>
   </si>
   <si>
     <t xml:space="preserve">0.131116479635239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131555616855621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13406503200531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131179213523865</t>
+    <t xml:space="preserve">0.131555631756783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134065017104149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131179198622704</t>
   </si>
   <si>
     <t xml:space="preserve">0.133688613772392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134880587458611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134190484881401</t>
+    <t xml:space="preserve">0.134880602359772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134190499782562</t>
   </si>
   <si>
     <t xml:space="preserve">0.130614578723907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132873028516769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128481611609459</t>
+    <t xml:space="preserve">0.132873058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
     <t xml:space="preserve">0.121078841388226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120200544595718</t>
+    <t xml:space="preserve">0.120200574398041</t>
   </si>
   <si>
     <t xml:space="preserve">0.1218316629529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110413856804371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233199179173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366181194782</t>
+    <t xml:space="preserve">0.110413871705532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233184278011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366188645363</t>
   </si>
   <si>
     <t xml:space="preserve">0.111794032156467</t>
@@ -365,40 +365,40 @@
     <t xml:space="preserve">0.114052496850491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105395063757896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893177747726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041232943535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904471457005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354887485504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727563500404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277125120163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102822914719582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501723587513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716254889965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110790282487869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554397761822</t>
+    <t xml:space="preserve">0.105395056307316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893192648888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041218042374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904486358166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354902386665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727541148663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277110219002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102822907269001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501716136932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716247439384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110790267586708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554412662983</t>
   </si>
   <si>
     <t xml:space="preserve">0.11292327940464</t>
@@ -419,82 +419,82 @@
     <t xml:space="preserve">0.115746356546879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115432672202587</t>
+    <t xml:space="preserve">0.115432679653168</t>
   </si>
   <si>
     <t xml:space="preserve">0.114805333316326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116185501217842</t>
+    <t xml:space="preserve">0.116185516119003</t>
   </si>
   <si>
     <t xml:space="preserve">0.118569418787956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118820391595364</t>
+    <t xml:space="preserve">0.118820384144783</t>
   </si>
   <si>
     <t xml:space="preserve">0.115934573113918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109159164130688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088901102543</t>
+    <t xml:space="preserve">0.109159156680107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088908553123</t>
   </si>
   <si>
     <t xml:space="preserve">0.10614787787199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104140356183052</t>
+    <t xml:space="preserve">0.104140348732471</t>
   </si>
   <si>
     <t xml:space="preserve">0.105646014213562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10746531188488</t>
+    <t xml:space="preserve">0.107465289533138</t>
   </si>
   <si>
     <t xml:space="preserve">0.108531810343266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107590802013874</t>
+    <t xml:space="preserve">0.107590809464455</t>
   </si>
   <si>
     <t xml:space="preserve">0.109535574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1048304438591</t>
+    <t xml:space="preserve">0.10483043640852</t>
   </si>
   <si>
     <t xml:space="preserve">0.108092673122883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108029916882515</t>
+    <t xml:space="preserve">0.108029924333096</t>
   </si>
   <si>
     <t xml:space="preserve">0.10765352845192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109849259257317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978491604328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11160583794117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738842308521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864302635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11028841137886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225655138493</t>
+    <t xml:space="preserve">0.109849244356155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978484153748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111605852842331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11373882740736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864317536354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11028840392828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225647687912</t>
   </si>
   <si>
     <t xml:space="preserve">0.108845479786396</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">0.108406342566013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10451678186655</t>
+    <t xml:space="preserve">0.104516759514809</t>
   </si>
   <si>
     <t xml:space="preserve">0.105018652975559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106649748980999</t>
+    <t xml:space="preserve">0.10664976388216</t>
   </si>
   <si>
     <t xml:space="preserve">0.105834200978279</t>
@@ -524,166 +524,166 @@
     <t xml:space="preserve">0.106085151433945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10978651791811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104391306638718</t>
+    <t xml:space="preserve">0.109786503016949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104391291737556</t>
   </si>
   <si>
     <t xml:space="preserve">0.107778988778591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107214383780956</t>
+    <t xml:space="preserve">0.107214391231537</t>
   </si>
   <si>
     <t xml:space="preserve">0.11606003344059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114742591977119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112421378493309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425172865391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295925617218</t>
+    <t xml:space="preserve">0.114742577075958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112421400845051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11342516541481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295918166637</t>
   </si>
   <si>
     <t xml:space="preserve">0.106022417545319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106712512671947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837965548038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520538985729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265838861465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760180830956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003594696522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579515755177</t>
+    <t xml:space="preserve">0.106712505221367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520524084568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265823960304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760188281536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003587245941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579508304596</t>
   </si>
   <si>
     <t xml:space="preserve">0.102885670959949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103889413177967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254530251026</t>
+    <t xml:space="preserve">0.103889420628548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254552602768</t>
   </si>
   <si>
     <t xml:space="preserve">0.100564457476139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101066321134567</t>
+    <t xml:space="preserve">0.101066328585148</t>
   </si>
   <si>
     <t xml:space="preserve">0.101630948483944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106524296104908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109911985695362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539354383945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110915765166283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657293021679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112609595060349</t>
+    <t xml:space="preserve">0.106524273753166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109911993145943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539369285107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110915757715702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657278120518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112609602510929</t>
   </si>
   <si>
     <t xml:space="preserve">0.111292168498039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109410107135773</t>
+    <t xml:space="preserve">0.109410114586353</t>
   </si>
   <si>
     <t xml:space="preserve">0.108343608677387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108280897140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033681452274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351137816906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544360399246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153701156377792</t>
+    <t xml:space="preserve">0.108280889689922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033711254597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351122915745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
     <t xml:space="preserve">0.144918203353882</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142408803105354</t>
+    <t xml:space="preserve">0.142408818006516</t>
   </si>
   <si>
     <t xml:space="preserve">0.132371172308922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132684841752052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134253218770027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304681301117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134692400693893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135821610689163</t>
+    <t xml:space="preserve">0.132684856653214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134253233671188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304666399956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134692370891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135821595788002</t>
   </si>
   <si>
     <t xml:space="preserve">0.139836668968201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14265975356102</t>
+    <t xml:space="preserve">0.142659738659859</t>
   </si>
   <si>
     <t xml:space="preserve">0.144855469465256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143161624670029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141781449317932</t>
+    <t xml:space="preserve">0.143161609768867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141781464219093</t>
   </si>
   <si>
     <t xml:space="preserve">0.133500412106514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129861786961555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130175441503525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131681084632874</t>
+    <t xml:space="preserve">0.129861757159233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130175456404686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131681099534035</t>
   </si>
   <si>
     <t xml:space="preserve">0.130112707614899</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">0.124842949211597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126097649335861</t>
+    <t xml:space="preserve">0.126097664237022</t>
   </si>
   <si>
     <t xml:space="preserve">0.126975953578949</t>
@@ -704,40 +704,40 @@
     <t xml:space="preserve">0.127289623022079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127226889133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126411348581314</t>
+    <t xml:space="preserve">0.127226904034615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126411333680153</t>
   </si>
   <si>
     <t xml:space="preserve">0.125470295548439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126536801457405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215610325336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125972211360931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551889538765</t>
+    <t xml:space="preserve">0.126536816358566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215640127659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12597219645977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551874637604</t>
   </si>
   <si>
     <t xml:space="preserve">0.130677312612534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132182955741882</t>
+    <t xml:space="preserve">0.132182970643044</t>
   </si>
   <si>
     <t xml:space="preserve">0.129171699285507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132245689630508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006055235863</t>
+    <t xml:space="preserve">0.13224570453167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006070137024</t>
   </si>
   <si>
     <t xml:space="preserve">0.133939564228058</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">0.134943321347237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137766405940056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13801734149456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777677297592</t>
+    <t xml:space="preserve">0.137766391038895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138017326593399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
     <t xml:space="preserve">0.145733773708344</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">0.144165396690369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143977180123329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141154080629349</t>
+    <t xml:space="preserve">0.143977165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14115409553051</t>
   </si>
   <si>
     <t xml:space="preserve">0.137640923261642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629651904106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002283215523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133437663316727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129673555493355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128356143832207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496654987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135633394122124</t>
+    <t xml:space="preserve">0.136762633919716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629637002945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002268314362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133437678217888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129673570394516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128356128931046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496669888496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135633409023285</t>
   </si>
   <si>
     <t xml:space="preserve">0.137891888618469</t>
@@ -809,46 +809,46 @@
     <t xml:space="preserve">0.132433906197548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13205748796463</t>
+    <t xml:space="preserve">0.132057502865791</t>
   </si>
   <si>
     <t xml:space="preserve">0.134504184126854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134502440690994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132989749312401</t>
+    <t xml:space="preserve">0.134502425789833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13298973441124</t>
   </si>
   <si>
     <t xml:space="preserve">0.131729170680046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130720719695091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13317883014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565442800522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943634271622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131792187690735</t>
+    <t xml:space="preserve">0.13072070479393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133178815245628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565427899361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943619370461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131792202591896</t>
   </si>
   <si>
     <t xml:space="preserve">0.131477057933807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132359445095062</t>
+    <t xml:space="preserve">0.132359430193901</t>
   </si>
   <si>
     <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468621850014</t>
+    <t xml:space="preserve">0.130468606948853</t>
   </si>
   <si>
     <t xml:space="preserve">0.129964381456375</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">0.127506271004677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129586189985275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002030611038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127947479486465</t>
+    <t xml:space="preserve">0.129586204886436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002045512199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127947464585304</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128703817725182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371785998344</t>
+    <t xml:space="preserve">0.12870380282402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.125930562615395</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">0.126056626439095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12479604780674</t>
+    <t xml:space="preserve">0.124796062707901</t>
   </si>
   <si>
     <t xml:space="preserve">0.124669998884201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124165788292885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12517423927784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125237241387367</t>
+    <t xml:space="preserve">0.124165773391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125174224376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125237256288528</t>
   </si>
   <si>
     <t xml:space="preserve">0.129018932580948</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">0.127380222082138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128451704978943</t>
+    <t xml:space="preserve">0.128451690077782</t>
   </si>
   <si>
     <t xml:space="preserve">0.128136545419693</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">0.127443239092827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126938998699188</t>
+    <t xml:space="preserve">0.126939028501511</t>
   </si>
   <si>
     <t xml:space="preserve">0.128262624144554</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">0.126875981688499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126497834920883</t>
+    <t xml:space="preserve">0.126497805118561</t>
   </si>
   <si>
     <t xml:space="preserve">0.126308739185333</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">0.135762974619865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136456295847893</t>
+    <t xml:space="preserve">0.136456280946732</t>
   </si>
   <si>
     <t xml:space="preserve">0.135636925697327</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">0.132485508918762</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133556962013245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135195732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136141136288643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134439393877983</t>
+    <t xml:space="preserve">0.133556976914406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135195717215538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136141166090965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134439378976822</t>
   </si>
   <si>
     <t xml:space="preserve">0.137464746832848</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">0.13677142560482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136204168200493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13500665128231</t>
+    <t xml:space="preserve">0.136204183101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006636381149</t>
   </si>
   <si>
     <t xml:space="preserve">0.134754523634911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135069668292999</t>
+    <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
     <t xml:space="preserve">0.137401714920998</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">0.153789073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152780652046204</t>
+    <t xml:space="preserve">0.152780637145042</t>
   </si>
   <si>
     <t xml:space="preserve">0.151267945766449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145280256867409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147045031189919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444715499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15939861536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156625360250473</t>
+    <t xml:space="preserve">0.145280241966248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147045016288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444700598717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159398600459099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
     <t xml:space="preserve">0.157570779323578</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">0.152654573321342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151898235082626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153095781803131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150259494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148746803402901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15334789454937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805990099907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419362545013</t>
+    <t xml:space="preserve">0.151898220181465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15309576690197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150259479880333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746818304062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153347879648209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805975198746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419377446175</t>
   </si>
   <si>
     <t xml:space="preserve">0.156940504908562</t>
@@ -1064,34 +1064,34 @@
     <t xml:space="preserve">0.15914648771286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167655304074287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050397515297</t>
+    <t xml:space="preserve">0.167655318975449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050382614136</t>
   </si>
   <si>
     <t xml:space="preserve">0.167214125394821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172067314386368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945811629295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175218716263771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336329102516</t>
+    <t xml:space="preserve">0.172067329287529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811296820641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17521870136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336314201355</t>
   </si>
   <si>
     <t xml:space="preserve">0.170176446437836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176479250192642</t>
+    <t xml:space="preserve">0.176479265093803</t>
   </si>
   <si>
     <t xml:space="preserve">0.173643007874489</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">0.166205659508705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168222576379776</t>
+    <t xml:space="preserve">0.168222561478615</t>
   </si>
   <si>
     <t xml:space="preserve">0.168600723147392</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">0.162487000226974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747534155846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873597979546</t>
+    <t xml:space="preserve">0.163747549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873612880707</t>
   </si>
   <si>
     <t xml:space="preserve">0.161037310957909</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">0.158011987805367</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157759845256805</t>
+    <t xml:space="preserve">0.157759860157967</t>
   </si>
   <si>
     <t xml:space="preserve">0.167970448732376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167718335986137</t>
+    <t xml:space="preserve">0.167718321084976</t>
   </si>
   <si>
     <t xml:space="preserve">0.1652602404356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163117274641991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163810595870018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159461617469788</t>
+    <t xml:space="preserve">0.163117289543152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163810580968857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159461602568626</t>
   </si>
   <si>
     <t xml:space="preserve">0.147675335407257</t>
@@ -1169,40 +1169,40 @@
     <t xml:space="preserve">0.147486239671707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150007382035255</t>
+    <t xml:space="preserve">0.150007396936417</t>
   </si>
   <si>
     <t xml:space="preserve">0.150448590517044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150511637330055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151078850030899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151646122336388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150322526693344</t>
+    <t xml:space="preserve">0.150511622428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15107886493206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151646137237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150322511792183</t>
   </si>
   <si>
     <t xml:space="preserve">0.148494705557823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15082673728466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151772171258926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881333112717</t>
+    <t xml:space="preserve">0.150826752185822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151772156357765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881318211555</t>
   </si>
   <si>
     <t xml:space="preserve">0.151583075523376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149629190564156</t>
+    <t xml:space="preserve">0.149629220366478</t>
   </si>
   <si>
     <t xml:space="preserve">0.151709154248238</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">0.148935914039612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148116528987885</t>
+    <t xml:space="preserve">0.148116514086723</t>
   </si>
   <si>
     <t xml:space="preserve">0.150763720273972</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">0.150637656450272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151204913854599</t>
+    <t xml:space="preserve">0.15120492875576</t>
   </si>
   <si>
     <t xml:space="preserve">0.149944365024567</t>
@@ -1235,10 +1235,10 @@
     <t xml:space="preserve">0.152528509497643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149377092719078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157255634665489</t>
+    <t xml:space="preserve">0.149377107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15725564956665</t>
   </si>
   <si>
     <t xml:space="preserve">0.156310215592384</t>
@@ -1247,124 +1247,124 @@
     <t xml:space="preserve">0.164503902196884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163243308663368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613019347191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982759833336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163558483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165764465928078</t>
+    <t xml:space="preserve">0.163243323564529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162613034248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982774734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163558468222618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165764451026917</t>
   </si>
   <si>
     <t xml:space="preserve">0.165449306368828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166079595685005</t>
+    <t xml:space="preserve">0.166079610586166</t>
   </si>
   <si>
     <t xml:space="preserve">0.160722211003304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162297904491425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061962962151</t>
+    <t xml:space="preserve">0.162297919392586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061948060989</t>
   </si>
   <si>
     <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146540805697441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146225690841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142759099602699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334822893143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140237987041473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139607712626457</t>
+    <t xml:space="preserve">0.146540820598602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146225675940514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14275911450386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334807991982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140237972140312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139607697725296</t>
   </si>
   <si>
     <t xml:space="preserve">0.138032004237175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139922842383385</t>
+    <t xml:space="preserve">0.139922857284546</t>
   </si>
   <si>
     <t xml:space="preserve">0.135826021432877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138347133994102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813710331917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140553116798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141183406114578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138662278652191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135510861873627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250313043594</t>
+    <t xml:space="preserve">0.138347148895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498550772667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813695430756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140553131699562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141183421015739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138662293553352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135510876774788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134250298142433</t>
   </si>
   <si>
     <t xml:space="preserve">0.133935153484344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132674619555473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143074259161949</t>
+    <t xml:space="preserve">0.132674604654312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14307427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144965127110481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443984746933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575853228569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864416241646</t>
   </si>
   <si>
     <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443999648094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575838327408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864416241646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146253705024719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145609393715858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455082058907</t>
+    <t xml:space="preserve">0.146253690123558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14560940861702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455096960068</t>
   </si>
   <si>
     <t xml:space="preserve">0.142710089683533</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">0.139488652348518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135622918605804</t>
+    <t xml:space="preserve">0.135622933506966</t>
   </si>
   <si>
     <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13272362947464</t>
+    <t xml:space="preserve">0.132723614573479</t>
   </si>
   <si>
     <t xml:space="preserve">0.132079318165779</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">0.125765293836594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12499213218689</t>
+    <t xml:space="preserve">0.124992147088051</t>
   </si>
   <si>
     <t xml:space="preserve">0.126796156167984</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">0.129180029034615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133367896080017</t>
+    <t xml:space="preserve">0.133367910981178</t>
   </si>
   <si>
     <t xml:space="preserve">0.131757184863091</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">0.126925006508827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125378727912903</t>
+    <t xml:space="preserve">0.125378713011742</t>
   </si>
   <si>
     <t xml:space="preserve">0.128600165247917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127440452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127955868840218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127827018499374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126023009419441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124347850680351</t>
+    <t xml:space="preserve">0.130468592047691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127440437674522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127955853939056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127827033400536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12602299451828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124347858130932</t>
   </si>
   <si>
     <t xml:space="preserve">0.123703561723232</t>
@@ -1466,25 +1466,25 @@
     <t xml:space="preserve">0.12834244966507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129502177238464</t>
+    <t xml:space="preserve">0.129502162337303</t>
   </si>
   <si>
     <t xml:space="preserve">0.130146458745003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134012177586555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134656473994255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138522207736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138200059533119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300755500793</t>
+    <t xml:space="preserve">0.134012207388878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134656488895416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13852222263813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13820007443428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300770401955</t>
   </si>
   <si>
     <t xml:space="preserve">0.130790755152702</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">0.128084719181061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128857880830765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12524987757206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122157268226147</t>
+    <t xml:space="preserve">0.128857895731926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125249862670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122157290577888</t>
   </si>
   <si>
     <t xml:space="preserve">0.123316995799541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125507563352585</t>
+    <t xml:space="preserve">0.125507578253746</t>
   </si>
   <si>
     <t xml:space="preserve">0.128213584423065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126151844859123</t>
+    <t xml:space="preserve">0.126151859760284</t>
   </si>
   <si>
     <t xml:space="preserve">0.127182722091675</t>
@@ -1529,25 +1529,25 @@
     <t xml:space="preserve">0.122414991259575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.117260657250881</t>
+    <t xml:space="preserve">0.117260672152042</t>
   </si>
   <si>
     <t xml:space="preserve">0.113266080617905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113394938409328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848630011082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112106367945671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114425785839558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683501422405</t>
+    <t xml:space="preserve">0.113394945859909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848644912243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11210635304451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114425800740719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683516323566</t>
   </si>
   <si>
     <t xml:space="preserve">0.112235210835934</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">0.110817790031433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108240611851215</t>
+    <t xml:space="preserve">0.108240626752377</t>
   </si>
   <si>
     <t xml:space="preserve">0.106565468013287</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105921186506748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101926580071449</t>
+    <t xml:space="preserve">0.105921179056168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101926572620869</t>
   </si>
   <si>
     <t xml:space="preserve">0.10501916706562</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">0.103086292743683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104374893009663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105663470923901</t>
+    <t xml:space="preserve">0.104374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117177426815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105663478374481</t>
   </si>
   <si>
     <t xml:space="preserve">0.107982911169529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108627192676067</t>
+    <t xml:space="preserve">0.108627177774906</t>
   </si>
   <si>
     <t xml:space="preserve">0.108111754059792</t>
@@ -1595,13 +1595,13 @@
     <t xml:space="preserve">0.111462064087391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112750649452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756043016911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173478722572</t>
+    <t xml:space="preserve">0.112750634551048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756057918072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173486173153</t>
   </si>
   <si>
     <t xml:space="preserve">0.109529197216034</t>
@@ -1613,10 +1613,10 @@
     <t xml:space="preserve">0.101153440773487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103988312184811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699741721153</t>
+    <t xml:space="preserve">0.10398830473423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699734270573</t>
   </si>
   <si>
     <t xml:space="preserve">0.105276882648468</t>
@@ -1625,16 +1625,16 @@
     <t xml:space="preserve">0.111204355955124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115585535764694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1158432289958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327790379524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113008357584476</t>
+    <t xml:space="preserve">0.115585528314114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843243896961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327805280685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113008365035057</t>
   </si>
   <si>
     <t xml:space="preserve">0.10940033942461</t>
@@ -1643,25 +1643,25 @@
     <t xml:space="preserve">0.11043119430542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107854045927525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730589151382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106307744979858</t>
+    <t xml:space="preserve">0.107854053378105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730596601963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106307752430439</t>
   </si>
   <si>
     <t xml:space="preserve">0.103859454393387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114554651081562</t>
+    <t xml:space="preserve">0.114554665982723</t>
   </si>
   <si>
     <t xml:space="preserve">0.109142631292343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109013766050339</t>
+    <t xml:space="preserve">0.109013758599758</t>
   </si>
   <si>
     <t xml:space="preserve">0.108884915709496</t>
@@ -1670,34 +1670,34 @@
     <t xml:space="preserve">0.109271474182606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107338607311249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442018687725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411156356335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055445313454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100251421332359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999937132000923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10128229111433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797729730606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766852498055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105148024857044</t>
+    <t xml:space="preserve">0.10733862221241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442011237144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411148905754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055437862873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10025142878294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999937206506729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101282298564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797722280025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766845047474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105148032307625</t>
   </si>
   <si>
     <t xml:space="preserve">0.109915770590305</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">0.1110754981637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112621776759624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302358865738</t>
+    <t xml:space="preserve">0.112621791660786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302366316319</t>
   </si>
   <si>
     <t xml:space="preserve">0.110688917338848</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">0.104761451482773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105534605681896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467472553253</t>
+    <t xml:space="preserve">0.105534598231316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467465102673</t>
   </si>
   <si>
     <t xml:space="preserve">0.108498334884644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107080906629562</t>
+    <t xml:space="preserve">0.107080891728401</t>
   </si>
   <si>
     <t xml:space="preserve">0.104503728449345</t>
@@ -1748,31 +1748,31 @@
     <t xml:space="preserve">0.108562767505646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109207041561604</t>
+    <t xml:space="preserve">0.109207056462765</t>
   </si>
   <si>
     <t xml:space="preserve">0.110185064375401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109857127070427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11116885393858</t>
+    <t xml:space="preserve">0.109857134521008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111168868839741</t>
   </si>
   <si>
     <t xml:space="preserve">0.110512994229794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107889533042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106905743479729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10592196136713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103954367339611</t>
+    <t xml:space="preserve">0.107889547944069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106905750930309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921968817711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10395435988903</t>
   </si>
   <si>
     <t xml:space="preserve">0.104282289743423</t>
@@ -1781,28 +1781,28 @@
     <t xml:space="preserve">0.105594016611576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108217470347881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266086757183</t>
+    <t xml:space="preserve">0.108217485249043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266101658344</t>
   </si>
   <si>
     <t xml:space="preserve">0.104938149452209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102970570325851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103626437485218</t>
+    <t xml:space="preserve">0.102970577776432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103626430034637</t>
   </si>
   <si>
     <t xml:space="preserve">0.103298492729664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101658843457699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100347109138966</t>
+    <t xml:space="preserve">0.101658828556538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100347116589546</t>
   </si>
   <si>
     <t xml:space="preserve">0.101330898702145</t>
@@ -1817,7 +1817,7 @@
     <t xml:space="preserve">0.0973957180976868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0951002016663551</t>
+    <t xml:space="preserve">0.0951001942157745</t>
   </si>
   <si>
     <t xml:space="preserve">0.098051592707634</t>
@@ -1832,16 +1832,16 @@
     <t xml:space="preserve">0.0993633270263672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100019186735153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002983748913</t>
+    <t xml:space="preserve">0.100019179284573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002991199493</t>
   </si>
   <si>
     <t xml:space="preserve">0.100675046443939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102642640471458</t>
+    <t xml:space="preserve">0.102642633020878</t>
   </si>
   <si>
     <t xml:space="preserve">0.098379522562027</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">0.099691241979599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0990353748202324</t>
+    <t xml:space="preserve">0.0990353673696518</t>
   </si>
   <si>
     <t xml:space="preserve">0.104610227048397</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">0.107561618089676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108873330056667</t>
+    <t xml:space="preserve">0.108873337507248</t>
   </si>
   <si>
     <t xml:space="preserve">0.108545407652855</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">0.112152650952339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114448174834251</t>
+    <t xml:space="preserve">0.114448167383671</t>
   </si>
   <si>
     <t xml:space="preserve">0.111824728548527</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">0.113136447966099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112480588257313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496791243553</t>
+    <t xml:space="preserve">0.112480580806732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496776342392</t>
   </si>
   <si>
     <t xml:space="preserve">0.130516827106476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139698922634125</t>
+    <t xml:space="preserve">0.139698907732964</t>
   </si>
   <si>
     <t xml:space="preserve">0.132484421133995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141010642051697</t>
+    <t xml:space="preserve">0.141010656952858</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686552524567</t>
@@ -1919,19 +1919,19 @@
     <t xml:space="preserve">0.155439645051956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150848597288132</t>
+    <t xml:space="preserve">0.150848612189293</t>
   </si>
   <si>
     <t xml:space="preserve">0.154127910733223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157407239079475</t>
+    <t xml:space="preserve">0.157407224178314</t>
   </si>
   <si>
     <t xml:space="preserve">0.156751379370689</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15281617641449</t>
+    <t xml:space="preserve">0.152816191315651</t>
   </si>
   <si>
     <t xml:space="preserve">0.148881003260612</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">0.146257549524307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146913409233093</t>
+    <t xml:space="preserve">0.146913424134254</t>
   </si>
   <si>
     <t xml:space="preserve">0.150192722678185</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">0.162654146552086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161342427134514</t>
+    <t xml:space="preserve">0.161342412233353</t>
   </si>
   <si>
     <t xml:space="preserve">0.141666501760483</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139043062925339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135107889771461</t>
+    <t xml:space="preserve">0.1390430778265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1351078748703</t>
   </si>
   <si>
     <t xml:space="preserve">0.133140295743942</t>
@@ -1982,49 +1982,49 @@
     <t xml:space="preserve">0.137731313705444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154783770442009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156095489859581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153472051024437</t>
+    <t xml:space="preserve">0.154783800244331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156095504760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153472036123276</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135763719677925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137075453996658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125597849488258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126581639051437</t>
+    <t xml:space="preserve">0.135763734579086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13707546889782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12559786438942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12658166885376</t>
   </si>
   <si>
     <t xml:space="preserve">0.123958192765713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118711277842522</t>
+    <t xml:space="preserve">0.118711292743683</t>
   </si>
   <si>
     <t xml:space="preserve">0.110840931534767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0967398434877396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0826388001441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0878857150673866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0872298404574394</t>
+    <t xml:space="preserve">0.0967398509383202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0826388075947762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087885707616806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08722984790802</t>
   </si>
   <si>
     <t xml:space="preserve">0.088541567325592</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">0.0944443419575691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0960840061306953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0931326150894165</t>
+    <t xml:space="preserve">0.0960839986801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0931326076388359</t>
   </si>
   <si>
     <t xml:space="preserve">0.0957560613751411</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0937884822487831</t>
+    <t xml:space="preserve">0.0937884747982025</t>
   </si>
   <si>
     <t xml:space="preserve">0.0965431109070778</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">0.0978548303246498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0971989706158638</t>
+    <t xml:space="preserve">0.0971989631652832</t>
   </si>
   <si>
     <t xml:space="preserve">0.0924767479300499</t>
@@ -2072,16 +2072,16 @@
     <t xml:space="preserve">0.0940508171916008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0939196422696114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0941819921135902</t>
+    <t xml:space="preserve">0.093919649720192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0941819995641708</t>
   </si>
   <si>
     <t xml:space="preserve">0.0949690341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0954937189817429</t>
+    <t xml:space="preserve">0.0954937115311623</t>
   </si>
   <si>
     <t xml:space="preserve">0.0982483550906181</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">0.0968054458498955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0966742783784866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709756612778</t>
+    <t xml:space="preserve">0.096674270927906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709749162197</t>
   </si>
   <si>
     <t xml:space="preserve">0.0979860052466393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.099166564643383</t>
+    <t xml:space="preserve">0.0991665571928024</t>
   </si>
   <si>
     <t xml:space="preserve">0.0936572998762131</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">0.100084774196148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102183535695076</t>
+    <t xml:space="preserve">0.102183520793915</t>
   </si>
   <si>
     <t xml:space="preserve">0.0999535992741585</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">0.137403398752213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135435804724693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136419609189034</t>
+    <t xml:space="preserve">0.135435789823532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136419624090195</t>
   </si>
   <si>
     <t xml:space="preserve">0.134452015161514</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">0.134779959917068</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131172686815262</t>
+    <t xml:space="preserve">0.131172701716423</t>
   </si>
   <si>
     <t xml:space="preserve">0.130779176950455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130123317241669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129336282610893</t>
+    <t xml:space="preserve">0.130123302340508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129336267709732</t>
   </si>
   <si>
     <t xml:space="preserve">0.130385652184486</t>
@@ -2183,37 +2183,37 @@
     <t xml:space="preserve">0.130910351872444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133468210697174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129992127418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975178718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127631038427353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128549233078957</t>
+    <t xml:space="preserve">0.133468225598335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129992142319679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975163817406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127631023526192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128549247980118</t>
   </si>
   <si>
     <t xml:space="preserve">0.133796140551567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132156491279602</t>
+    <t xml:space="preserve">0.132156476378441</t>
   </si>
   <si>
     <t xml:space="preserve">0.130648016929626</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129205107688904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129598632454872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140026837587357</t>
+    <t xml:space="preserve">0.129205122590065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129598617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140026852488518</t>
   </si>
   <si>
     <t xml:space="preserve">0.129729807376862</t>
@@ -2237,19 +2237,19 @@
     <t xml:space="preserve">0.143634095788002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143962040543556</t>
+    <t xml:space="preserve">0.143962055444717</t>
   </si>
   <si>
     <t xml:space="preserve">0.139370992779732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136091664433479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138059258460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136747524142265</t>
+    <t xml:space="preserve">0.136091679334641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13805927336216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136747539043427</t>
   </si>
   <si>
     <t xml:space="preserve">0.140682712197304</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">0.144945830106735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142650306224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141994446516037</t>
+    <t xml:space="preserve">0.142650291323662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141994461417198</t>
   </si>
   <si>
     <t xml:space="preserve">0.144289970397949</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">0.152488261461258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157079294323921</t>
+    <t xml:space="preserve">0.157079309225082</t>
   </si>
   <si>
     <t xml:space="preserve">0.152160316705704</t>
@@ -2288,7 +2288,7 @@
     <t xml:space="preserve">0.155767574906349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160358637571335</t>
+    <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
     <t xml:space="preserve">0.159702762961388</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">0.163310006260872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162326216697693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16101448237896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15904688835144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159374818205833</t>
+    <t xml:space="preserve">0.162326201796532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161014467477798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159046903252602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159374803304672</t>
   </si>
   <si>
     <t xml:space="preserve">0.158718973398209</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">0.158391028642654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160030692815781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1580630838871</t>
+    <t xml:space="preserve">0.160030707716942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158063098788261</t>
   </si>
   <si>
     <t xml:space="preserve">0.165341436862946</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">0.163571193814278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16250903904438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161092832684517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158614471554756</t>
+    <t xml:space="preserve">0.162863090634346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162509024143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161092847585678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
     <t xml:space="preserve">0.157198280096054</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157552316784859</t>
+    <t xml:space="preserve">0.15755233168602</t>
   </si>
   <si>
     <t xml:space="preserve">0.161800920963287</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">0.155073970556259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153303727507591</t>
+    <t xml:space="preserve">0.153303742408752</t>
   </si>
   <si>
     <t xml:space="preserve">0.155782088637352</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">0.154719933867455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155428037047386</t>
+    <t xml:space="preserve">0.155428051948547</t>
   </si>
   <si>
     <t xml:space="preserve">0.156844228506088</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011830687523</t>
+    <t xml:space="preserve">0.154011815786362</t>
   </si>
   <si>
     <t xml:space="preserve">0.156136125326157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152241572737694</t>
+    <t xml:space="preserve">0.152241587638855</t>
   </si>
   <si>
     <t xml:space="preserve">0.154365882277489</t>
@@ -2414,31 +2414,31 @@
     <t xml:space="preserve">0.151887521147728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151179417967796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15011727809906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150825381278992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149763211607933</t>
+    <t xml:space="preserve">0.151179432868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150117293000221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150825366377831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
     <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149055123329163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146222725510597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147284880280495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1426822245121</t>
+    <t xml:space="preserve">0.149055138230324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146222710609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147284895181656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142682209610939</t>
   </si>
   <si>
     <t xml:space="preserve">0.143390327692032</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">0.145514637231827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148347035050392</t>
+    <t xml:space="preserve">0.148347020149231</t>
   </si>
   <si>
     <t xml:space="preserve">0.149409174919128</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">0.1451605707407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147638916969299</t>
+    <t xml:space="preserve">0.147638931870461</t>
   </si>
   <si>
     <t xml:space="preserve">0.148701056838036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146576762199402</t>
+    <t xml:space="preserve">0.146576777100563</t>
   </si>
   <si>
     <t xml:space="preserve">0.144452467560768</t>
@@ -2477,28 +2477,28 @@
     <t xml:space="preserve">0.144806534051895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144098415970802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145868688821793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147992968559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165695488452911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168527871370316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167111679911613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167465731501579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164987370371819</t>
+    <t xml:space="preserve">0.144098430871964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145868673920631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147992983460426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16569547355175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168527886271477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167111709713936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167465716600418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16498738527298</t>
   </si>
   <si>
     <t xml:space="preserve">0.163217127323151</t>
@@ -2513,16 +2513,16 @@
     <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167021736502647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161695286631584</t>
+    <t xml:space="preserve">0.167021751403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161695301532745</t>
   </si>
   <si>
     <t xml:space="preserve">0.161314845085144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159793004393578</t>
+    <t xml:space="preserve">0.159792989492416</t>
   </si>
   <si>
     <t xml:space="preserve">0.163978055119514</t>
@@ -2531,10 +2531,7 @@
     <t xml:space="preserve">0.16055391728878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158271163702011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163217142224312</t>
+    <t xml:space="preserve">0.158271178603172</t>
   </si>
   <si>
     <t xml:space="preserve">0.160934373736382</t>
@@ -2543,25 +2540,25 @@
     <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16511943936348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163597583770752</t>
+    <t xml:space="preserve">0.165119424462318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163597598671913</t>
   </si>
   <si>
     <t xml:space="preserve">0.162456214427948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159032091498375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159412547945976</t>
+    <t xml:space="preserve">0.159032076597214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159412533044815</t>
   </si>
   <si>
     <t xml:space="preserve">0.16017347574234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165880337357521</t>
+    <t xml:space="preserve">0.165880352258682</t>
   </si>
   <si>
     <t xml:space="preserve">0.170445874333382</t>
@@ -2570,13 +2567,13 @@
     <t xml:space="preserve">0.169684946537018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170826330780983</t>
+    <t xml:space="preserve">0.170826315879822</t>
   </si>
   <si>
     <t xml:space="preserve">0.171967700123787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17006541788578</t>
+    <t xml:space="preserve">0.170065402984619</t>
   </si>
   <si>
     <t xml:space="preserve">0.157129764556885</t>
@@ -2591,25 +2588,25 @@
     <t xml:space="preserve">0.14427025616169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147770464420319</t>
+    <t xml:space="preserve">0.14777047932148</t>
   </si>
   <si>
     <t xml:space="preserve">0.155227482318878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155988395214081</t>
+    <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
     <t xml:space="preserve">0.157510250806808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164738968014717</t>
+    <t xml:space="preserve">0.164738982915878</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168924048542976</t>
+    <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
     <t xml:space="preserve">0.166641265153885</t>
@@ -2633,10 +2630,10 @@
     <t xml:space="preserve">0.173462808132172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171426862478256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168983712792397</t>
+    <t xml:space="preserve">0.171426877379417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168983727693558</t>
   </si>
   <si>
     <t xml:space="preserve">0.166133388876915</t>
@@ -2648,7 +2645,7 @@
     <t xml:space="preserve">0.16816933453083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167354986071587</t>
+    <t xml:space="preserve">0.167354971170425</t>
   </si>
   <si>
     <t xml:space="preserve">0.16531902551651</t>
@@ -2657,7 +2654,7 @@
     <t xml:space="preserve">0.16654060781002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166947767138481</t>
+    <t xml:space="preserve">0.166947782039642</t>
   </si>
   <si>
     <t xml:space="preserve">0.167762160301208</t>
@@ -2669,7 +2666,7 @@
     <t xml:space="preserve">0.169390931725502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16287587583065</t>
+    <t xml:space="preserve">0.162875890731812</t>
   </si>
   <si>
     <t xml:space="preserve">0.151963204145432</t>
@@ -2678,16 +2675,16 @@
     <t xml:space="preserve">0.155709356069565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157175227999687</t>
+    <t xml:space="preserve">0.157175242900848</t>
   </si>
   <si>
     <t xml:space="preserve">0.156360849738121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157338112592697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155546456575394</t>
+    <t xml:space="preserve">0.157338097691536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155546471476555</t>
   </si>
   <si>
     <t xml:space="preserve">0.154243469238281</t>
@@ -2699,10 +2696,10 @@
     <t xml:space="preserve">0.152451813220978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152614712715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163690268993378</t>
+    <t xml:space="preserve">0.152614697813988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163690254092216</t>
   </si>
   <si>
     <t xml:space="preserve">0.162387251853943</t>
@@ -2711,7 +2708,7 @@
     <t xml:space="preserve">0.158478230237961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160432741045952</t>
+    <t xml:space="preserve">0.160432755947113</t>
   </si>
   <si>
     <t xml:space="preserve">0.157012343406677</t>
@@ -2723,16 +2720,16 @@
     <t xml:space="preserve">0.161735743284225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161572888493538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157500967383385</t>
+    <t xml:space="preserve">0.161572873592377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157500982284546</t>
   </si>
   <si>
     <t xml:space="preserve">0.160269856452942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159129738807678</t>
+    <t xml:space="preserve">0.159129723906517</t>
   </si>
   <si>
     <t xml:space="preserve">0.160595610737801</t>
@@ -2759,7 +2756,7 @@
     <t xml:space="preserve">0.154732078313828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966854214668</t>
+    <t xml:space="preserve">0.158966869115829</t>
   </si>
   <si>
     <t xml:space="preserve">0.15652371942997</t>
@@ -2777,7 +2774,7 @@
     <t xml:space="preserve">0.156035095453262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157663851976395</t>
+    <t xml:space="preserve">0.157663837075233</t>
   </si>
   <si>
     <t xml:space="preserve">0.155383586883545</t>
@@ -2792,7 +2789,7 @@
     <t xml:space="preserve">0.156686589121819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153103336691856</t>
+    <t xml:space="preserve">0.153103321790695</t>
   </si>
   <si>
     <t xml:space="preserve">0.15228895843029</t>
@@ -2810,7 +2807,7 @@
     <t xml:space="preserve">0.160921365022659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159292608499527</t>
+    <t xml:space="preserve">0.159292623400688</t>
   </si>
   <si>
     <t xml:space="preserve">0.158641114830971</t>
@@ -2822,7 +2819,7 @@
     <t xml:space="preserve">0.164504647254944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163283064961433</t>
+    <t xml:space="preserve">0.163283079862595</t>
   </si>
   <si>
     <t xml:space="preserve">0.164097443223</t>
@@ -2831,25 +2828,25 @@
     <t xml:space="preserve">0.162224382162094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162550136446953</t>
+    <t xml:space="preserve">0.162550121545792</t>
   </si>
   <si>
     <t xml:space="preserve">0.161084249615669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15880398452282</t>
+    <t xml:space="preserve">0.158803969621658</t>
   </si>
   <si>
     <t xml:space="preserve">0.159618362784386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159455493092537</t>
+    <t xml:space="preserve">0.159455478191376</t>
   </si>
   <si>
     <t xml:space="preserve">0.162713006138802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165726199746132</t>
+    <t xml:space="preserve">0.165726214647293</t>
   </si>
   <si>
     <t xml:space="preserve">0.170205295085907</t>
@@ -2861,25 +2858,25 @@
     <t xml:space="preserve">0.17305563390255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176720336079597</t>
+    <t xml:space="preserve">0.176720321178436</t>
   </si>
   <si>
     <t xml:space="preserve">0.177534714341164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179163455963135</t>
+    <t xml:space="preserve">0.179163470864296</t>
   </si>
   <si>
     <t xml:space="preserve">0.175091579556465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171019673347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172241255640984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172648429870605</t>
+    <t xml:space="preserve">0.171019658446312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172241240739822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172648444771767</t>
   </si>
   <si>
     <t xml:space="preserve">0.171834051609039</t>
@@ -2888,7 +2885,7 @@
     <t xml:space="preserve">0.169798105955124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183235362172127</t>
+    <t xml:space="preserve">0.183235347270966</t>
   </si>
   <si>
     <t xml:space="preserve">0.181606605648994</t>
@@ -2900,7 +2897,7 @@
     <t xml:space="preserve">0.182420998811722</t>
   </si>
   <si>
-    <t xml:space="preserve">0.184864118695259</t>
+    <t xml:space="preserve">0.18486413359642</t>
   </si>
   <si>
     <t xml:space="preserve">0.185678496956825</t>
@@ -2909,28 +2906,31 @@
     <t xml:space="preserve">0.188121646642685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182920128107071</t>
+    <t xml:space="preserve">0.18292011320591</t>
   </si>
   <si>
     <t xml:space="preserve">0.186387807130814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187254726886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189855486154556</t>
+    <t xml:space="preserve">0.18725474178791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189855471253395</t>
   </si>
   <si>
     <t xml:space="preserve">0.190722405910492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188988566398621</t>
+    <t xml:space="preserve">0.188988551497459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188121631741524</t>
   </si>
   <si>
     <t xml:space="preserve">0.185520887374878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183787047863007</t>
+    <t xml:space="preserve">0.183787032961845</t>
   </si>
   <si>
     <t xml:space="preserve">0.182053208351135</t>
@@ -2948,25 +2948,25 @@
     <t xml:space="preserve">0.179452449083328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177718609571457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176851689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175984755158424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175117835402489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174250915646553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173383995890617</t>
+    <t xml:space="preserve">0.178585514426231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177718594670296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17685167491436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175984770059586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17511785030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174250930547714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173384010791779</t>
   </si>
   <si>
     <t xml:space="preserve">0.191589325666428</t>
@@ -42928,7 +42928,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1511" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42954,7 +42954,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1512" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -42980,7 +42980,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1513" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43058,7 +43058,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1516" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43084,7 +43084,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1517" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43110,7 +43110,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1518" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43136,7 +43136,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1519" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43188,7 +43188,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1521" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43214,7 +43214,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1522" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43292,7 +43292,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1525" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43318,7 +43318,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1526" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43344,7 +43344,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1527" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43370,7 +43370,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1528" t="s">
-        <v>840</v>
+        <v>829</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43422,7 +43422,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1530" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43448,7 +43448,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1531" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43500,7 +43500,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1533" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43656,7 +43656,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1539" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43734,7 +43734,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1542" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43760,7 +43760,7 @@
         <v>0.209499999880791</v>
       </c>
       <c r="G1543" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43786,7 +43786,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1544" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -43864,7 +43864,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1547" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43890,7 +43890,7 @@
         <v>0.209499999880791</v>
       </c>
       <c r="G1548" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43942,7 +43942,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1550" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -43968,7 +43968,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1551" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44072,7 +44072,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1555" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44098,7 +44098,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G1556" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44124,7 +44124,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1557" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44150,7 +44150,7 @@
         <v>0.224500000476837</v>
       </c>
       <c r="G1558" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44176,7 +44176,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1559" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44202,7 +44202,7 @@
         <v>0.223499998450279</v>
       </c>
       <c r="G1560" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44228,7 +44228,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1561" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44280,7 +44280,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1563" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44306,7 +44306,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1564" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44332,7 +44332,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1565" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44410,7 +44410,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1568" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44436,7 +44436,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1569" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44462,7 +44462,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1570" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44488,7 +44488,7 @@
         <v>0.189600005745888</v>
       </c>
       <c r="G1571" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44514,7 +44514,7 @@
         <v>0.194199994206429</v>
       </c>
       <c r="G1572" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44540,7 +44540,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1573" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44566,7 +44566,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1574" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44592,7 +44592,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1575" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44618,7 +44618,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1576" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44644,7 +44644,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1577" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44670,7 +44670,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1578" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44722,7 +44722,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G1580" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44748,7 +44748,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G1581" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44800,7 +44800,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G1583" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44904,7 +44904,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1587" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44930,7 +44930,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G1588" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44956,7 +44956,7 @@
         <v>0.223499998450279</v>
       </c>
       <c r="G1589" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45008,7 +45008,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G1591" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45034,7 +45034,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G1592" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45060,7 +45060,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1593" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45086,7 +45086,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1594" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45138,7 +45138,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G1596" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45190,7 +45190,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1598" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45216,7 +45216,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G1599" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45242,7 +45242,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1600" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45268,7 +45268,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1601" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45294,7 +45294,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1602" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45320,7 +45320,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1603" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45346,7 +45346,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1604" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45372,7 +45372,7 @@
         <v>0.224500000476837</v>
       </c>
       <c r="G1605" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45398,7 +45398,7 @@
         <v>0.224500000476837</v>
       </c>
       <c r="G1606" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45424,7 +45424,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G1607" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45450,7 +45450,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G1608" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45476,7 +45476,7 @@
         <v>0.228499993681908</v>
       </c>
       <c r="G1609" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45502,7 +45502,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1610" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45528,7 +45528,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1611" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45554,7 +45554,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1612" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45580,7 +45580,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1613" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45606,7 +45606,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1614" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45632,7 +45632,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1615" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45658,7 +45658,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1616" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45684,7 +45684,7 @@
         <v>0.209499999880791</v>
       </c>
       <c r="G1617" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45710,7 +45710,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1618" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45736,7 +45736,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1619" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45762,7 +45762,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1620" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45788,7 +45788,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1621" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -45814,7 +45814,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45840,7 +45840,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1623" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45866,7 +45866,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1624" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45892,7 +45892,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1625" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45918,7 +45918,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1626" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45944,7 +45944,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G1627" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -45970,7 +45970,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1628" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -45996,7 +45996,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G1629" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46022,7 +46022,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1630" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46048,7 +46048,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1631" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46074,7 +46074,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1632" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46100,7 +46100,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1633" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46126,7 +46126,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1634" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46152,7 +46152,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1635" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46178,7 +46178,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1636" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46204,7 +46204,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1637" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46230,7 +46230,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1638" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46256,7 +46256,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1639" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46282,7 +46282,7 @@
         <v>0.186599999666214</v>
       </c>
       <c r="G1640" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46308,7 +46308,7 @@
         <v>0.191200003027916</v>
       </c>
       <c r="G1641" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46334,7 +46334,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1642" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46360,7 +46360,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1643" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46386,7 +46386,7 @@
         <v>0.193200007081032</v>
       </c>
       <c r="G1644" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46412,7 +46412,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1645" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46438,7 +46438,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1646" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46464,7 +46464,7 @@
         <v>0.189400002360344</v>
       </c>
       <c r="G1647" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46490,7 +46490,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G1648" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46516,7 +46516,7 @@
         <v>0.187199994921684</v>
       </c>
       <c r="G1649" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46542,7 +46542,7 @@
         <v>0.187399998307228</v>
       </c>
       <c r="G1650" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46568,7 +46568,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1651" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46594,7 +46594,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1652" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46620,7 +46620,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G1653" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46646,7 +46646,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1654" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46672,7 +46672,7 @@
         <v>0.192800000309944</v>
       </c>
       <c r="G1655" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46698,7 +46698,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1656" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46724,7 +46724,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1657" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46750,7 +46750,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1658" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46776,7 +46776,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1659" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -46802,7 +46802,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1660" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46828,7 +46828,7 @@
         <v>0.198599994182587</v>
       </c>
       <c r="G1661" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46854,7 +46854,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G1662" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46880,7 +46880,7 @@
         <v>0.193399995565414</v>
       </c>
       <c r="G1663" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46906,7 +46906,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G1664" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46932,7 +46932,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G1665" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46958,7 +46958,7 @@
         <v>0.197200000286102</v>
       </c>
       <c r="G1666" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -46984,7 +46984,7 @@
         <v>0.196199998259544</v>
       </c>
       <c r="G1667" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47010,7 +47010,7 @@
         <v>0.191200003027916</v>
       </c>
       <c r="G1668" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47036,7 +47036,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1669" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47062,7 +47062,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1670" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47088,7 +47088,7 @@
         <v>0.190400004386902</v>
       </c>
       <c r="G1671" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47114,7 +47114,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1672" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47140,7 +47140,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1673" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47166,7 +47166,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1674" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47192,7 +47192,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1675" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47218,7 +47218,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1676" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47244,7 +47244,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1677" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47270,7 +47270,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1678" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47296,7 +47296,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1679" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47322,7 +47322,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1680" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47348,7 +47348,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1681" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47374,7 +47374,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1682" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47400,7 +47400,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1683" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47426,7 +47426,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G1684" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47452,7 +47452,7 @@
         <v>0.19820000231266</v>
       </c>
       <c r="G1685" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47478,7 +47478,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1686" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47504,7 +47504,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1687" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47530,7 +47530,7 @@
         <v>0.196400001645088</v>
       </c>
       <c r="G1688" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47556,7 +47556,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47582,7 +47582,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G1690" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47608,7 +47608,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47634,7 +47634,7 @@
         <v>0.192200005054474</v>
       </c>
       <c r="G1692" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47660,7 +47660,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1693" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47686,7 +47686,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1694" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47712,7 +47712,7 @@
         <v>0.190599992871284</v>
       </c>
       <c r="G1695" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47738,7 +47738,7 @@
         <v>0.19140000641346</v>
       </c>
       <c r="G1696" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47764,7 +47764,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47790,7 +47790,7 @@
         <v>0.191799998283386</v>
       </c>
       <c r="G1698" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47816,7 +47816,7 @@
         <v>0.191599994897842</v>
       </c>
       <c r="G1699" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47842,7 +47842,7 @@
         <v>0.192200005054474</v>
       </c>
       <c r="G1700" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47868,7 +47868,7 @@
         <v>0.193599998950958</v>
       </c>
       <c r="G1701" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -47894,7 +47894,7 @@
         <v>0.190799996256828</v>
       </c>
       <c r="G1702" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47920,7 +47920,7 @@
         <v>0.193599998950958</v>
       </c>
       <c r="G1703" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47946,7 +47946,7 @@
         <v>0.193800002336502</v>
       </c>
       <c r="G1704" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47972,7 +47972,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1705" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47998,7 +47998,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1706" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48024,7 +48024,7 @@
         <v>0.193599998950958</v>
       </c>
       <c r="G1707" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48050,7 +48050,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1708" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48076,7 +48076,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1709" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48102,7 +48102,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1710" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48128,7 +48128,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1711" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48154,7 +48154,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1712" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48180,7 +48180,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1713" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48206,7 +48206,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1714" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48232,7 +48232,7 @@
         <v>0.194199994206429</v>
       </c>
       <c r="G1715" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48258,7 +48258,7 @@
         <v>0.194199994206429</v>
       </c>
       <c r="G1716" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48284,7 +48284,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G1717" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48310,7 +48310,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1718" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48336,7 +48336,7 @@
         <v>0.192399993538857</v>
       </c>
       <c r="G1719" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48362,7 +48362,7 @@
         <v>0.193399995565414</v>
       </c>
       <c r="G1720" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48388,7 +48388,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1721" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48414,7 +48414,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1722" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48440,7 +48440,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1723" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48466,7 +48466,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1724" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48492,7 +48492,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G1725" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48518,7 +48518,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G1726" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48544,7 +48544,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G1727" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48570,7 +48570,7 @@
         <v>0.190200001001358</v>
       </c>
       <c r="G1728" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48596,7 +48596,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G1729" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48622,7 +48622,7 @@
         <v>0.190400004386902</v>
       </c>
       <c r="G1730" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48648,7 +48648,7 @@
         <v>0.189600005745888</v>
       </c>
       <c r="G1731" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48674,7 +48674,7 @@
         <v>0.189400002360344</v>
       </c>
       <c r="G1732" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48700,7 +48700,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G1733" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48726,7 +48726,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1734" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48752,7 +48752,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1735" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48778,7 +48778,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1736" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48804,7 +48804,7 @@
         <v>0.190200001001358</v>
       </c>
       <c r="G1737" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48830,7 +48830,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1738" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48856,7 +48856,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1739" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48882,7 +48882,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G1740" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48908,7 +48908,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1741" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48934,7 +48934,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G1742" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48960,7 +48960,7 @@
         <v>0.195600003004074</v>
       </c>
       <c r="G1743" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48986,7 +48986,7 @@
         <v>0.19480000436306</v>
       </c>
       <c r="G1744" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49012,7 +49012,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G1745" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49038,7 +49038,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1746" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49064,7 +49064,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1747" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49090,7 +49090,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G1748" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49116,7 +49116,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1749" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49142,7 +49142,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G1750" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49168,7 +49168,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1751" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49194,7 +49194,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1752" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49220,7 +49220,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1753" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49246,7 +49246,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1754" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49272,7 +49272,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1755" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49298,7 +49298,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1756" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49324,7 +49324,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G1757" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49350,7 +49350,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G1758" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49376,7 +49376,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1759" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49402,7 +49402,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1760" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49428,7 +49428,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1761" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49454,7 +49454,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G1762" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49480,7 +49480,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1763" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49506,7 +49506,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1764" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49532,7 +49532,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G1765" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49558,7 +49558,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1766" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49584,7 +49584,7 @@
         <v>0.19820000231266</v>
       </c>
       <c r="G1767" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49610,7 +49610,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G1768" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49636,7 +49636,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1769" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49662,7 +49662,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G1770" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49688,7 +49688,7 @@
         <v>0.196199998259544</v>
       </c>
       <c r="G1771" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49714,7 +49714,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G1772" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49740,7 +49740,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1773" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49766,7 +49766,7 @@
         <v>0.196400001645088</v>
       </c>
       <c r="G1774" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49792,7 +49792,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1775" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49818,7 +49818,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1776" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49844,7 +49844,7 @@
         <v>0.195999994874001</v>
       </c>
       <c r="G1777" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49870,7 +49870,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G1778" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49896,7 +49896,7 @@
         <v>0.198599994182587</v>
       </c>
       <c r="G1779" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49922,7 +49922,7 @@
         <v>0.195800006389618</v>
       </c>
       <c r="G1780" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49948,7 +49948,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G1781" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49974,7 +49974,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1782" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50000,7 +50000,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G1783" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50026,7 +50026,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1784" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50052,7 +50052,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1785" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50078,7 +50078,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1786" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50104,7 +50104,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1787" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50130,7 +50130,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G1788" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50156,7 +50156,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1789" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50182,7 +50182,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G1790" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50208,7 +50208,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1791" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50234,7 +50234,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1792" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50260,7 +50260,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1793" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50286,7 +50286,7 @@
         <v>0.19820000231266</v>
       </c>
       <c r="G1794" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50312,7 +50312,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1795" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50338,7 +50338,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50364,7 +50364,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1797" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50390,7 +50390,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1798" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50416,7 +50416,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50442,7 +50442,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1800" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50468,7 +50468,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1801" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50494,7 +50494,7 @@
         <v>0.203500002622604</v>
       </c>
       <c r="G1802" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50520,7 +50520,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1803" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50546,7 +50546,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1804" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50572,7 +50572,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G1805" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50598,7 +50598,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1806" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50624,7 +50624,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G1807" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50650,7 +50650,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1808" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50676,7 +50676,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1809" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50702,7 +50702,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1810" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50728,7 +50728,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1811" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50754,7 +50754,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1812" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50780,7 +50780,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1813" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -50806,7 +50806,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1814" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -50832,7 +50832,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1815" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -50858,7 +50858,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1816" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -50884,7 +50884,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1817" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50910,7 +50910,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1818" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50936,7 +50936,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G1819" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50962,7 +50962,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1820" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50988,7 +50988,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1821" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51014,7 +51014,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1822" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51040,7 +51040,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1823" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51066,7 +51066,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1824" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51092,7 +51092,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1825" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51118,7 +51118,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1826" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51144,7 +51144,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1827" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51170,7 +51170,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1828" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51196,7 +51196,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1829" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51222,7 +51222,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G1830" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51248,7 +51248,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1831" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51274,7 +51274,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1832" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51300,7 +51300,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1833" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51326,7 +51326,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1834" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51352,7 +51352,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1835" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51378,7 +51378,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1836" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51404,7 +51404,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1837" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51430,7 +51430,7 @@
         <v>0.203500002622604</v>
       </c>
       <c r="G1838" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51456,7 +51456,7 @@
         <v>0.208499997854233</v>
       </c>
       <c r="G1839" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51482,7 +51482,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1840" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51508,7 +51508,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1841" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51534,7 +51534,7 @@
         <v>0.208499997854233</v>
       </c>
       <c r="G1842" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51560,7 +51560,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1843" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51586,7 +51586,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1844" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51612,7 +51612,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1845" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51638,7 +51638,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1846" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51664,7 +51664,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1847" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51690,7 +51690,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1848" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51716,7 +51716,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1849" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51742,7 +51742,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1850" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51768,7 +51768,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1851" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -51794,7 +51794,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G1852" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -51820,7 +51820,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1853" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -51846,7 +51846,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1854" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51872,7 +51872,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1855" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51898,7 +51898,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1856" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51924,7 +51924,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G1857" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51950,7 +51950,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1858" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51976,7 +51976,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52002,7 +52002,7 @@
         <v>0.228000000119209</v>
       </c>
       <c r="G1860" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52028,7 +52028,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1861" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52054,7 +52054,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G1862" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52080,7 +52080,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1863" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52106,7 +52106,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52132,7 +52132,7 @@
         <v>0.231000006198883</v>
       </c>
       <c r="G1865" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52158,7 +52158,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1866" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52184,7 +52184,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1867" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52210,7 +52210,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G1868" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52236,7 +52236,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1869" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52262,7 +52262,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1870" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52288,7 +52288,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1871" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52314,7 +52314,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1872" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52340,7 +52340,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1873" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52366,7 +52366,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1874" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52496,7 +52496,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1879" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52548,7 +52548,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1881" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52574,7 +52574,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1882" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52678,7 +52678,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1886" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52704,7 +52704,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1887" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52964,7 +52964,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1897" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -53120,7 +53120,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1903" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53198,7 +53198,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1906" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53224,7 +53224,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1907" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53354,7 +53354,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1912" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53432,7 +53432,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1915" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53770,7 +53770,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1928" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53822,7 +53822,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1930" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -54758,7 +54758,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1966" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -58138,7 +58138,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2096" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58164,7 +58164,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2097" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58216,7 +58216,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2099" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58242,7 +58242,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2100" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58372,7 +58372,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2105" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58424,7 +58424,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2107" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58476,7 +58476,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2109" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58684,7 +58684,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2117" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -68884,7 +68884,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911342593</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>469937</v>
@@ -68905,6 +68905,32 @@
         <v>1091</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911689815</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>736857</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>0.162499994039536</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>0.162499994039536</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>0.159500002861023</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="1102">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053904771805</t>
+    <t xml:space="preserve">0.158053889870644</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481374382973</t>
+    <t xml:space="preserve">0.158481389284134</t>
   </si>
   <si>
     <t xml:space="preserve">0.155000314116478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153229221701622</t>
+    <t xml:space="preserve">0.153229206800461</t>
   </si>
   <si>
     <t xml:space="preserve">0.150542050600052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148099198937416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150297775864601</t>
+    <t xml:space="preserve">0.148099184036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15029776096344</t>
   </si>
   <si>
     <t xml:space="preserve">0.151580289006233</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">0.147366315126419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142358422279358</t>
+    <t xml:space="preserve">0.142358437180519</t>
   </si>
   <si>
     <t xml:space="preserve">0.132831230759621</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131121203303337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134358003735542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419083595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143335595726967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13802233338356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778043746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140465214848518</t>
+    <t xml:space="preserve">0.131121218204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134358033537865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419113397598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143335610628128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138022348284721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778058648109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140465199947357</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
@@ -107,49 +107,49 @@
     <t xml:space="preserve">0.136190176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792992353439</t>
+    <t xml:space="preserve">0.131793007254601</t>
   </si>
   <si>
     <t xml:space="preserve">0.129166930913925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129289075732231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967927992344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754402458668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116158619523048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11847934871912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125807985663414</t>
+    <t xml:space="preserve">0.12928906083107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967913091183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754387557507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116158626973629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479363620281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12580794095993</t>
   </si>
   <si>
     <t xml:space="preserve">0.125197246670723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129960849881172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125014021992683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999073386192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12910583615303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128617286682129</t>
+    <t xml:space="preserve">0.129960834980011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127029404044151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125014036893845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999058485031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129105851054192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128617271780968</t>
   </si>
   <si>
     <t xml:space="preserve">0.130205139517784</t>
@@ -158,13 +158,13 @@
     <t xml:space="preserve">0.130510479211807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129533350467682</t>
+    <t xml:space="preserve">0.129533335566521</t>
   </si>
   <si>
     <t xml:space="preserve">0.133808374404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138755202293396</t>
+    <t xml:space="preserve">0.138755217194557</t>
   </si>
   <si>
     <t xml:space="preserve">0.139671266078949</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">0.136739820241928</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136495515704155</t>
+    <t xml:space="preserve">0.136495545506477</t>
   </si>
   <si>
     <t xml:space="preserve">0.140159845352173</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">0.141747713088989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147122040390968</t>
+    <t xml:space="preserve">0.147122025489807</t>
   </si>
   <si>
     <t xml:space="preserve">0.149015262722969</t>
@@ -191,46 +191,46 @@
     <t xml:space="preserve">0.146572381258011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14571738243103</t>
+    <t xml:space="preserve">0.145717367529869</t>
   </si>
   <si>
     <t xml:space="preserve">0.143213450908661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144129514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892699360847</t>
+    <t xml:space="preserve">0.144129529595375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140892714262009</t>
   </si>
   <si>
     <t xml:space="preserve">0.139793425798416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134968727827072</t>
+    <t xml:space="preserve">0.134968742728233</t>
   </si>
   <si>
     <t xml:space="preserve">0.136068031191826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13594588637352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135823741555214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133136585354805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130693733692169</t>
+    <t xml:space="preserve">0.135945871472359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135823726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133136570453644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130693718791008</t>
   </si>
   <si>
     <t xml:space="preserve">0.12886156141758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125258296728134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133930504322052</t>
+    <t xml:space="preserve">0.125258341431618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133930519223213</t>
   </si>
   <si>
     <t xml:space="preserve">0.137472674250603</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">0.142480581998825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142114147543907</t>
+    <t xml:space="preserve">0.142114162445068</t>
   </si>
   <si>
     <t xml:space="preserve">0.141320213675499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142175227403641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138327687978745</t>
+    <t xml:space="preserve">0.14217521250248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138327702879906</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236277461052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1382055580616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140526741743088</t>
+    <t xml:space="preserve">0.138205528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140526756644249</t>
   </si>
   <si>
     <t xml:space="preserve">0.139899387955666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136135295033455</t>
+    <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
     <t xml:space="preserve">0.136637181043625</t>
@@ -272,40 +272,40 @@
     <t xml:space="preserve">0.133876815438271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133814096450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132998526096344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129234433174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128732532262802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125156611204147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126662269234657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126725003123283</t>
+    <t xml:space="preserve">0.133814081549644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132998511195183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129234403371811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128732547163963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125156626105309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126662284135818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126725018024445</t>
   </si>
   <si>
     <t xml:space="preserve">0.127352371811867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127979710698128</t>
+    <t xml:space="preserve">0.127979725599289</t>
   </si>
   <si>
     <t xml:space="preserve">0.126599535346031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127916976809502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130489140748978</t>
+    <t xml:space="preserve">0.12791696190834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
     <t xml:space="preserve">0.1317438185215</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">0.131116464734077</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131555616855621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134065017104149</t>
+    <t xml:space="preserve">0.131555631756783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134065002202988</t>
   </si>
   <si>
     <t xml:space="preserve">0.131179213523865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133688628673553</t>
+    <t xml:space="preserve">0.133688613772392</t>
   </si>
   <si>
     <t xml:space="preserve">0.134880587458611</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">0.134190499782562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130614593625069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132873043417931</t>
+    <t xml:space="preserve">0.130614578723907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132873058319092</t>
   </si>
   <si>
     <t xml:space="preserve">0.128481596708298</t>
@@ -344,103 +344,103 @@
     <t xml:space="preserve">0.121078848838806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12020056694746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1218316629529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413886606693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233191728592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366166293621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794054508209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052504301071</t>
+    <t xml:space="preserve">0.12020055949688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831677854061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413864254951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233184278011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366196095943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794032156467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114052511751652</t>
   </si>
   <si>
     <t xml:space="preserve">0.105395071208477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104893177747726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041210591793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904456555843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354887485504</t>
+    <t xml:space="preserve">0.104893170297146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041232943535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904464006424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354894936085</t>
   </si>
   <si>
     <t xml:space="preserve">0.110727541148663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107277132570744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102822922170162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501723587513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716269791126</t>
+    <t xml:space="preserve">0.107277102768421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102822929620743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501716136932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716262340546</t>
   </si>
   <si>
     <t xml:space="preserve">0.11079028993845</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114554390311241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11292327940464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303462207317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632160127163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11656192690134</t>
+    <t xml:space="preserve">0.114554405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11292327195406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303439855576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632182478905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116561904549599</t>
   </si>
   <si>
     <t xml:space="preserve">0.116373710334301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115746356546879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432679653168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805325865746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185516119003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569441139698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820384144783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934543311596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159179031849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088901102543</t>
+    <t xml:space="preserve">0.115746363997459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432694554329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805340766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185523569584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569433689117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820376694202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934573113918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10915918648243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088908553123</t>
   </si>
   <si>
     <t xml:space="preserve">0.10614787787199</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">0.104140356183052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105646006762981</t>
+    <t xml:space="preserve">0.10564599186182</t>
   </si>
   <si>
     <t xml:space="preserve">0.107465319335461</t>
@@ -458,124 +458,124 @@
     <t xml:space="preserve">0.108531817793846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107590787112713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535582363605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104830451309681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092658221722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029954135418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849259257317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978484153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111605852842331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738849759102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864310085773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110288389027119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845502138138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723798930645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339859008789</t>
+    <t xml:space="preserve">0.107590794563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535560011864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104830428957939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092665672302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029924333096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107653513550758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849274158478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978491604328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111605830490589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113738842308521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864302635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11028841137886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225655138493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845487236977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723769128323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339851558208</t>
   </si>
   <si>
     <t xml:space="preserve">0.108406350016594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10451678186655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105018645524979</t>
+    <t xml:space="preserve">0.104516759514809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105018638074398</t>
   </si>
   <si>
     <t xml:space="preserve">0.10664976388216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10583420842886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085136532784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10978652536869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104391276836395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107779003679752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214376330376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116060048341751</t>
+    <t xml:space="preserve">0.105834193527699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085151433945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10978651791811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104391306638718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107779011130333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214368879795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060040891171</t>
   </si>
   <si>
     <t xml:space="preserve">0.114742606878281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112421378493309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425172865391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295933067799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022402644157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712490320206</t>
+    <t xml:space="preserve">0.11242139339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113425150513649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295925617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022417545319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712505221367</t>
   </si>
   <si>
     <t xml:space="preserve">0.106837965548038</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105520524084568</t>
+    <t xml:space="preserve">0.105520531535149</t>
   </si>
   <si>
     <t xml:space="preserve">0.104265823960304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102760195732117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003609597683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579500854015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885656058788</t>
+    <t xml:space="preserve">0.102760173380375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003602147102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579515755177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885648608208</t>
   </si>
   <si>
     <t xml:space="preserve">0.103889420628548</t>
@@ -584,58 +584,58 @@
     <t xml:space="preserve">0.101254537701607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100564450025558</t>
+    <t xml:space="preserve">0.10056446492672</t>
   </si>
   <si>
     <t xml:space="preserve">0.101066328585148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101630933582783</t>
+    <t xml:space="preserve">0.101630948483944</t>
   </si>
   <si>
     <t xml:space="preserve">0.106524288654327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109911985695362</t>
+    <t xml:space="preserve">0.109912000596523</t>
   </si>
   <si>
     <t xml:space="preserve">0.110539346933365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110915750265121</t>
+    <t xml:space="preserve">0.110915757715702</t>
   </si>
   <si>
     <t xml:space="preserve">0.108657285571098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112609602510929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111292161047459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410107135773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108343631029129</t>
+    <t xml:space="preserve">0.112609587609768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111292153596878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410114586353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108343601226807</t>
   </si>
   <si>
     <t xml:space="preserve">0.108280874788761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109033703804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351122915745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544345498085</t>
+    <t xml:space="preserve">0.109033696353436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351130366325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544330596924</t>
   </si>
   <si>
     <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144918218255043</t>
+    <t xml:space="preserve">0.144918203353882</t>
   </si>
   <si>
     <t xml:space="preserve">0.142408803105354</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">0.132371187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132684871554375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13425324857235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304666399956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134692370891571</t>
+    <t xml:space="preserve">0.132684856653214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134253233671188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304681301117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13469235599041</t>
   </si>
   <si>
     <t xml:space="preserve">0.135821610689163</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">0.139836654067039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142659723758698</t>
+    <t xml:space="preserve">0.142659738659859</t>
   </si>
   <si>
     <t xml:space="preserve">0.144855469465256</t>
@@ -671,31 +671,31 @@
     <t xml:space="preserve">0.143161624670029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141781449317932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133500412106514</t>
+    <t xml:space="preserve">0.141781464219093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133500397205353</t>
   </si>
   <si>
     <t xml:space="preserve">0.129861772060394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130175426602364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131681084632874</t>
+    <t xml:space="preserve">0.130175456404686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131681099534035</t>
   </si>
   <si>
     <t xml:space="preserve">0.130112707614899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130740061402321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842964112759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097679138184</t>
+    <t xml:space="preserve">0.130740091204643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842956662178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097664237022</t>
   </si>
   <si>
     <t xml:space="preserve">0.126975953578949</t>
@@ -704,34 +704,34 @@
     <t xml:space="preserve">0.127289637923241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127226889133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126411333680153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125470325350761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126536816358566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215617775917</t>
+    <t xml:space="preserve">0.127226904034615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126411348581314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1254703104496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126536801457405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215595424175</t>
   </si>
   <si>
     <t xml:space="preserve">0.12597219645977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130551844835281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182955741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171699285507</t>
+    <t xml:space="preserve">0.130551859736443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677312612534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182970643044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171669483185</t>
   </si>
   <si>
     <t xml:space="preserve">0.13224570453167</t>
@@ -740,46 +740,46 @@
     <t xml:space="preserve">0.135006055235863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133939564228058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127780795097</t>
+    <t xml:space="preserve">0.133939549326897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127765893936</t>
   </si>
   <si>
     <t xml:space="preserve">0.136260747909546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134943306446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766405940056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138017326593399</t>
+    <t xml:space="preserve">0.134943321347237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766420841217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138017356395721</t>
   </si>
   <si>
     <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145733758807182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144165381789207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143977180123329</t>
+    <t xml:space="preserve">0.145733773708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165396690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14397719502449</t>
   </si>
   <si>
     <t xml:space="preserve">0.14115409553051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137640923261642</t>
+    <t xml:space="preserve">0.137640938162804</t>
   </si>
   <si>
     <t xml:space="preserve">0.136762633919716</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134629622101784</t>
+    <t xml:space="preserve">0.134629637002945</t>
   </si>
   <si>
     <t xml:space="preserve">0.134002283215523</t>
@@ -788,19 +788,19 @@
     <t xml:space="preserve">0.133437678217888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129673555493355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128356143832207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496654987335</t>
+    <t xml:space="preserve">0.129673570394516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128356128931046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496640086174</t>
   </si>
   <si>
     <t xml:space="preserve">0.135633409023285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137891858816147</t>
+    <t xml:space="preserve">0.137891873717308</t>
   </si>
   <si>
     <t xml:space="preserve">0.13770367205143</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">0.132433906197548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132057502865791</t>
+    <t xml:space="preserve">0.13205748796463</t>
   </si>
   <si>
     <t xml:space="preserve">0.134504154324532</t>
@@ -818,25 +818,25 @@
     <t xml:space="preserve">0.134502410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13298973441124</t>
+    <t xml:space="preserve">0.132989749312401</t>
   </si>
   <si>
     <t xml:space="preserve">0.131729155778885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13072070479393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133178815245628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565457701683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943619370461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131792187690735</t>
+    <t xml:space="preserve">0.130720719695091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13317883014679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565442800522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943604469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131792202591896</t>
   </si>
   <si>
     <t xml:space="preserve">0.131477057933807</t>
@@ -851,34 +851,34 @@
     <t xml:space="preserve">0.130468606948853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129964366555214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129586204886436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002045512199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127947464585304</t>
+    <t xml:space="preserve">0.129964396357536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127506285905838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129586189985275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002060413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127947479486465</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128703817725182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371771097183</t>
+    <t xml:space="preserve">0.12870380282402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.125930562615395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127128109335899</t>
+    <t xml:space="preserve">0.127128094434738</t>
   </si>
   <si>
     <t xml:space="preserve">0.126056626439095</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">0.12479604780674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124669998884201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124165765941143</t>
+    <t xml:space="preserve">0.12466999143362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124165758490562</t>
   </si>
   <si>
     <t xml:space="preserve">0.12517423927784</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">0.127380207180977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128451719880104</t>
+    <t xml:space="preserve">0.128451690077782</t>
   </si>
   <si>
     <t xml:space="preserve">0.128136560320854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127884432673454</t>
+    <t xml:space="preserve">0.127884447574615</t>
   </si>
   <si>
     <t xml:space="preserve">0.127443239092827</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">0.126939013600349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128262624144554</t>
+    <t xml:space="preserve">0.128262609243393</t>
   </si>
   <si>
     <t xml:space="preserve">0.126875996589661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126497820019722</t>
+    <t xml:space="preserve">0.126497805118561</t>
   </si>
   <si>
     <t xml:space="preserve">0.126308724284172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430942893028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135573908686638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135762974619865</t>
+    <t xml:space="preserve">0.133430927991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135573893785477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135762959718704</t>
   </si>
   <si>
     <t xml:space="preserve">0.136456295847893</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">0.135636925697327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134061232209206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132485494017601</t>
+    <t xml:space="preserve">0.134061217308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132485523819923</t>
   </si>
   <si>
     <t xml:space="preserve">0.133556976914406</t>
@@ -959,88 +959,88 @@
     <t xml:space="preserve">0.135195732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136141136288643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134439408779144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137464731931686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137716844677925</t>
+    <t xml:space="preserve">0.136141180992126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134439378976822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137464746832848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137716874480247</t>
   </si>
   <si>
     <t xml:space="preserve">0.138221070170403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137842923402786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136330246925354</t>
+    <t xml:space="preserve">0.137842938303947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136330232024193</t>
   </si>
   <si>
     <t xml:space="preserve">0.13708658516407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136771440505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136204183101654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13500665128231</t>
+    <t xml:space="preserve">0.13677142560482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136204198002815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006636381149</t>
   </si>
   <si>
     <t xml:space="preserve">0.134754538536072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135069668292999</t>
+    <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
     <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15114189684391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153789073228836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152780592441559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151267945766449</t>
+    <t xml:space="preserve">0.151141881942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153789088129997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152780637145042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267930865288</t>
   </si>
   <si>
     <t xml:space="preserve">0.145280256867409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147045031189919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444730401039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159398600459099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156625345349312</t>
+    <t xml:space="preserve">0.147045060992241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444715499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15939861536026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156625360250473</t>
   </si>
   <si>
     <t xml:space="preserve">0.157570779323578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152843669056892</t>
+    <t xml:space="preserve">0.152843654155731</t>
   </si>
   <si>
     <t xml:space="preserve">0.152654573321342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151898220181465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15309576690197</t>
+    <t xml:space="preserve">0.151898235082626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153095752000809</t>
   </si>
   <si>
     <t xml:space="preserve">0.150259494781494</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">0.148746818304062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15334789454937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805990099907</t>
+    <t xml:space="preserve">0.153347879648209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805975198746</t>
   </si>
   <si>
     <t xml:space="preserve">0.154419362545013</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">0.156940490007401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159146502614021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167655304074287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167214125394821</t>
+    <t xml:space="preserve">0.15914648771286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167655318975449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050397515297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16721411049366</t>
   </si>
   <si>
     <t xml:space="preserve">0.172067284584045</t>
@@ -1082,55 +1082,55 @@
     <t xml:space="preserve">0.178811311721802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175218731164932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336314201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176461338997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479265093803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173643007874489</t>
+    <t xml:space="preserve">0.17521870136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336299300194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176476240158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479279994965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173642978072166</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365542173386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166205644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222546577454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168600738048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166520789265633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166394740343094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161730632185936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160091906785965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156688392162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161226436495781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162486985325813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163747549057007</t>
+    <t xml:space="preserve">0.166205659508705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222561478615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168600723147392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166520819067955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166394725441933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161730661988258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160091921687126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156688377261162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16122642159462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162487000226974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163747534155846</t>
   </si>
   <si>
     <t xml:space="preserve">0.163873597979546</t>
@@ -1145,121 +1145,121 @@
     <t xml:space="preserve">0.157759860157967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167970448732376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167718335986137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165260225534439</t>
+    <t xml:space="preserve">0.167970433831215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167718321084976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1652602404356</t>
   </si>
   <si>
     <t xml:space="preserve">0.163117274641991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163810580968857</t>
+    <t xml:space="preserve">0.163810566067696</t>
   </si>
   <si>
     <t xml:space="preserve">0.159461632370949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147675320506096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147486254572868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150007396936417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150448590517044</t>
+    <t xml:space="preserve">0.147675335407257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147486239671707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150007382035255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150448575615883</t>
   </si>
   <si>
     <t xml:space="preserve">0.150511607527733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151078879833221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151646107435226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150322511792183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494705557823</t>
+    <t xml:space="preserve">0.15107886493206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151646122336388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150322526693344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494690656662</t>
   </si>
   <si>
     <t xml:space="preserve">0.150826752185822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151772171258926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881318211555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583105325699</t>
+    <t xml:space="preserve">0.151772156357765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881303310394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583090424538</t>
   </si>
   <si>
     <t xml:space="preserve">0.149629205465317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151709139347076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15101583302021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148935899138451</t>
+    <t xml:space="preserve">0.151709154248238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151015818119049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148935928940773</t>
   </si>
   <si>
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763735175133</t>
+    <t xml:space="preserve">0.150763720273972</t>
   </si>
   <si>
     <t xml:space="preserve">0.150637656450272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151204898953438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149944350123405</t>
+    <t xml:space="preserve">0.151204913854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149944335222244</t>
   </si>
   <si>
     <t xml:space="preserve">0.152213364839554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152528509497643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157255634665489</t>
+    <t xml:space="preserve">0.152528524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1493771225214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15725564956665</t>
   </si>
   <si>
     <t xml:space="preserve">0.156310215592384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164503902196884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243308663368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613019347191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982774734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163558453321457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165764465928078</t>
+    <t xml:space="preserve">0.164503887295723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243338465691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162613034248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982759833336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163558468222618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165764480829239</t>
   </si>
   <si>
     <t xml:space="preserve">0.165449321269989</t>
@@ -1271,40 +1271,40 @@
     <t xml:space="preserve">0.160722196102142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162297904491425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061948060989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147171095013618</t>
+    <t xml:space="preserve">0.162297874689102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061962962151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540820598602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146225675940514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142759129405022</t>
+    <t xml:space="preserve">0.146225661039352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142759144306183</t>
   </si>
   <si>
     <t xml:space="preserve">0.144334837794304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140238001942635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139607697725296</t>
+    <t xml:space="preserve">0.140237987041473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139607682824135</t>
   </si>
   <si>
     <t xml:space="preserve">0.138031989336014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139922872185707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135826021432877</t>
+    <t xml:space="preserve">0.139922842383385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135825991630554</t>
   </si>
   <si>
     <t xml:space="preserve">0.138347148895264</t>
@@ -1328,31 +1328,31 @@
     <t xml:space="preserve">0.135510876774788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134250283241272</t>
+    <t xml:space="preserve">0.134250298142433</t>
   </si>
   <si>
     <t xml:space="preserve">0.133935153484344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132674604654312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143074259161949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965127110481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143389403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
+    <t xml:space="preserve">0.132674589753151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14307427406311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144965097308159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443999648094</t>
   </si>
   <si>
     <t xml:space="preserve">0.146575838327408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147864416241646</t>
+    <t xml:space="preserve">0.147864431142807</t>
   </si>
   <si>
     <t xml:space="preserve">0.14496511220932</t>
@@ -1361,37 +1361,37 @@
     <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145609423518181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455082058907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142710104584694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141421526670456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13916651904583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777245163918</t>
+    <t xml:space="preserve">0.14560940861702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455067157745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142710089683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141421511769295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139166533946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777230262756</t>
   </si>
   <si>
     <t xml:space="preserve">0.139488652348518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135622903704643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133690044283867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13272362947464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132079318165779</t>
+    <t xml:space="preserve">0.135622918605804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133690059185028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132723599672318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13207933306694</t>
   </si>
   <si>
     <t xml:space="preserve">0.129824325442314</t>
@@ -1415,16 +1415,16 @@
     <t xml:space="preserve">0.131757184863091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125894129276276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126925006508827</t>
+    <t xml:space="preserve">0.125894159078598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126924991607666</t>
   </si>
   <si>
     <t xml:space="preserve">0.125378727912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128600165247917</t>
+    <t xml:space="preserve">0.128600150346756</t>
   </si>
   <si>
     <t xml:space="preserve">0.130468592047691</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">0.127955883741379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127827033400536</t>
+    <t xml:space="preserve">0.127827003598213</t>
   </si>
   <si>
     <t xml:space="preserve">0.126023009419441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124347850680351</t>
+    <t xml:space="preserve">0.124347843229771</t>
   </si>
   <si>
     <t xml:space="preserve">0.123703554272652</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">0.127311587333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127569302916527</t>
+    <t xml:space="preserve">0.127569288015366</t>
   </si>
   <si>
     <t xml:space="preserve">0.12666729092598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126538425683975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128729030489922</t>
+    <t xml:space="preserve">0.126538455486298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12872901558876</t>
   </si>
   <si>
     <t xml:space="preserve">0.12834244966507</t>
@@ -1472,13 +1472,13 @@
     <t xml:space="preserve">0.130146458745003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134012177586555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134656488895416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13852222263813</t>
+    <t xml:space="preserve">0.134012207388878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134656473994255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138522207736969</t>
   </si>
   <si>
     <t xml:space="preserve">0.13820007443428</t>
@@ -1487,25 +1487,25 @@
     <t xml:space="preserve">0.135300770401955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130790740251541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128084734082222</t>
+    <t xml:space="preserve">0.130790755152702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128084719181061</t>
   </si>
   <si>
     <t xml:space="preserve">0.128857880830765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12524987757206</t>
+    <t xml:space="preserve">0.125249832868576</t>
   </si>
   <si>
     <t xml:space="preserve">0.122157268226147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123316988348961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125507578253746</t>
+    <t xml:space="preserve">0.12331698089838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125507563352585</t>
   </si>
   <si>
     <t xml:space="preserve">0.128213599324226</t>
@@ -1514,31 +1514,31 @@
     <t xml:space="preserve">0.126151859760284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127182736992836</t>
+    <t xml:space="preserve">0.127182722091675</t>
   </si>
   <si>
     <t xml:space="preserve">0.125636428594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120482116937637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122286133468151</t>
+    <t xml:space="preserve">0.120482131838799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122286111116409</t>
   </si>
   <si>
     <t xml:space="preserve">0.122414998710155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.117260672152042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266065716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113394938409328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848637461662</t>
+    <t xml:space="preserve">0.117260657250881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266080617905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113394923508167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848652362823</t>
   </si>
   <si>
     <t xml:space="preserve">0.11210636049509</t>
@@ -1547,91 +1547,91 @@
     <t xml:space="preserve">0.114425793290138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114683516323566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112235203385353</t>
+    <t xml:space="preserve">0.114683531224728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112235210835934</t>
   </si>
   <si>
     <t xml:space="preserve">0.110817782580853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108240619301796</t>
+    <t xml:space="preserve">0.108240634202957</t>
   </si>
   <si>
     <t xml:space="preserve">0.106565460562706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105921171605587</t>
+    <t xml:space="preserve">0.105921179056168</t>
   </si>
   <si>
     <t xml:space="preserve">0.101926580071449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105019174516201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103086300194263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374870657921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117169976234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105663470923901</t>
+    <t xml:space="preserve">0.10501916706562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103086277842522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10566346347332</t>
   </si>
   <si>
     <t xml:space="preserve">0.107982903718948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108627177774906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108111754059792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11146205663681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750649452209</t>
+    <t xml:space="preserve">0.108627185225487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108111768960953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111462064087391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750634551048</t>
   </si>
   <si>
     <t xml:space="preserve">0.108756050467491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110173508524895</t>
+    <t xml:space="preserve">0.110173478722572</t>
   </si>
   <si>
     <t xml:space="preserve">0.109529197216034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106952033936977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153425872326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103988312184811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699734270573</t>
+    <t xml:space="preserve">0.106952041387558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153440773487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10398830473423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699726819992</t>
   </si>
   <si>
     <t xml:space="preserve">0.105276882648468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111204341053963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115585513412952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115843214094639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327812731266</t>
+    <t xml:space="preserve">0.111204348504543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115585520863533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1158432289958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327805280685</t>
   </si>
   <si>
     <t xml:space="preserve">0.113008365035057</t>
@@ -1643,82 +1643,82 @@
     <t xml:space="preserve">0.11043119430542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107854045927525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730604052544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106307752430439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103859469294548</t>
+    <t xml:space="preserve">0.107854038476944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730589151382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10630775988102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103859454393387</t>
   </si>
   <si>
     <t xml:space="preserve">0.114554658532143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109142631292343</t>
+    <t xml:space="preserve">0.109142638742924</t>
   </si>
   <si>
     <t xml:space="preserve">0.109013758599758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108884900808334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271474182606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10733862221241</t>
+    <t xml:space="preserve">0.108884915709496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271481633186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107338614761829</t>
   </si>
   <si>
     <t xml:space="preserve">0.102442011237144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101411141455173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055452764034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100251443684101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999937132000923</t>
+    <t xml:space="preserve">0.101411148905754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055430412292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100251436233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999937206506729</t>
   </si>
   <si>
     <t xml:space="preserve">0.10128229111433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101797722280025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766852498055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105148024857044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915778040886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111075483262539</t>
+    <t xml:space="preserve">0.101797729730606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766859948635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105148032307625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915763139725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11107549071312</t>
   </si>
   <si>
     <t xml:space="preserve">0.112621776759624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110302351415157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110688909888268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761444032192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534613132477</t>
+    <t xml:space="preserve">0.110302336513996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11068893969059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761451482773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534598231316</t>
   </si>
   <si>
     <t xml:space="preserve">0.107467480003834</t>
@@ -1730,25 +1730,25 @@
     <t xml:space="preserve">0.107080891728401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104503743350506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792313814163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436610221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105341322720051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596330344677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562760055065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207041561604</t>
+    <t xml:space="preserve">0.104503735899925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792328715324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436595320702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105341300368309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596322894096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562774956226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207049012184</t>
   </si>
   <si>
     <t xml:space="preserve">0.110185064375401</t>
@@ -1757,13 +1757,13 @@
     <t xml:space="preserve">0.109857141971588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111168839037418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110513001680374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889533042908</t>
+    <t xml:space="preserve">0.11116886138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110513009130955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889540493488</t>
   </si>
   <si>
     <t xml:space="preserve">0.106905750930309</t>
@@ -1772,67 +1772,67 @@
     <t xml:space="preserve">0.10592196136713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103954367339611</t>
+    <t xml:space="preserve">0.10395435988903</t>
   </si>
   <si>
     <t xml:space="preserve">0.104282289743423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105594024062157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266086757183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104938142001629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102970562875271</t>
+    <t xml:space="preserve">0.105594031512737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217485249043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266079306602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10493815690279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102970570325851</t>
   </si>
   <si>
     <t xml:space="preserve">0.103626452386379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103298492729664</t>
+    <t xml:space="preserve">0.103298500180244</t>
   </si>
   <si>
     <t xml:space="preserve">0.101658843457699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100347109138966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101330913603306</t>
+    <t xml:space="preserve">0.100347101688385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101330906152725</t>
   </si>
   <si>
     <t xml:space="preserve">0.0970677956938744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0977236703038216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957180976868</t>
+    <t xml:space="preserve">0.0977236554026604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957255482674</t>
   </si>
   <si>
     <t xml:space="preserve">0.0951002016663551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.098051592707634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0964119285345078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09870745241642</t>
+    <t xml:space="preserve">0.0980515852570534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0964119136333466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0987074449658394</t>
   </si>
   <si>
     <t xml:space="preserve">0.0993633195757866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100019186735153</t>
+    <t xml:space="preserve">0.100019179284573</t>
   </si>
   <si>
     <t xml:space="preserve">0.101002976298332</t>
@@ -1853,10 +1853,10 @@
     <t xml:space="preserve">0.099035382270813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104610219597816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107561603188515</t>
+    <t xml:space="preserve">0.104610227048397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107561610639095</t>
   </si>
   <si>
     <t xml:space="preserve">0.108873330056667</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">0.108545415103436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10920125991106</t>
+    <t xml:space="preserve">0.109201282262802</t>
   </si>
   <si>
     <t xml:space="preserve">0.107233680784702</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">0.11215265840292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114448182284832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111824735999107</t>
+    <t xml:space="preserve">0.114448189735413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111824721097946</t>
   </si>
   <si>
     <t xml:space="preserve">0.112808518111706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113136447966099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480588257313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496791243553</t>
+    <t xml:space="preserve">0.113136455416679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480595707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496798694134</t>
   </si>
   <si>
     <t xml:space="preserve">0.130516842007637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139698937535286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132484421133995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141010642051697</t>
+    <t xml:space="preserve">0.139698922634125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132484436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141010656952858</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686552524567</t>
@@ -1916,31 +1916,31 @@
     <t xml:space="preserve">0.16724519431591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155439645051956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150848612189293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154127925634384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157407239079475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156751379370689</t>
+    <t xml:space="preserve">0.155439630150795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150848597288132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154127910733223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157407224178314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156751364469528</t>
   </si>
   <si>
     <t xml:space="preserve">0.152816191315651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148880988359451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145601704716682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146257549524307</t>
+    <t xml:space="preserve">0.148881003260612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145601689815521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146257564425468</t>
   </si>
   <si>
     <t xml:space="preserve">0.146913424134254</t>
@@ -1949,16 +1949,16 @@
     <t xml:space="preserve">0.150192737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14953687787056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142978221178055</t>
+    <t xml:space="preserve">0.149536862969398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
     <t xml:space="preserve">0.147569268941879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148225158452988</t>
+    <t xml:space="preserve">0.148225143551826</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654146552086</t>
@@ -1967,13 +1967,13 @@
     <t xml:space="preserve">0.161342427134514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141666516661644</t>
+    <t xml:space="preserve">0.141666531562805</t>
   </si>
   <si>
     <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1351078748703</t>
+    <t xml:space="preserve">0.135107889771461</t>
   </si>
   <si>
     <t xml:space="preserve">0.133140295743942</t>
@@ -1982,10 +1982,10 @@
     <t xml:space="preserve">0.137731328606606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154783770442009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156095519661903</t>
+    <t xml:space="preserve">0.15478378534317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156095504760742</t>
   </si>
   <si>
     <t xml:space="preserve">0.153472036123276</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">0.131828561425209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135763734579086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137075453996658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12559786438942</t>
+    <t xml:space="preserve">0.135763749480247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137075483798981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125597849488258</t>
   </si>
   <si>
     <t xml:space="preserve">0.126581639051437</t>
@@ -2009,19 +2009,19 @@
     <t xml:space="preserve">0.123958192765713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118711292743683</t>
+    <t xml:space="preserve">0.118711277842522</t>
   </si>
   <si>
     <t xml:space="preserve">0.110840924084187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0967398583889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0826388001441956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0878857001662254</t>
+    <t xml:space="preserve">0.0967398509383202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0826388075947762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0878857150673866</t>
   </si>
   <si>
     <t xml:space="preserve">0.08722984790802</t>
@@ -2036,16 +2036,16 @@
     <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0928046926856041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0944443345069885</t>
+    <t xml:space="preserve">0.0928046852350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0944443270564079</t>
   </si>
   <si>
     <t xml:space="preserve">0.0960839986801147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0931326150894165</t>
+    <t xml:space="preserve">0.0931326076388359</t>
   </si>
   <si>
     <t xml:space="preserve">0.0957560613751411</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">0.0937884822487831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0965431183576584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0969366058707237</t>
+    <t xml:space="preserve">0.0965431109070778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0969366207718849</t>
   </si>
   <si>
     <t xml:space="preserve">0.0978548377752304</t>
@@ -2066,76 +2066,76 @@
     <t xml:space="preserve">0.0971989706158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0924767479300499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0940508246421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.093919649720192</t>
+    <t xml:space="preserve">0.0924767404794693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.094050832092762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
     <t xml:space="preserve">0.0941819995641708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0949690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937264323235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483550906181</t>
+    <t xml:space="preserve">0.0949690267443657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937338829041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483625411987</t>
   </si>
   <si>
     <t xml:space="preserve">0.100740633904934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0968054533004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0966742858290672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709756612778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0979859977960587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099166564643383</t>
+    <t xml:space="preserve">0.0968054458498955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0966742783784866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709764063358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0979859903454781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0991665571928024</t>
   </si>
   <si>
     <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0948378592729568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084766745567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102183535695076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999535918235779</t>
+    <t xml:space="preserve">0.0948378667235374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102183528244495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999535843729973</t>
   </si>
   <si>
     <t xml:space="preserve">0.10323291271925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104806989431381</t>
+    <t xml:space="preserve">0.104806981980801</t>
   </si>
   <si>
     <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125925794243813</t>
+    <t xml:space="preserve">0.125925779342651</t>
   </si>
   <si>
     <t xml:space="preserve">0.138387188315392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14232237637043</t>
+    <t xml:space="preserve">0.142322361469269</t>
   </si>
   <si>
     <t xml:space="preserve">0.137403398752213</t>
@@ -2153,34 +2153,34 @@
     <t xml:space="preserve">0.134124085307121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131041511893272</t>
+    <t xml:space="preserve">0.131041526794434</t>
   </si>
   <si>
     <t xml:space="preserve">0.127893373370171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134779930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131172686815262</t>
+    <t xml:space="preserve">0.134779945015907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131172716617584</t>
   </si>
   <si>
     <t xml:space="preserve">0.130779162049294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130123317241669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129336282610893</t>
+    <t xml:space="preserve">0.130123302340508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129336267709732</t>
   </si>
   <si>
     <t xml:space="preserve">0.130385667085648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131500631570816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130910336971283</t>
+    <t xml:space="preserve">0.131500646471977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130910351872444</t>
   </si>
   <si>
     <t xml:space="preserve">0.133468225598335</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">0.127631038427353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128549233078957</t>
+    <t xml:space="preserve">0.128549247980118</t>
   </si>
   <si>
     <t xml:space="preserve">0.133796155452728</t>
@@ -2210,61 +2210,61 @@
     <t xml:space="preserve">0.129205107688904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129598632454872</t>
+    <t xml:space="preserve">0.129598617553711</t>
   </si>
   <si>
     <t xml:space="preserve">0.140026852488518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129729807376862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129860952496529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130254477262497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129073917865753</t>
+    <t xml:space="preserve">0.1297297924757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12986096739769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130254492163658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129073932766914</t>
   </si>
   <si>
     <t xml:space="preserve">0.125138744711876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124614059925079</t>
+    <t xml:space="preserve">0.124614045023918</t>
   </si>
   <si>
     <t xml:space="preserve">0.143634095788002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143962025642395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139370977878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136091679334641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138059243559837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136747539043427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140682697296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144945845007896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142650321125984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141994461417198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144289970397949</t>
+    <t xml:space="preserve">0.143962040543556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139370992779732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136091664433479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138059258460999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136747524142265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140682712197304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144945830106735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142650306224823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141994446516037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144289955496788</t>
   </si>
   <si>
     <t xml:space="preserve">0.153799995779991</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153144136071205</t>
+    <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
     <t xml:space="preserve">0.155111700296402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155767560005188</t>
+    <t xml:space="preserve">0.155767574906349</t>
   </si>
   <si>
     <t xml:space="preserve">0.160358622670174</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">0.166917249560356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163310006260872</t>
+    <t xml:space="preserve">0.163310021162033</t>
   </si>
   <si>
     <t xml:space="preserve">0.162326216697693</t>
@@ -2309,10 +2309,10 @@
     <t xml:space="preserve">0.16101448237896</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159046918153763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159374818205833</t>
+    <t xml:space="preserve">0.15904688835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159374833106995</t>
   </si>
   <si>
     <t xml:space="preserve">0.158718958497047</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">0.160030692815781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1580630838871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165341451764107</t>
+    <t xml:space="preserve">0.158063098788261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165341436862946</t>
   </si>
   <si>
     <t xml:space="preserve">0.163571178913116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863105535507</t>
+    <t xml:space="preserve">0.162863075733185</t>
   </si>
   <si>
     <t xml:space="preserve">0.16250903904438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161092832684517</t>
+    <t xml:space="preserve">0.161092847585678</t>
   </si>
   <si>
     <t xml:space="preserve">0.158614486455917</t>
@@ -2363,10 +2363,10 @@
     <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157552346587181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161800935864449</t>
+    <t xml:space="preserve">0.15755233168602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161800920963287</t>
   </si>
   <si>
     <t xml:space="preserve">0.155073970556259</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">0.155782088637352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151533469557762</t>
+    <t xml:space="preserve">0.151533484458923</t>
   </si>
   <si>
     <t xml:space="preserve">0.15259562432766</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154719933867455</t>
+    <t xml:space="preserve">0.154719948768616</t>
   </si>
   <si>
     <t xml:space="preserve">0.155428037047386</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011830687523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156136125326157</t>
+    <t xml:space="preserve">0.154011815786362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156136140227318</t>
   </si>
   <si>
     <t xml:space="preserve">0.152241587638855</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">0.151887521147728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151179432868958</t>
+    <t xml:space="preserve">0.151179417967796</t>
   </si>
   <si>
     <t xml:space="preserve">0.15011727809906</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">0.150825381278992</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149763241410255</t>
+    <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
     <t xml:space="preserve">0.150471314787865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149055108428001</t>
+    <t xml:space="preserve">0.149055138230324</t>
   </si>
   <si>
     <t xml:space="preserve">0.146222725510597</t>
@@ -2441,10 +2441,10 @@
     <t xml:space="preserve">0.1426822245121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143390312790871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145514622330666</t>
+    <t xml:space="preserve">0.143390327692032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145514637231827</t>
   </si>
   <si>
     <t xml:space="preserve">0.148347035050392</t>
@@ -2459,46 +2459,46 @@
     <t xml:space="preserve">0.145160585641861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147638931870461</t>
+    <t xml:space="preserve">0.147638916969299</t>
   </si>
   <si>
     <t xml:space="preserve">0.148701086640358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146576777100563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144452467560768</t>
+    <t xml:space="preserve">0.146576792001724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144452482461929</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144806534051895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144098445773125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14586865901947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147992968559265</t>
+    <t xml:space="preserve">0.144806519150734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144098430871964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145868673920631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147992983460426</t>
   </si>
   <si>
     <t xml:space="preserve">0.16569547355175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168527886271477</t>
+    <t xml:space="preserve">0.168527871370316</t>
   </si>
   <si>
     <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16746574640274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164987400174141</t>
+    <t xml:space="preserve">0.167465731501579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16498738527298</t>
   </si>
   <si>
     <t xml:space="preserve">0.163217127323151</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167021736502647</t>
+    <t xml:space="preserve">0.167021751403809</t>
   </si>
   <si>
     <t xml:space="preserve">0.161695286631584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161314845085144</t>
+    <t xml:space="preserve">0.161314830183983</t>
   </si>
   <si>
     <t xml:space="preserve">0.159793004393578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163978055119514</t>
+    <t xml:space="preserve">0.163978040218353</t>
   </si>
   <si>
     <t xml:space="preserve">0.16055391728878</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">0.158271163702011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160934388637543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162836670875549</t>
+    <t xml:space="preserve">0.160934373736382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162836685776711</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">0.163597598671913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162456214427948</t>
+    <t xml:space="preserve">0.162456229329109</t>
   </si>
   <si>
     <t xml:space="preserve">0.159032076597214</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.159412547945976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160173445940018</t>
+    <t xml:space="preserve">0.16017347574234</t>
   </si>
   <si>
     <t xml:space="preserve">0.165880352258682</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">0.170445874333382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169684946537018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170826330780983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171967715024948</t>
+    <t xml:space="preserve">0.169684961438179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170826315879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171967700123787</t>
   </si>
   <si>
     <t xml:space="preserve">0.170065402984619</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">0.15789070725441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153705641627312</t>
+    <t xml:space="preserve">0.153705656528473</t>
   </si>
   <si>
     <t xml:space="preserve">0.14427025616169</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157510235905647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164738968014717</t>
+    <t xml:space="preserve">0.157510250806808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164738982915878</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168924033641815</t>
+    <t xml:space="preserve">0.168924018740654</t>
   </si>
   <si>
     <t xml:space="preserve">0.166641265153885</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">0.174277201294899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173462823033333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171426862478256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168983712792397</t>
+    <t xml:space="preserve">0.173462808132172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171426877379417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168983727693558</t>
   </si>
   <si>
     <t xml:space="preserve">0.166133388876915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17061248421669</t>
+    <t xml:space="preserve">0.170612499117851</t>
   </si>
   <si>
     <t xml:space="preserve">0.168169349431992</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">0.166540592908859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166947767138481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167762145400047</t>
+    <t xml:space="preserve">0.166947782039642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167762160301208</t>
   </si>
   <si>
     <t xml:space="preserve">0.168576538562775</t>
@@ -2669,31 +2669,31 @@
     <t xml:space="preserve">0.162875890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15196318924427</t>
+    <t xml:space="preserve">0.151963204145432</t>
   </si>
   <si>
     <t xml:space="preserve">0.155709341168404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157175213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15636083483696</t>
+    <t xml:space="preserve">0.157175227999687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156360849738121</t>
   </si>
   <si>
     <t xml:space="preserve">0.157338112592697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155546456575394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154243469238281</t>
+    <t xml:space="preserve">0.155546471476555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15424345433712</t>
   </si>
   <si>
     <t xml:space="preserve">0.150660187005997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152451828122139</t>
+    <t xml:space="preserve">0.152451813220978</t>
   </si>
   <si>
     <t xml:space="preserve">0.152614697813988</t>
@@ -2702,16 +2702,16 @@
     <t xml:space="preserve">0.163690268993378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162387236952782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158478245139122</t>
+    <t xml:space="preserve">0.162387251853943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158478230237961</t>
   </si>
   <si>
     <t xml:space="preserve">0.160432755947113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157012358307838</t>
+    <t xml:space="preserve">0.157012343406677</t>
   </si>
   <si>
     <t xml:space="preserve">0.161247119307518</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">0.154732093214989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966839313507</t>
+    <t xml:space="preserve">0.158966854214668</t>
   </si>
   <si>
     <t xml:space="preserve">0.15652371942997</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">0.156035095453262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157663851976395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155383601784706</t>
+    <t xml:space="preserve">0.157663837075233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155383586883545</t>
   </si>
   <si>
     <t xml:space="preserve">0.157826721668243</t>
@@ -2822,10 +2822,10 @@
     <t xml:space="preserve">0.163283064961433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164097443223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162224397063255</t>
+    <t xml:space="preserve">0.164097458124161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162224382162094</t>
   </si>
   <si>
     <t xml:space="preserve">0.162550121545792</t>
@@ -2834,10 +2834,10 @@
     <t xml:space="preserve">0.161084249615669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15880398452282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159618362784386</t>
+    <t xml:space="preserve">0.158803969621658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159618347883224</t>
   </si>
   <si>
     <t xml:space="preserve">0.159455493092537</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">0.170205295085907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175905972719193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17305563390255</t>
+    <t xml:space="preserve">0.175905957818031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173055619001389</t>
   </si>
   <si>
     <t xml:space="preserve">0.176720321178436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177534699440002</t>
+    <t xml:space="preserve">0.177534714341164</t>
   </si>
   <si>
     <t xml:space="preserve">0.179163470864296</t>
@@ -2870,10 +2870,13 @@
     <t xml:space="preserve">0.175091579556465</t>
   </si>
   <si>
+    <t xml:space="preserve">0.173870012164116</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.171019673347473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172241255640984</t>
+    <t xml:space="preserve">0.172241240739822</t>
   </si>
   <si>
     <t xml:space="preserve">0.172648429870605</t>
@@ -2888,19 +2891,19 @@
     <t xml:space="preserve">0.183235347270966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181606605648994</t>
+    <t xml:space="preserve">0.181606620550156</t>
   </si>
   <si>
     <t xml:space="preserve">0.184049740433693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182420983910561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.184864118695259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.185678511857986</t>
+    <t xml:space="preserve">0.182420998811722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18486413359642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.185678496956825</t>
   </si>
   <si>
     <t xml:space="preserve">0.188121646642685</t>
@@ -50887,7 +50890,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1817" t="s">
-        <v>869</v>
+        <v>952</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50913,7 +50916,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1818" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -50965,7 +50968,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1820" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -50991,7 +50994,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1821" t="s">
-        <v>869</v>
+        <v>952</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51069,7 +51072,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1824" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -51095,7 +51098,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1825" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -51121,7 +51124,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1826" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -51147,7 +51150,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1827" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -51173,7 +51176,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1828" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -51199,7 +51202,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1829" t="s">
-        <v>869</v>
+        <v>952</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51251,7 +51254,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1831" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -51277,7 +51280,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1832" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51459,7 +51462,7 @@
         <v>0.208499997854233</v>
       </c>
       <c r="G1839" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -51485,7 +51488,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1840" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -51537,7 +51540,7 @@
         <v>0.208499997854233</v>
       </c>
       <c r="G1842" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -51615,7 +51618,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1845" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -51641,7 +51644,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1846" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -51667,7 +51670,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1847" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51797,7 +51800,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G1852" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -51823,7 +51826,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1853" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -51849,7 +51852,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1854" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51875,7 +51878,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1855" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51901,7 +51904,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1856" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51927,7 +51930,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G1857" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -51953,7 +51956,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1858" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51979,7 +51982,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G1859" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -52005,7 +52008,7 @@
         <v>0.228000000119209</v>
       </c>
       <c r="G1860" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -52031,7 +52034,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1861" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -52057,7 +52060,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G1862" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -52083,7 +52086,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1863" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -52109,7 +52112,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G1864" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -52135,7 +52138,7 @@
         <v>0.231000006198883</v>
       </c>
       <c r="G1865" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -52161,7 +52164,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1866" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -52187,7 +52190,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1867" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52213,7 +52216,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G1868" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -52239,7 +52242,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1869" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -52265,7 +52268,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1870" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -52291,7 +52294,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1871" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -52317,7 +52320,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1872" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52343,7 +52346,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1873" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52369,7 +52372,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1874" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -52395,7 +52398,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1875" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52421,7 +52424,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1876" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52447,7 +52450,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1877" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52473,7 +52476,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1878" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52499,7 +52502,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1879" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52525,7 +52528,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1880" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52551,7 +52554,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1881" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52577,7 +52580,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1882" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52603,7 +52606,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1883" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52629,7 +52632,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1884" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52655,7 +52658,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1885" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52681,7 +52684,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1886" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52707,7 +52710,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1887" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52733,7 +52736,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1888" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52759,7 +52762,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1889" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52785,7 +52788,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1890" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52811,7 +52814,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1891" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52837,7 +52840,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1892" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52863,7 +52866,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1893" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52889,7 +52892,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1894" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52915,7 +52918,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1895" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52941,7 +52944,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1896" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52967,7 +52970,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1897" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52993,7 +52996,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1898" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53019,7 +53022,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1899" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53045,7 +53048,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1900" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53071,7 +53074,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1901" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53097,7 +53100,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1902" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53123,7 +53126,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1903" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -53149,7 +53152,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1904" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53175,7 +53178,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1905" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53201,7 +53204,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1906" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -53227,7 +53230,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1907" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -53253,7 +53256,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1908" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53279,7 +53282,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1909" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53305,7 +53308,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1910" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53331,7 +53334,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1911" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53357,7 +53360,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1912" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53383,7 +53386,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1913" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53409,7 +53412,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1914" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53435,7 +53438,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1915" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53461,7 +53464,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1916" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53487,7 +53490,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1917" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53513,7 +53516,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1918" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53539,7 +53542,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1919" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53565,7 +53568,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1920" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53591,7 +53594,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1921" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53617,7 +53620,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1922" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53643,7 +53646,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1923" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53669,7 +53672,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1924" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53695,7 +53698,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1925" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53721,7 +53724,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1926" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53747,7 +53750,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1927" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53773,7 +53776,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1928" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53799,7 +53802,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1929" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53825,7 +53828,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G1930" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53851,7 +53854,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1931" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53877,7 +53880,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1932" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53903,7 +53906,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1933" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53929,7 +53932,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1934" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53955,7 +53958,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1935" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53981,7 +53984,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1936" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54007,7 +54010,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54033,7 +54036,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1938" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54059,7 +54062,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1939" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54085,7 +54088,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1940" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54111,7 +54114,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1941" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54137,7 +54140,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1942" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54163,7 +54166,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54189,7 +54192,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54215,7 +54218,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1945" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54241,7 +54244,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1946" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54267,7 +54270,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54293,7 +54296,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1948" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54319,7 +54322,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54345,7 +54348,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1950" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54371,7 +54374,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54397,7 +54400,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1952" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54423,7 +54426,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1953" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54449,7 +54452,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1954" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54475,7 +54478,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1955" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54501,7 +54504,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1956" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54527,7 +54530,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1957" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54553,7 +54556,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1958" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54579,7 +54582,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1959" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54605,7 +54608,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1960" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54631,7 +54634,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1961" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54657,7 +54660,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1962" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54683,7 +54686,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54709,7 +54712,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54735,7 +54738,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1965" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54761,7 +54764,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1966" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54787,7 +54790,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1967" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54813,7 +54816,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1968" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54839,7 +54842,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1969" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54865,7 +54868,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1970" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54891,7 +54894,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1971" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54917,7 +54920,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1972" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54943,7 +54946,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1973" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54969,7 +54972,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1974" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54995,7 +54998,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1975" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55021,7 +55024,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55047,7 +55050,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1977" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55073,7 +55076,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1978" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55099,7 +55102,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55125,7 +55128,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1980" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55151,7 +55154,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1981" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55177,7 +55180,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1982" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55203,7 +55206,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1983" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55229,7 +55232,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1984" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55255,7 +55258,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1985" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55281,7 +55284,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1986" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55307,7 +55310,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1987" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55333,7 +55336,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55359,7 +55362,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1989" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55385,7 +55388,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55411,7 +55414,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1991" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55437,7 +55440,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1992" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55463,7 +55466,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1993" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55489,7 +55492,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1994" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55515,7 +55518,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1995" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55541,7 +55544,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1996" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55567,7 +55570,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1997" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55593,7 +55596,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1998" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55619,7 +55622,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1999" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55645,7 +55648,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2000" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55671,7 +55674,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55697,7 +55700,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2002" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55723,7 +55726,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2003" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55749,7 +55752,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2004" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55775,7 +55778,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55801,7 +55804,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2006" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55827,7 +55830,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2007" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55853,7 +55856,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2008" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55879,7 +55882,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2009" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55905,7 +55908,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2010" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55931,7 +55934,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2011" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55957,7 +55960,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2012" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55983,7 +55986,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2013" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56009,7 +56012,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2014" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56035,7 +56038,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2015" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56061,7 +56064,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2016" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56087,7 +56090,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2017" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56113,7 +56116,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2018" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56139,7 +56142,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2019" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56165,7 +56168,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2020" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56191,7 +56194,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2021" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56217,7 +56220,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56243,7 +56246,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2023" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56269,7 +56272,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2024" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56295,7 +56298,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2025" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56321,7 +56324,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56347,7 +56350,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2027" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56373,7 +56376,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56399,7 +56402,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2029" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56425,7 +56428,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2030" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56451,7 +56454,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2031" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56477,7 +56480,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2032" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56503,7 +56506,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56529,7 +56532,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2034" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56555,7 +56558,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2035" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56581,7 +56584,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2036" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56607,7 +56610,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2037" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56633,7 +56636,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2038" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56659,7 +56662,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2039" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56685,7 +56688,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56711,7 +56714,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2041" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56737,7 +56740,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2042" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56763,7 +56766,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2043" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56789,7 +56792,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2044" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56815,7 +56818,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2045" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56841,7 +56844,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2046" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56867,7 +56870,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2047" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56893,7 +56896,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2048" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56919,7 +56922,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2049" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56945,7 +56948,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2050" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56971,7 +56974,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2051" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56997,7 +57000,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2052" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57023,7 +57026,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2053" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57049,7 +57052,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2054" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57075,7 +57078,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2055" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57101,7 +57104,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2056" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57127,7 +57130,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2057" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57153,7 +57156,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2058" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57179,7 +57182,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2059" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57205,7 +57208,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2060" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57231,7 +57234,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2061" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57257,7 +57260,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2062" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57283,7 +57286,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2063" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57309,7 +57312,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2064" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57335,7 +57338,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2065" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57361,7 +57364,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57387,7 +57390,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57413,7 +57416,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2068" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57439,7 +57442,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57465,7 +57468,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57491,7 +57494,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57517,7 +57520,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57543,7 +57546,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57569,7 +57572,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2074" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57595,7 +57598,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2075" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57621,7 +57624,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2076" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57647,7 +57650,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2077" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57673,7 +57676,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2078" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57699,7 +57702,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2079" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57725,7 +57728,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2080" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57751,7 +57754,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2081" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57777,7 +57780,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2082" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57803,7 +57806,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2083" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57829,7 +57832,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2084" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57855,7 +57858,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2085" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57881,7 +57884,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2086" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57907,7 +57910,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2087" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57933,7 +57936,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2088" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57959,7 +57962,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2089" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57985,7 +57988,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2090" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58011,7 +58014,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2091" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58037,7 +58040,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2092" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58063,7 +58066,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2093" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58089,7 +58092,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2094" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58115,7 +58118,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2095" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58141,7 +58144,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2096" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -58167,7 +58170,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2097" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -58193,7 +58196,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2098" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58219,7 +58222,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2099" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -58245,7 +58248,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2100" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -58271,7 +58274,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2101" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58297,7 +58300,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2102" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58323,7 +58326,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2103" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58349,7 +58352,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2104" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58375,7 +58378,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2105" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58401,7 +58404,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2106" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58427,7 +58430,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2107" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58453,7 +58456,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2108" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58479,7 +58482,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2109" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58505,7 +58508,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2110" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58531,7 +58534,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2111" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58557,7 +58560,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2112" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58583,7 +58586,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2113" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58609,7 +58612,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2114" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58635,7 +58638,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2115" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58661,7 +58664,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2116" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58687,7 +58690,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2117" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58713,7 +58716,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2118" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58739,7 +58742,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2119" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58765,7 +58768,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2120" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58791,7 +58794,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2121" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58817,7 +58820,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2122" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58843,7 +58846,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2123" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58869,7 +58872,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2124" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58895,7 +58898,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2125" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58921,7 +58924,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2126" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58947,7 +58950,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2127" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58973,7 +58976,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2128" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58999,7 +59002,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2129" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59025,7 +59028,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2130" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59051,7 +59054,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2131" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59077,7 +59080,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2132" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59103,7 +59106,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2133" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59129,7 +59132,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2134" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59155,7 +59158,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2135" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59181,7 +59184,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2136" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59207,7 +59210,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2137" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59233,7 +59236,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2138" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59259,7 +59262,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2139" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59285,7 +59288,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2140" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59311,7 +59314,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2141" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59337,7 +59340,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2142" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59363,7 +59366,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2143" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59389,7 +59392,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2144" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59415,7 +59418,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2145" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59441,7 +59444,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2146" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59467,7 +59470,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2147" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59493,7 +59496,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2148" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59519,7 +59522,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2149" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59545,7 +59548,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2150" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59571,7 +59574,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2151" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59597,7 +59600,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2152" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59623,7 +59626,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2153" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59649,7 +59652,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2154" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59675,7 +59678,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2155" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59701,7 +59704,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2156" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59727,7 +59730,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2157" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59753,7 +59756,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2158" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59779,7 +59782,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2159" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59805,7 +59808,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2160" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59831,7 +59834,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2161" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59857,7 +59860,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2162" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59883,7 +59886,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2163" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59909,7 +59912,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2164" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59935,7 +59938,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2165" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59961,7 +59964,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G2166" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59987,7 +59990,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2167" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60013,7 +60016,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2168" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60039,7 +60042,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2169" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60065,7 +60068,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2170" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60091,7 +60094,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2171" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60117,7 +60120,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2172" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60143,7 +60146,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2173" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60169,7 +60172,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2174" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60195,7 +60198,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2175" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60221,7 +60224,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2176" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60247,7 +60250,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2177" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60273,7 +60276,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2178" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60299,7 +60302,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2179" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60325,7 +60328,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2180" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60351,7 +60354,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G2181" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60377,7 +60380,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2182" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60403,7 +60406,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2183" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60429,7 +60432,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2184" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60455,7 +60458,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2185" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60481,7 +60484,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2186" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60507,7 +60510,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2187" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60533,7 +60536,7 @@
         <v>0.195500001311302</v>
       </c>
       <c r="G2188" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60559,7 +60562,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2189" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60585,7 +60588,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2190" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60611,7 +60614,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2191" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60637,7 +60640,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2192" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60663,7 +60666,7 @@
         <v>0.194499999284744</v>
       </c>
       <c r="G2193" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60689,7 +60692,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2194" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60715,7 +60718,7 @@
         <v>0.195999994874001</v>
       </c>
       <c r="G2195" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60741,7 +60744,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2196" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60767,7 +60770,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2197" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60793,7 +60796,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2198" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60819,7 +60822,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2199" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60845,7 +60848,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2200" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60871,7 +60874,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2201" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60897,7 +60900,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2202" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60923,7 +60926,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2203" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60949,7 +60952,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2204" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60975,7 +60978,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2205" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61001,7 +61004,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2206" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61027,7 +61030,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2207" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61053,7 +61056,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2208" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61079,7 +61082,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2209" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61105,7 +61108,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2210" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61131,7 +61134,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2211" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61157,7 +61160,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2212" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61183,7 +61186,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2213" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61209,7 +61212,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2214" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61235,7 +61238,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2215" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61261,7 +61264,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2216" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61287,7 +61290,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2217" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61313,7 +61316,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2218" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61339,7 +61342,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2219" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61365,7 +61368,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2220" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61391,7 +61394,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2221" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61417,7 +61420,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2222" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61443,7 +61446,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2223" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61469,7 +61472,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2224" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61495,7 +61498,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2225" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61521,7 +61524,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2226" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61547,7 +61550,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2227" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61573,7 +61576,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2228" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61599,7 +61602,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2229" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61625,7 +61628,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2230" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61651,7 +61654,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2231" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61677,7 +61680,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2232" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61703,7 +61706,7 @@
         <v>0.197500005364418</v>
       </c>
       <c r="G2233" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61729,7 +61732,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2234" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61755,7 +61758,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2235" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61781,7 +61784,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2236" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61807,7 +61810,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2237" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61833,7 +61836,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2238" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61859,7 +61862,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2239" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61885,7 +61888,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2240" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61911,7 +61914,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2241" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61937,7 +61940,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2242" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61963,7 +61966,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2243" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61989,7 +61992,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2244" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62015,7 +62018,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2245" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62041,7 +62044,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2246" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62067,7 +62070,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2247" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62093,7 +62096,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2248" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62119,7 +62122,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62145,7 +62148,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G2250" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62171,7 +62174,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2251" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62197,7 +62200,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2252" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62223,7 +62226,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2253" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62249,7 +62252,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2254" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62275,7 +62278,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2255" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62301,7 +62304,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62327,7 +62330,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2257" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62353,7 +62356,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2258" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62379,7 +62382,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2259" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62405,7 +62408,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2260" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62431,7 +62434,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2261" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62457,7 +62460,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2262" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62483,7 +62486,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2263" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62509,7 +62512,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2264" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62535,7 +62538,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2265" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62561,7 +62564,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2266" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62587,7 +62590,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2267" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62613,7 +62616,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2268" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62639,7 +62642,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2269" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62665,7 +62668,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2270" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62691,7 +62694,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2271" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62717,7 +62720,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2272" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62743,7 +62746,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2273" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62769,7 +62772,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2274" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62795,7 +62798,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2275" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62821,7 +62824,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2276" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62847,7 +62850,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2277" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62873,7 +62876,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2278" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62899,7 +62902,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2279" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62925,7 +62928,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2280" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62951,7 +62954,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2281" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62977,7 +62980,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G2282" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63003,7 +63006,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2283" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63029,7 +63032,7 @@
         <v>0.19149999320507</v>
       </c>
       <c r="G2284" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63055,7 +63058,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2285" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63081,7 +63084,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2286" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63107,7 +63110,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2287" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63133,7 +63136,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2288" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63159,7 +63162,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2289" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63185,7 +63188,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2290" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63211,7 +63214,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G2291" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63237,7 +63240,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2292" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63263,7 +63266,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G2293" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63289,7 +63292,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2294" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63315,7 +63318,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2295" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63341,7 +63344,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2296" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63367,7 +63370,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2297" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63393,7 +63396,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2298" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63419,7 +63422,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2299" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63445,7 +63448,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2300" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63471,7 +63474,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2301" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63497,7 +63500,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2302" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63523,7 +63526,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2303" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63549,7 +63552,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2304" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63575,7 +63578,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2305" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63601,7 +63604,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2306" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63627,7 +63630,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2307" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63653,7 +63656,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2308" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63679,7 +63682,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2309" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63705,7 +63708,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2310" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63731,7 +63734,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2311" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63757,7 +63760,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2312" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63783,7 +63786,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2313" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63809,7 +63812,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2314" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63835,7 +63838,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2315" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63861,7 +63864,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2316" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63887,7 +63890,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2317" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63913,7 +63916,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2318" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63939,7 +63942,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2319" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63965,7 +63968,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2320" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63991,7 +63994,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2321" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64017,7 +64020,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2322" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64043,7 +64046,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2323" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64069,7 +64072,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2324" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64095,7 +64098,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2325" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64121,7 +64124,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2326" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64147,7 +64150,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2327" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64173,7 +64176,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2328" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64199,7 +64202,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2329" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64225,7 +64228,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2330" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64251,7 +64254,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2331" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64277,7 +64280,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2332" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64303,7 +64306,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2333" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64329,7 +64332,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2334" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64355,7 +64358,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2335" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64381,7 +64384,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2336" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64407,7 +64410,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2337" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64433,7 +64436,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2338" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64459,7 +64462,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64485,7 +64488,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2340" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64511,7 +64514,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2341" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64537,7 +64540,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2342" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64563,7 +64566,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2343" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64589,7 +64592,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2344" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64615,7 +64618,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2345" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64641,7 +64644,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2346" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64667,7 +64670,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2347" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64693,7 +64696,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64719,7 +64722,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2349" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64745,7 +64748,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2350" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64771,7 +64774,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2351" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64797,7 +64800,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2352" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64823,7 +64826,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2353" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64849,7 +64852,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G2354" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64875,7 +64878,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2355" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64901,7 +64904,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2356" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64927,7 +64930,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2357" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64953,7 +64956,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2358" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64979,7 +64982,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2359" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65005,7 +65008,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2360" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65031,7 +65034,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2361" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65057,7 +65060,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65083,7 +65086,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2363" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65109,7 +65112,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G2364" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65135,7 +65138,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2365" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65161,7 +65164,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2366" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65187,7 +65190,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2367" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65213,7 +65216,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2368" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65239,7 +65242,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2369" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65265,7 +65268,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2370" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65291,7 +65294,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2371" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65317,7 +65320,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2372" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65343,7 +65346,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2373" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65369,7 +65372,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2374" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65395,7 +65398,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2375" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65421,7 +65424,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2376" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65447,7 +65450,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2377" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65473,7 +65476,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2378" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65499,7 +65502,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2379" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65525,7 +65528,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2380" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65551,7 +65554,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2381" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65577,7 +65580,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2382" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65603,7 +65606,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2383" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65629,7 +65632,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65655,7 +65658,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2385" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65681,7 +65684,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2386" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65707,7 +65710,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2387" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65733,7 +65736,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2388" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65759,7 +65762,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2389" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65785,7 +65788,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2390" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65811,7 +65814,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2391" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65837,7 +65840,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2392" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65863,7 +65866,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2393" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65889,7 +65892,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2394" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65915,7 +65918,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2395" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65941,7 +65944,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2396" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65967,7 +65970,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2397" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65993,7 +65996,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2398" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66019,7 +66022,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2399" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66045,7 +66048,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2400" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66071,7 +66074,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2401" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66097,7 +66100,7 @@
         <v>0.172499999403954</v>
       </c>
       <c r="G2402" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66123,7 +66126,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2403" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66149,7 +66152,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2404" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66175,7 +66178,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2405" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66201,7 +66204,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2406" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66227,7 +66230,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2407" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66253,7 +66256,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2408" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66279,7 +66282,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2409" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66305,7 +66308,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2410" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66331,7 +66334,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2411" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66357,7 +66360,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2412" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66383,7 +66386,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2413" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66409,7 +66412,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2414" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66435,7 +66438,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2415" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66461,7 +66464,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2416" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66487,7 +66490,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2417" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66513,7 +66516,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2418" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66539,7 +66542,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2419" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66565,7 +66568,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2420" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66591,7 +66594,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2421" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66617,7 +66620,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2422" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66643,7 +66646,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2423" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66669,7 +66672,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2424" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66695,7 +66698,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2425" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66721,7 +66724,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2426" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66747,7 +66750,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66773,7 +66776,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2428" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66799,7 +66802,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2429" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66825,7 +66828,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2430" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66851,7 +66854,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2431" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66877,7 +66880,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2432" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66903,7 +66906,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2433" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66929,7 +66932,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66955,7 +66958,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2435" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66981,7 +66984,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2436" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67007,7 +67010,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2437" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67033,7 +67036,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2438" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67059,7 +67062,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2439" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67085,7 +67088,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2440" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67111,7 +67114,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2441" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67137,7 +67140,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2442" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67163,7 +67166,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2443" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67189,7 +67192,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67215,7 +67218,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2445" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67241,7 +67244,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2446" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67267,7 +67270,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2447" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67293,7 +67296,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2448" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67319,7 +67322,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2449" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67345,7 +67348,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2450" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67371,7 +67374,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67397,7 +67400,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2452" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67423,7 +67426,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2453" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67449,7 +67452,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2454" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67475,7 +67478,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2455" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67501,7 +67504,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2456" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67527,7 +67530,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2457" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67553,7 +67556,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2458" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67579,7 +67582,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67605,7 +67608,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2460" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67631,7 +67634,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2461" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67657,7 +67660,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2462" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67683,7 +67686,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2463" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67709,7 +67712,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2464" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67735,7 +67738,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2465" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67761,7 +67764,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2466" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67787,7 +67790,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2467" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67813,7 +67816,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2468" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67839,7 +67842,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67865,7 +67868,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2470" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67891,7 +67894,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2471" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67917,7 +67920,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2472" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67943,7 +67946,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2473" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67969,7 +67972,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2474" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67995,7 +67998,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2475" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68021,7 +68024,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2476" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68047,7 +68050,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2477" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68073,7 +68076,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2478" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68099,7 +68102,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2479" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68125,7 +68128,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2480" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68151,7 +68154,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68177,7 +68180,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2482" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68203,7 +68206,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2483" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68229,7 +68232,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2484" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68255,7 +68258,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2485" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68281,7 +68284,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2486" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68307,7 +68310,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2487" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68333,7 +68336,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68359,7 +68362,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2489" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68385,7 +68388,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2490" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68411,7 +68414,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2491" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68437,7 +68440,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2492" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68463,7 +68466,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2493" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68489,7 +68492,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2494" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68515,7 +68518,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2495" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68541,7 +68544,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68567,7 +68570,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2497" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68593,7 +68596,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2498" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68619,7 +68622,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2499" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68645,7 +68648,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2500" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68671,7 +68674,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2501" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68697,7 +68700,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2502" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68723,7 +68726,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2503" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68749,7 +68752,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2504" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68775,7 +68778,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2505" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68801,7 +68804,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G2506" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68827,7 +68830,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2507" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68853,7 +68856,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2508" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68879,7 +68882,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2509" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68905,7 +68908,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2510" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68931,7 +68934,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2511" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68957,7 +68960,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G2512" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68965,7 +68968,7 @@
     </row>
     <row r="2513">
       <c r="A2513" s="1" t="n">
-        <v>45978.6911574074</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2513" t="n">
         <v>421272</v>
@@ -68983,9 +68986,35 @@
         <v>0.157499998807907</v>
       </c>
       <c r="G2513" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H2513" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2514">
+      <c r="A2514" s="1" t="n">
+        <v>45979.6911111111</v>
+      </c>
+      <c r="B2514" t="n">
+        <v>608330</v>
+      </c>
+      <c r="C2514" t="n">
+        <v>0.158000007271767</v>
+      </c>
+      <c r="D2514" t="n">
+        <v>0.156499996781349</v>
+      </c>
+      <c r="E2514" t="n">
+        <v>0.157499998807907</v>
+      </c>
+      <c r="F2514" t="n">
+        <v>0.156499996781349</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H2514" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1102" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="1103">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053889870644</t>
+    <t xml:space="preserve">0.158053904771805</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
@@ -47,55 +47,55 @@
     <t xml:space="preserve">0.158481389284134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155000314116478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153229206800461</t>
+    <t xml:space="preserve">0.155000299215317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153229221701622</t>
   </si>
   <si>
     <t xml:space="preserve">0.150542050600052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148099184036255</t>
+    <t xml:space="preserve">0.148099198937416</t>
   </si>
   <si>
     <t xml:space="preserve">0.15029776096344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151580289006233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147366315126419</t>
+    <t xml:space="preserve">0.151580274105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14736633002758</t>
   </si>
   <si>
     <t xml:space="preserve">0.142358437180519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132831230759621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134541243314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125319391489029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131121218204498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134358033537865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419113397598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143335610628128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138022348284721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778058648109</t>
+    <t xml:space="preserve">0.132831245660782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134541258215904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12531940639019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131121203303337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134358018636703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419098496437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143335580825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13802233338356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778028845787</t>
   </si>
   <si>
     <t xml:space="preserve">0.140465199947357</t>
@@ -110,37 +110,37 @@
     <t xml:space="preserve">0.131793007254601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129166930913925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12928906083107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967913091183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754387557507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116158626973629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118479363620281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12580794095993</t>
+    <t xml:space="preserve">0.129166916012764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129289045929909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967920541763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754380106926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116158604621887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11847934871912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125807955861092</t>
   </si>
   <si>
     <t xml:space="preserve">0.125197246670723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129960834980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127029404044151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125014036893845</t>
+    <t xml:space="preserve">0.129960849881172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127029418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125014021992683</t>
   </si>
   <si>
     <t xml:space="preserve">0.130999058485031</t>
@@ -149,112 +149,112 @@
     <t xml:space="preserve">0.129105851054192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128617271780968</t>
+    <t xml:space="preserve">0.128617256879807</t>
   </si>
   <si>
     <t xml:space="preserve">0.130205139517784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130510479211807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129533335566521</t>
+    <t xml:space="preserve">0.130510523915291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
     <t xml:space="preserve">0.133808374404907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138755217194557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139671266078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136739820241928</t>
+    <t xml:space="preserve">0.138755187392235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13967128098011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136739835143089</t>
   </si>
   <si>
     <t xml:space="preserve">0.136495545506477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140159845352173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141747713088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147122025489807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149015262722969</t>
+    <t xml:space="preserve">0.140159830451012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14174772799015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147122040390968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14901527762413</t>
   </si>
   <si>
     <t xml:space="preserve">0.146572381258011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145717367529869</t>
+    <t xml:space="preserve">0.14571738243103</t>
   </si>
   <si>
     <t xml:space="preserve">0.143213450908661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144129529595375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892714262009</t>
+    <t xml:space="preserve">0.144129514694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14089272916317</t>
   </si>
   <si>
     <t xml:space="preserve">0.139793425798416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134968742728233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068031191826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135945871472359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135823726654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133136570453644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130693718791008</t>
+    <t xml:space="preserve">0.134968727827072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068016290665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13594588637352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135823741555214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133136585354805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130693733692169</t>
   </si>
   <si>
     <t xml:space="preserve">0.12886156141758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125258341431618</t>
+    <t xml:space="preserve">0.125258326530457</t>
   </si>
   <si>
     <t xml:space="preserve">0.133930519223213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137472674250603</t>
+    <t xml:space="preserve">0.137472704052925</t>
   </si>
   <si>
     <t xml:space="preserve">0.142480581998825</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142114162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141320213675499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14217521250248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138327702879906</t>
+    <t xml:space="preserve">0.14211417734623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141320198774338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142175227403641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138327687978745</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236277461052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138205528259277</t>
+    <t xml:space="preserve">0.138205543160439</t>
   </si>
   <si>
     <t xml:space="preserve">0.140526756644249</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136637181043625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133876815438271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133814081549644</t>
+    <t xml:space="preserve">0.136637166142464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133876830339432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133814096450806</t>
   </si>
   <si>
     <t xml:space="preserve">0.132998511195183</t>
@@ -290,25 +290,25 @@
     <t xml:space="preserve">0.126662284135818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126725018024445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127352371811867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127979725599289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126599535346031</t>
+    <t xml:space="preserve">0.126724988222122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127352386713028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127979710698128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126599550247192</t>
   </si>
   <si>
     <t xml:space="preserve">0.12791696190834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130489125847816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1317438185215</t>
+    <t xml:space="preserve">0.130489140748978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131743833422661</t>
   </si>
   <si>
     <t xml:space="preserve">0.131116464734077</t>
@@ -317,1123 +317,1123 @@
     <t xml:space="preserve">0.131555631756783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134065002202988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131179213523865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133688613772392</t>
+    <t xml:space="preserve">0.134065046906471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131179198622704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133688598871231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134880572557449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134190499782562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130614578723907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132873058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128481581807137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121078856289387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12020055949688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831648051739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413864254951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233176827431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366196095943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794039607048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114052511751652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395056307316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893192648888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041232943535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904471457005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354902386665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727541148663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277140021324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102822929620743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501708686352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110790275037289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554397761822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923294305801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303454756737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632182478905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116561904549599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11637370288372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746349096298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432687103748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805310964584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185516119003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569433689117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820384144783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934573113918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159156680107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088908553123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10614787787199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104140341281891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10564599186182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107465319335461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108531802892685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590802013874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535582363605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104830451309681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092680573463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029931783676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107653521001339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849259257317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978491604328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11160584539175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11373882740736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864310085773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110288389027119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225655138493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845479786396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723769128323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339844107628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406357467175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104516766965389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105018652975559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10664975643158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10583420842886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085151433945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109786532819271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104391291737556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107778988778591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214383780956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11606003344059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114742614328861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112421371042728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11342516541481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295918166637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022410094738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712505221367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837965548038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10552054643631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265816509724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760188281536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003609597683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579523205757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885641157627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889428079128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254545152187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10056446492672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101066343486309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101630948483944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106524288654327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109911985695362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539346933365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110915757715702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657278120518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112609587609768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111292168498039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410114586353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108343608677387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108280867338181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033696353436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351130366325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153701141476631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144918218255043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142408818006516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132371172308922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132684856653214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13425324857235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304681301117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134692370891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135821610689163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836654067039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855469465256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143161624670029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141781449317932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133500412106514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129861772060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130175456404686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131681114435196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13011272251606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130740076303482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842964112759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097664237022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975953578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289637923241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226904034615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126411333680153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1254703104496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126536801457405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215595424175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12597219645977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551874637604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677312612534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182955741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171699285507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132245719432831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006040334702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133939549326897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127780795097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136260747909546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943321347237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766405940056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13801734149456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777692198753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145733743906021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165396690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141154110431671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137640938162804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136762633919716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629637002945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002268314362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133437678217888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129673540592194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128356143832207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496640086174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135633409023285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137891888618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137703686952591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433906197548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132057502865791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134504169225693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134502425789833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132989719510078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131729155778885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130720719695091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133178815245628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565427899361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943619370461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131792202591896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131477057933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132359459996223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13090980052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130468621850014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129964411258698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127506271004677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129586219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002030611038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127947479486465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128199577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12870380282402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371771097183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125930562615395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127128094434738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056611537933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12479604780674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124669998884201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124165773391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125174224376678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125237256288528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129018932580948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127380222082138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128451690077782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136560320854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884447574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443239092827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126939013600349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128262624144554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126875996589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126497805118561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126308739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133430927991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135573908686638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135762974619865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136456295847893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135636910796165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134061217308044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132485494017601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133556991815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135195732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136141151189804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134439378976822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137464746832848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137716859579086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138221070170403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137842923402786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136330232024193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137086570262909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136771410703659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136204168200493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13500665128231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134754538536072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13506968319416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137401714920998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15114189684391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153789088129997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152780622243881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267945766449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145280256867409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14704504609108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444730401039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159398600459099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156625345349312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157570779323578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152843654155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152654573321342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151898220181465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15309576690197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150259479880333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746818304062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15334789454937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805990099907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419362545013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156940475106239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15914648771286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167655304074287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050397515297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16721411049366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067299485207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945811629295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811281919479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175218716263771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336299300194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176461338997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479279994965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173642978072166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170365527272224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166205644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222576379776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168600752949715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166520789265633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166394725441933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161730647087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160091906785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156688392162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161226436495781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162487000226974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163747549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873597979546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161037340760231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158011972904205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157759875059128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970448732376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167718335986137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165260225534439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163117274641991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163810566067696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159461617469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147675335407257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147486239671707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150007382035255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150448590517044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511607527733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151078879833221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151646122336388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150322526693344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494705557823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15082673728466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151772156357765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881318211555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583090424538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149629220366478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709139347076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15101583302021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148935914039612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148116543889046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150763720273972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150637656450272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151204898953438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149944350123405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213379740715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528509497643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149377107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15725564956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156310215592384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164503902196884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243338465691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162613034248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982759833336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163558468222618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165764465928078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165449306368828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079610586166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160722196102142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162297904491425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061948060989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14717110991478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146540805697441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146225675940514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142759129405022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334837794304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140238001942635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139607712626457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138032004237175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139922842383385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135826006531715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138347163796425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813695430756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140553131699562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141183435916901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138662293553352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135510861873627</t>
   </si>
   <si>
     <t xml:space="preserve">0.134880587458611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134190499782562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130614578723907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132873058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128481596708298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121078848838806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12020055949688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831677854061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413864254951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233184278011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366196095943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794032156467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052511751652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395071208477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893170297146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041232943535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904464006424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354894936085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727541148663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277102768421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102822929620743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501716136932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716262340546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11079028993845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11292327195406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303439855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632182478905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116561904549599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116373710334301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746363997459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432694554329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805340766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185523569584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569433689117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820376694202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934573113918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10915918648243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088908553123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10614787787199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104140356183052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10564599186182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107465319335461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108531817793846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535560011864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104830428957939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092665672302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029924333096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653513550758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849274158478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978491604328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111605830490589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738842308521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864302635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11028841137886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225655138493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845487236977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723769128323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339851558208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406350016594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104516759514809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105018638074398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10664976388216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105834193527699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085151433945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10978651791811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104391306638718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107779011130333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214368879795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116060040891171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114742606878281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11242139339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425150513649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295925617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022417545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712505221367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837965548038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520531535149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265823960304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760173380375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003602147102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579515755177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885648608208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889420628548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254537701607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10056446492672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101066328585148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101630948483944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106524288654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109912000596523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539346933365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110915757715702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657285571098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112609587609768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111292153596878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410114586353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108343601226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108280874788761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033696353436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351130366325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15370112657547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144918203353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142408803105354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132684856653214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134253233671188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304681301117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13469235599041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135821610689163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836654067039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855469465256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143161624670029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141781464219093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133500397205353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129861772060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130175456404686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131681099534035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130112707614899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130740091204643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842956662178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097664237022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975953578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289637923241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226904034615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126411348581314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1254703104496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126536801457405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215595424175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12597219645977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551859736443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677312612534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182970643044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171669483185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13224570453167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006055235863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133939549326897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127765893936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136260747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943321347237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766420841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138017356395721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777692198753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145733773708344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144165396690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14397719502449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14115409553051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137640938162804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136762633919716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629637002945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002283215523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133437678217888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129673570394516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128356128931046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496640086174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135633409023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137891873717308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13770367205143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433906197548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13205748796463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134504154324532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134502410888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132989749312401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131729155778885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130720719695091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13317883014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565442800522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943604469299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131792202591896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131477057933807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132359445095062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13090980052948</t>
+    <t xml:space="preserve">0.134250313043594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935153484344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132674604654312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143074259161949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14496511220932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443984746933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575853228569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864416241646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146253705024719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14560940861702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455082058907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142710089683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141421526670456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13916651904583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777230262756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139488652348518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135622933506966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133690059185028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13272362947464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13207933306694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129824310541153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125765293836594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124992147088051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126796141266823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129180014133453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133367925882339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131757184863091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125894144177437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126925006508827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125378713011742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128600150346756</t>
   </si>
   <si>
     <t xml:space="preserve">0.130468606948853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129964396357536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127506285905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129586189985275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002060413361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127947479486465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128199577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12870380282402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125930562615395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127128094434738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056626439095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479604780674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12466999143362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124165758490562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12517423927784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125237241387367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129018947482109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127380207180977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128451690077782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136560320854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884447574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443239092827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126939013600349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128262609243393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126875996589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126308724284172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133430927991867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135573893785477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135762959718704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136456295847893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135636925697327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134061217308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132485523819923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133556976914406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135195732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136141180992126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134439378976822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137464746832848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137716874480247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138221070170403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137842938303947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136330232024193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13708658516407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13677142560482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136204198002815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006636381149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134754538536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13506968319416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137401714920998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151141881942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153789088129997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152780637145042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151267930865288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145280256867409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147045060992241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444715499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15939861536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156625360250473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157570779323578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152843654155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152654573321342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151898235082626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153095752000809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150259494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148746818304062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153347879648209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805975198746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419362545013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156940490007401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15914648771286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167655318975449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050397515297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16721411049366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067284584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17521870136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336299300194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176476240158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479279994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173642978072166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170365542173386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166205659508705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222561478615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168600723147392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166520819067955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166394725441933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161730661988258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160091921687126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156688377261162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16122642159462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162487000226974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163747534155846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873597979546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16103732585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158011972904205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157759860157967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970433831215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167718321084976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1652602404356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163117274641991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163810566067696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159461632370949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147675335407257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147486239671707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150007382035255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150448575615883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511607527733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15107886493206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151646122336388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150322526693344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494690656662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150826752185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151772156357765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881303310394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583090424538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149629205465317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709154248238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151015818119049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148935928940773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148116528987885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150763720273972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150637656450272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151204913854599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149944335222244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213364839554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1493771225214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15725564956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156310215592384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164503887295723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243338465691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613034248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982759833336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163558468222618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165764480829239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165449321269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079595685005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160722196102142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162297874689102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061962962151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14717110991478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146540820598602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146225661039352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142759144306183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334837794304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140237987041473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139607682824135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138031989336014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139922842383385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135825991630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138347148895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498550772667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813695430756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140553131699562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141183421015739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138662293553352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135510876774788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250298142433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935153484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132674589753151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14307427406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443999648094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575838327408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864431142807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14496511220932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146253690123558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14560940861702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455067157745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142710089683533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141421511769295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139166533946991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139488652348518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135622918605804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133690059185028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132723599672318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13207933306694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129824325442314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125765278935432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124992154538631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126796141266823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129180014133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133367910981178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131757184863091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125894159078598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126924991607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125378727912903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128600150346756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130468592047691</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.127440437674522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127955883741379</t>
+    <t xml:space="preserve">0.127955868840218</t>
   </si>
   <si>
     <t xml:space="preserve">0.127827003598213</t>
@@ -1442,13 +1442,13 @@
     <t xml:space="preserve">0.126023009419441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124347843229771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703554272652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127311587333679</t>
+    <t xml:space="preserve">0.124347850680351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703576624393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127311572432518</t>
   </si>
   <si>
     <t xml:space="preserve">0.127569288015366</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">0.12666729092598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126538455486298</t>
+    <t xml:space="preserve">0.126538440585136</t>
   </si>
   <si>
     <t xml:space="preserve">0.12872901558876</t>
@@ -1472,82 +1472,82 @@
     <t xml:space="preserve">0.130146458745003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134012207388878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134656473994255</t>
+    <t xml:space="preserve">0.134012192487717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134656488895416</t>
   </si>
   <si>
     <t xml:space="preserve">0.138522207736969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13820007443428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300770401955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130790755152702</t>
+    <t xml:space="preserve">0.138200059533119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300785303116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130790770053864</t>
   </si>
   <si>
     <t xml:space="preserve">0.128084719181061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128857880830765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125249832868576</t>
+    <t xml:space="preserve">0.128857865929604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125249862670898</t>
   </si>
   <si>
     <t xml:space="preserve">0.122157268226147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12331698089838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125507563352585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128213599324226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126151859760284</t>
+    <t xml:space="preserve">0.123316995799541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125507578253746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128213584423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126151874661446</t>
   </si>
   <si>
     <t xml:space="preserve">0.127182722091675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125636428594589</t>
+    <t xml:space="preserve">0.125636413693428</t>
   </si>
   <si>
     <t xml:space="preserve">0.120482131838799</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122286111116409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122414998710155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260657250881</t>
+    <t xml:space="preserve">0.12228611856699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122414991259575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260672152042</t>
   </si>
   <si>
     <t xml:space="preserve">0.113266080617905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113394923508167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848652362823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11210636049509</t>
+    <t xml:space="preserve">0.113394930958748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848644912243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112106345593929</t>
   </si>
   <si>
     <t xml:space="preserve">0.114425793290138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114683531224728</t>
+    <t xml:space="preserve">0.114683516323566</t>
   </si>
   <si>
     <t xml:space="preserve">0.112235210835934</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">0.110817782580853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108240634202957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565460562706</t>
+    <t xml:space="preserve">0.108240619301796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565468013287</t>
   </si>
   <si>
     <t xml:space="preserve">0.105921179056168</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">0.10501916706562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103086277842522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374885559082</t>
+    <t xml:space="preserve">0.103086292743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374893009663</t>
   </si>
   <si>
     <t xml:space="preserve">0.104117155075073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10566346347332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107982903718948</t>
+    <t xml:space="preserve">0.105663456022739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107982896268368</t>
   </si>
   <si>
     <t xml:space="preserve">0.108627185225487</t>
@@ -1592,16 +1592,16 @@
     <t xml:space="preserve">0.108111768960953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111462064087391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750634551048</t>
+    <t xml:space="preserve">0.11146204918623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750649452209</t>
   </si>
   <si>
     <t xml:space="preserve">0.108756050467491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110173478722572</t>
+    <t xml:space="preserve">0.110173493623734</t>
   </si>
   <si>
     <t xml:space="preserve">0.109529197216034</t>
@@ -1613,19 +1613,19 @@
     <t xml:space="preserve">0.101153440773487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10398830473423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699726819992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105276882648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111204348504543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115585520863533</t>
+    <t xml:space="preserve">0.103988319635391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699741721153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105276875197887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111204341053963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115585513412952</t>
   </si>
   <si>
     <t xml:space="preserve">0.1158432289958</t>
@@ -1634,37 +1634,37 @@
     <t xml:space="preserve">0.115327805280685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113008365035057</t>
+    <t xml:space="preserve">0.113008357584476</t>
   </si>
   <si>
     <t xml:space="preserve">0.10940033942461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11043119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107854038476944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730589151382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10630775988102</t>
+    <t xml:space="preserve">0.110431186854839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107854045927525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730604052544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106307744979858</t>
   </si>
   <si>
     <t xml:space="preserve">0.103859454393387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114554658532143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109142638742924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013758599758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884915709496</t>
+    <t xml:space="preserve">0.114554651081562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109142631292343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013773500919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884893357754</t>
   </si>
   <si>
     <t xml:space="preserve">0.109271481633186</t>
@@ -1673,10 +1673,10 @@
     <t xml:space="preserve">0.107338614761829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102442011237144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411148905754</t>
+    <t xml:space="preserve">0.102442026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411156356335</t>
   </si>
   <si>
     <t xml:space="preserve">0.102055430412292</t>
@@ -1688,67 +1688,67 @@
     <t xml:space="preserve">0.0999937206506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10128229111433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797729730606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766859948635</t>
+    <t xml:space="preserve">0.10128228366375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797744631767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766867399216</t>
   </si>
   <si>
     <t xml:space="preserve">0.105148032307625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109915763139725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11107549071312</t>
+    <t xml:space="preserve">0.109915770590305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111075505614281</t>
   </si>
   <si>
     <t xml:space="preserve">0.112621776759624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110302336513996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11068893969059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761451482773</t>
+    <t xml:space="preserve">0.110302351415157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761444032192</t>
   </si>
   <si>
     <t xml:space="preserve">0.105534598231316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107467480003834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108498334884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080891728401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503735899925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792328715324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436595320702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105341300368309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596322894096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562774956226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207049012184</t>
+    <t xml:space="preserve">0.107467487454414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108498342335224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080884277821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503720998764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792313814163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436610221863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105341322720051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596315443516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562767505646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207026660442</t>
   </si>
   <si>
     <t xml:space="preserve">0.110185064375401</t>
@@ -1757,91 +1757,91 @@
     <t xml:space="preserve">0.109857141971588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11116886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110513009130955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889540493488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106905750930309</t>
+    <t xml:space="preserve">0.111168839037418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110513001680374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889533042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10690575838089</t>
   </si>
   <si>
     <t xml:space="preserve">0.10592196136713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10395435988903</t>
+    <t xml:space="preserve">0.103954374790192</t>
   </si>
   <si>
     <t xml:space="preserve">0.104282289743423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105594031512737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217485249043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266079306602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10493815690279</t>
+    <t xml:space="preserve">0.105594024062157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217470347881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104938149452209</t>
   </si>
   <si>
     <t xml:space="preserve">0.102970570325851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103626452386379</t>
+    <t xml:space="preserve">0.103626444935799</t>
   </si>
   <si>
     <t xml:space="preserve">0.103298500180244</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101658843457699</t>
+    <t xml:space="preserve">0.101658850908279</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347101688385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330906152725</t>
+    <t xml:space="preserve">0.101330913603306</t>
   </si>
   <si>
     <t xml:space="preserve">0.0970677956938744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0977236554026604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957255482674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951002016663551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0980515852570534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0964119136333466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0987074449658394</t>
+    <t xml:space="preserve">0.097723662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957180976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951002091169357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098051592707634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0964119285345078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09870745241642</t>
   </si>
   <si>
     <t xml:space="preserve">0.0993633195757866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100019179284573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002976298332</t>
+    <t xml:space="preserve">0.100019186735153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002968847752</t>
   </si>
   <si>
     <t xml:space="preserve">0.100675046443939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102642633020878</t>
+    <t xml:space="preserve">0.102642625570297</t>
   </si>
   <si>
     <t xml:space="preserve">0.098379522562027</t>
@@ -1856,55 +1856,55 @@
     <t xml:space="preserve">0.104610227048397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107561610639095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108873330056667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545415103436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109201282262802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107233680784702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249883770943</t>
+    <t xml:space="preserve">0.107561603188515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108873337507248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545385301113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109201274812222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107233673334122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249891221523</t>
   </si>
   <si>
     <t xml:space="preserve">0.11215265840292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114448189735413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111824721097946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808518111706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113136455416679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480595707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496798694134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130516842007637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139698922634125</t>
+    <t xml:space="preserve">0.114448174834251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111824728548527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808525562286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113136447966099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480588257313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496776342392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130516827106476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139698937535286</t>
   </si>
   <si>
     <t xml:space="preserve">0.132484436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141010656952858</t>
+    <t xml:space="preserve">0.141010642051697</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686552524567</t>
@@ -1916,22 +1916,22 @@
     <t xml:space="preserve">0.16724519431591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155439630150795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150848597288132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154127910733223</t>
+    <t xml:space="preserve">0.155439659953117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150848612189293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154127925634384</t>
   </si>
   <si>
     <t xml:space="preserve">0.157407224178314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156751364469528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152816191315651</t>
+    <t xml:space="preserve">0.156751379370689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152816206216812</t>
   </si>
   <si>
     <t xml:space="preserve">0.148881003260612</t>
@@ -1946,10 +1946,10 @@
     <t xml:space="preserve">0.146913424134254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150192737579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149536862969398</t>
+    <t xml:space="preserve">0.150192752480507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14953687787056</t>
   </si>
   <si>
     <t xml:space="preserve">0.142978236079216</t>
@@ -1967,67 +1967,67 @@
     <t xml:space="preserve">0.161342427134514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141666531562805</t>
+    <t xml:space="preserve">0.141666501760483</t>
   </si>
   <si>
     <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135107889771461</t>
+    <t xml:space="preserve">0.1351078748703</t>
   </si>
   <si>
     <t xml:space="preserve">0.133140295743942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137731328606606</t>
+    <t xml:space="preserve">0.137731343507767</t>
   </si>
   <si>
     <t xml:space="preserve">0.15478378534317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156095504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153472036123276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131828561425209</t>
+    <t xml:space="preserve">0.156095519661903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153472051024437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13182857632637</t>
   </si>
   <si>
     <t xml:space="preserve">0.135763749480247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137075483798981</t>
+    <t xml:space="preserve">0.13707546889782</t>
   </si>
   <si>
     <t xml:space="preserve">0.125597849488258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126581639051437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123958192765713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118711277842522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110840924084187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0967398509383202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0826388075947762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0878857150673866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08722984790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0885415747761726</t>
+    <t xml:space="preserve">0.126581653952599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123958207666874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118711292743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110840916633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0967398434877396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.082638792693615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0878857001662254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0872298404574394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0885415822267532</t>
   </si>
   <si>
     <t xml:space="preserve">0.0911650210618973</t>
@@ -2039,13 +2039,13 @@
     <t xml:space="preserve">0.0928046852350235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0944443270564079</t>
+    <t xml:space="preserve">0.0944443345069885</t>
   </si>
   <si>
     <t xml:space="preserve">0.0960839986801147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0931326076388359</t>
+    <t xml:space="preserve">0.0931326225399971</t>
   </si>
   <si>
     <t xml:space="preserve">0.0957560613751411</t>
@@ -2057,49 +2057,49 @@
     <t xml:space="preserve">0.0965431109070778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0969366207718849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0978548377752304</t>
+    <t xml:space="preserve">0.0969366058707237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0978548228740692</t>
   </si>
   <si>
     <t xml:space="preserve">0.0971989706158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0924767404794693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.094050832092762</t>
+    <t xml:space="preserve">0.0924767479300499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0940508246421814</t>
   </si>
   <si>
     <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0941819995641708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0949690267443657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937338829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740633904934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0968054458498955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0966742783784866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709764063358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0979859903454781</t>
+    <t xml:space="preserve">0.0941820070147514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0949690341949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937189817429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483550906181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740641355515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0968054533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0966742858290672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709749162197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0979859977960587</t>
   </si>
   <si>
     <t xml:space="preserve">0.0991665571928024</t>
@@ -2108,40 +2108,40 @@
     <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0948378667235374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102183528244495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999535843729973</t>
+    <t xml:space="preserve">0.0948378592729568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084774196148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102183520793915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999535918235779</t>
   </si>
   <si>
     <t xml:space="preserve">0.10323291271925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104806981980801</t>
+    <t xml:space="preserve">0.10480697453022</t>
   </si>
   <si>
     <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125925779342651</t>
+    <t xml:space="preserve">0.125925794243813</t>
   </si>
   <si>
     <t xml:space="preserve">0.138387188315392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142322361469269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137403398752213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135435819625854</t>
+    <t xml:space="preserve">0.14232237637043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137403413653374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135435804724693</t>
   </si>
   <si>
     <t xml:space="preserve">0.136419609189034</t>
@@ -2150,34 +2150,34 @@
     <t xml:space="preserve">0.134452015161514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134124085307121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131041526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127893373370171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134779945015907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131172716617584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130779162049294</t>
+    <t xml:space="preserve">0.13412407040596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131041511893272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127893358469009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134779959917068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131172686815262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130779176950455</t>
   </si>
   <si>
     <t xml:space="preserve">0.130123302340508</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129336267709732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130385667085648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131500646471977</t>
+    <t xml:space="preserve">0.129336282610893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130385652184486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131500616669655</t>
   </si>
   <si>
     <t xml:space="preserve">0.130910351872444</t>
@@ -2189,40 +2189,40 @@
     <t xml:space="preserve">0.129992142319679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975178718567</t>
+    <t xml:space="preserve">0.126975163817406</t>
   </si>
   <si>
     <t xml:space="preserve">0.127631038427353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128549247980118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133796155452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132156476378441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130648016929626</t>
+    <t xml:space="preserve">0.128549218177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133796140551567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132156491279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130648031830788</t>
   </si>
   <si>
     <t xml:space="preserve">0.129205107688904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129598617553711</t>
+    <t xml:space="preserve">0.129598632454872</t>
   </si>
   <si>
     <t xml:space="preserve">0.140026852488518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1297297924757</t>
+    <t xml:space="preserve">0.129729807376862</t>
   </si>
   <si>
     <t xml:space="preserve">0.12986096739769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130254492163658</t>
+    <t xml:space="preserve">0.130254477262497</t>
   </si>
   <si>
     <t xml:space="preserve">0.129073932766914</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">0.125138744711876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124614045023918</t>
+    <t xml:space="preserve">0.124614059925079</t>
   </si>
   <si>
     <t xml:space="preserve">0.143634095788002</t>
@@ -2243,10 +2243,10 @@
     <t xml:space="preserve">0.139370992779732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136091664433479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138059258460999</t>
+    <t xml:space="preserve">0.136091679334641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13805927336216</t>
   </si>
   <si>
     <t xml:space="preserve">0.136747524142265</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">0.142650306224823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141994446516037</t>
+    <t xml:space="preserve">0.141994431614876</t>
   </si>
   <si>
     <t xml:space="preserve">0.144289955496788</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">0.152488261461258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157079294323921</t>
+    <t xml:space="preserve">0.157079309225082</t>
   </si>
   <si>
     <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153144121170044</t>
+    <t xml:space="preserve">0.153144136071205</t>
   </si>
   <si>
     <t xml:space="preserve">0.155111700296402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155767574906349</t>
+    <t xml:space="preserve">0.15576758980751</t>
   </si>
   <si>
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702762961388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162982076406479</t>
+    <t xml:space="preserve">0.159702748060226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16298209130764</t>
   </si>
   <si>
     <t xml:space="preserve">0.166917249560356</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">0.163310021162033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162326216697693</t>
+    <t xml:space="preserve">0.162326201796532</t>
   </si>
   <si>
     <t xml:space="preserve">0.16101448237896</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">0.15904688835144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159374833106995</t>
+    <t xml:space="preserve">0.159374818205833</t>
   </si>
   <si>
     <t xml:space="preserve">0.158718958497047</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">0.160030692815781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158063098788261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165341436862946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163571178913116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162863075733185</t>
+    <t xml:space="preserve">0.1580630838871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165341451764107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163571193814278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162863090634346</t>
   </si>
   <si>
     <t xml:space="preserve">0.16250903904438</t>
@@ -2351,19 +2351,19 @@
     <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162154987454414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158968538045883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160384744405746</t>
+    <t xml:space="preserve">0.162155002355576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158968523144722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160384729504585</t>
   </si>
   <si>
     <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15755233168602</t>
+    <t xml:space="preserve">0.157552346587181</t>
   </si>
   <si>
     <t xml:space="preserve">0.161800920963287</t>
@@ -2372,25 +2372,25 @@
     <t xml:space="preserve">0.155073970556259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153303727507591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155782088637352</t>
+    <t xml:space="preserve">0.15330371260643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155782073736191</t>
   </si>
   <si>
     <t xml:space="preserve">0.151533484458923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15259562432766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154719948768616</t>
+    <t xml:space="preserve">0.152595609426498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154719933867455</t>
   </si>
   <si>
     <t xml:space="preserve">0.155428037047386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156844228506088</t>
+    <t xml:space="preserve">0.156844213604927</t>
   </si>
   <si>
     <t xml:space="preserve">0.156490176916122</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011815786362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156136140227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152241587638855</t>
+    <t xml:space="preserve">0.154011830687523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156136125326157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152241572737694</t>
   </si>
   <si>
     <t xml:space="preserve">0.154365882277489</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">0.151887521147728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151179417967796</t>
+    <t xml:space="preserve">0.151179432868958</t>
   </si>
   <si>
     <t xml:space="preserve">0.15011727809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150825381278992</t>
+    <t xml:space="preserve">0.150825396180153</t>
   </si>
   <si>
     <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150471314787865</t>
+    <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
     <t xml:space="preserve">0.149055138230324</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">0.145514637231827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148347035050392</t>
+    <t xml:space="preserve">0.148347049951553</t>
   </si>
   <si>
     <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152949690818787</t>
+    <t xml:space="preserve">0.152949675917625</t>
   </si>
   <si>
     <t xml:space="preserve">0.145160585641861</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">0.146576792001724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144452482461929</t>
+    <t xml:space="preserve">0.144452467560768</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
@@ -2486,10 +2486,10 @@
     <t xml:space="preserve">0.147992983460426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16569547355175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168527871370316</t>
+    <t xml:space="preserve">0.165695488452911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168527901172638</t>
   </si>
   <si>
     <t xml:space="preserve">0.167111694812775</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">0.167465731501579</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16498738527298</t>
+    <t xml:space="preserve">0.164987400174141</t>
   </si>
   <si>
     <t xml:space="preserve">0.163217127323151</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167021751403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161695286631584</t>
+    <t xml:space="preserve">0.167021736502647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161695301532745</t>
   </si>
   <si>
     <t xml:space="preserve">0.161314830183983</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">0.158271163702011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160934373736382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162836685776711</t>
+    <t xml:space="preserve">0.160934388637543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2546,13 +2546,13 @@
     <t xml:space="preserve">0.163597598671913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162456229329109</t>
+    <t xml:space="preserve">0.162456214427948</t>
   </si>
   <si>
     <t xml:space="preserve">0.159032076597214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159412547945976</t>
+    <t xml:space="preserve">0.159412562847137</t>
   </si>
   <si>
     <t xml:space="preserve">0.16017347574234</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">0.170065402984619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157129779458046</t>
+    <t xml:space="preserve">0.157129794359207</t>
   </si>
   <si>
     <t xml:space="preserve">0.15789070725441</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">0.153705656528473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14427025616169</t>
+    <t xml:space="preserve">0.144270241260529</t>
   </si>
   <si>
     <t xml:space="preserve">0.14777047932148</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">0.157510250806808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164738982915878</t>
+    <t xml:space="preserve">0.164738968014717</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">0.167402192950249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168543562293053</t>
+    <t xml:space="preserve">0.168543547391891</t>
   </si>
   <si>
     <t xml:space="preserve">0.173869997262955</t>
@@ -3318,6 +3318,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.157499998807907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156000003218651</t>
   </si>
 </sst>
 </file>
@@ -18494,7 +18497,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G571" t="s">
-        <v>104</v>
+        <v>438</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18520,7 +18523,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G572" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18546,7 +18549,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G573" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18572,7 +18575,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G574" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18598,7 +18601,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G575" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18624,7 +18627,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18858,7 +18861,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18884,7 +18887,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G586" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18936,7 +18939,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G588" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19040,7 +19043,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G592" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19066,7 +19069,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G593" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19092,7 +19095,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G594" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19118,7 +19121,7 @@
         <v>0.229499995708466</v>
       </c>
       <c r="G595" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19144,7 +19147,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -68994,7 +68997,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6911111111</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>608330</v>
@@ -69015,6 +69018,32 @@
         <v>1096</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6913194444</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>391269</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.156000003218651</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.158999994397163</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.156000003218651</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053889870644</t>
+    <t xml:space="preserve">0.158053860068321</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481389284134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155000299215317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153229206800461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150542080402374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148099184036255</t>
+    <t xml:space="preserve">0.158481374382973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155000314116478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153229221701622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150542050600052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148099198937416</t>
   </si>
   <si>
     <t xml:space="preserve">0.15029776096344</t>
@@ -65,37 +65,37 @@
     <t xml:space="preserve">0.151580289006233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147366300225258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358422279358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132831230759621</t>
+    <t xml:space="preserve">0.147366344928741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142358407378197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132831215858459</t>
   </si>
   <si>
     <t xml:space="preserve">0.134541258215904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125319391489029</t>
+    <t xml:space="preserve">0.12531940639019</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121218204498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134358033537865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419098496437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143335580825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13802233338356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778043746948</t>
+    <t xml:space="preserve">0.134358018636703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419113397598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143335610628128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138022318482399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778058648109</t>
   </si>
   <si>
     <t xml:space="preserve">0.140465214848518</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136190190911293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131793007254601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129166916012764</t>
+    <t xml:space="preserve">0.136190176010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131792992353439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129166930913925</t>
   </si>
   <si>
     <t xml:space="preserve">0.12928906083107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118967927992344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754372656345</t>
+    <t xml:space="preserve">0.118967935442924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754365205765</t>
   </si>
   <si>
     <t xml:space="preserve">0.116158612072468</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">0.118479363620281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125807985663414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125197246670723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960849881172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12702938914299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125014021992683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999058485031</t>
+    <t xml:space="preserve">0.125807970762253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125197231769562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960864782333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127029418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125014036893845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999073386192</t>
   </si>
   <si>
     <t xml:space="preserve">0.129105851054192</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">0.128617271780968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130205139517784</t>
+    <t xml:space="preserve">0.130205154418945</t>
   </si>
   <si>
     <t xml:space="preserve">0.130510494112968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129533365368843</t>
+    <t xml:space="preserve">0.129533335566521</t>
   </si>
   <si>
     <t xml:space="preserve">0.133808389306068</t>
@@ -170,19 +170,19 @@
     <t xml:space="preserve">0.139671266078949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136739820241928</t>
+    <t xml:space="preserve">0.13673985004425</t>
   </si>
   <si>
     <t xml:space="preserve">0.136495530605316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140159830451012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141747742891312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147122025489807</t>
+    <t xml:space="preserve">0.140159845352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141747698187828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147122040390968</t>
   </si>
   <si>
     <t xml:space="preserve">0.14901527762413</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">0.146572381258011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14571738243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1432134360075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144129529595375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892714262009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139793425798416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968742728233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068060994148</t>
+    <t xml:space="preserve">0.145717367529869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143213450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144129499793053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140892699360847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139793410897255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968727827072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068046092987</t>
   </si>
   <si>
     <t xml:space="preserve">0.13594588637352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135823741555214</t>
+    <t xml:space="preserve">0.135823756456375</t>
   </si>
   <si>
     <t xml:space="preserve">0.133136585354805</t>
@@ -224,58 +224,58 @@
     <t xml:space="preserve">0.130693718791008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128861531615257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125258326530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133930534124374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137472689151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142480581998825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142114147543907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14132022857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142175242304802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138327687978745</t>
+    <t xml:space="preserve">0.128861546516418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125258311629295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133930519223213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137472674250603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142480567097664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142114132642746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141320198774338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142175227403641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138327673077583</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236277461052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1382055580616</t>
+    <t xml:space="preserve">0.138205543160439</t>
   </si>
   <si>
     <t xml:space="preserve">0.140526756644249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139899387955666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136135265231133</t>
+    <t xml:space="preserve">0.139899402856827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
     <t xml:space="preserve">0.136637166142464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133876815438271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133814081549644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132998526096344</t>
+    <t xml:space="preserve">0.133876785635948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133814096450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132998540997505</t>
   </si>
   <si>
     <t xml:space="preserve">0.129234418272972</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">0.128732532262802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125156611204147</t>
+    <t xml:space="preserve">0.125156626105309</t>
   </si>
   <si>
     <t xml:space="preserve">0.126662284135818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126725003123283</t>
+    <t xml:space="preserve">0.126725018024445</t>
   </si>
   <si>
     <t xml:space="preserve">0.127352371811867</t>
@@ -305,22 +305,22 @@
     <t xml:space="preserve">0.127916976809502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130489140748978</t>
+    <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
     <t xml:space="preserve">0.1317438185215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131116464734077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131555616855621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134065046906471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131179213523865</t>
+    <t xml:space="preserve">0.131116479635239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131555631756783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134065017104149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131179183721542</t>
   </si>
   <si>
     <t xml:space="preserve">0.133688613772392</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">0.134880572557449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134190499782562</t>
+    <t xml:space="preserve">0.13419046998024</t>
   </si>
   <si>
     <t xml:space="preserve">0.130614593625069</t>
@@ -341,58 +341,58 @@
     <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121078856289387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120200552046299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831677854061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413886606693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233176827431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366196095943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794039607048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052504301071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395063757896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893177747726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041225492954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904493808746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354902386665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727548599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277117669582</t>
+    <t xml:space="preserve">0.121078841388226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120200574398041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831670403481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413871705532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233184278011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366181194782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794054508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114052496850491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395048856735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893185198307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041218042374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904456555843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354880034924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727556049824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277110219002</t>
   </si>
   <si>
     <t xml:space="preserve">0.102822929620743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100501723587513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716247439384</t>
+    <t xml:space="preserve">0.100501716136932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
   </si>
   <si>
     <t xml:space="preserve">0.110790282487869</t>
@@ -401,49 +401,49 @@
     <t xml:space="preserve">0.114554397761822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112923294305801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303447306156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632189929485</t>
+    <t xml:space="preserve">0.11292327940464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303462207317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632175028324</t>
   </si>
   <si>
     <t xml:space="preserve">0.116561912000179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116373710334301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746363997459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432687103748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805333316326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185516119003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569441139698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820369243622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934565663338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159179031849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088886201382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10614787042141</t>
+    <t xml:space="preserve">0.116373687982559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746349096298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432679653168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805318415165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185501217842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569448590279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820406496525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934558212757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159171581268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088893651962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10614787787199</t>
   </si>
   <si>
     <t xml:space="preserve">0.104140348732471</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">0.105646006762981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10746531188488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108531802892685</t>
+    <t xml:space="preserve">0.107465319335461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108531817793846</t>
   </si>
   <si>
     <t xml:space="preserve">0.107590794563293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109535597264767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1048304438591</t>
+    <t xml:space="preserve">0.109535574913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10483043640852</t>
   </si>
   <si>
     <t xml:space="preserve">0.108092665672302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108029939234257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10765352845192</t>
+    <t xml:space="preserve">0.108029931783676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107653521001339</t>
   </si>
   <si>
     <t xml:space="preserve">0.109849259257317</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.110978499054909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11160583794117</t>
+    <t xml:space="preserve">0.111605830490589</t>
   </si>
   <si>
     <t xml:space="preserve">0.113738834857941</t>
@@ -491,58 +491,58 @@
     <t xml:space="preserve">0.113864310085773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11028841137886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225640237331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845509588718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723769128323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339844107628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406350016594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10451677441597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105018652975559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106649771332741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105834200978279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085158884525</t>
+    <t xml:space="preserve">0.110288396477699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225670039654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845479786396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723791480064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406342566013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104516766965389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10501866042614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10664976388216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105834193527699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085143983364</t>
   </si>
   <si>
     <t xml:space="preserve">0.10978652536869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104391299188137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107779003679752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214383780956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116060025990009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114742591977119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11242138594389</t>
+    <t xml:space="preserve">0.104391284286976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107778996229172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214391231537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060040891171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114742606878281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11242139339447</t>
   </si>
   <si>
     <t xml:space="preserve">0.113425150513649</t>
@@ -551,52 +551,52 @@
     <t xml:space="preserve">0.112295925617218</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106022402644157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712505221367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1068379804492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520524084568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265823960304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760203182697</t>
+    <t xml:space="preserve">0.106022410094738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712482869625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520531535149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265831410885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760188281536</t>
   </si>
   <si>
     <t xml:space="preserve">0.101003594696522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104579493403435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885663509369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889420628548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254537701607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100564450025558</t>
+    <t xml:space="preserve">0.104579515755177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885648608208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889428079128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254545152187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100564442574978</t>
   </si>
   <si>
     <t xml:space="preserve">0.101066328585148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101630955934525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106524288654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109911993145943</t>
+    <t xml:space="preserve">0.101630963385105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106524296104908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109912000596523</t>
   </si>
   <si>
     <t xml:space="preserve">0.110539346933365</t>
@@ -605,67 +605,67 @@
     <t xml:space="preserve">0.110915742814541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108657278120518</t>
+    <t xml:space="preserve">0.108657285571098</t>
   </si>
   <si>
     <t xml:space="preserve">0.112609602510929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111292146146297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410107135773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108343616127968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108280867338181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033703804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351130366325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544345498085</t>
+    <t xml:space="preserve">0.111292153596878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410114586353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108343608677387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108280897140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033711254597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351137816906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544360399246</t>
   </si>
   <si>
     <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144918203353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142408803105354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132371187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132684826850891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134253218770027</t>
+    <t xml:space="preserve">0.144918218255043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142408788204193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132371172308922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132684841752052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13425324857235</t>
   </si>
   <si>
     <t xml:space="preserve">0.131304666399956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134692385792732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135821595788002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836654067039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855469465256</t>
+    <t xml:space="preserve">0.134692370891571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135821610689163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836639165878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855454564095</t>
   </si>
   <si>
     <t xml:space="preserve">0.143161624670029</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">0.133500397205353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129861757159233</t>
+    <t xml:space="preserve">0.129861772060394</t>
   </si>
   <si>
     <t xml:space="preserve">0.130175441503525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131681099534035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13011272251606</t>
+    <t xml:space="preserve">0.131681114435196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130112692713737</t>
   </si>
   <si>
     <t xml:space="preserve">0.130740061402321</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">0.124842964112759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126097664237022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975953578949</t>
+    <t xml:space="preserve">0.126097649335861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975938677788</t>
   </si>
   <si>
     <t xml:space="preserve">0.127289637923241</t>
@@ -707,70 +707,70 @@
     <t xml:space="preserve">0.127226904034615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126411333680153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125470325350761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126536816358566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125972181558609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551874637604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677312612534</t>
+    <t xml:space="preserve">0.126411348581314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1254703104496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126536831259727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215595424175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12597219645977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551859736443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677342414856</t>
   </si>
   <si>
     <t xml:space="preserve">0.132182970643044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129171699285507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132245719432831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006040334702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133939564228058</t>
+    <t xml:space="preserve">0.129171684384346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13224570453167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006055235863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133939549326897</t>
   </si>
   <si>
     <t xml:space="preserve">0.134127765893936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136260747909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943306446075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766391038895</t>
+    <t xml:space="preserve">0.136260762810707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943321347237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766420841217</t>
   </si>
   <si>
     <t xml:space="preserve">0.13801734149456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140777692198753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145733773708344</t>
+    <t xml:space="preserve">0.140777677297592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145733758807182</t>
   </si>
   <si>
     <t xml:space="preserve">0.144165396690369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143977180123329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141154065728188</t>
+    <t xml:space="preserve">0.14397719502449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14115409553051</t>
   </si>
   <si>
     <t xml:space="preserve">0.137640938162804</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">0.134629637002945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134002283215523</t>
+    <t xml:space="preserve">0.134002313017845</t>
   </si>
   <si>
     <t xml:space="preserve">0.133437663316727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129673555493355</t>
+    <t xml:space="preserve">0.129673570394516</t>
   </si>
   <si>
     <t xml:space="preserve">0.128356128931046</t>
@@ -800,31 +800,31 @@
     <t xml:space="preserve">0.135633409023285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137891873717308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137703657150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433921098709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132057517766953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134504169225693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134502425789833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13298973441124</t>
+    <t xml:space="preserve">0.137891858816147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13770367205143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433906197548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13205748796463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134504154324532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134502410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132989749312401</t>
   </si>
   <si>
     <t xml:space="preserve">0.131729170680046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130720719695091</t>
+    <t xml:space="preserve">0.13072070479393</t>
   </si>
   <si>
     <t xml:space="preserve">0.133178815245628</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">0.134943619370461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792202591896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131477057933807</t>
+    <t xml:space="preserve">0.131792172789574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131477043032646</t>
   </si>
   <si>
     <t xml:space="preserve">0.132359445095062</t>
@@ -848,49 +848,49 @@
     <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468621850014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129964396357536</t>
+    <t xml:space="preserve">0.130468606948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129964381456375</t>
   </si>
   <si>
     <t xml:space="preserve">0.127506271004677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129586219787598</t>
+    <t xml:space="preserve">0.129586204886436</t>
   </si>
   <si>
     <t xml:space="preserve">0.127002045512199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127947479486465</t>
+    <t xml:space="preserve">0.127947464585304</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199592232704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128703817725182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371771097183</t>
+    <t xml:space="preserve">0.12870380282402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.125930562615395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127128094434738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056626439095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479604780674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12466999143362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124165765941143</t>
+    <t xml:space="preserve">0.127128124237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056641340256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12479605525732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124669998884201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124165780842304</t>
   </si>
   <si>
     <t xml:space="preserve">0.125174224376678</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">0.125237256288528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129018932580948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127380222082138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12845167517662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136560320854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884447574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443253993988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126939013600349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128262609243393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126875996589661</t>
+    <t xml:space="preserve">0.129018947482109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127380207180977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128451704978943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136545419693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884462475777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443239092827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126938998699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128262624144554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126875981688499</t>
   </si>
   <si>
     <t xml:space="preserve">0.126497820019722</t>
@@ -932,13 +932,13 @@
     <t xml:space="preserve">0.126308724284172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430942893028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135573893785477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135762959718704</t>
+    <t xml:space="preserve">0.133430927991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135573908686638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135762989521027</t>
   </si>
   <si>
     <t xml:space="preserve">0.136456295847893</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">0.135636925697327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134061232209206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132485508918762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133556976914406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135195732116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136141166090965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134439378976822</t>
+    <t xml:space="preserve">0.134061202406883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132485494017601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133556991815567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135195717215538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136141151189804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134439408779144</t>
   </si>
   <si>
     <t xml:space="preserve">0.137464731931686</t>
@@ -977,31 +977,31 @@
     <t xml:space="preserve">0.137842923402786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136330246925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137086570262909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136771440505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136204183101654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13500665128231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134754538536072</t>
+    <t xml:space="preserve">0.136330232024193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137086555361748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13677142560482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136204168200493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006666183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134754523634911</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137401714920998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151141881942749</t>
+    <t xml:space="preserve">0.137401729822159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15114189684391</t>
   </si>
   <si>
     <t xml:space="preserve">0.153789088129997</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">0.157444715499878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159398585557938</t>
+    <t xml:space="preserve">0.159398600459099</t>
   </si>
   <si>
     <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570779323578</t>
+    <t xml:space="preserve">0.157570794224739</t>
   </si>
   <si>
     <t xml:space="preserve">0.152843654155731</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">0.152654573321342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151898235082626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153095752000809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150259494781494</t>
+    <t xml:space="preserve">0.151898220181465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153095781803131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150259479880333</t>
   </si>
   <si>
     <t xml:space="preserve">0.148746818304062</t>
@@ -1055,76 +1055,76 @@
     <t xml:space="preserve">0.155805990099907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154419377446175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156940504908562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159146472811699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167655304074287</t>
+    <t xml:space="preserve">0.154419347643852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156940490007401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15914648771286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16765533387661</t>
   </si>
   <si>
     <t xml:space="preserve">0.170050397515297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167214125394821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067284584045</t>
+    <t xml:space="preserve">0.16721411049366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067314386368</t>
   </si>
   <si>
     <t xml:space="preserve">0.179945826530457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178811311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175218716263771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336314201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176446437836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479279994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173643007874489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170365512371063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166205644607544</t>
+    <t xml:space="preserve">0.178811326622963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175218686461449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336299300194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176431536674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479294896126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173642992973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170365542173386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166205659508705</t>
   </si>
   <si>
     <t xml:space="preserve">0.168222546577454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168600723147392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166520789265633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166394725441933</t>
+    <t xml:space="preserve">0.168600738048553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166520804166794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166394755244255</t>
   </si>
   <si>
     <t xml:space="preserve">0.161730632185936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160091921687126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156688377261162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16122642159462</t>
+    <t xml:space="preserve">0.160091906785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156688392162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161226436495781</t>
   </si>
   <si>
     <t xml:space="preserve">0.162486985325813</t>
@@ -1136,64 +1136,64 @@
     <t xml:space="preserve">0.163873597979546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16103732585907</t>
+    <t xml:space="preserve">0.161037310957909</t>
   </si>
   <si>
     <t xml:space="preserve">0.158011972904205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157759845256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970448732376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167718321084976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165260210633278</t>
+    <t xml:space="preserve">0.157759860157967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970433831215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167718335986137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1652602404356</t>
   </si>
   <si>
     <t xml:space="preserve">0.163117274641991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163810595870018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159461602568626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147675320506096</t>
+    <t xml:space="preserve">0.163810580968857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159461617469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147675335407257</t>
   </si>
   <si>
     <t xml:space="preserve">0.147486239671707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150007382035255</t>
+    <t xml:space="preserve">0.150007367134094</t>
   </si>
   <si>
     <t xml:space="preserve">0.150448575615883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150511622428894</t>
+    <t xml:space="preserve">0.150511607527733</t>
   </si>
   <si>
     <t xml:space="preserve">0.15107886493206</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151646122336388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150322526693344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494690656662</t>
+    <t xml:space="preserve">0.151646107435226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150322541594505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494720458984</t>
   </si>
   <si>
     <t xml:space="preserve">0.15082673728466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151772171258926</t>
+    <t xml:space="preserve">0.151772186160088</t>
   </si>
   <si>
     <t xml:space="preserve">0.149881318211555</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">0.151583090424538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149629235267639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709154248238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15101583302021</t>
+    <t xml:space="preserve">0.149629220366478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709139347076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151015818119049</t>
   </si>
   <si>
     <t xml:space="preserve">0.148935899138451</t>
@@ -1217,43 +1217,43 @@
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763720273972</t>
+    <t xml:space="preserve">0.150763735175133</t>
   </si>
   <si>
     <t xml:space="preserve">0.150637671351433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151204913854599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149944335222244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213364839554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528509497643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157255634665489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156310200691223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164503902196884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243323564529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613019347191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982759833336</t>
+    <t xml:space="preserve">0.15120492875576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149944350123405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213379740715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149377092719078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15725564956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156310215592384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164503887295723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243338465691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162613049149513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982774734497</t>
   </si>
   <si>
     <t xml:space="preserve">0.163558468222618</t>
@@ -1262,37 +1262,37 @@
     <t xml:space="preserve">0.165764451026917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165449321269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079610586166</t>
+    <t xml:space="preserve">0.165449306368828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079595685005</t>
   </si>
   <si>
     <t xml:space="preserve">0.160722196102142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162297904491425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061933159828</t>
+    <t xml:space="preserve">0.162297889590263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061962962151</t>
   </si>
   <si>
     <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146540835499763</t>
+    <t xml:space="preserve">0.146540820598602</t>
   </si>
   <si>
     <t xml:space="preserve">0.146225675940514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142759129405022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334807991982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140237987041473</t>
+    <t xml:space="preserve">0.14275911450386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334837794304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140237972140312</t>
   </si>
   <si>
     <t xml:space="preserve">0.139607697725296</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">0.135826006531715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138347163796425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498565673828</t>
+    <t xml:space="preserve">0.138347148895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498535871506</t>
   </si>
   <si>
     <t xml:space="preserve">0.141813695430756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140553131699562</t>
+    <t xml:space="preserve">0.140553146600723</t>
   </si>
   <si>
     <t xml:space="preserve">0.141183421015739</t>
@@ -1325,61 +1325,61 @@
     <t xml:space="preserve">0.138662293553352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135510861873627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250327944756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935153484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132674604654312</t>
+    <t xml:space="preserve">0.135510876774788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134880587458611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134250313043594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935183286667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132674589753151</t>
   </si>
   <si>
     <t xml:space="preserve">0.143074259161949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144965127110481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14338943362236</t>
+    <t xml:space="preserve">0.144965097308159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
   </si>
   <si>
     <t xml:space="preserve">0.142443984746933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146575838327408</t>
+    <t xml:space="preserve">0.146575853228569</t>
   </si>
   <si>
     <t xml:space="preserve">0.147864401340485</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.146253705024719</t>
   </si>
   <si>
     <t xml:space="preserve">0.14560940861702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140455082058907</t>
+    <t xml:space="preserve">0.140455067157745</t>
   </si>
   <si>
     <t xml:space="preserve">0.142710089683533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141421556472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139166533946991</t>
+    <t xml:space="preserve">0.141421541571617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139166504144669</t>
   </si>
   <si>
     <t xml:space="preserve">0.140777230262756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139488637447357</t>
+    <t xml:space="preserve">0.139488652348518</t>
   </si>
   <si>
     <t xml:space="preserve">0.135622918605804</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132723614573479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132079318165779</t>
+    <t xml:space="preserve">0.132723599672318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13207933306694</t>
   </si>
   <si>
     <t xml:space="preserve">0.129824310541153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125765278935432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12499213963747</t>
+    <t xml:space="preserve">0.125765293836594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124992154538631</t>
   </si>
   <si>
     <t xml:space="preserve">0.126796156167984</t>
@@ -1409,91 +1409,91 @@
     <t xml:space="preserve">0.129180029034615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133367896080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131757199764252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125894144177437</t>
+    <t xml:space="preserve">0.133367925882339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131757184863091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125894159078598</t>
   </si>
   <si>
     <t xml:space="preserve">0.126925006508827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125378713011742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128600165247917</t>
+    <t xml:space="preserve">0.125378727912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128600150346756</t>
   </si>
   <si>
     <t xml:space="preserve">0.127440437674522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127955868840218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127827018499374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126023009419441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124347865581512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703569173813</t>
+    <t xml:space="preserve">0.127955853939056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127827033400536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12602299451828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124347850680351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703561723232</t>
   </si>
   <si>
     <t xml:space="preserve">0.127311587333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127569302916527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126667305827141</t>
+    <t xml:space="preserve">0.127569273114204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126667320728302</t>
   </si>
   <si>
     <t xml:space="preserve">0.126538440585136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128729045391083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128342464566231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129502162337303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130146458745003</t>
+    <t xml:space="preserve">0.128729030489922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12834244966507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129502177238464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130146443843842</t>
   </si>
   <si>
     <t xml:space="preserve">0.134012192487717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134656473994255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13852222263813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13820007443428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300755500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130790755152702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128084748983383</t>
+    <t xml:space="preserve">0.134656488895416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138522237539291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138200059533119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300770401955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130790740251541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128084719181061</t>
   </si>
   <si>
     <t xml:space="preserve">0.128857895731926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12524987757206</t>
+    <t xml:space="preserve">0.125249847769737</t>
   </si>
   <si>
     <t xml:space="preserve">0.122157283127308</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">0.128213584423065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126151859760284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127182722091675</t>
+    <t xml:space="preserve">0.126151874661446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127182736992836</t>
   </si>
   <si>
     <t xml:space="preserve">0.125636428594589</t>
@@ -1523,22 +1523,22 @@
     <t xml:space="preserve">0.122286133468151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122414983808994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260672152042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266080617905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113394938409328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848644912243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112106345593929</t>
+    <t xml:space="preserve">0.122414968907833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260664701462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266065716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113394916057587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848630011082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11210636049509</t>
   </si>
   <si>
     <t xml:space="preserve">0.114425800740719</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">0.114683516323566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112235195934772</t>
+    <t xml:space="preserve">0.112235210835934</t>
   </si>
   <si>
     <t xml:space="preserve">0.110817790031433</t>
@@ -1556,85 +1556,85 @@
     <t xml:space="preserve">0.108240626752377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106565460562706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921186506748</t>
+    <t xml:space="preserve">0.106565468013287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921171605587</t>
   </si>
   <si>
     <t xml:space="preserve">0.101926580071449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105019174516201</t>
+    <t xml:space="preserve">0.10501916706562</t>
   </si>
   <si>
     <t xml:space="preserve">0.103086292743683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104374885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117169976234</t>
+    <t xml:space="preserve">0.104374893009663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117162525654</t>
   </si>
   <si>
     <t xml:space="preserve">0.105663456022739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107982911169529</t>
+    <t xml:space="preserve">0.107982903718948</t>
   </si>
   <si>
     <t xml:space="preserve">0.108627177774906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108111754059792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11146205663681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750642001629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756057918072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173471271992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109529189765453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106952026486397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153448224068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103988319635391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699734270573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105276890099049</t>
+    <t xml:space="preserve">0.108111768960953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111462064087391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750664353371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756043016911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173478722572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109529204666615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106952041387558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103988312184811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699726819992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105276882648468</t>
   </si>
   <si>
     <t xml:space="preserve">0.111204348504543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115585513412952</t>
+    <t xml:space="preserve">0.115585528314114</t>
   </si>
   <si>
     <t xml:space="preserve">0.115843236446381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115327797830105</t>
+    <t xml:space="preserve">0.115327805280685</t>
   </si>
   <si>
     <t xml:space="preserve">0.113008357584476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10940033942461</t>
+    <t xml:space="preserve">0.109400354325771</t>
   </si>
   <si>
     <t xml:space="preserve">0.110431201756001</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">0.106307752430439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103859461843967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554651081562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109142631292343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013766050339</t>
+    <t xml:space="preserve">0.103859439492226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554636180401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109142616391182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013758599758</t>
   </si>
   <si>
     <t xml:space="preserve">0.108884900808334</t>
@@ -1667,25 +1667,25 @@
     <t xml:space="preserve">0.109271474182606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107338614761829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411163806915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055445313454</t>
+    <t xml:space="preserve">0.10733862221241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442003786564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411156356335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055460214615</t>
   </si>
   <si>
     <t xml:space="preserve">0.100251421332359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0999937206506729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10128228366375</t>
+    <t xml:space="preserve">0.0999937132000923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10128229111433</t>
   </si>
   <si>
     <t xml:space="preserve">0.101797737181187</t>
@@ -1694,49 +1694,49 @@
     <t xml:space="preserve">0.100766852498055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105148024857044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915770590305</t>
+    <t xml:space="preserve">0.105148039758205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915778040886</t>
   </si>
   <si>
     <t xml:space="preserve">0.1110754981637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112621799111366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302358865738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110688924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761451482773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534598231316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467472553253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108498349785805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080884277821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503743350506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792313814163</t>
+    <t xml:space="preserve">0.112621784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302351415157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688917338848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761458933353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534590780735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467480003834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108498334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080899178982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503735899925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792306363583</t>
   </si>
   <si>
     <t xml:space="preserve">0.106436610221863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10534130781889</t>
+    <t xml:space="preserve">0.10534131526947</t>
   </si>
   <si>
     <t xml:space="preserve">0.107596322894096</t>
@@ -1745,37 +1745,37 @@
     <t xml:space="preserve">0.108562767505646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109207049012184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110185064375401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857127070427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11116885393858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110512994229794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889533042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10690575838089</t>
+    <t xml:space="preserve">0.109207041561604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185071825981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857134521008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111168846487999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110513001680374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889540493488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106905743479729</t>
   </si>
   <si>
     <t xml:space="preserve">0.10592196136713</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10395435243845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104282304644585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105594016611576</t>
+    <t xml:space="preserve">0.10395435988903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104282289743423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105594009160995</t>
   </si>
   <si>
     <t xml:space="preserve">0.108217470347881</t>
@@ -1784,13 +1784,13 @@
     <t xml:space="preserve">0.105266094207764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104938142001629</t>
+    <t xml:space="preserve">0.104938149452209</t>
   </si>
   <si>
     <t xml:space="preserve">0.102970570325851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103626430034637</t>
+    <t xml:space="preserve">0.103626437485218</t>
   </si>
   <si>
     <t xml:space="preserve">0.103298492729664</t>
@@ -1805,40 +1805,40 @@
     <t xml:space="preserve">0.101330906152725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0970677956938744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0977236703038216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957180976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951001942157745</t>
+    <t xml:space="preserve">0.097067803144455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0977236554026604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957255482674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951002016663551</t>
   </si>
   <si>
     <t xml:space="preserve">0.0980515852570534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0964119285345078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0987074598670006</t>
+    <t xml:space="preserve">0.0964119359850883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09870745241642</t>
   </si>
   <si>
     <t xml:space="preserve">0.0993633195757866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100019179284573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002991199493</t>
+    <t xml:space="preserve">0.100019186735153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002976298332</t>
   </si>
   <si>
     <t xml:space="preserve">0.100675046443939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102642640471458</t>
+    <t xml:space="preserve">0.102642633020878</t>
   </si>
   <si>
     <t xml:space="preserve">0.098379522562027</t>
@@ -1847,76 +1847,76 @@
     <t xml:space="preserve">0.0996912494301796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.099035382270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104610219597816</t>
+    <t xml:space="preserve">0.0990353748202324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104610234498978</t>
   </si>
   <si>
     <t xml:space="preserve">0.107561610639095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108873322606087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545415103436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109201267361641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107233680784702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249883770943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112152650952339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114448182284832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111824728548527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808533012867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113136440515518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480580806732</t>
+    <t xml:space="preserve">0.108873337507248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545407652855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10920125991106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107233673334122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249891221523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11215265840292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114448174834251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111824713647366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808518111706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113136447966099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480573356152</t>
   </si>
   <si>
     <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130516812205315</t>
+    <t xml:space="preserve">0.130516827106476</t>
   </si>
   <si>
     <t xml:space="preserve">0.139698937535286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132484436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141010642051697</t>
+    <t xml:space="preserve">0.132484421133995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141010656952858</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686567425728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173803821206093</t>
+    <t xml:space="preserve">0.173803806304932</t>
   </si>
   <si>
     <t xml:space="preserve">0.167245179414749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155439659953117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150848612189293</t>
+    <t xml:space="preserve">0.155439645051956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150848597288132</t>
   </si>
   <si>
     <t xml:space="preserve">0.154127910733223</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">0.157407239079475</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156751379370689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152816161513329</t>
+    <t xml:space="preserve">0.156751394271851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15281617641449</t>
   </si>
   <si>
     <t xml:space="preserve">0.148881003260612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145601704716682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146257549524307</t>
+    <t xml:space="preserve">0.145601689815521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146257564425468</t>
   </si>
   <si>
     <t xml:space="preserve">0.146913409233093</t>
@@ -1946,37 +1946,37 @@
     <t xml:space="preserve">0.150192737579346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149536862969398</t>
+    <t xml:space="preserve">0.14953687787056</t>
   </si>
   <si>
     <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147569254040718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148225143551826</t>
+    <t xml:space="preserve">0.147569268941879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148225158452988</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654146552086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161342427134514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141666516661644</t>
+    <t xml:space="preserve">0.161342412233353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141666501760483</t>
   </si>
   <si>
     <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135107859969139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133140295743942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137731313705444</t>
+    <t xml:space="preserve">0.1351078748703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13314026594162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137731328606606</t>
   </si>
   <si>
     <t xml:space="preserve">0.154783770442009</t>
@@ -1985,28 +1985,28 @@
     <t xml:space="preserve">0.156095504760742</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153472036123276</t>
+    <t xml:space="preserve">0.153472065925598</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135763734579086</t>
+    <t xml:space="preserve">0.135763749480247</t>
   </si>
   <si>
     <t xml:space="preserve">0.13707546889782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12559786438942</t>
+    <t xml:space="preserve">0.125597849488258</t>
   </si>
   <si>
     <t xml:space="preserve">0.126581653952599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123958192765713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118711285293102</t>
+    <t xml:space="preserve">0.123958185315132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118711292743683</t>
   </si>
   <si>
     <t xml:space="preserve">0.110840916633606</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">0.0826388001441956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.087885707616806</t>
+    <t xml:space="preserve">0.0878856927156448</t>
   </si>
   <si>
     <t xml:space="preserve">0.08722984790802</t>
@@ -2027,19 +2027,19 @@
     <t xml:space="preserve">0.088541567325592</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0911650285124779</t>
+    <t xml:space="preserve">0.0911650210618973</t>
   </si>
   <si>
     <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0928046852350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0944443345069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0960840061306953</t>
+    <t xml:space="preserve">0.0928046777844429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0944443419575691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0960840135812759</t>
   </si>
   <si>
     <t xml:space="preserve">0.0931326150894165</t>
@@ -2048,25 +2048,25 @@
     <t xml:space="preserve">0.0957560688257217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0937884822487831</t>
+    <t xml:space="preserve">0.0937884896993637</t>
   </si>
   <si>
     <t xml:space="preserve">0.0965431109070778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0969366207718849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.097854845225811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0971989631652832</t>
+    <t xml:space="preserve">0.0969366282224655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0978548377752304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0971989706158638</t>
   </si>
   <si>
     <t xml:space="preserve">0.0924767553806305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0940508246421814</t>
+    <t xml:space="preserve">0.0940508171916008</t>
   </si>
   <si>
     <t xml:space="preserve">0.0939196422696114</t>
@@ -2081,85 +2081,85 @@
     <t xml:space="preserve">0.0954937264323235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0982483476400375</t>
+    <t xml:space="preserve">0.0982483550906181</t>
   </si>
   <si>
     <t xml:space="preserve">0.100740633904934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0968054533004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0966742858290672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709756612778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0979859903454781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0991665497422218</t>
+    <t xml:space="preserve">0.0968054458498955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0966742783784866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709749162197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0979860126972198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0991665571928024</t>
   </si>
   <si>
     <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0948378518223763</t>
+    <t xml:space="preserve">0.0948378592729568</t>
   </si>
   <si>
     <t xml:space="preserve">0.100084766745567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102183535695076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999536067247391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10323292016983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104806981980801</t>
+    <t xml:space="preserve">0.102183528244495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999535992741585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10323291271925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10480697453022</t>
   </si>
   <si>
     <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125925794243813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138387203216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14232237637043</t>
+    <t xml:space="preserve">0.125925779342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13838717341423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142322361469269</t>
   </si>
   <si>
     <t xml:space="preserve">0.137403398752213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135435804724693</t>
+    <t xml:space="preserve">0.135435819625854</t>
   </si>
   <si>
     <t xml:space="preserve">0.136419609189034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134452015161514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134124085307121</t>
+    <t xml:space="preserve">0.134452000260353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13412407040596</t>
   </si>
   <si>
     <t xml:space="preserve">0.131041526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127893373370171</t>
+    <t xml:space="preserve">0.127893358469009</t>
   </si>
   <si>
     <t xml:space="preserve">0.134779945015907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131172701716423</t>
+    <t xml:space="preserve">0.131172716617584</t>
   </si>
   <si>
     <t xml:space="preserve">0.130779176950455</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">0.130123317241669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129336267709732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130385652184486</t>
+    <t xml:space="preserve">0.129336282610893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130385667085648</t>
   </si>
   <si>
     <t xml:space="preserve">0.131500631570816</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">0.126975163817406</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127631023526192</t>
+    <t xml:space="preserve">0.127631038427353</t>
   </si>
   <si>
     <t xml:space="preserve">0.128549247980118</t>
@@ -2198,16 +2198,16 @@
     <t xml:space="preserve">0.133796155452728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132156476378441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130648016929626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129205092787743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129598632454872</t>
+    <t xml:space="preserve">0.132156491279602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130648002028465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129205107688904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129598617553711</t>
   </si>
   <si>
     <t xml:space="preserve">0.140026852488518</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">0.1297297924757</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12986096739769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130254477262497</t>
+    <t xml:space="preserve">0.129860952496529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130254462361336</t>
   </si>
   <si>
     <t xml:space="preserve">0.129073932766914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125138744711876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124614059925079</t>
+    <t xml:space="preserve">0.125138759613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124614052474499</t>
   </si>
   <si>
     <t xml:space="preserve">0.143634110689163</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">0.143962055444717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370992779732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136091664433479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13805927336216</t>
+    <t xml:space="preserve">0.139371007680893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136091679334641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138059258460999</t>
   </si>
   <si>
     <t xml:space="preserve">0.136747539043427</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">0.140682712197304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144945845007896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142650321125984</t>
+    <t xml:space="preserve">0.144945830106735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142650306224823</t>
   </si>
   <si>
     <t xml:space="preserve">0.141994431614876</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">0.153799995779991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152488261461258</t>
+    <t xml:space="preserve">0.152488276362419</t>
   </si>
   <si>
     <t xml:space="preserve">0.157079309225082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152160316705704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153144121170044</t>
+    <t xml:space="preserve">0.152160331606865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153144136071205</t>
   </si>
   <si>
     <t xml:space="preserve">0.155111700296402</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702762961388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16298209130764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166917249560356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163310006260872</t>
+    <t xml:space="preserve">0.159702748060226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162982061505318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166917264461517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163309991359711</t>
   </si>
   <si>
     <t xml:space="preserve">0.162326216697693</t>
@@ -2324,34 +2324,34 @@
     <t xml:space="preserve">0.158063098788261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165341451764107</t>
+    <t xml:space="preserve">0.165341436862946</t>
   </si>
   <si>
     <t xml:space="preserve">0.163571178913116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863090634346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16250903904438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161092832684517</t>
+    <t xml:space="preserve">0.162863075733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162509024143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161092847585678</t>
   </si>
   <si>
     <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157198280096054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158260449767113</t>
+    <t xml:space="preserve">0.157198294997215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
     <t xml:space="preserve">0.162154987454414</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158968523144722</t>
+    <t xml:space="preserve">0.158968538045883</t>
   </si>
   <si>
     <t xml:space="preserve">0.160384744405746</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">0.161800935864449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155073955655098</t>
+    <t xml:space="preserve">0.15507398545742</t>
   </si>
   <si>
     <t xml:space="preserve">0.153303727507591</t>
@@ -2375,22 +2375,22 @@
     <t xml:space="preserve">0.155782073736191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151533469557762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152595639228821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154719948768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155428037047386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156844228506088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156490191817284</t>
+    <t xml:space="preserve">0.151533484458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15259562432766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154719933867455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155428051948547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156844243407249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156490176916122</t>
   </si>
   <si>
     <t xml:space="preserve">0.153657779097557</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">0.154011830687523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156136125326157</t>
+    <t xml:space="preserve">0.156136140227318</t>
   </si>
   <si>
     <t xml:space="preserve">0.152241587638855</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">0.15011727809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150825381278992</t>
+    <t xml:space="preserve">0.150825396180153</t>
   </si>
   <si>
     <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150471329689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149055138230324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146222710609436</t>
+    <t xml:space="preserve">0.150471344590187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149055123329163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146222725510597</t>
   </si>
   <si>
     <t xml:space="preserve">0.147284880280495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1426822245121</t>
+    <t xml:space="preserve">0.142682209610939</t>
   </si>
   <si>
     <t xml:space="preserve">0.143390327692032</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">0.145514622330666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148347035050392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149409174919128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152949690818787</t>
+    <t xml:space="preserve">0.148347020149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149409160017967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152949675917625</t>
   </si>
   <si>
     <t xml:space="preserve">0.1451605707407</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">0.147638931870461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148701086640358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146576777100563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144452467560768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143744379281998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144806534051895</t>
+    <t xml:space="preserve">0.148701071739197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146576792001724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144452482461929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143744364380836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144806519150734</t>
   </si>
   <si>
     <t xml:space="preserve">0.144098430871964</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">0.145868673920631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147992968559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16569547355175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168527871370316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167111694812775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16746574640274</t>
+    <t xml:space="preserve">0.147992983460426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165695488452911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168527886271477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167111679911613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167465731501579</t>
   </si>
   <si>
     <t xml:space="preserve">0.164987370371819</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">0.161695301532745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161314830183983</t>
+    <t xml:space="preserve">0.161314845085144</t>
   </si>
   <si>
     <t xml:space="preserve">0.159793004393578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163978070020676</t>
+    <t xml:space="preserve">0.163978040218353</t>
   </si>
   <si>
     <t xml:space="preserve">0.16055391728878</t>
@@ -2531,10 +2531,10 @@
     <t xml:space="preserve">0.158271163702011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160934373736382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162836670875549</t>
+    <t xml:space="preserve">0.160934388637543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162836685776711</t>
   </si>
   <si>
     <t xml:space="preserve">0.16511943936348</t>
@@ -2546,16 +2546,16 @@
     <t xml:space="preserve">0.162456214427948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159032076597214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159412547945976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16017347574234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165880352258682</t>
+    <t xml:space="preserve">0.159032091498375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159412533044815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160173460841179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165880367159843</t>
   </si>
   <si>
     <t xml:space="preserve">0.170445874333382</t>
@@ -2564,55 +2564,55 @@
     <t xml:space="preserve">0.169684946537018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170826315879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171967700123787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17006541788578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157129764556885</t>
+    <t xml:space="preserve">0.170826330780983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171967715024948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170065388083458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157129779458046</t>
   </si>
   <si>
     <t xml:space="preserve">0.157890692353249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153705656528473</t>
+    <t xml:space="preserve">0.153705641627312</t>
   </si>
   <si>
     <t xml:space="preserve">0.14427025616169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14777047932148</t>
+    <t xml:space="preserve">0.147770464420319</t>
   </si>
   <si>
     <t xml:space="preserve">0.155227482318878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155988395214081</t>
+    <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
     <t xml:space="preserve">0.157510250806808</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164738968014717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166260823607445</t>
+    <t xml:space="preserve">0.164738953113556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166260808706284</t>
   </si>
   <si>
     <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166641250252724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168163120746613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167402178049088</t>
+    <t xml:space="preserve">0.166641265153885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168163105845451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167402192950249</t>
   </si>
   <si>
     <t xml:space="preserve">0.168543562293053</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">0.173869997262955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174277186393738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173462808132172</t>
+    <t xml:space="preserve">0.174277201294899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173462823033333</t>
   </si>
   <si>
     <t xml:space="preserve">0.171426862478256</t>
@@ -2633,25 +2633,25 @@
     <t xml:space="preserve">0.168983712792397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166133388876915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17061248421669</t>
+    <t xml:space="preserve">0.166133403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170612469315529</t>
   </si>
   <si>
     <t xml:space="preserve">0.16816933453083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167354986071587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16531902551651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16654060781002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166947767138481</t>
+    <t xml:space="preserve">0.167354971170425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165319010615349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166540592908859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166947782039642</t>
   </si>
   <si>
     <t xml:space="preserve">0.167762160301208</t>
@@ -2660,31 +2660,31 @@
     <t xml:space="preserve">0.168576538562775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169390931725502</t>
+    <t xml:space="preserve">0.169390916824341</t>
   </si>
   <si>
     <t xml:space="preserve">0.16287587583065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151963204145432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155709356069565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157175227999687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156360849738121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157338112592697</t>
+    <t xml:space="preserve">0.15196318924427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155709341168404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157175213098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15636083483696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157338097691536</t>
   </si>
   <si>
     <t xml:space="preserve">0.155546456575394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154243469238281</t>
+    <t xml:space="preserve">0.15424345433712</t>
   </si>
   <si>
     <t xml:space="preserve">0.150660187005997</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">0.152451813220978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152614712715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163690268993378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162387251853943</t>
+    <t xml:space="preserve">0.152614697813988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163690254092216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162387236952782</t>
   </si>
   <si>
     <t xml:space="preserve">0.158478230237961</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">0.161247119307518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161735743284225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161572888493538</t>
+    <t xml:space="preserve">0.161735728383064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161572873592377</t>
   </si>
   <si>
     <t xml:space="preserve">0.157500967383385</t>
@@ -2726,10 +2726,10 @@
     <t xml:space="preserve">0.160269856452942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159129738807678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160595610737801</t>
+    <t xml:space="preserve">0.159129723906517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160595625638962</t>
   </si>
   <si>
     <t xml:space="preserve">0.159781232476234</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">0.161410003900528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159944117069244</t>
+    <t xml:space="preserve">0.159944102168083</t>
   </si>
   <si>
     <t xml:space="preserve">0.154732078313828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966854214668</t>
+    <t xml:space="preserve">0.158966839313507</t>
   </si>
   <si>
     <t xml:space="preserve">0.15652371942997</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">0.156197965145111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156035095453262</t>
+    <t xml:space="preserve">0.156035080552101</t>
   </si>
   <si>
     <t xml:space="preserve">0.157663851976395</t>
@@ -2780,16 +2780,16 @@
     <t xml:space="preserve">0.157826736569405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158152475953102</t>
+    <t xml:space="preserve">0.158152461051941</t>
   </si>
   <si>
     <t xml:space="preserve">0.156686589121819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153103336691856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15228895843029</t>
+    <t xml:space="preserve">0.153103321790695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152288943529129</t>
   </si>
   <si>
     <t xml:space="preserve">0.154894962906837</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">0.158641114830971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164911821484566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164504647254944</t>
+    <t xml:space="preserve">0.164911836385727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164504632353783</t>
   </si>
   <si>
     <t xml:space="preserve">0.163283064961433</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">0.162224382162094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162550136446953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161084249615669</t>
+    <t xml:space="preserve">0.162550121545792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161084234714508</t>
   </si>
   <si>
     <t xml:space="preserve">0.15880398452282</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">0.159455493092537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162713006138802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165726199746132</t>
+    <t xml:space="preserve">0.16271299123764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165726214647293</t>
   </si>
   <si>
     <t xml:space="preserve">0.170205295085907</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">0.177534714341164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179163455963135</t>
+    <t xml:space="preserve">0.179163470864296</t>
   </si>
   <si>
     <t xml:space="preserve">0.175091579556465</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">0.172241255640984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172648429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171834051609039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169798105955124</t>
+    <t xml:space="preserve">0.172648444771767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171834066510201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.169798091053963</t>
   </si>
   <si>
     <t xml:space="preserve">0.183235362172127</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">0.184049740433693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182420998811722</t>
+    <t xml:space="preserve">0.182420983910561</t>
   </si>
   <si>
     <t xml:space="preserve">0.184864118695259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185678496956825</t>
+    <t xml:space="preserve">0.185678511857986</t>
   </si>
   <si>
     <t xml:space="preserve">0.188121646642685</t>
@@ -18512,7 +18512,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G571" t="s">
-        <v>104</v>
+        <v>438</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18538,7 +18538,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G572" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18564,7 +18564,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G573" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18590,7 +18590,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G574" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18616,7 +18616,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G575" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18642,7 +18642,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18876,7 +18876,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18902,7 +18902,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G586" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18954,7 +18954,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G588" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19058,7 +19058,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G592" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19084,7 +19084,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G593" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19110,7 +19110,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G594" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19136,7 +19136,7 @@
         <v>0.229499995708466</v>
       </c>
       <c r="G595" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19162,7 +19162,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -69324,7 +69324,7 @@
     </row>
     <row r="2526">
       <c r="A2526" s="1" t="n">
-        <v>45995.6911805556</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2526" t="n">
         <v>2184507</v>
@@ -69345,6 +69345,32 @@
         <v>1107</v>
       </c>
       <c r="H2526" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>45996.6911458333</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>1722172</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>0.156000003218651</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>0.151500001549721</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>0.153999999165535</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>0.156000003218651</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H2527" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.148099198937416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15029776096344</t>
+    <t xml:space="preserve">0.150297775864601</t>
   </si>
   <si>
     <t xml:space="preserve">0.151580274105072</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">0.14736633002758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142358437180519</t>
+    <t xml:space="preserve">0.142358422279358</t>
   </si>
   <si>
     <t xml:space="preserve">0.132831215858459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134541258215904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125319376587868</t>
+    <t xml:space="preserve">0.134541228413582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121203303337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134358018636703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419098496437</t>
+    <t xml:space="preserve">0.134358003735542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419083595276</t>
   </si>
   <si>
     <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138022348284721</t>
+    <t xml:space="preserve">0.13802233338356</t>
   </si>
   <si>
     <t xml:space="preserve">0.137778058648109</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">0.140465214848518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139854475855827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136190190911293</t>
+    <t xml:space="preserve">0.139854490756989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136190176010132</t>
   </si>
   <si>
     <t xml:space="preserve">0.131793022155762</t>
@@ -116,40 +116,40 @@
     <t xml:space="preserve">0.129289075732231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118967935442924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754380106926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116158619523048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118479363620281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125807955861092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125197231769562</t>
+    <t xml:space="preserve">0.118967942893505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754372656345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116158626973629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479371070862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125807970762253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125197246670723</t>
   </si>
   <si>
     <t xml:space="preserve">0.129960849881172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125014021992683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999088287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129105865955353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128617271780968</t>
+    <t xml:space="preserve">0.127029404044151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125014036893845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999058485031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12910583615303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128617286682129</t>
   </si>
   <si>
     <t xml:space="preserve">0.130205139517784</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">0.130510494112968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129533335566521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133808374404907</t>
+    <t xml:space="preserve">0.129533350467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133808389306068</t>
   </si>
   <si>
     <t xml:space="preserve">0.138755187392235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139671266078949</t>
+    <t xml:space="preserve">0.139671251177788</t>
   </si>
   <si>
     <t xml:space="preserve">0.136739835143089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136495530605316</t>
+    <t xml:space="preserve">0.136495545506477</t>
   </si>
   <si>
     <t xml:space="preserve">0.140159830451012</t>
@@ -185,43 +185,43 @@
     <t xml:space="preserve">0.147122040390968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149015262722969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146572396159172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145717367529869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1432134360075</t>
+    <t xml:space="preserve">0.149015247821808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146572381258011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145717397332191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143213465809822</t>
   </si>
   <si>
     <t xml:space="preserve">0.144129514694214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140892699360847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139793425798416</t>
+    <t xml:space="preserve">0.140892714262009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139793410897255</t>
   </si>
   <si>
     <t xml:space="preserve">0.134968742728233</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136068046092987</t>
+    <t xml:space="preserve">0.136068031191826</t>
   </si>
   <si>
     <t xml:space="preserve">0.13594588637352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135823741555214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133136570453644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130693718791008</t>
+    <t xml:space="preserve">0.135823726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133136585354805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130693733692169</t>
   </si>
   <si>
     <t xml:space="preserve">0.128861546516418</t>
@@ -233,31 +233,31 @@
     <t xml:space="preserve">0.133930519223213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137472689151764</t>
+    <t xml:space="preserve">0.137472674250603</t>
   </si>
   <si>
     <t xml:space="preserve">0.142480567097664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142114162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141320213675499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142175227403641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138327687978745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142236307263374</t>
+    <t xml:space="preserve">0.142114147543907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141320198774338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14217521250248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138327717781067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142236262559891</t>
   </si>
   <si>
     <t xml:space="preserve">0.1382055580616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14052677154541</t>
+    <t xml:space="preserve">0.140526726841927</t>
   </si>
   <si>
     <t xml:space="preserve">0.139899387955666</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136637166142464</t>
+    <t xml:space="preserve">0.136637181043625</t>
   </si>
   <si>
     <t xml:space="preserve">0.133876815438271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133814066648483</t>
+    <t xml:space="preserve">0.133814081549644</t>
   </si>
   <si>
     <t xml:space="preserve">0.132998526096344</t>
@@ -281,31 +281,31 @@
     <t xml:space="preserve">0.129234418272972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128732532262802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125156626105309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126662284135818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126725032925606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127352371811867</t>
+    <t xml:space="preserve">0.128732547163963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12515664100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126662269234657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126725003123283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127352356910706</t>
   </si>
   <si>
     <t xml:space="preserve">0.127979710698128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126599550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127916976809502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130489140748978</t>
+    <t xml:space="preserve">0.126599535346031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127916991710663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
     <t xml:space="preserve">0.1317438185215</t>
@@ -314,100 +314,100 @@
     <t xml:space="preserve">0.131116479635239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13155560195446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134065017104149</t>
+    <t xml:space="preserve">0.131555616855621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13406503200531</t>
   </si>
   <si>
     <t xml:space="preserve">0.131179213523865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133688598871231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134880572557449</t>
+    <t xml:space="preserve">0.133688613772392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134880587458611</t>
   </si>
   <si>
     <t xml:space="preserve">0.134190499782562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130614593625069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132873058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128481596708298</t>
+    <t xml:space="preserve">0.130614578723907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132873043417931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128481581807137</t>
   </si>
   <si>
     <t xml:space="preserve">0.121078856289387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120200544595718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831670403481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413864254951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233184278011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366188645363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11179406195879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052496850491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395063757896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893170297146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041225492954</t>
+    <t xml:space="preserve">0.120200552046299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831677854061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413871705532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233199179173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366181194782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794039607048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11405248939991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395056307316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893192648888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041210591793</t>
   </si>
   <si>
     <t xml:space="preserve">0.107904464006424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111354887485504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727556049824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277110219002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102822914719582</t>
+    <t xml:space="preserve">0.111354909837246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727541148663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277117669582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102822922170162</t>
   </si>
   <si>
     <t xml:space="preserve">0.100501731038094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107716269791126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110790267586708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11455437541008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11292327195406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303439855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632160127163</t>
+    <t xml:space="preserve">0.107716262340546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110790275037289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11292327940464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303447306156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632175028324</t>
   </si>
   <si>
     <t xml:space="preserve">0.116561912000179</t>
@@ -416,34 +416,34 @@
     <t xml:space="preserve">0.116373710334301</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115746349096298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11543270200491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805333316326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185501217842</t>
+    <t xml:space="preserve">0.115746356546879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432694554329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805325865746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185516119003</t>
   </si>
   <si>
     <t xml:space="preserve">0.118569441139698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118820391595364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934565663338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159164130688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088901102543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10614787787199</t>
+    <t xml:space="preserve">0.118820384144783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934558212757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159171581268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088908553123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106147885322571</t>
   </si>
   <si>
     <t xml:space="preserve">0.104140356183052</t>
@@ -452,115 +452,115 @@
     <t xml:space="preserve">0.105645999312401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10746531188488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108531802892685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590802013874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535589814186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104830428957939</t>
+    <t xml:space="preserve">0.107465319335461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108531817793846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590787112713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535597264767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1048304438591</t>
   </si>
   <si>
     <t xml:space="preserve">0.108092673122883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108029916882515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653543353081</t>
+    <t xml:space="preserve">0.108029939234257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107653506100178</t>
   </si>
   <si>
     <t xml:space="preserve">0.109849244356155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110978484153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11160584539175</t>
+    <t xml:space="preserve">0.110978469252586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111605852842331</t>
   </si>
   <si>
     <t xml:space="preserve">0.113738849759102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113864317536354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110288389027119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845479786396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723769128323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339851558208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406350016594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104516766965389</t>
+    <t xml:space="preserve">0.113864310085773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11028840392828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225662589073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845494687557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723761677742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406357467175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104516752064228</t>
   </si>
   <si>
     <t xml:space="preserve">0.105018652975559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10664975643158</t>
+    <t xml:space="preserve">0.106649771332741</t>
   </si>
   <si>
     <t xml:space="preserve">0.10583420842886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106085151433945</t>
+    <t xml:space="preserve">0.106085158884525</t>
   </si>
   <si>
     <t xml:space="preserve">0.10978652536869</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104391291737556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107779011130333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214361429214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11606003344059</t>
+    <t xml:space="preserve">0.104391306638718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107778981328011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214383780956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060048341751</t>
   </si>
   <si>
     <t xml:space="preserve">0.114742591977119</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11242139339447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11342516541481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295940518379</t>
+    <t xml:space="preserve">0.112421378493309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11342515796423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295925617218</t>
   </si>
   <si>
     <t xml:space="preserve">0.106022402644157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106712505221367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520531535149</t>
+    <t xml:space="preserve">0.106712512671947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837965548038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520524084568</t>
   </si>
   <si>
     <t xml:space="preserve">0.104265823960304</t>
@@ -569,70 +569,70 @@
     <t xml:space="preserve">0.102760180830956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101003602147102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579508304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885656058788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889420628548</t>
+    <t xml:space="preserve">0.101003594696522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579500854015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885663509369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889413177967</t>
   </si>
   <si>
     <t xml:space="preserve">0.101254537701607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100564450025558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101066313683987</t>
+    <t xml:space="preserve">0.100564457476139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101066336035728</t>
   </si>
   <si>
     <t xml:space="preserve">0.101630948483944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106524288654327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109911985695362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539332032204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110915742814541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657285571098</t>
+    <t xml:space="preserve">0.106524296104908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109912015497684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539354383945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11091573536396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657270669937</t>
   </si>
   <si>
     <t xml:space="preserve">0.112609602510929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111292161047459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410114586353</t>
+    <t xml:space="preserve">0.111292153596878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410122036934</t>
   </si>
   <si>
     <t xml:space="preserve">0.108343608677387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108280867338181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033696353436</t>
+    <t xml:space="preserve">0.108280874788761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033703804016</t>
   </si>
   <si>
     <t xml:space="preserve">0.110351137816906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128544345498085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153701141476631</t>
+    <t xml:space="preserve">0.128544330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
     <t xml:space="preserve">0.144918203353882</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">0.132371172308922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132684856653214</t>
+    <t xml:space="preserve">0.132684871554375</t>
   </si>
   <si>
     <t xml:space="preserve">0.13425324857235</t>
@@ -653,43 +653,43 @@
     <t xml:space="preserve">0.131304681301117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134692370891571</t>
+    <t xml:space="preserve">0.13469235599041</t>
   </si>
   <si>
     <t xml:space="preserve">0.135821610689163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139836654067039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14265975356102</t>
+    <t xml:space="preserve">0.139836683869362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142659738659859</t>
   </si>
   <si>
     <t xml:space="preserve">0.144855469465256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143161624670029</t>
+    <t xml:space="preserve">0.143161609768867</t>
   </si>
   <si>
     <t xml:space="preserve">0.141781449317932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133500397205353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129861757159233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130175426602364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131681099534035</t>
+    <t xml:space="preserve">0.133500412106514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129861772060394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130175441503525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131681084632874</t>
   </si>
   <si>
     <t xml:space="preserve">0.130112707614899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130740061402321</t>
+    <t xml:space="preserve">0.13074004650116</t>
   </si>
   <si>
     <t xml:space="preserve">0.124842949211597</t>
@@ -698,46 +698,46 @@
     <t xml:space="preserve">0.126097664237022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12697596848011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289623022079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226918935776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126411318778992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1254703104496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126536816358566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215610325336</t>
+    <t xml:space="preserve">0.126975953578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289637923241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226889133453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126411333680153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125470295548439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126536801457405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215625226498</t>
   </si>
   <si>
     <t xml:space="preserve">0.125972181558609</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130551859736443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677327513695</t>
+    <t xml:space="preserve">0.130551844835281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677312612534</t>
   </si>
   <si>
     <t xml:space="preserve">0.132182970643044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129171699285507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132245689630508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006040334702</t>
+    <t xml:space="preserve">0.129171684384346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13224570453167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006055235863</t>
   </si>
   <si>
     <t xml:space="preserve">0.133939549326897</t>
@@ -749,97 +749,97 @@
     <t xml:space="preserve">0.136260762810707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134943321347237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766405940056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13801734149456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777677297592</t>
+    <t xml:space="preserve">0.134943306446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766391038895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138017326593399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
     <t xml:space="preserve">0.145733758807182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144165396690369</t>
+    <t xml:space="preserve">0.144165381789207</t>
   </si>
   <si>
     <t xml:space="preserve">0.143977180123329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141154080629349</t>
+    <t xml:space="preserve">0.14115409553051</t>
   </si>
   <si>
     <t xml:space="preserve">0.137640923261642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629637002945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002283215523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133437678217888</t>
+    <t xml:space="preserve">0.136762648820877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629651904106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002298116684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133437648415565</t>
   </si>
   <si>
     <t xml:space="preserve">0.129673555493355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356114029884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496640086174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135633409023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137891858816147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137703657150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433921098709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132057502865791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134504154324532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134502440690994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132989749312401</t>
+    <t xml:space="preserve">0.128356128931046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496654987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135633423924446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137891843914986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137703686952591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433906197548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13205748796463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134504169225693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134502410888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132989719510078</t>
   </si>
   <si>
     <t xml:space="preserve">0.131729170680046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13072070479393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133178815245628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565427899361</t>
+    <t xml:space="preserve">0.130720719695091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13317883014679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565442800522</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943619370461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792187690735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131477057933807</t>
+    <t xml:space="preserve">0.131792202591896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131477043032646</t>
   </si>
   <si>
     <t xml:space="preserve">0.132359445095062</t>
@@ -848,7 +848,7 @@
     <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468606948853</t>
+    <t xml:space="preserve">0.130468621850014</t>
   </si>
   <si>
     <t xml:space="preserve">0.129964381456375</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">0.127506256103516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129586204886436</t>
+    <t xml:space="preserve">0.129586234688759</t>
   </si>
   <si>
     <t xml:space="preserve">0.127002045512199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127947479486465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128199577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128703817725182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371756196022</t>
+    <t xml:space="preserve">0.127947464585304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128199592232704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12870380282402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371771097183</t>
   </si>
   <si>
     <t xml:space="preserve">0.125930562615395</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">0.127128094434738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126056656241417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479605525732</t>
+    <t xml:space="preserve">0.126056611537933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124796077609062</t>
   </si>
   <si>
     <t xml:space="preserve">0.124669998884201</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">0.124165765941143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125174209475517</t>
+    <t xml:space="preserve">0.125174224376678</t>
   </si>
   <si>
     <t xml:space="preserve">0.125237256288528</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">0.129018947482109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127380222082138</t>
+    <t xml:space="preserve">0.127380192279816</t>
   </si>
   <si>
     <t xml:space="preserve">0.128451690077782</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">0.128136560320854</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127884447574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443239092827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126938998699188</t>
+    <t xml:space="preserve">0.127884432673454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443253993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126939013600349</t>
   </si>
   <si>
     <t xml:space="preserve">0.128262609243393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126875981688499</t>
+    <t xml:space="preserve">0.126875996589661</t>
   </si>
   <si>
     <t xml:space="preserve">0.126497820019722</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">0.126308724284172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430927991867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135573893785477</t>
+    <t xml:space="preserve">0.133430957794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135573908686638</t>
   </si>
   <si>
     <t xml:space="preserve">0.135762989521027</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">0.136456295847893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135636940598488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134061217308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132485508918762</t>
+    <t xml:space="preserve">0.135636925697327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134061202406883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132485494017601</t>
   </si>
   <si>
     <t xml:space="preserve">0.133556991815567</t>
@@ -959,19 +959,19 @@
     <t xml:space="preserve">0.135195732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136141166090965</t>
+    <t xml:space="preserve">0.136141151189804</t>
   </si>
   <si>
     <t xml:space="preserve">0.134439393877983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137464746832848</t>
+    <t xml:space="preserve">0.137464731931686</t>
   </si>
   <si>
     <t xml:space="preserve">0.137716859579086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138221070170403</t>
+    <t xml:space="preserve">0.138221085071564</t>
   </si>
   <si>
     <t xml:space="preserve">0.137842923402786</t>
@@ -983,28 +983,28 @@
     <t xml:space="preserve">0.137086570262909</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136771440505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136204198002815</t>
+    <t xml:space="preserve">0.13677142560482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136204183101654</t>
   </si>
   <si>
     <t xml:space="preserve">0.13500665128231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134754508733749</t>
+    <t xml:space="preserve">0.134754538536072</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137401700019836</t>
+    <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
     <t xml:space="preserve">0.15114189684391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153789073228836</t>
+    <t xml:space="preserve">0.153789058327675</t>
   </si>
   <si>
     <t xml:space="preserve">0.152780622243881</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">0.151267945766449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145280241966248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14704504609108</t>
+    <t xml:space="preserve">0.145280256867409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147045031189919</t>
   </si>
   <si>
     <t xml:space="preserve">0.157444715499878</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570764422417</t>
+    <t xml:space="preserve">0.157570779323578</t>
   </si>
   <si>
     <t xml:space="preserve">0.152843669056892</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152654573321342</t>
+    <t xml:space="preserve">0.152654558420181</t>
   </si>
   <si>
     <t xml:space="preserve">0.151898235082626</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">0.15309576690197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150259494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148746803402901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153347879648209</t>
+    <t xml:space="preserve">0.150259509682655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746818304062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15334789454937</t>
   </si>
   <si>
     <t xml:space="preserve">0.155805990099907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154419362545013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156940504908562</t>
+    <t xml:space="preserve">0.154419347643852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156940490007401</t>
   </si>
   <si>
     <t xml:space="preserve">0.15914648771286</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">0.167655318975449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170050382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167214125394821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067314386368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945841431618</t>
+    <t xml:space="preserve">0.170050397515297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16721411049366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067284584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945826530457</t>
   </si>
   <si>
     <t xml:space="preserve">0.178811311721802</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">0.174336314201355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170176431536674</t>
+    <t xml:space="preserve">0.170176461338997</t>
   </si>
   <si>
     <t xml:space="preserve">0.176479279994965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173643007874489</t>
+    <t xml:space="preserve">0.17364302277565</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365527272224</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">0.168600752949715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166520819067955</t>
+    <t xml:space="preserve">0.166520804166794</t>
   </si>
   <si>
     <t xml:space="preserve">0.166394740343094</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">0.160091906785965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156688362360001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16122642159462</t>
+    <t xml:space="preserve">0.156688392162323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161226436495781</t>
   </si>
   <si>
     <t xml:space="preserve">0.162487000226974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747519254684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873612880707</t>
+    <t xml:space="preserve">0.163747549057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873597979546</t>
   </si>
   <si>
     <t xml:space="preserve">0.161037310957909</t>
@@ -1142,34 +1142,34 @@
     <t xml:space="preserve">0.158011972904205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157759845256805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970433831215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167718321084976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165260225534439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163117274641991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163810595870018</t>
+    <t xml:space="preserve">0.157759860157967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970463633537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167718335986137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165260210633278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163117259740829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163810580968857</t>
   </si>
   <si>
     <t xml:space="preserve">0.159461617469788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147675320506096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147486239671707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150007382035255</t>
+    <t xml:space="preserve">0.147675335407257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147486254572868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150007396936417</t>
   </si>
   <si>
     <t xml:space="preserve">0.150448575615883</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">0.150511607527733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151078850030899</t>
+    <t xml:space="preserve">0.15107886493206</t>
   </si>
   <si>
     <t xml:space="preserve">0.151646122336388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150322511792183</t>
+    <t xml:space="preserve">0.150322526693344</t>
   </si>
   <si>
     <t xml:space="preserve">0.148494705557823</t>
@@ -1193,40 +1193,40 @@
     <t xml:space="preserve">0.150826752185822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151772186160088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881303310394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583090424538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149629220366478</t>
+    <t xml:space="preserve">0.151772171258926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881333112717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583105325699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149629205465317</t>
   </si>
   <si>
     <t xml:space="preserve">0.151709154248238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151015818119049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148935899138451</t>
+    <t xml:space="preserve">0.15101583302021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148935914039612</t>
   </si>
   <si>
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763735175133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150637671351433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15120492875576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149944350123405</t>
+    <t xml:space="preserve">0.150763720273972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150637656450272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151204913854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149944335222244</t>
   </si>
   <si>
     <t xml:space="preserve">0.152213364839554</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">0.152528494596481</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149377092719078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157255619764328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156310215592384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164503872394562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243323564529</t>
+    <t xml:space="preserve">0.149377107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157255634665489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156310230493546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164503917098045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243308663368</t>
   </si>
   <si>
     <t xml:space="preserve">0.162613019347191</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">0.161982759833336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163558453321457</t>
+    <t xml:space="preserve">0.163558468222618</t>
   </si>
   <si>
     <t xml:space="preserve">0.165764451026917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165449306368828</t>
+    <t xml:space="preserve">0.165449321269989</t>
   </si>
   <si>
     <t xml:space="preserve">0.166079610586166</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">0.160722196102142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162297889590263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061948060989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14717110991478</t>
+    <t xml:space="preserve">0.162297904491425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061962962151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147171095013618</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540820598602</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">0.142759144306183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144334822893143</t>
+    <t xml:space="preserve">0.144334837794304</t>
   </si>
   <si>
     <t xml:space="preserve">0.140238001942635</t>
@@ -1307,34 +1307,31 @@
     <t xml:space="preserve">0.135826006531715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138347148895264</t>
+    <t xml:space="preserve">0.138347163796425</t>
   </si>
   <si>
     <t xml:space="preserve">0.141498550772667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141813680529594</t>
+    <t xml:space="preserve">0.141813695430756</t>
   </si>
   <si>
     <t xml:space="preserve">0.140553131699562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141183421015739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138662278652191</t>
+    <t xml:space="preserve">0.141183406114578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138662293553352</t>
   </si>
   <si>
     <t xml:space="preserve">0.135510876774788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134880587458611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250298142433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935153484344</t>
+    <t xml:space="preserve">0.134250313043594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935168385506</t>
   </si>
   <si>
     <t xml:space="preserve">0.132674589753151</t>
@@ -1346,13 +1343,13 @@
     <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443969845772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575853228569</t>
+    <t xml:space="preserve">0.143389403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443984746933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575823426247</t>
   </si>
   <si>
     <t xml:space="preserve">0.147864416241646</t>
@@ -1361,22 +1358,22 @@
     <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14560940861702</t>
+    <t xml:space="preserve">0.145609423518181</t>
   </si>
   <si>
     <t xml:space="preserve">0.140455082058907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142710104584694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141421541571617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139166504144669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
+    <t xml:space="preserve">0.142710089683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141421556472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13916651904583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777245163918</t>
   </si>
   <si>
     <t xml:space="preserve">0.139488652348518</t>
@@ -1388,25 +1385,25 @@
     <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132723599672318</t>
+    <t xml:space="preserve">0.132723614573479</t>
   </si>
   <si>
     <t xml:space="preserve">0.13207933306694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129824310541153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125765278935432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124992124736309</t>
+    <t xml:space="preserve">0.129824325442314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125765293836594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124992154538631</t>
   </si>
   <si>
     <t xml:space="preserve">0.126796141266823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129180029034615</t>
+    <t xml:space="preserve">0.129180014133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.133367910981178</t>
@@ -1415,7 +1412,7 @@
     <t xml:space="preserve">0.131757184863091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125894159078598</t>
+    <t xml:space="preserve">0.125894144177437</t>
   </si>
   <si>
     <t xml:space="preserve">0.126925006508827</t>
@@ -1424,10 +1421,13 @@
     <t xml:space="preserve">0.125378727912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128600150346756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127440437674522</t>
+    <t xml:space="preserve">0.128600165247917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130468592047691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127440452575684</t>
   </si>
   <si>
     <t xml:space="preserve">0.127955868840218</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">0.124347850680351</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123703576624393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127311587333679</t>
+    <t xml:space="preserve">0.123703569173813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12731160223484</t>
   </si>
   <si>
     <t xml:space="preserve">0.127569317817688</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">0.126538440585136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12872901558876</t>
+    <t xml:space="preserve">0.128729030489922</t>
   </si>
   <si>
     <t xml:space="preserve">0.12834244966507</t>
@@ -1466,13 +1466,13 @@
     <t xml:space="preserve">0.129502177238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130146443843842</t>
+    <t xml:space="preserve">0.130146458745003</t>
   </si>
   <si>
     <t xml:space="preserve">0.134012192487717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134656473994255</t>
+    <t xml:space="preserve">0.134656488895416</t>
   </si>
   <si>
     <t xml:space="preserve">0.13852222263813</t>
@@ -1484,40 +1484,40 @@
     <t xml:space="preserve">0.135300770401955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130790740251541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128084734082222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128857865929604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125249862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122157268226147</t>
+    <t xml:space="preserve">0.13079072535038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128084719181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128857880830765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12524987757206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122157283127308</t>
   </si>
   <si>
     <t xml:space="preserve">0.123316988348961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125507578253746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128213584423065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126151874661446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127182707190514</t>
+    <t xml:space="preserve">0.125507593154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128213599324226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126151859760284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127182736992836</t>
   </si>
   <si>
     <t xml:space="preserve">0.125636428594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120482102036476</t>
+    <t xml:space="preserve">0.120482131838799</t>
   </si>
   <si>
     <t xml:space="preserve">0.122286133468151</t>
@@ -1532,82 +1532,82 @@
     <t xml:space="preserve">0.113266065716743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113394930958748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848630011082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112106345593929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114425793290138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683508872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112235225737095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110817797482014</t>
+    <t xml:space="preserve">0.113394923508167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848637461662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11210636049509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114425808191299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683516323566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112235218286514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110817782580853</t>
   </si>
   <si>
     <t xml:space="preserve">0.108240611851215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106565460562706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921171605587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101926572620869</t>
+    <t xml:space="preserve">0.106565475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921186506748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101926565170288</t>
   </si>
   <si>
     <t xml:space="preserve">0.105019174516201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103086307644844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374893009663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117169976234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10566346347332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107982903718948</t>
+    <t xml:space="preserve">0.103086300194263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117177426815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105663470923901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107982911169529</t>
   </si>
   <si>
     <t xml:space="preserve">0.108627177774906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108111754059792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11146205663681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750642001629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756050467491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173493623734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109529197216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106952026486397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153448224068</t>
+    <t xml:space="preserve">0.108111768960953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111462064087391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750649452209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756043016911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173478722572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109529212117195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106952033936977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153433322906</t>
   </si>
   <si>
     <t xml:space="preserve">0.103988312184811</t>
@@ -1616,124 +1616,124 @@
     <t xml:space="preserve">0.102699734270573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105276875197887</t>
+    <t xml:space="preserve">0.105276882648468</t>
   </si>
   <si>
     <t xml:space="preserve">0.111204355955124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115585528314114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115843236446381</t>
+    <t xml:space="preserve">0.115585513412952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843243896961</t>
   </si>
   <si>
     <t xml:space="preserve">0.115327805280685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113008365035057</t>
+    <t xml:space="preserve">0.113008379936218</t>
   </si>
   <si>
     <t xml:space="preserve">0.10940033942461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110431186854839</t>
+    <t xml:space="preserve">0.11043119430542</t>
   </si>
   <si>
     <t xml:space="preserve">0.107854053378105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103730574250221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1063077673316</t>
+    <t xml:space="preserve">0.103730581700802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10630775988102</t>
   </si>
   <si>
     <t xml:space="preserve">0.103859454393387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114554673433304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109142631292343</t>
+    <t xml:space="preserve">0.114554658532143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109142616391182</t>
   </si>
   <si>
     <t xml:space="preserve">0.109013773500919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108884923160076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271481633186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10733862221241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442011237144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411148905754</t>
+    <t xml:space="preserve">0.108884900808334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271474182606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107338607311249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442003786564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411141455173</t>
   </si>
   <si>
     <t xml:space="preserve">0.102055437862873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100251421332359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999937206506729</t>
+    <t xml:space="preserve">0.10025142878294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999937281012535</t>
   </si>
   <si>
     <t xml:space="preserve">0.10128229111433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101797714829445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766852498055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105148017406464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915763139725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111075475811958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112621784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302351415157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110688924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761451482773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534613132477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467472553253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108498327434063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080884277821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503750801086</t>
+    <t xml:space="preserve">0.101797722280025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766859948635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105148039758205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915770590305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111075505614281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112621791660786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302336513996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688909888268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761458933353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534598231316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467480003834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108498319983482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080891728401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503743350506</t>
   </si>
   <si>
     <t xml:space="preserve">0.105792313814163</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106436617672443</t>
+    <t xml:space="preserve">0.106436610221863</t>
   </si>
   <si>
     <t xml:space="preserve">0.105341322720051</t>
@@ -1742,19 +1742,19 @@
     <t xml:space="preserve">0.107596330344677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108562767505646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11018505692482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857141971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111168846487999</t>
+    <t xml:space="preserve">0.108562774956226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207056462765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185064375401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857127070427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11116885393858</t>
   </si>
   <si>
     <t xml:space="preserve">0.110513001680374</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">0.106905750930309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105921968817711</t>
+    <t xml:space="preserve">0.10592196136713</t>
   </si>
   <si>
     <t xml:space="preserve">0.103954367339611</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">0.104282289743423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105594001710415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217485249043</t>
+    <t xml:space="preserve">0.105594009160995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217477798462</t>
   </si>
   <si>
     <t xml:space="preserve">0.105266101658344</t>
@@ -1787,16 +1787,16 @@
     <t xml:space="preserve">0.10493815690279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102970577776432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103626422584057</t>
+    <t xml:space="preserve">0.102970570325851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103626437485218</t>
   </si>
   <si>
     <t xml:space="preserve">0.103298492729664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101658850908279</t>
+    <t xml:space="preserve">0.101658843457699</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347101688385</t>
@@ -1814,37 +1814,37 @@
     <t xml:space="preserve">0.0973957255482674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0951002016663551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0980515778064728</t>
+    <t xml:space="preserve">0.0951002091169357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0980515852570534</t>
   </si>
   <si>
     <t xml:space="preserve">0.0964119285345078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.09870745241642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0993633195757866</t>
+    <t xml:space="preserve">0.0987074598670006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099363312125206</t>
   </si>
   <si>
     <t xml:space="preserve">0.100019179284573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101002961397171</t>
+    <t xml:space="preserve">0.101002976298332</t>
   </si>
   <si>
     <t xml:space="preserve">0.1006750613451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102642633020878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0983795374631882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0996912494301796</t>
+    <t xml:space="preserve">0.102642647922039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.098379522562027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099691241979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.0990353748202324</t>
@@ -1853,28 +1853,28 @@
     <t xml:space="preserve">0.104610219597816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107561618089676</t>
+    <t xml:space="preserve">0.107561610639095</t>
   </si>
   <si>
     <t xml:space="preserve">0.108873330056667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108545407652855</t>
+    <t xml:space="preserve">0.108545415103436</t>
   </si>
   <si>
     <t xml:space="preserve">0.109201274812222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107233673334122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249891221523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11215265840292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114448174834251</t>
+    <t xml:space="preserve">0.107233680784702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249876320362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112152650952339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114448182284832</t>
   </si>
   <si>
     <t xml:space="preserve">0.111824721097946</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">0.112808525562286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113136447966099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480580806732</t>
+    <t xml:space="preserve">0.113136440515518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480603158474</t>
   </si>
   <si>
     <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130516827106476</t>
+    <t xml:space="preserve">0.130516842007637</t>
   </si>
   <si>
     <t xml:space="preserve">0.139698937535286</t>
@@ -1904,25 +1904,25 @@
     <t xml:space="preserve">0.141010642051697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160686567425728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173803806304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16724519431591</t>
+    <t xml:space="preserve">0.160686552524567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173803821206093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167245179414749</t>
   </si>
   <si>
     <t xml:space="preserve">0.155439645051956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150848597288132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154127910733223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157407224178314</t>
+    <t xml:space="preserve">0.150848612189293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154127925634384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157407239079475</t>
   </si>
   <si>
     <t xml:space="preserve">0.156751364469528</t>
@@ -1931,31 +1931,31 @@
     <t xml:space="preserve">0.15281617641449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148881003260612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145601689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146257564425468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146913424134254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150192722678185</t>
+    <t xml:space="preserve">0.148880988359451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145601704716682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146257549524307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146913409233093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150192737579346</t>
   </si>
   <si>
     <t xml:space="preserve">0.14953687787056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142978236079216</t>
+    <t xml:space="preserve">0.142978221178055</t>
   </si>
   <si>
     <t xml:space="preserve">0.14756928384304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148225143551826</t>
+    <t xml:space="preserve">0.148225158452988</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654146552086</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">0.135107859969139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133140280842781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137731343507767</t>
+    <t xml:space="preserve">0.133140295743942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137731328606606</t>
   </si>
   <si>
     <t xml:space="preserve">0.154783770442009</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">0.156095519661903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153472065925598</t>
+    <t xml:space="preserve">0.153472051024437</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
@@ -1997,19 +1997,19 @@
     <t xml:space="preserve">0.137075453996658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125597849488258</t>
+    <t xml:space="preserve">0.12559786438942</t>
   </si>
   <si>
     <t xml:space="preserve">0.126581653952599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123958200216293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118711277842522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110840931534767</t>
+    <t xml:space="preserve">0.123958192765713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118711292743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110840924084187</t>
   </si>
   <si>
     <t xml:space="preserve">0.0967398583889008</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">0.0826388001441956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.087885707616806</t>
+    <t xml:space="preserve">0.0878857001662254</t>
   </si>
   <si>
     <t xml:space="preserve">0.08722984790802</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">0.0918208956718445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0928046703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0944443419575691</t>
+    <t xml:space="preserve">0.0928046777844429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0944443345069885</t>
   </si>
   <si>
     <t xml:space="preserve">0.0960839986801147</t>
@@ -2045,40 +2045,40 @@
     <t xml:space="preserve">0.0931326150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0957560613751411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0937884822487831</t>
+    <t xml:space="preserve">0.0957560688257217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0937884747982025</t>
   </si>
   <si>
     <t xml:space="preserve">0.0965431109070778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0969366207718849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.097854845225811</t>
+    <t xml:space="preserve">0.0969366133213043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0978548377752304</t>
   </si>
   <si>
     <t xml:space="preserve">0.0971989706158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0924767553806305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0940508246421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0939196348190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0941819921135902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0949690416455269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937264323235</t>
+    <t xml:space="preserve">0.0924767479300499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0940508171916008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.093919649720192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0941819995641708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0949690490961075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937189817429</t>
   </si>
   <si>
     <t xml:space="preserve">0.0982483625411987</t>
@@ -2087,73 +2087,73 @@
     <t xml:space="preserve">0.100740633904934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0968054383993149</t>
+    <t xml:space="preserve">0.0968054607510567</t>
   </si>
   <si>
     <t xml:space="preserve">0.0966742858290672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110709749162197</t>
+    <t xml:space="preserve">0.110709756612778</t>
   </si>
   <si>
     <t xml:space="preserve">0.0979860052466393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0991665497422218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0936572998762131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0948378592729568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102183520793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999536067247391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103232905268669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104806981980801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14035476744175</t>
+    <t xml:space="preserve">0.0991665571928024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0936573073267937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0948378667235374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084774196148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102183535695076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999535992741585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10323291271925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104806989431381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
     <t xml:space="preserve">0.125925794243813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13838717341423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142322361469269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137403413653374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135435819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136419594287872</t>
+    <t xml:space="preserve">0.138387188315392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14232237637043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137403398752213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135435804724693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136419624090195</t>
   </si>
   <si>
     <t xml:space="preserve">0.134452015161514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134124085307121</t>
+    <t xml:space="preserve">0.13412407040596</t>
   </si>
   <si>
     <t xml:space="preserve">0.131041526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127893373370171</t>
+    <t xml:space="preserve">0.127893388271332</t>
   </si>
   <si>
     <t xml:space="preserve">0.134779945015907</t>
@@ -2174,16 +2174,16 @@
     <t xml:space="preserve">0.130385667085648</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131500616669655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130910351872444</t>
+    <t xml:space="preserve">0.131500631570816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130910336971283</t>
   </si>
   <si>
     <t xml:space="preserve">0.133468210697174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129992127418518</t>
+    <t xml:space="preserve">0.12999215722084</t>
   </si>
   <si>
     <t xml:space="preserve">0.126975163817406</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">0.133796155452728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132156506180763</t>
+    <t xml:space="preserve">0.132156491279602</t>
   </si>
   <si>
     <t xml:space="preserve">0.130648016929626</t>
@@ -2207,19 +2207,19 @@
     <t xml:space="preserve">0.129205092787743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129598617553711</t>
+    <t xml:space="preserve">0.129598632454872</t>
   </si>
   <si>
     <t xml:space="preserve">0.140026852488518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1297297924757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129860982298851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130254492163658</t>
+    <t xml:space="preserve">0.129729807376862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12986096739769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130254477262497</t>
   </si>
   <si>
     <t xml:space="preserve">0.129073917865753</t>
@@ -2228,19 +2228,19 @@
     <t xml:space="preserve">0.125138744711876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12461406737566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143634110689163</t>
+    <t xml:space="preserve">0.124614059925079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143634095788002</t>
   </si>
   <si>
     <t xml:space="preserve">0.143962040543556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370992779732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136091664433479</t>
+    <t xml:space="preserve">0.139370977878571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136091679334641</t>
   </si>
   <si>
     <t xml:space="preserve">0.138059258460999</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">0.140682712197304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144945815205574</t>
+    <t xml:space="preserve">0.144945830106735</t>
   </si>
   <si>
     <t xml:space="preserve">0.142650306224823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141994446516037</t>
+    <t xml:space="preserve">0.141994461417198</t>
   </si>
   <si>
     <t xml:space="preserve">0.144289970397949</t>
@@ -2270,34 +2270,34 @@
     <t xml:space="preserve">0.152488246560097</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157079309225082</t>
+    <t xml:space="preserve">0.157079294323921</t>
   </si>
   <si>
     <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153144136071205</t>
+    <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
     <t xml:space="preserve">0.155111715197563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155767574906349</t>
+    <t xml:space="preserve">0.155767560005188</t>
   </si>
   <si>
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702748060226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16298209130764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166917249560356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163309991359711</t>
+    <t xml:space="preserve">0.159702762961388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162982076406479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166917264461517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163310006260872</t>
   </si>
   <si>
     <t xml:space="preserve">0.162326201796532</t>
@@ -2309,19 +2309,19 @@
     <t xml:space="preserve">0.159046903252602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159374818205833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158718958497047</t>
+    <t xml:space="preserve">0.159374833106995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158718943595886</t>
   </si>
   <si>
     <t xml:space="preserve">0.158391028642654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160030677914619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158063098788261</t>
+    <t xml:space="preserve">0.160030692815781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1580630838871</t>
   </si>
   <si>
     <t xml:space="preserve">0.165341436862946</t>
@@ -2330,19 +2330,19 @@
     <t xml:space="preserve">0.163571178913116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162509024143219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161092847585678</t>
+    <t xml:space="preserve">0.162863090634346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16250903904438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161092832684517</t>
   </si>
   <si>
     <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157198294997215</t>
+    <t xml:space="preserve">0.157198280096054</t>
   </si>
   <si>
     <t xml:space="preserve">0.158260434865952</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">0.160384744405746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159322589635849</t>
+    <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
     <t xml:space="preserve">0.15755233168602</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">0.161800935864449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15507398545742</t>
+    <t xml:space="preserve">0.155073970556259</t>
   </si>
   <si>
     <t xml:space="preserve">0.153303727507591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155782073736191</t>
+    <t xml:space="preserve">0.155782088637352</t>
   </si>
   <si>
     <t xml:space="preserve">0.151533469557762</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011830687523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156136140227318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152241572737694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154365882277489</t>
+    <t xml:space="preserve">0.154011815786362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156136125326157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152241587638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15436589717865</t>
   </si>
   <si>
     <t xml:space="preserve">0.151887536048889</t>
@@ -2417,16 +2417,16 @@
     <t xml:space="preserve">0.15011727809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150825396180153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149763226509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150471329689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149055123329163</t>
+    <t xml:space="preserve">0.150825381278992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149763241410255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150471314787865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149055108428001</t>
   </si>
   <si>
     <t xml:space="preserve">0.146222725510597</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">0.147284880280495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1426822245121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143390327692032</t>
+    <t xml:space="preserve">0.142682239413261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143390312790871</t>
   </si>
   <si>
     <t xml:space="preserve">0.145514622330666</t>
@@ -2447,13 +2447,13 @@
     <t xml:space="preserve">0.148347035050392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149409160017967</t>
+    <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
     <t xml:space="preserve">0.152949675917625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1451605707407</t>
+    <t xml:space="preserve">0.145160585641861</t>
   </si>
   <si>
     <t xml:space="preserve">0.147638931870461</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">0.148701086640358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146576792001724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144452482461929</t>
+    <t xml:space="preserve">0.146576777100563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144452467560768</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">0.144806519150734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144098430871964</t>
+    <t xml:space="preserve">0.144098445773125</t>
   </si>
   <si>
     <t xml:space="preserve">0.14586865901947</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">0.147992968559265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165695488452911</t>
+    <t xml:space="preserve">0.16569547355175</t>
   </si>
   <si>
     <t xml:space="preserve">0.168527901172638</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">0.16746574640274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16498738527298</t>
+    <t xml:space="preserve">0.164987400174141</t>
   </si>
   <si>
     <t xml:space="preserve">0.163217127323151</t>
@@ -18524,7 +18524,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G571" t="s">
-        <v>438</v>
+        <v>104</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18550,7 +18550,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G572" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18576,7 +18576,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G573" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18602,7 +18602,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G574" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18628,7 +18628,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G575" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18654,7 +18654,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18888,7 +18888,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18914,7 +18914,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G586" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18966,7 +18966,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G588" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19070,7 +19070,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G592" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19096,7 +19096,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G593" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19122,7 +19122,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G594" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19148,7 +19148,7 @@
         <v>0.229499995708466</v>
       </c>
       <c r="G595" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19174,7 +19174,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19200,7 +19200,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G597" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19226,7 +19226,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G598" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19252,7 +19252,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G599" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19278,7 +19278,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G600" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19304,7 +19304,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G601" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19330,7 +19330,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G602" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19356,7 +19356,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G603" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19382,7 +19382,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G604" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19408,7 +19408,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G605" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19434,7 +19434,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G606" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19460,7 +19460,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19486,7 +19486,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G608" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19512,7 +19512,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G609" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19538,7 +19538,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G610" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19564,7 +19564,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G611" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19590,7 +19590,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G612" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19616,7 +19616,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G613" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19642,7 +19642,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19668,7 +19668,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G615" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19694,7 +19694,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G616" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19720,7 +19720,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G617" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19746,7 +19746,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G618" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19772,7 +19772,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G619" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19798,7 +19798,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G620" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19824,7 +19824,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G621" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19850,7 +19850,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19876,7 +19876,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G623" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19902,7 +19902,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G624" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19928,7 +19928,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G625" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19954,7 +19954,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G626" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19980,7 +19980,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G627" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20032,7 +20032,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G629" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20084,7 +20084,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G631" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20318,7 +20318,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G640" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20448,7 +20448,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G645" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20630,7 +20630,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G652" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20682,7 +20682,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G654" t="s">
-        <v>278</v>
+        <v>470</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20734,7 +20734,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G656" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20890,7 +20890,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G662" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20942,7 +20942,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G664" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20968,7 +20968,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G665" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20994,7 +20994,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G666" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21176,7 +21176,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G673" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21228,7 +21228,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G675" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21254,7 +21254,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G676" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21540,7 +21540,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G687" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21592,7 +21592,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G689" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21696,7 +21696,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G693" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21722,7 +21722,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21826,7 +21826,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G698" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -69695,6 +69695,32 @@
         <v>1078</v>
       </c>
       <c r="H2539" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2540">
+      <c r="A2540" s="1" t="n">
+        <v>46020.6910648148</v>
+      </c>
+      <c r="B2540" t="n">
+        <v>1302031</v>
+      </c>
+      <c r="C2540" t="n">
+        <v>0.172999992966652</v>
+      </c>
+      <c r="D2540" t="n">
+        <v>0.167500004172325</v>
+      </c>
+      <c r="E2540" t="n">
+        <v>0.167999997735023</v>
+      </c>
+      <c r="F2540" t="n">
+        <v>0.170499995350838</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H2540" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053874969482</t>
+    <t xml:space="preserve">0.158053904771805</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">0.155000299215317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153229236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150542065501213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148099184036255</t>
+    <t xml:space="preserve">0.153229206800461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150542050600052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148099198937416</t>
   </si>
   <si>
     <t xml:space="preserve">0.15029776096344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151580259203911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14736633002758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358422279358</t>
+    <t xml:space="preserve">0.151580274105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147366315126419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142358437180519</t>
   </si>
   <si>
     <t xml:space="preserve">0.132831230759621</t>
@@ -77,37 +77,37 @@
     <t xml:space="preserve">0.134541243314743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125319376587868</t>
+    <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121203303337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134358018636703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419098496437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143335595726967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138022348284721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137778058648109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140465185046196</t>
+    <t xml:space="preserve">0.134358033537865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419113397598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143335580825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13802233338356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137778043746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140465199947357</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136190190911293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131793007254601</t>
+    <t xml:space="preserve">0.136190161108971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131793022155762</t>
   </si>
   <si>
     <t xml:space="preserve">0.129166916012764</t>
@@ -116,49 +116,49 @@
     <t xml:space="preserve">0.12928906083107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118967927992344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754380106926</t>
+    <t xml:space="preserve">0.118967920541763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754387557507</t>
   </si>
   <si>
     <t xml:space="preserve">0.116158626973629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118479356169701</t>
+    <t xml:space="preserve">0.118479333817959</t>
   </si>
   <si>
     <t xml:space="preserve">0.125807970762253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125197246670723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960834980011</t>
+    <t xml:space="preserve">0.125197261571884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960864782333</t>
   </si>
   <si>
     <t xml:space="preserve">0.127029404044151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125014021992683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999073386192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129105865955353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128617256879807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130205154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130510494112968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129533335566521</t>
+    <t xml:space="preserve">0.125014051795006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999058485031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12910583615303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128617271780968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130205139517784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13051050901413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
     <t xml:space="preserve">0.133808389306068</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">0.138755187392235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13967128098011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136739835143089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136495545506477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140159860253334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14174772799015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147122040390968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14901527762413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146572381258011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145717367529869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143213450908661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144129499793053</t>
+    <t xml:space="preserve">0.139671266078949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136739820241928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136495530605316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140159830451012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141747698187828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14712205529213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149015262722969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146572396159172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14571738243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1432134360075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144129529595375</t>
   </si>
   <si>
     <t xml:space="preserve">0.140892714262009</t>
@@ -206,43 +206,43 @@
     <t xml:space="preserve">0.139793425798416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134968727827072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068031191826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13594588637352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135823726654053</t>
+    <t xml:space="preserve">0.134968757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068046092987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135945901274681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135823741555214</t>
   </si>
   <si>
     <t xml:space="preserve">0.133136585354805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130693718791008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128861576318741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125258296728134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133930519223213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137472689151764</t>
+    <t xml:space="preserve">0.130693703889847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128861546516418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125258311629295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133930534124374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137472674250603</t>
   </si>
   <si>
     <t xml:space="preserve">0.142480567097664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142114132642746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141320213675499</t>
+    <t xml:space="preserve">0.142114162445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141320183873177</t>
   </si>
   <si>
     <t xml:space="preserve">0.14217521250248</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">0.138327687978745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142236292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138205528259277</t>
+    <t xml:space="preserve">0.142236277461052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1382055580616</t>
   </si>
   <si>
     <t xml:space="preserve">0.140526756644249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139899402856827</t>
+    <t xml:space="preserve">0.139899387955666</t>
   </si>
   <si>
     <t xml:space="preserve">0.136135280132294</t>
@@ -272,79 +272,79 @@
     <t xml:space="preserve">0.133876830339432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133814081549644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132998496294022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129234418272972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128732517361641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125156626105309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126662284135818</t>
+    <t xml:space="preserve">0.133814066648483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132998511195183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129234433174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128732547163963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12515664100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126662269234657</t>
   </si>
   <si>
     <t xml:space="preserve">0.126725018024445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127352356910706</t>
+    <t xml:space="preserve">0.127352371811867</t>
   </si>
   <si>
     <t xml:space="preserve">0.127979710698128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126599535346031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127916976809502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130489125847816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131743803620338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131116464734077</t>
+    <t xml:space="preserve">0.126599550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127916991710663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130489110946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1317438185215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131116479635239</t>
   </si>
   <si>
     <t xml:space="preserve">0.131555631756783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134065017104149</t>
+    <t xml:space="preserve">0.134065046906471</t>
   </si>
   <si>
     <t xml:space="preserve">0.131179198622704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133688613772392</t>
+    <t xml:space="preserve">0.133688628673553</t>
   </si>
   <si>
     <t xml:space="preserve">0.134880587458611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134190499782562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130614593625069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132873043417931</t>
+    <t xml:space="preserve">0.134190484881401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13061460852623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132873058319092</t>
   </si>
   <si>
     <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121078848838806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120200552046299</t>
+    <t xml:space="preserve">0.121078841388226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12020055949688</t>
   </si>
   <si>
     <t xml:space="preserve">0.1218316629529</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">0.110413864254951</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112233199179173</t>
+    <t xml:space="preserve">0.112233191728592</t>
   </si>
   <si>
     <t xml:space="preserve">0.114366188645363</t>
@@ -362,34 +362,34 @@
     <t xml:space="preserve">0.111794047057629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114052504301071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395063757896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893192648888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041232943535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904493808746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354909837246</t>
+    <t xml:space="preserve">0.11405248939991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395071208477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893162846565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041225492954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904464006424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354887485504</t>
   </si>
   <si>
     <t xml:space="preserve">0.110727541148663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107277132570744</t>
+    <t xml:space="preserve">0.107277110219002</t>
   </si>
   <si>
     <t xml:space="preserve">0.102822914719582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100501723587513</t>
+    <t xml:space="preserve">0.100501716136932</t>
   </si>
   <si>
     <t xml:space="preserve">0.107716262340546</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">0.110790275037289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114554405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923286855221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303447306156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632189929485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116561897099018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116373710334301</t>
+    <t xml:space="preserve">0.114554397761822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11292327195406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303454756737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632182478905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116561904549599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11637369543314</t>
   </si>
   <si>
     <t xml:space="preserve">0.115746349096298</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">0.115432694554329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114805318415165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185523569584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569456040859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820384144783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934573113918</t>
+    <t xml:space="preserve">0.114805303514004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185516119003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569448590279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820391595364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934558212757</t>
   </si>
   <si>
     <t xml:space="preserve">0.109159171581268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107088908553123</t>
+    <t xml:space="preserve">0.107088901102543</t>
   </si>
   <si>
     <t xml:space="preserve">0.10614787787199</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">0.105645999312401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107465319335461</t>
+    <t xml:space="preserve">0.10746531188488</t>
   </si>
   <si>
     <t xml:space="preserve">0.108531817793846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107590794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535567462444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10483043640852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092673122883</t>
+    <t xml:space="preserve">0.107590802013874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535589814186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1048304438591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092665672302</t>
   </si>
   <si>
     <t xml:space="preserve">0.108029924333096</t>
@@ -476,76 +476,76 @@
     <t xml:space="preserve">0.107653513550758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109849251806736</t>
+    <t xml:space="preserve">0.109849259257317</t>
   </si>
   <si>
     <t xml:space="preserve">0.110978484153748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111605852842331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738834857941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864310085773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11028841137886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225670039654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845479786396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723791480064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339859008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406357467175</t>
+    <t xml:space="preserve">0.11160583794117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113738849759102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864302635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110288396477699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225662589073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845494687557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723776578903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339851558208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406350016594</t>
   </si>
   <si>
     <t xml:space="preserve">0.104516759514809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105018652975559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10664976388216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105834186077118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085151433945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10978652536869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104391306638718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107778988778591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214383780956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11606003344059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1147425994277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11242138594389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425150513649</t>
+    <t xml:space="preserve">0.105018645524979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106649771332741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10583421587944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085136532784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10978651791811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104391291737556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107778996229172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214398682117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060040891171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114742584526539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112421408295631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11342516541481</t>
   </si>
   <si>
     <t xml:space="preserve">0.112295925617218</t>
@@ -554,40 +554,40 @@
     <t xml:space="preserve">0.106022417545319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106712505221367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837958097458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520524084568</t>
+    <t xml:space="preserve">0.106712497770786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520531535149</t>
   </si>
   <si>
     <t xml:space="preserve">0.104265823960304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102760173380375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003602147102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579508304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885663509369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889413177967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254545152187</t>
+    <t xml:space="preserve">0.102760188281536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003587245941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579500854015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885648608208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889428079128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254537701607</t>
   </si>
   <si>
     <t xml:space="preserve">0.10056446492672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101066328585148</t>
+    <t xml:space="preserve">0.101066336035728</t>
   </si>
   <si>
     <t xml:space="preserve">0.101630955934525</t>
@@ -596,22 +596,22 @@
     <t xml:space="preserve">0.106524296104908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109911993145943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539354383945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110915750265121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657278120518</t>
+    <t xml:space="preserve">0.109911985695362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539346933365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110915757715702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657293021679</t>
   </si>
   <si>
     <t xml:space="preserve">0.11260960996151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111292161047459</t>
+    <t xml:space="preserve">0.111292153596878</t>
   </si>
   <si>
     <t xml:space="preserve">0.109410114586353</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">0.108343601226807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108280874788761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033703804016</t>
+    <t xml:space="preserve">0.1082808598876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033696353436</t>
   </si>
   <si>
     <t xml:space="preserve">0.110351145267487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128544345498085</t>
+    <t xml:space="preserve">0.128544330596924</t>
   </si>
   <si>
     <t xml:space="preserve">0.15370112657547</t>
@@ -641,46 +641,46 @@
     <t xml:space="preserve">0.142408788204193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132371187210083</t>
+    <t xml:space="preserve">0.132371172308922</t>
   </si>
   <si>
     <t xml:space="preserve">0.132684856653214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134253233671188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304666399956</t>
+    <t xml:space="preserve">0.13425324857235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304681301117</t>
   </si>
   <si>
     <t xml:space="preserve">0.134692370891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135821625590324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836668968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855469465256</t>
+    <t xml:space="preserve">0.135821610689163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836654067039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855484366417</t>
   </si>
   <si>
     <t xml:space="preserve">0.143161624670029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141781464219093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133500397205353</t>
+    <t xml:space="preserve">0.141781434416771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133500427007675</t>
   </si>
   <si>
     <t xml:space="preserve">0.129861772060394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130175456404686</t>
+    <t xml:space="preserve">0.130175441503525</t>
   </si>
   <si>
     <t xml:space="preserve">0.131681084632874</t>
@@ -692,46 +692,46 @@
     <t xml:space="preserve">0.130740076303482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124842964112759</t>
+    <t xml:space="preserve">0.124842949211597</t>
   </si>
   <si>
     <t xml:space="preserve">0.126097664237022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975953578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289652824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226904034615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126411333680153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1254703104496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126536801457405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215617775917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12597219645977</t>
+    <t xml:space="preserve">0.126975983381271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289623022079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226889133453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126411348581314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125470325350761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126536786556244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215595424175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125972181558609</t>
   </si>
   <si>
     <t xml:space="preserve">0.130551859736443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130677327513695</t>
+    <t xml:space="preserve">0.130677312612534</t>
   </si>
   <si>
     <t xml:space="preserve">0.132182970643044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129171699285507</t>
+    <t xml:space="preserve">0.129171684384346</t>
   </si>
   <si>
     <t xml:space="preserve">0.13224570453167</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">0.133939549326897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134127765893936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136260747909546</t>
+    <t xml:space="preserve">0.134127750992775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136260762810707</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943321347237</t>
@@ -755,55 +755,55 @@
     <t xml:space="preserve">0.137766391038895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13801734149456</t>
+    <t xml:space="preserve">0.138017326593399</t>
   </si>
   <si>
     <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145733758807182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144165381789207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14397719502449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14115409553051</t>
+    <t xml:space="preserve">0.145733773708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165396690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141154065728188</t>
   </si>
   <si>
     <t xml:space="preserve">0.137640938162804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136762633919716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629637002945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002298116684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133437663316727</t>
+    <t xml:space="preserve">0.136762604117393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629651904106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002283215523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133437678217888</t>
   </si>
   <si>
     <t xml:space="preserve">0.129673555493355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356128931046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496654987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135633409023285</t>
+    <t xml:space="preserve">0.128356114029884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496640086174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135633379220963</t>
   </si>
   <si>
     <t xml:space="preserve">0.137891873717308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137703657150269</t>
+    <t xml:space="preserve">0.137703686952591</t>
   </si>
   <si>
     <t xml:space="preserve">0.132433906197548</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">0.131729170680046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130720719695091</t>
+    <t xml:space="preserve">0.13072070479393</t>
   </si>
   <si>
     <t xml:space="preserve">0.13317883014679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134565442800522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943619370461</t>
+    <t xml:space="preserve">0.134565427899361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943604469299</t>
   </si>
   <si>
     <t xml:space="preserve">0.131792187690735</t>
@@ -854,43 +854,43 @@
     <t xml:space="preserve">0.129964381456375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129586219787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002045512199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127947464585304</t>
+    <t xml:space="preserve">0.127506271004677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129586204886436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002060413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127947479486465</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199577331543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12870380282402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371771097183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125930577516556</t>
+    <t xml:space="preserve">0.128703817725182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125930562615395</t>
   </si>
   <si>
     <t xml:space="preserve">0.127128094434738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126056626439095</t>
+    <t xml:space="preserve">0.126056641340256</t>
   </si>
   <si>
     <t xml:space="preserve">0.12479604780674</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124669998884201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124165765941143</t>
+    <t xml:space="preserve">0.124670013785362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124165773391724</t>
   </si>
   <si>
     <t xml:space="preserve">0.125174224376678</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">0.125237256288528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129018932580948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127380207180977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128451704978943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136545419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884432673454</t>
+    <t xml:space="preserve">0.129018947482109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127380222082138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128451690077782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136560320854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884447574615</t>
   </si>
   <si>
     <t xml:space="preserve">0.127443239092827</t>
@@ -920,22 +920,22 @@
     <t xml:space="preserve">0.126938998699188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128262624144554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126875996589661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126497834920883</t>
+    <t xml:space="preserve">0.128262609243393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126875981688499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126497820019722</t>
   </si>
   <si>
     <t xml:space="preserve">0.126308724284172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430913090706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135573908686638</t>
+    <t xml:space="preserve">0.133430927991867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135573893785477</t>
   </si>
   <si>
     <t xml:space="preserve">0.135762974619865</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">0.134061217308044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132485508918762</t>
+    <t xml:space="preserve">0.132485494017601</t>
   </si>
   <si>
     <t xml:space="preserve">0.133556991815567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13519574701786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136141166090965</t>
+    <t xml:space="preserve">0.135195732116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136141151189804</t>
   </si>
   <si>
     <t xml:space="preserve">0.134439378976822</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">0.137464746832848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137716844677925</t>
+    <t xml:space="preserve">0.137716874480247</t>
   </si>
   <si>
     <t xml:space="preserve">0.138221085071564</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">0.137842923402786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136330246925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13708658516407</t>
+    <t xml:space="preserve">0.136330232024193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137086570262909</t>
   </si>
   <si>
     <t xml:space="preserve">0.13677142560482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136204183101654</t>
+    <t xml:space="preserve">0.136204198002815</t>
   </si>
   <si>
     <t xml:space="preserve">0.13500665128231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134754508733749</t>
+    <t xml:space="preserve">0.134754523634911</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137401714920998</t>
+    <t xml:space="preserve">0.137401700019836</t>
   </si>
   <si>
     <t xml:space="preserve">0.15114189684391</t>
@@ -1010,10 +1010,10 @@
     <t xml:space="preserve">0.152780622243881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151267945766449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14528027176857</t>
+    <t xml:space="preserve">0.151267930865288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145280241966248</t>
   </si>
   <si>
     <t xml:space="preserve">0.14704504609108</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570779323578</t>
+    <t xml:space="preserve">0.157570764422417</t>
   </si>
   <si>
     <t xml:space="preserve">0.152843669056892</t>
@@ -1037,109 +1037,109 @@
     <t xml:space="preserve">0.152654573321342</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151898220181465</t>
+    <t xml:space="preserve">0.151898235082626</t>
   </si>
   <si>
     <t xml:space="preserve">0.15309576690197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150259494781494</t>
+    <t xml:space="preserve">0.150259479880333</t>
   </si>
   <si>
     <t xml:space="preserve">0.148746818304062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153347879648209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805960297585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419347643852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156940490007401</t>
+    <t xml:space="preserve">0.15334789454937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805990099907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419362545013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156940504908562</t>
   </si>
   <si>
     <t xml:space="preserve">0.15914648771286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16765533387661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050397515297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167214095592499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067284584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945841431618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811311721802</t>
+    <t xml:space="preserve">0.167655304074287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050382614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167214140295982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067314386368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811296820641</t>
   </si>
   <si>
     <t xml:space="preserve">0.17521870136261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174336299300194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176461338997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479279994965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173642992973328</t>
+    <t xml:space="preserve">0.174336314201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176431536674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479265093803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173643007874489</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365527272224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166205644607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222561478615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168600723147392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166520819067955</t>
+    <t xml:space="preserve">0.166205659508705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222576379776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168600752949715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166520804166794</t>
   </si>
   <si>
     <t xml:space="preserve">0.166394740343094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161730661988258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160091921687126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156688392162323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16122642159462</t>
+    <t xml:space="preserve">0.161730647087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160091906785965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156688377261162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161226436495781</t>
   </si>
   <si>
     <t xml:space="preserve">0.162486985325813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747534155846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873583078384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161037340760231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158011972904205</t>
+    <t xml:space="preserve">0.163747519254684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873612880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161037310957909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158011987805367</t>
   </si>
   <si>
     <t xml:space="preserve">0.157759845256805</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">0.167718335986137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1652602404356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163117259740829</t>
+    <t xml:space="preserve">0.165260225534439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163117274641991</t>
   </si>
   <si>
     <t xml:space="preserve">0.163810580968857</t>
@@ -1166,16 +1166,16 @@
     <t xml:space="preserve">0.147675335407257</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147486254572868</t>
+    <t xml:space="preserve">0.147486224770546</t>
   </si>
   <si>
     <t xml:space="preserve">0.150007382035255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150448590517044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511607527733</t>
+    <t xml:space="preserve">0.150448575615883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511622428894</t>
   </si>
   <si>
     <t xml:space="preserve">0.15107886493206</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">0.151646122336388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150322511792183</t>
+    <t xml:space="preserve">0.150322496891022</t>
   </si>
   <si>
     <t xml:space="preserve">0.148494690656662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150826767086983</t>
+    <t xml:space="preserve">0.15082673728466</t>
   </si>
   <si>
     <t xml:space="preserve">0.151772171258926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149881333112717</t>
+    <t xml:space="preserve">0.149881318211555</t>
   </si>
   <si>
     <t xml:space="preserve">0.151583090424538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149629220366478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709154248238</t>
+    <t xml:space="preserve">0.149629205465317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709169149399</t>
   </si>
   <si>
     <t xml:space="preserve">0.15101583302021</t>
@@ -1220,64 +1220,64 @@
     <t xml:space="preserve">0.150763720273972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150637671351433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151204913854599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149944350123405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213364839554</t>
+    <t xml:space="preserve">0.150637656450272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15120492875576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149944365024567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213379740715</t>
   </si>
   <si>
     <t xml:space="preserve">0.152528509497643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149377092719078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157255634665489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156310200691223</t>
+    <t xml:space="preserve">0.149377107620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157255619764328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156310215592384</t>
   </si>
   <si>
     <t xml:space="preserve">0.164503887295723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163243338465691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613019347191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982759833336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163558468222618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165764451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165449321269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079595685005</t>
+    <t xml:space="preserve">0.163243323564529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16261300444603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982744932175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163558453321457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165764465928078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165449306368828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079610586166</t>
   </si>
   <si>
     <t xml:space="preserve">0.160722196102142</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162297904491425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149061933159828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147171095013618</t>
+    <t xml:space="preserve">0.162297889590263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149061948060989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540820598602</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">0.146225675940514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142759129405022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334837794304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140237987041473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139607682824135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138032004237175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139922842383385</t>
+    <t xml:space="preserve">0.142759144306183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334822893143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140238001942635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139607697725296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138032019138336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139922857284546</t>
   </si>
   <si>
     <t xml:space="preserve">0.135826006531715</t>
@@ -1310,28 +1310,31 @@
     <t xml:space="preserve">0.138347148895264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141498535871506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813695430756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140553161501884</t>
+    <t xml:space="preserve">0.141498550772667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813680529594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140553116798401</t>
   </si>
   <si>
     <t xml:space="preserve">0.141183421015739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138662293553352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135510861873627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250298142433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935168385506</t>
+    <t xml:space="preserve">0.138662278652191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135510876774788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134880602359772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134250313043594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935153484344</t>
   </si>
   <si>
     <t xml:space="preserve">0.132674604654312</t>
@@ -1346,19 +1349,16 @@
     <t xml:space="preserve">0.143389418721199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142443984746933</t>
+    <t xml:space="preserve">0.142443969845772</t>
   </si>
   <si>
     <t xml:space="preserve">0.146575838327408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147864431142807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146253705024719</t>
+    <t xml:space="preserve">0.147864416241646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
     <t xml:space="preserve">0.14560940861702</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">0.140777230262756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139488652348518</t>
+    <t xml:space="preserve">0.13948866724968</t>
   </si>
   <si>
     <t xml:space="preserve">0.135622918605804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133690059185028</t>
+    <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
     <t xml:space="preserve">0.132723599672318</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">0.129824310541153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125765278935432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12499213963747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126796156167984</t>
+    <t xml:space="preserve">0.125765293836594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12499213218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126796141266823</t>
   </si>
   <si>
     <t xml:space="preserve">0.129180029034615</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">0.133367910981178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131757184863091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125894129276276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126924991607666</t>
+    <t xml:space="preserve">0.131757169961929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125894159078598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126925006508827</t>
   </si>
   <si>
     <t xml:space="preserve">0.125378727912903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128600165247917</t>
+    <t xml:space="preserve">0.128600150346756</t>
   </si>
   <si>
     <t xml:space="preserve">0.127440437674522</t>
@@ -1436,19 +1436,19 @@
     <t xml:space="preserve">0.127827018499374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12602299451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124347865581512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703569173813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127311587333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127569302916527</t>
+    <t xml:space="preserve">0.126023009419441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124347850680351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703576624393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12731160223484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127569317817688</t>
   </si>
   <si>
     <t xml:space="preserve">0.12666729092598</t>
@@ -1460,10 +1460,10 @@
     <t xml:space="preserve">0.128729030489922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128342464566231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129502162337303</t>
+    <t xml:space="preserve">0.12834244966507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129502177238464</t>
   </si>
   <si>
     <t xml:space="preserve">0.130146458745003</t>
@@ -1475,40 +1475,40 @@
     <t xml:space="preserve">0.134656473994255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13852222263813</t>
+    <t xml:space="preserve">0.138522207736969</t>
   </si>
   <si>
     <t xml:space="preserve">0.13820007443428</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135300770401955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130790740251541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128084719181061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128857895731926</t>
+    <t xml:space="preserve">0.135300785303116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130790755152702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128084734082222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128857880830765</t>
   </si>
   <si>
     <t xml:space="preserve">0.125249862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122157283127308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123317003250122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125507578253746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128213599324226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126151859760284</t>
+    <t xml:space="preserve">0.122157268226147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12331698089838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125507563352585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128213584423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126151874661446</t>
   </si>
   <si>
     <t xml:space="preserve">0.127182722091675</t>
@@ -1517,70 +1517,70 @@
     <t xml:space="preserve">0.125636428594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120482131838799</t>
+    <t xml:space="preserve">0.120482116937637</t>
   </si>
   <si>
     <t xml:space="preserve">0.122286133468151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122414983808994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260664701462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266073167324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113394930958748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848644912243</t>
+    <t xml:space="preserve">0.122414991259575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260672152042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266065716743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113394923508167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848637461662</t>
   </si>
   <si>
     <t xml:space="preserve">0.112106345593929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114425785839558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683516323566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112235195934772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110817782580853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108240619301796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565460562706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921171605587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101926580071449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105019152164459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103086285293102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374878108501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117162525654</t>
+    <t xml:space="preserve">0.114425793290138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683508872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112235218286514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110817797482014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108240611851215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565468013287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921179056168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101926572620869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105019174516201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103086307644844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374893009663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117169976234</t>
   </si>
   <si>
     <t xml:space="preserve">0.10566346347332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107982903718948</t>
+    <t xml:space="preserve">0.107982911169529</t>
   </si>
   <si>
     <t xml:space="preserve">0.108627177774906</t>
@@ -1589,76 +1589,76 @@
     <t xml:space="preserve">0.108111754059792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111462064087391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750649452209</t>
+    <t xml:space="preserve">0.11146205663681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750642001629</t>
   </si>
   <si>
     <t xml:space="preserve">0.108756043016911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110173493623734</t>
+    <t xml:space="preserve">0.110173486173153</t>
   </si>
   <si>
     <t xml:space="preserve">0.109529197216034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106952041387558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153425872326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103988312184811</t>
+    <t xml:space="preserve">0.106952026486397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153448224068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103988319635391</t>
   </si>
   <si>
     <t xml:space="preserve">0.102699734270573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105276897549629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111204341053963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115585520863533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1158432289958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327805280685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113008372485638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109400361776352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110431201756001</t>
+    <t xml:space="preserve">0.105276867747307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111204355955124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115585528314114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843243896961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327797830105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113008365035057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10940033197403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110431186854839</t>
   </si>
   <si>
     <t xml:space="preserve">0.107854053378105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103730589151382</t>
+    <t xml:space="preserve">0.103730574250221</t>
   </si>
   <si>
     <t xml:space="preserve">0.10630775988102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103859461843967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554665982723</t>
+    <t xml:space="preserve">0.103859454393387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554673433304</t>
   </si>
   <si>
     <t xml:space="preserve">0.109142638742924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109013758599758</t>
+    <t xml:space="preserve">0.109013766050339</t>
   </si>
   <si>
     <t xml:space="preserve">0.108884923160076</t>
@@ -1673,40 +1673,40 @@
     <t xml:space="preserve">0.102442011237144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101411156356335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055437862873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100251436233521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999937206506729</t>
+    <t xml:space="preserve">0.101411148905754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055430412292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100251421332359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999937281012535</t>
   </si>
   <si>
     <t xml:space="preserve">0.10128228366375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101797729730606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766867399216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105148032307625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915770590305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11107549071312</t>
+    <t xml:space="preserve">0.101797714829445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766852498055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105148024857044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915763139725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111075483262539</t>
   </si>
   <si>
     <t xml:space="preserve">0.112621784210205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110302343964577</t>
+    <t xml:space="preserve">0.110302358865738</t>
   </si>
   <si>
     <t xml:space="preserve">0.110688932240009</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">0.104761451482773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105534598231316</t>
+    <t xml:space="preserve">0.105534613132477</t>
   </si>
   <si>
     <t xml:space="preserve">0.107467472553253</t>
@@ -1727,43 +1727,43 @@
     <t xml:space="preserve">0.107080891728401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104503743350506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792328715324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436602771282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10534130781889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596322894096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562774956226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207041561604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110185064375401</t>
+    <t xml:space="preserve">0.104503750801086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792306363583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436617672443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105341322720051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596330344677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562767505646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185049474239</t>
   </si>
   <si>
     <t xml:space="preserve">0.109857149422169</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111168839037418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110512994229794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889547944069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10690575838089</t>
+    <t xml:space="preserve">0.111168846487999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110513001680374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889533042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106905750930309</t>
   </si>
   <si>
     <t xml:space="preserve">0.10592196136713</t>
@@ -1772,112 +1772,112 @@
     <t xml:space="preserve">0.103954374790192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104282297194004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105594016611576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266079306602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104938149452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102970562875271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103626444935799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103298500180244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101658843457699</t>
+    <t xml:space="preserve">0.104282282292843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105594001710415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217492699623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266101658344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10493815690279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102970577776432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103626430034637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103298492729664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101658850908279</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347101688385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330913603306</t>
+    <t xml:space="preserve">0.101330898702145</t>
   </si>
   <si>
     <t xml:space="preserve">0.0970677956938744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0977236703038216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957180976868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951002091169357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.098051592707634</t>
+    <t xml:space="preserve">0.097723662853241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957255482674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951002016663551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0980515778064728</t>
   </si>
   <si>
     <t xml:space="preserve">0.0964119285345078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0987074598670006</t>
+    <t xml:space="preserve">0.09870745241642</t>
   </si>
   <si>
     <t xml:space="preserve">0.0993633195757866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100019179284573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002983748913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100675046443939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102642618119717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0983795300126076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099691241979599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099035382270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104610219597816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107561603188515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108873337507248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545392751694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109201267361641</t>
+    <t xml:space="preserve">0.100019186735153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002961397171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10067505389452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102642625570297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0983795374631882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0996912494301796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0990353673696518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104610227048397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107561610639095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108873330056667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545407652855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109201274812222</t>
   </si>
   <si>
     <t xml:space="preserve">0.107233673334122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106249891221523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112152673304081</t>
+    <t xml:space="preserve">0.106249898672104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11215265840292</t>
   </si>
   <si>
     <t xml:space="preserve">0.114448174834251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111824743449688</t>
+    <t xml:space="preserve">0.111824728548527</t>
   </si>
   <si>
     <t xml:space="preserve">0.112808533012867</t>
@@ -1886,73 +1886,73 @@
     <t xml:space="preserve">0.113136447966099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112480588257313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496783792973</t>
+    <t xml:space="preserve">0.112480580806732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
     <t xml:space="preserve">0.130516827106476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139698922634125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132484436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141010656952858</t>
+    <t xml:space="preserve">0.139698937535286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132484421133995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141010642051697</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686552524567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173803806304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16724519431591</t>
+    <t xml:space="preserve">0.173803821206093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167245179414749</t>
   </si>
   <si>
     <t xml:space="preserve">0.155439645051956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150848612189293</t>
+    <t xml:space="preserve">0.150848597288132</t>
   </si>
   <si>
     <t xml:space="preserve">0.154127910733223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157407239079475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156751379370689</t>
+    <t xml:space="preserve">0.157407224178314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156751364469528</t>
   </si>
   <si>
     <t xml:space="preserve">0.152816191315651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148881018161774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145601689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146257564425468</t>
+    <t xml:space="preserve">0.148881003260612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145601704716682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146257549524307</t>
   </si>
   <si>
     <t xml:space="preserve">0.146913424134254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150192752480507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149536862969398</t>
+    <t xml:space="preserve">0.150192722678185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149536892771721</t>
   </si>
   <si>
     <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147569268941879</t>
+    <t xml:space="preserve">0.14756928384304</t>
   </si>
   <si>
     <t xml:space="preserve">0.148225143551826</t>
@@ -1961,40 +1961,40 @@
     <t xml:space="preserve">0.162654146552086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161342427134514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141666516661644</t>
+    <t xml:space="preserve">0.161342442035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141666501760483</t>
   </si>
   <si>
     <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1351078748703</t>
+    <t xml:space="preserve">0.135107859969139</t>
   </si>
   <si>
     <t xml:space="preserve">0.133140295743942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137731328606606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154783800244331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156095504760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153472036123276</t>
+    <t xml:space="preserve">0.137731343507767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15478378534317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156095519661903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153472051024437</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135763734579086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13707546889782</t>
+    <t xml:space="preserve">0.135763749480247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137075453996658</t>
   </si>
   <si>
     <t xml:space="preserve">0.125597849488258</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">0.126581653952599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123958192765713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118711292743683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110840924084187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0967398509383202</t>
+    <t xml:space="preserve">0.123958207666874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118711277842522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110840931534767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0967398583889008</t>
   </si>
   <si>
     <t xml:space="preserve">0.0826388001441956</t>
@@ -2024,37 +2024,37 @@
     <t xml:space="preserve">0.08722984790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0885415822267532</t>
+    <t xml:space="preserve">0.0885415747761726</t>
   </si>
   <si>
     <t xml:space="preserve">0.0911650210618973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0918208882212639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0928046852350235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0944443270564079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0960839986801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0931326225399971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0957560688257217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0937884747982025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0965431183576584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0969366058707237</t>
+    <t xml:space="preserve">0.0918208956718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0928046703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0944443345069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0960839912295341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0931326076388359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0957560613751411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0937884822487831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0965431109070778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0969366133213043</t>
   </si>
   <si>
     <t xml:space="preserve">0.0978548377752304</t>
@@ -2066,25 +2066,25 @@
     <t xml:space="preserve">0.0924767479300499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.094050832092762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.093919649720192</t>
+    <t xml:space="preserve">0.0940508246421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
     <t xml:space="preserve">0.0941819995641708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0949690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937115311623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483550906181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740641355515</t>
+    <t xml:space="preserve">0.0949690416455269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937264323235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740626454353</t>
   </si>
   <si>
     <t xml:space="preserve">0.0968054458498955</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">0.0966742858290672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110709756612778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0979859903454781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0991665571928024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0936573073267937</t>
+    <t xml:space="preserve">0.110709749162197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0979860052466393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0991665497422218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0936572998762131</t>
   </si>
   <si>
     <t xml:space="preserve">0.0948378592729568</t>
@@ -2111,16 +2111,16 @@
     <t xml:space="preserve">0.100084774196148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102183528244495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999535992741585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10323292016983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10480697453022</t>
+    <t xml:space="preserve">0.102183520793915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999536067247391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103232905268669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104806981980801</t>
   </si>
   <si>
     <t xml:space="preserve">0.140354782342911</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">0.125925794243813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138387188315392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142322361469269</t>
+    <t xml:space="preserve">0.13838717341423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14232237637043</t>
   </si>
   <si>
     <t xml:space="preserve">0.137403398752213</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">0.13412407040596</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131041541695595</t>
+    <t xml:space="preserve">0.131041511893272</t>
   </si>
   <si>
     <t xml:space="preserve">0.127893373370171</t>
@@ -2159,34 +2159,34 @@
     <t xml:space="preserve">0.134779945015907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131172701716423</t>
+    <t xml:space="preserve">0.131172686815262</t>
   </si>
   <si>
     <t xml:space="preserve">0.130779176950455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130123317241669</t>
+    <t xml:space="preserve">0.130123302340508</t>
   </si>
   <si>
     <t xml:space="preserve">0.129336282610893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130385652184486</t>
+    <t xml:space="preserve">0.130385667085648</t>
   </si>
   <si>
     <t xml:space="preserve">0.131500631570816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130910336971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133468210697174</t>
+    <t xml:space="preserve">0.130910351872444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133468225598335</t>
   </si>
   <si>
     <t xml:space="preserve">0.129992142319679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975148916245</t>
+    <t xml:space="preserve">0.126975163817406</t>
   </si>
   <si>
     <t xml:space="preserve">0.127631023526192</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">0.128549233078957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133796140551567</t>
+    <t xml:space="preserve">0.133796155452728</t>
   </si>
   <si>
     <t xml:space="preserve">0.132156491279602</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">0.129205107688904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129598617553711</t>
+    <t xml:space="preserve">0.129598632454872</t>
   </si>
   <si>
     <t xml:space="preserve">0.140026852488518</t>
@@ -2216,31 +2216,31 @@
     <t xml:space="preserve">0.129729807376862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12986096739769</t>
+    <t xml:space="preserve">0.129860982298851</t>
   </si>
   <si>
     <t xml:space="preserve">0.130254477262497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129073932766914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125138759613037</t>
+    <t xml:space="preserve">0.129073917865753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125138744711876</t>
   </si>
   <si>
     <t xml:space="preserve">0.124614059925079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143634095788002</t>
+    <t xml:space="preserve">0.143634110689163</t>
   </si>
   <si>
     <t xml:space="preserve">0.143962040543556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370977878571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136091664433479</t>
+    <t xml:space="preserve">0.139370992779732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136091679334641</t>
   </si>
   <si>
     <t xml:space="preserve">0.138059258460999</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">0.136747539043427</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140682712197304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144945830106735</t>
+    <t xml:space="preserve">0.140682727098465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144945815205574</t>
   </si>
   <si>
     <t xml:space="preserve">0.142650306224823</t>
@@ -2261,10 +2261,10 @@
     <t xml:space="preserve">0.141994446516037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144289970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15379998087883</t>
+    <t xml:space="preserve">0.144289955496788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153799995779991</t>
   </si>
   <si>
     <t xml:space="preserve">0.152488261461258</t>
@@ -2279,25 +2279,25 @@
     <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155111700296402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155767560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160358622670174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159702748060226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162982076406479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166917234659195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163310006260872</t>
+    <t xml:space="preserve">0.155111715197563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155767574906349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160358607769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159702762961388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16298209130764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166917249560356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163309991359711</t>
   </si>
   <si>
     <t xml:space="preserve">0.162326201796532</t>
@@ -2315,118 +2315,118 @@
     <t xml:space="preserve">0.158718958497047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158391028642654</t>
+    <t xml:space="preserve">0.158391043543816</t>
   </si>
   <si>
     <t xml:space="preserve">0.160030692815781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1580630838871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165341451764107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163571193814278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162863090634346</t>
+    <t xml:space="preserve">0.158063098788261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165341436862946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163571178913116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162863075733185</t>
   </si>
   <si>
     <t xml:space="preserve">0.162509024143219</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161092832684517</t>
+    <t xml:space="preserve">0.161092847585678</t>
   </si>
   <si>
     <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157198280096054</t>
+    <t xml:space="preserve">0.157198294997215</t>
   </si>
   <si>
     <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162154987454414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158968523144722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160384729504585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159322574734688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157552346587181</t>
+    <t xml:space="preserve">0.162154972553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158968538045883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160384744405746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159322589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15755233168602</t>
   </si>
   <si>
     <t xml:space="preserve">0.161800935864449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155073970556259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153303742408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155782088637352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151533484458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152595609426498</t>
+    <t xml:space="preserve">0.15507398545742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153303727507591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155782073736191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151533469557762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15259562432766</t>
   </si>
   <si>
     <t xml:space="preserve">0.154719933867455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155428051948547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156844228506088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156490176916122</t>
+    <t xml:space="preserve">0.155428037047386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156844243407249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156490162014961</t>
   </si>
   <si>
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011815786362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156136125326157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152241587638855</t>
+    <t xml:space="preserve">0.154011830687523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156136140227318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152241572737694</t>
   </si>
   <si>
     <t xml:space="preserve">0.154365882277489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151887521147728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151179447770119</t>
+    <t xml:space="preserve">0.151887536048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151179432868958</t>
   </si>
   <si>
     <t xml:space="preserve">0.15011727809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150825381278992</t>
+    <t xml:space="preserve">0.150825396180153</t>
   </si>
   <si>
     <t xml:space="preserve">0.149763226509094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150471314787865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149055138230324</t>
+    <t xml:space="preserve">0.150471329689026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149055123329163</t>
   </si>
   <si>
     <t xml:space="preserve">0.146222725510597</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">0.147284880280495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142682239413261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143390312790871</t>
+    <t xml:space="preserve">0.1426822245121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143390327692032</t>
   </si>
   <si>
     <t xml:space="preserve">0.145514622330666</t>
@@ -2447,46 +2447,46 @@
     <t xml:space="preserve">0.148347035050392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149409174919128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152949690818787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145160585641861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147638916969299</t>
+    <t xml:space="preserve">0.149409160017967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152949675917625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1451605707407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147638931870461</t>
   </si>
   <si>
     <t xml:space="preserve">0.148701086640358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146576777100563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144452467560768</t>
+    <t xml:space="preserve">0.146576792001724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144452482461929</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144806534051895</t>
+    <t xml:space="preserve">0.144806519150734</t>
   </si>
   <si>
     <t xml:space="preserve">0.144098430871964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145868673920631</t>
+    <t xml:space="preserve">0.14586865901947</t>
   </si>
   <si>
     <t xml:space="preserve">0.147992968559265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16569547355175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168527886271477</t>
+    <t xml:space="preserve">0.165695488452911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168527901172638</t>
   </si>
   <si>
     <t xml:space="preserve">0.167111694812775</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">0.163217127323151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164358526468277</t>
+    <t xml:space="preserve">0.164358511567116</t>
   </si>
   <si>
     <t xml:space="preserve">0.162075757980347</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167021751403809</t>
+    <t xml:space="preserve">0.167021736502647</t>
   </si>
   <si>
     <t xml:space="preserve">0.161695286631584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161314830183983</t>
+    <t xml:space="preserve">0.161314845085144</t>
   </si>
   <si>
     <t xml:space="preserve">0.159793004393578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163978040218353</t>
+    <t xml:space="preserve">0.163978055119514</t>
   </si>
   <si>
     <t xml:space="preserve">0.16055391728878</t>
@@ -2531,10 +2531,13 @@
     <t xml:space="preserve">0.158271163702011</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160934373736382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162836685776711</t>
+    <t xml:space="preserve">0.163217142224312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160934388637543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2543,7 +2546,7 @@
     <t xml:space="preserve">0.163597598671913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162456229329109</t>
+    <t xml:space="preserve">0.162456214427948</t>
   </si>
   <si>
     <t xml:space="preserve">0.159032076597214</t>
@@ -2552,22 +2555,22 @@
     <t xml:space="preserve">0.159412547945976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16017347574234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165880352258682</t>
+    <t xml:space="preserve">0.160173445940018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165880367159843</t>
   </si>
   <si>
     <t xml:space="preserve">0.170445874333382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169684961438179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170826315879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171967700123787</t>
+    <t xml:space="preserve">0.169684946537018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170826330780983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171967715024948</t>
   </si>
   <si>
     <t xml:space="preserve">0.170065402984619</t>
@@ -2579,7 +2582,7 @@
     <t xml:space="preserve">0.15789070725441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153705656528473</t>
+    <t xml:space="preserve">0.153705641627312</t>
   </si>
   <si>
     <t xml:space="preserve">0.14427025616169</t>
@@ -2594,28 +2597,28 @@
     <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157510250806808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164738982915878</t>
+    <t xml:space="preserve">0.157510235905647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164738968014717</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168924018740654</t>
+    <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
     <t xml:space="preserve">0.166641265153885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168163105845451</t>
+    <t xml:space="preserve">0.16816309094429</t>
   </si>
   <si>
     <t xml:space="preserve">0.167402192950249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168543562293053</t>
+    <t xml:space="preserve">0.168543577194214</t>
   </si>
   <si>
     <t xml:space="preserve">0.173869997262955</t>
@@ -2624,19 +2627,19 @@
     <t xml:space="preserve">0.174277201294899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173462808132172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171426877379417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168983727693558</t>
+    <t xml:space="preserve">0.173462823033333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171426862478256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168983712792397</t>
   </si>
   <si>
     <t xml:space="preserve">0.166133388876915</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170612499117851</t>
+    <t xml:space="preserve">0.17061248421669</t>
   </si>
   <si>
     <t xml:space="preserve">0.168169349431992</t>
@@ -2651,10 +2654,10 @@
     <t xml:space="preserve">0.166540592908859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166947782039642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167762160301208</t>
+    <t xml:space="preserve">0.166947767138481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167762145400047</t>
   </si>
   <si>
     <t xml:space="preserve">0.168576538562775</t>
@@ -2666,31 +2669,31 @@
     <t xml:space="preserve">0.162875890731812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151963204145432</t>
+    <t xml:space="preserve">0.15196318924427</t>
   </si>
   <si>
     <t xml:space="preserve">0.155709341168404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157175227999687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156360849738121</t>
+    <t xml:space="preserve">0.157175213098526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15636083483696</t>
   </si>
   <si>
     <t xml:space="preserve">0.157338112592697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155546471476555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15424345433712</t>
+    <t xml:space="preserve">0.155546456575394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154243469238281</t>
   </si>
   <si>
     <t xml:space="preserve">0.150660187005997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152451813220978</t>
+    <t xml:space="preserve">0.152451828122139</t>
   </si>
   <si>
     <t xml:space="preserve">0.152614697813988</t>
@@ -2699,16 +2702,16 @@
     <t xml:space="preserve">0.163690268993378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162387251853943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158478230237961</t>
+    <t xml:space="preserve">0.162387236952782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158478245139122</t>
   </si>
   <si>
     <t xml:space="preserve">0.160432755947113</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157012343406677</t>
+    <t xml:space="preserve">0.157012358307838</t>
   </si>
   <si>
     <t xml:space="preserve">0.161247119307518</t>
@@ -2753,7 +2756,7 @@
     <t xml:space="preserve">0.154732093214989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966854214668</t>
+    <t xml:space="preserve">0.158966839313507</t>
   </si>
   <si>
     <t xml:space="preserve">0.15652371942997</t>
@@ -2771,10 +2774,10 @@
     <t xml:space="preserve">0.156035095453262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157663837075233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155383586883545</t>
+    <t xml:space="preserve">0.157663851976395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155383601784706</t>
   </si>
   <si>
     <t xml:space="preserve">0.157826721668243</t>
@@ -2819,10 +2822,10 @@
     <t xml:space="preserve">0.163283064961433</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164097458124161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162224382162094</t>
+    <t xml:space="preserve">0.164097443223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162224397063255</t>
   </si>
   <si>
     <t xml:space="preserve">0.162550121545792</t>
@@ -2831,10 +2834,10 @@
     <t xml:space="preserve">0.161084249615669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158803969621658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159618347883224</t>
+    <t xml:space="preserve">0.15880398452282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159618362784386</t>
   </si>
   <si>
     <t xml:space="preserve">0.159455493092537</t>
@@ -2849,16 +2852,16 @@
     <t xml:space="preserve">0.170205295085907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.175905957818031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173055619001389</t>
+    <t xml:space="preserve">0.175905972719193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17305563390255</t>
   </si>
   <si>
     <t xml:space="preserve">0.176720321178436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.177534714341164</t>
+    <t xml:space="preserve">0.177534699440002</t>
   </si>
   <si>
     <t xml:space="preserve">0.179163470864296</t>
@@ -2867,13 +2870,10 @@
     <t xml:space="preserve">0.175091579556465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173870012164116</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.171019673347473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172241240739822</t>
+    <t xml:space="preserve">0.172241255640984</t>
   </si>
   <si>
     <t xml:space="preserve">0.172648429870605</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">0.183235347270966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.181606620550156</t>
+    <t xml:space="preserve">0.181606605648994</t>
   </si>
   <si>
     <t xml:space="preserve">0.184049740433693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182420998811722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.18486413359642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.185678496956825</t>
+    <t xml:space="preserve">0.182420983910561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.184864118695259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.185678511857986</t>
   </si>
   <si>
     <t xml:space="preserve">0.188121646642685</t>
@@ -18524,7 +18524,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G571" t="s">
-        <v>104</v>
+        <v>438</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18550,7 +18550,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G572" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18576,7 +18576,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G573" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18602,7 +18602,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G574" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18628,7 +18628,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G575" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18654,7 +18654,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18888,7 +18888,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18914,7 +18914,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G586" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18966,7 +18966,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G588" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19070,7 +19070,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G592" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19096,7 +19096,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G593" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19122,7 +19122,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G594" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19148,7 +19148,7 @@
         <v>0.229499995708466</v>
       </c>
       <c r="G595" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19174,7 +19174,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -42964,7 +42964,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1511" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -42990,7 +42990,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1512" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -43016,7 +43016,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1513" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -43094,7 +43094,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1516" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -43120,7 +43120,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1517" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -43146,7 +43146,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1518" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -43172,7 +43172,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1519" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -43224,7 +43224,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1521" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -43250,7 +43250,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1522" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -43328,7 +43328,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1525" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -43354,7 +43354,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1526" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -43380,7 +43380,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1527" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -43406,7 +43406,7 @@
         <v>0.214499995112419</v>
       </c>
       <c r="G1528" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -43458,7 +43458,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1530" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -43484,7 +43484,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1531" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -43536,7 +43536,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1533" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -43692,7 +43692,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1539" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -43770,7 +43770,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1542" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -43796,7 +43796,7 @@
         <v>0.209499999880791</v>
       </c>
       <c r="G1543" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -43822,7 +43822,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1544" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -43900,7 +43900,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1547" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -43926,7 +43926,7 @@
         <v>0.209499999880791</v>
       </c>
       <c r="G1548" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -43978,7 +43978,7 @@
         <v>0.211500003933907</v>
       </c>
       <c r="G1550" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -44004,7 +44004,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1551" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -44108,7 +44108,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1555" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -44134,7 +44134,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G1556" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -44160,7 +44160,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1557" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -44186,7 +44186,7 @@
         <v>0.224500000476837</v>
       </c>
       <c r="G1558" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -44212,7 +44212,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1559" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -44238,7 +44238,7 @@
         <v>0.223499998450279</v>
       </c>
       <c r="G1560" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -44264,7 +44264,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G1561" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -44316,7 +44316,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G1563" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -44342,7 +44342,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1564" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -44368,7 +44368,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1565" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -44446,7 +44446,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1568" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -44472,7 +44472,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1569" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -44498,7 +44498,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1570" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -44524,7 +44524,7 @@
         <v>0.189600005745888</v>
       </c>
       <c r="G1571" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -44550,7 +44550,7 @@
         <v>0.194199994206429</v>
       </c>
       <c r="G1572" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -44576,7 +44576,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1573" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -44602,7 +44602,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1574" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -44628,7 +44628,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1575" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -44654,7 +44654,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1576" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -44680,7 +44680,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1577" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -44706,7 +44706,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1578" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -44758,7 +44758,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G1580" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -44784,7 +44784,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G1581" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -44836,7 +44836,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G1583" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -44940,7 +44940,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1587" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -44966,7 +44966,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G1588" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -44992,7 +44992,7 @@
         <v>0.223499998450279</v>
       </c>
       <c r="G1589" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -45044,7 +45044,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G1591" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -45070,7 +45070,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G1592" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -45096,7 +45096,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1593" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -45122,7 +45122,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1594" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -45174,7 +45174,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G1596" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -45226,7 +45226,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1598" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -45252,7 +45252,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G1599" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -45278,7 +45278,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1600" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -45304,7 +45304,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1601" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -45330,7 +45330,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1602" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -45356,7 +45356,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G1603" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -45382,7 +45382,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1604" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -45408,7 +45408,7 @@
         <v>0.224500000476837</v>
       </c>
       <c r="G1605" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -45434,7 +45434,7 @@
         <v>0.224500000476837</v>
       </c>
       <c r="G1606" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -45460,7 +45460,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G1607" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -45486,7 +45486,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G1608" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -45512,7 +45512,7 @@
         <v>0.228499993681908</v>
       </c>
       <c r="G1609" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -45538,7 +45538,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1610" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -45564,7 +45564,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1611" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -45590,7 +45590,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1612" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -45616,7 +45616,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1613" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -45642,7 +45642,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1614" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -45668,7 +45668,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1615" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -45694,7 +45694,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1616" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -45720,7 +45720,7 @@
         <v>0.209499999880791</v>
       </c>
       <c r="G1617" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -45746,7 +45746,7 @@
         <v>0.206499993801117</v>
       </c>
       <c r="G1618" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -45772,7 +45772,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G1619" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -45798,7 +45798,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1620" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -45824,7 +45824,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1621" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -45850,7 +45850,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1622" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -45876,7 +45876,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1623" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -45902,7 +45902,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1624" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -45928,7 +45928,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1625" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -45954,7 +45954,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1626" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -45980,7 +45980,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G1627" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -46006,7 +46006,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1628" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -46032,7 +46032,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G1629" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -46058,7 +46058,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1630" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -46084,7 +46084,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1631" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -46110,7 +46110,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1632" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -46136,7 +46136,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1633" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -46162,7 +46162,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1634" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -46188,7 +46188,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1635" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -46214,7 +46214,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1636" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -46240,7 +46240,7 @@
         <v>0.20550000667572</v>
       </c>
       <c r="G1637" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -46266,7 +46266,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1638" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -46292,7 +46292,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1639" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -46318,7 +46318,7 @@
         <v>0.186599999666214</v>
       </c>
       <c r="G1640" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -46344,7 +46344,7 @@
         <v>0.191200003027916</v>
       </c>
       <c r="G1641" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -46370,7 +46370,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1642" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -46396,7 +46396,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1643" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -46422,7 +46422,7 @@
         <v>0.193200007081032</v>
       </c>
       <c r="G1644" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -46448,7 +46448,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1645" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -46474,7 +46474,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1646" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -46500,7 +46500,7 @@
         <v>0.189400002360344</v>
       </c>
       <c r="G1647" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -46526,7 +46526,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G1648" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -46552,7 +46552,7 @@
         <v>0.187199994921684</v>
       </c>
       <c r="G1649" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -46578,7 +46578,7 @@
         <v>0.187399998307228</v>
       </c>
       <c r="G1650" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -46604,7 +46604,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1651" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -46630,7 +46630,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1652" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -46656,7 +46656,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G1653" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -46682,7 +46682,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1654" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -46708,7 +46708,7 @@
         <v>0.192800000309944</v>
       </c>
       <c r="G1655" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -46734,7 +46734,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1656" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -46760,7 +46760,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1657" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -46786,7 +46786,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1658" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -46812,7 +46812,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1659" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -46838,7 +46838,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1660" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -46864,7 +46864,7 @@
         <v>0.198599994182587</v>
       </c>
       <c r="G1661" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -46890,7 +46890,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G1662" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -46916,7 +46916,7 @@
         <v>0.193399995565414</v>
       </c>
       <c r="G1663" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -46942,7 +46942,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G1664" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -46968,7 +46968,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G1665" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -46994,7 +46994,7 @@
         <v>0.197200000286102</v>
       </c>
       <c r="G1666" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -47020,7 +47020,7 @@
         <v>0.196199998259544</v>
       </c>
       <c r="G1667" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -47046,7 +47046,7 @@
         <v>0.191200003027916</v>
       </c>
       <c r="G1668" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -47072,7 +47072,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1669" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -47098,7 +47098,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1670" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -47124,7 +47124,7 @@
         <v>0.190400004386902</v>
       </c>
       <c r="G1671" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -47150,7 +47150,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1672" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -47176,7 +47176,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1673" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -47202,7 +47202,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1674" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -47228,7 +47228,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1675" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -47254,7 +47254,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1676" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -47280,7 +47280,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1677" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -47306,7 +47306,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1678" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47332,7 +47332,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1679" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -47358,7 +47358,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1680" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47384,7 +47384,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1681" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47410,7 +47410,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1682" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -47436,7 +47436,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1683" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -47462,7 +47462,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G1684" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -47488,7 +47488,7 @@
         <v>0.19820000231266</v>
       </c>
       <c r="G1685" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -47514,7 +47514,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1686" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47540,7 +47540,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1687" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47566,7 +47566,7 @@
         <v>0.196400001645088</v>
       </c>
       <c r="G1688" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47592,7 +47592,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1689" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47618,7 +47618,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G1690" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -47644,7 +47644,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1691" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -47670,7 +47670,7 @@
         <v>0.192200005054474</v>
       </c>
       <c r="G1692" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47696,7 +47696,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G1693" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47722,7 +47722,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1694" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47748,7 +47748,7 @@
         <v>0.190599992871284</v>
       </c>
       <c r="G1695" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -47774,7 +47774,7 @@
         <v>0.19140000641346</v>
       </c>
       <c r="G1696" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -47800,7 +47800,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47826,7 +47826,7 @@
         <v>0.191799998283386</v>
       </c>
       <c r="G1698" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47852,7 +47852,7 @@
         <v>0.191599994897842</v>
       </c>
       <c r="G1699" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47878,7 +47878,7 @@
         <v>0.192200005054474</v>
       </c>
       <c r="G1700" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47904,7 +47904,7 @@
         <v>0.193599998950958</v>
       </c>
       <c r="G1701" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -47930,7 +47930,7 @@
         <v>0.190799996256828</v>
       </c>
       <c r="G1702" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47956,7 +47956,7 @@
         <v>0.193599998950958</v>
       </c>
       <c r="G1703" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47982,7 +47982,7 @@
         <v>0.193800002336502</v>
       </c>
       <c r="G1704" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -48008,7 +48008,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1705" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -48034,7 +48034,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1706" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -48060,7 +48060,7 @@
         <v>0.193599998950958</v>
       </c>
       <c r="G1707" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -48086,7 +48086,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1708" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -48112,7 +48112,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1709" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -48138,7 +48138,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1710" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -48164,7 +48164,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1711" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -48190,7 +48190,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1712" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -48216,7 +48216,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1713" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -48242,7 +48242,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1714" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -48268,7 +48268,7 @@
         <v>0.194199994206429</v>
       </c>
       <c r="G1715" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -48294,7 +48294,7 @@
         <v>0.194199994206429</v>
       </c>
       <c r="G1716" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -48320,7 +48320,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G1717" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48346,7 +48346,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1718" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48372,7 +48372,7 @@
         <v>0.192399993538857</v>
       </c>
       <c r="G1719" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48398,7 +48398,7 @@
         <v>0.193399995565414</v>
       </c>
       <c r="G1720" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48424,7 +48424,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1721" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48450,7 +48450,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1722" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48476,7 +48476,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G1723" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48502,7 +48502,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1724" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48528,7 +48528,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G1725" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48554,7 +48554,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G1726" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48580,7 +48580,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G1727" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48606,7 +48606,7 @@
         <v>0.190200001001358</v>
       </c>
       <c r="G1728" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48632,7 +48632,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G1729" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48658,7 +48658,7 @@
         <v>0.190400004386902</v>
       </c>
       <c r="G1730" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48684,7 +48684,7 @@
         <v>0.189600005745888</v>
       </c>
       <c r="G1731" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48710,7 +48710,7 @@
         <v>0.189400002360344</v>
       </c>
       <c r="G1732" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48736,7 +48736,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G1733" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48762,7 +48762,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1734" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48788,7 +48788,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1735" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48814,7 +48814,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G1736" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48840,7 +48840,7 @@
         <v>0.190200001001358</v>
       </c>
       <c r="G1737" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48866,7 +48866,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G1738" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48892,7 +48892,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G1739" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48918,7 +48918,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G1740" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48944,7 +48944,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G1741" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48970,7 +48970,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G1742" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48996,7 +48996,7 @@
         <v>0.195600003004074</v>
       </c>
       <c r="G1743" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -49022,7 +49022,7 @@
         <v>0.19480000436306</v>
       </c>
       <c r="G1744" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -49048,7 +49048,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G1745" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -49074,7 +49074,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1746" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -49100,7 +49100,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1747" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -49126,7 +49126,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G1748" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -49152,7 +49152,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1749" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -49178,7 +49178,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G1750" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -49204,7 +49204,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1751" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -49230,7 +49230,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1752" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -49256,7 +49256,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1753" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -49282,7 +49282,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1754" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -49308,7 +49308,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1755" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -49334,7 +49334,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1756" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49360,7 +49360,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G1757" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49386,7 +49386,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G1758" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49412,7 +49412,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1759" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49438,7 +49438,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1760" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49464,7 +49464,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1761" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49490,7 +49490,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G1762" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49516,7 +49516,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G1763" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49542,7 +49542,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1764" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49568,7 +49568,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G1765" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49594,7 +49594,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1766" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49620,7 +49620,7 @@
         <v>0.19820000231266</v>
       </c>
       <c r="G1767" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49646,7 +49646,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G1768" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49672,7 +49672,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1769" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49698,7 +49698,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G1770" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49724,7 +49724,7 @@
         <v>0.196199998259544</v>
       </c>
       <c r="G1771" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49750,7 +49750,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G1772" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49776,7 +49776,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1773" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49802,7 +49802,7 @@
         <v>0.196400001645088</v>
       </c>
       <c r="G1774" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49828,7 +49828,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1775" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49854,7 +49854,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1776" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49880,7 +49880,7 @@
         <v>0.195999994874001</v>
       </c>
       <c r="G1777" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49906,7 +49906,7 @@
         <v>0.198400005698204</v>
       </c>
       <c r="G1778" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49932,7 +49932,7 @@
         <v>0.198599994182587</v>
       </c>
       <c r="G1779" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49958,7 +49958,7 @@
         <v>0.195800006389618</v>
       </c>
       <c r="G1780" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49984,7 +49984,7 @@
         <v>0.19760000705719</v>
       </c>
       <c r="G1781" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -50010,7 +50010,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1782" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -50036,7 +50036,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G1783" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -50062,7 +50062,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1784" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -50088,7 +50088,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1785" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -50114,7 +50114,7 @@
         <v>0.197799995541573</v>
       </c>
       <c r="G1786" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -50140,7 +50140,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1787" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -50166,7 +50166,7 @@
         <v>0.199200004339218</v>
       </c>
       <c r="G1788" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -50192,7 +50192,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1789" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -50218,7 +50218,7 @@
         <v>0.199799999594688</v>
       </c>
       <c r="G1790" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -50244,7 +50244,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1791" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -50270,7 +50270,7 @@
         <v>0.197999998927116</v>
       </c>
       <c r="G1792" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -50296,7 +50296,7 @@
         <v>0.199399992823601</v>
       </c>
       <c r="G1793" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -50322,7 +50322,7 @@
         <v>0.19820000231266</v>
       </c>
       <c r="G1794" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50348,7 +50348,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1795" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50374,7 +50374,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50400,7 +50400,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1797" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50426,7 +50426,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1798" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50452,7 +50452,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50478,7 +50478,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1800" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50504,7 +50504,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1801" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50530,7 +50530,7 @@
         <v>0.203500002622604</v>
       </c>
       <c r="G1802" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50556,7 +50556,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1803" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -50582,7 +50582,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1804" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50608,7 +50608,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G1805" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50634,7 +50634,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1806" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50660,7 +50660,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G1807" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50686,7 +50686,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1808" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50712,7 +50712,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1809" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -50738,7 +50738,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G1810" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -50764,7 +50764,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G1811" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50790,7 +50790,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1812" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -50816,7 +50816,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1813" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -50842,7 +50842,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1814" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -50868,7 +50868,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1815" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -50894,7 +50894,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G1816" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -50920,7 +50920,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1817" t="s">
-        <v>951</v>
+        <v>869</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -50972,7 +50972,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G1819" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -51024,7 +51024,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1821" t="s">
-        <v>951</v>
+        <v>869</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -51050,7 +51050,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G1822" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -51076,7 +51076,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1823" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -51232,7 +51232,7 @@
         <v>0.213499993085861</v>
       </c>
       <c r="G1829" t="s">
-        <v>951</v>
+        <v>869</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -51258,7 +51258,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G1830" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -51336,7 +51336,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1833" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51362,7 +51362,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1834" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51388,7 +51388,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1835" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51414,7 +51414,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G1836" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -51440,7 +51440,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1837" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -51466,7 +51466,7 @@
         <v>0.203500002622604</v>
       </c>
       <c r="G1838" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51544,7 +51544,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1841" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -51596,7 +51596,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1843" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -51622,7 +51622,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1844" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51726,7 +51726,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1848" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -51752,7 +51752,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1849" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -51778,7 +51778,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1850" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -51804,7 +51804,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1851" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="1114">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481404185295</t>
+    <t xml:space="preserve">0.158481374382973</t>
   </si>
   <si>
     <t xml:space="preserve">0.155000314116478</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">0.153229221701622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150542080402374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148099198937416</t>
+    <t xml:space="preserve">0.150542065501213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148099184036255</t>
   </si>
   <si>
     <t xml:space="preserve">0.15029776096344</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">0.151580274105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14736633002758</t>
+    <t xml:space="preserve">0.147366315126419</t>
   </si>
   <si>
     <t xml:space="preserve">0.142358437180519</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132831230759621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134541243314743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12531940639019</t>
+    <t xml:space="preserve">0.132831215858459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134541228413582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121203303337</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">0.134358018636703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134419098496437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143335595726967</t>
+    <t xml:space="preserve">0.134419083595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
     <t xml:space="preserve">0.13802233338356</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">0.137778058648109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140465214848518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139854475855827</t>
+    <t xml:space="preserve">0.140465199947357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
     <t xml:space="preserve">0.136190176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131793022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129166916012764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129289075732231</t>
+    <t xml:space="preserve">0.131792992353439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129166930913925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12928906083107</t>
   </si>
   <si>
     <t xml:space="preserve">0.118967920541763</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">0.122754395008087</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116158612072468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118479356169701</t>
+    <t xml:space="preserve">0.116158619523048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479363620281</t>
   </si>
   <si>
     <t xml:space="preserve">0.125807970762253</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">0.127029404044151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125014021992683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999073386192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12910583615303</t>
+    <t xml:space="preserve">0.125014036893845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999058485031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129105851054192</t>
   </si>
   <si>
     <t xml:space="preserve">0.128617271780968</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">0.130205154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13051050901413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129533365368843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133808374404907</t>
+    <t xml:space="preserve">0.130510494112968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129533350467682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133808389306068</t>
   </si>
   <si>
     <t xml:space="preserve">0.138755187392235</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">0.136495545506477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140159860253334</t>
+    <t xml:space="preserve">0.140159845352173</t>
   </si>
   <si>
     <t xml:space="preserve">0.141747713088989</t>
@@ -188,37 +188,37 @@
     <t xml:space="preserve">0.149015262722969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146572396159172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14571738243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143213450908661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144129529595375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892714262009</t>
+    <t xml:space="preserve">0.146572411060333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145717352628708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1432134360075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144129514694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14089272916317</t>
   </si>
   <si>
     <t xml:space="preserve">0.139793410897255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134968727827072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068046092987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135945871472359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135823741555214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133136600255966</t>
+    <t xml:space="preserve">0.134968772530556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068031191826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135945901274681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135823756456375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133136585354805</t>
   </si>
   <si>
     <t xml:space="preserve">0.130693718791008</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">0.12886156141758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125258326530457</t>
+    <t xml:space="preserve">0.125258311629295</t>
   </si>
   <si>
     <t xml:space="preserve">0.133930534124374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137472689151764</t>
+    <t xml:space="preserve">0.137472704052925</t>
   </si>
   <si>
     <t xml:space="preserve">0.142480567097664</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142114132642746</t>
+    <t xml:space="preserve">0.142114162445068</t>
   </si>
   <si>
     <t xml:space="preserve">0.141320198774338</t>
@@ -248,46 +248,46 @@
     <t xml:space="preserve">0.142175227403641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138327687978745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142236277461052</t>
+    <t xml:space="preserve">0.138327702879906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142236292362213</t>
   </si>
   <si>
     <t xml:space="preserve">0.1382055580616</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140526756644249</t>
+    <t xml:space="preserve">0.140526741743088</t>
   </si>
   <si>
     <t xml:space="preserve">0.139899387955666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136135265231133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136637181043625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133876830339432</t>
+    <t xml:space="preserve">0.136135280132294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136637166142464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133876815438271</t>
   </si>
   <si>
     <t xml:space="preserve">0.133814096450806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132998526096344</t>
+    <t xml:space="preserve">0.132998540997505</t>
   </si>
   <si>
     <t xml:space="preserve">0.129234418272972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128732547163963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125156626105309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126662269234657</t>
+    <t xml:space="preserve">0.128732532262802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12515664100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126662284135818</t>
   </si>
   <si>
     <t xml:space="preserve">0.126725018024445</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">0.127352371811867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127979710698128</t>
+    <t xml:space="preserve">0.127979725599289</t>
   </si>
   <si>
     <t xml:space="preserve">0.126599535346031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12791696190834</t>
+    <t xml:space="preserve">0.127916976809502</t>
   </si>
   <si>
     <t xml:space="preserve">0.130489125847816</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">0.131116479635239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131555616855621</t>
+    <t xml:space="preserve">0.13155560195446</t>
   </si>
   <si>
     <t xml:space="preserve">0.13406503200531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131179213523865</t>
+    <t xml:space="preserve">0.131179198622704</t>
   </si>
   <si>
     <t xml:space="preserve">0.133688613772392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134880572557449</t>
+    <t xml:space="preserve">0.134880587458611</t>
   </si>
   <si>
     <t xml:space="preserve">0.134190499782562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130614578723907</t>
+    <t xml:space="preserve">0.130614593625069</t>
   </si>
   <si>
     <t xml:space="preserve">0.132873058319092</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121078871190548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120200544595718</t>
+    <t xml:space="preserve">0.121078856289387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120200537145138</t>
   </si>
   <si>
     <t xml:space="preserve">0.121831670403481</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">0.110413871705532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112233199179173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366196095943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794039607048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052511751652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395041406155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893177747726</t>
+    <t xml:space="preserve">0.112233206629753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366188645363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794047057629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114052496850491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395063757896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893170297146</t>
   </si>
   <si>
     <t xml:space="preserve">0.111041225492954</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">0.107904464006424</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111354872584343</t>
+    <t xml:space="preserve">0.111354887485504</t>
   </si>
   <si>
     <t xml:space="preserve">0.110727556049824</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">0.107277117669582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102822929620743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501731038094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716262340546</t>
+    <t xml:space="preserve">0.102822922170162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501708686352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
   </si>
   <si>
     <t xml:space="preserve">0.110790282487869</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">0.114554390311241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112923286855221</t>
+    <t xml:space="preserve">0.112923264503479</t>
   </si>
   <si>
     <t xml:space="preserve">0.114303462207317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118632189929485</t>
+    <t xml:space="preserve">0.118632167577744</t>
   </si>
   <si>
     <t xml:space="preserve">0.11656192690134</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">0.115746356546879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115432694554329</t>
+    <t xml:space="preserve">0.115432687103748</t>
   </si>
   <si>
     <t xml:space="preserve">0.114805348217487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116185508668423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569448590279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820384144783</t>
+    <t xml:space="preserve">0.116185501217842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569433689117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820406496525</t>
   </si>
   <si>
     <t xml:space="preserve">0.115934558212757</t>
@@ -440,55 +440,55 @@
     <t xml:space="preserve">0.109159156680107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107088893651962</t>
+    <t xml:space="preserve">0.107088908553123</t>
   </si>
   <si>
     <t xml:space="preserve">0.106147885322571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10414033383131</t>
+    <t xml:space="preserve">0.104140348732471</t>
   </si>
   <si>
     <t xml:space="preserve">0.105646006762981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107465319335461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108531810343266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535589814186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104830451309681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092650771141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029939234257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849251806736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978469252586</t>
+    <t xml:space="preserve">0.107465296983719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108531802892685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590787112713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535582363605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1048304438591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092680573463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029931783676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1076535359025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849259257317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978499054909</t>
   </si>
   <si>
     <t xml:space="preserve">0.11160583794117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113738849759102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864302635193</t>
+    <t xml:space="preserve">0.113738834857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864317536354</t>
   </si>
   <si>
     <t xml:space="preserve">0.110288389027119</t>
@@ -497,43 +497,43 @@
     <t xml:space="preserve">0.110225662589073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108845494687557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723784029484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339851558208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406357467175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104516766965389</t>
+    <t xml:space="preserve">0.108845509588718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723769128323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10733986645937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406350016594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10451677441597</t>
   </si>
   <si>
     <t xml:space="preserve">0.105018638074398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106649771332741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10583420842886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085143983364</t>
+    <t xml:space="preserve">0.106649748980999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105834200978279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085151433945</t>
   </si>
   <si>
     <t xml:space="preserve">0.109786532819271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104391299188137</t>
+    <t xml:space="preserve">0.104391284286976</t>
   </si>
   <si>
     <t xml:space="preserve">0.107778988778591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107214361429214</t>
+    <t xml:space="preserve">0.107214391231537</t>
   </si>
   <si>
     <t xml:space="preserve">0.11606003344059</t>
@@ -545,28 +545,28 @@
     <t xml:space="preserve">0.11242138594389</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11342515796423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295933067799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022410094738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712512671947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837972998619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520538985729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265816509724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760180830956</t>
+    <t xml:space="preserve">0.113425150513649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295925617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022417545319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712497770786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837965548038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520531535149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265831410885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760188281536</t>
   </si>
   <si>
     <t xml:space="preserve">0.101003594696522</t>
@@ -575,34 +575,34 @@
     <t xml:space="preserve">0.104579500854015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102885648608208</t>
+    <t xml:space="preserve">0.102885663509369</t>
   </si>
   <si>
     <t xml:space="preserve">0.103889405727386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101254545152187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100564450025558</t>
+    <t xml:space="preserve">0.101254530251026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100564457476139</t>
   </si>
   <si>
     <t xml:space="preserve">0.101066343486309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101630948483944</t>
+    <t xml:space="preserve">0.101630955934525</t>
   </si>
   <si>
     <t xml:space="preserve">0.106524296104908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109912000596523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539354383945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110915750265121</t>
+    <t xml:space="preserve">0.109911993145943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539339482784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110915757715702</t>
   </si>
   <si>
     <t xml:space="preserve">0.108657278120518</t>
@@ -611,22 +611,22 @@
     <t xml:space="preserve">0.112609602510929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111292146146297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410107135773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108343601226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108280867338181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033711254597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351145267487</t>
+    <t xml:space="preserve">0.111292161047459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410099685192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108343623578548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108280874788761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033696353436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351122915745</t>
   </si>
   <si>
     <t xml:space="preserve">0.128544330596924</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144918203353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142408773303032</t>
+    <t xml:space="preserve">0.144918218255043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142408788204193</t>
   </si>
   <si>
     <t xml:space="preserve">0.132371172308922</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">0.134253233671188</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131304681301117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134692370891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135821595788002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836668968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14265975356102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855469465256</t>
+    <t xml:space="preserve">0.131304666399956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134692385792732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135821610689163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836654067039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142659738659859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855484366417</t>
   </si>
   <si>
     <t xml:space="preserve">0.143161624670029</t>
@@ -674,40 +674,40 @@
     <t xml:space="preserve">0.141781449317932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133500412106514</t>
+    <t xml:space="preserve">0.133500397205353</t>
   </si>
   <si>
     <t xml:space="preserve">0.129861772060394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130175441503525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131681084632874</t>
+    <t xml:space="preserve">0.130175456404686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131681114435196</t>
   </si>
   <si>
     <t xml:space="preserve">0.130112707614899</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13074004650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842964112759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097679138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975953578949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289608120918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127226889133453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126411333680153</t>
+    <t xml:space="preserve">0.130740076303482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842941761017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097664237022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975938677788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289637923241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127226918935776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126411318778992</t>
   </si>
   <si>
     <t xml:space="preserve">0.1254703104496</t>
@@ -716,28 +716,28 @@
     <t xml:space="preserve">0.126536816358566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215595424175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125972181558609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551859736443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182955741882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171684384346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13224570453167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006040334702</t>
+    <t xml:space="preserve">0.124215602874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12597219645977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551874637604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677342414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182985544205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171669483185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132245719432831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006070137024</t>
   </si>
   <si>
     <t xml:space="preserve">0.133939549326897</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">0.136260762810707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134943306446075</t>
+    <t xml:space="preserve">0.134943321347237</t>
   </si>
   <si>
     <t xml:space="preserve">0.137766391038895</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">0.13801734149456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140777677297592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145733758807182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144165396690369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14397719502449</t>
+    <t xml:space="preserve">0.140777692198753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145733773708344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165381789207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977180123329</t>
   </si>
   <si>
     <t xml:space="preserve">0.14115409553051</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">0.137640938162804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136762648820877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629622101784</t>
+    <t xml:space="preserve">0.136762633919716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629651904106</t>
   </si>
   <si>
     <t xml:space="preserve">0.134002283215523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133437693119049</t>
+    <t xml:space="preserve">0.133437678217888</t>
   </si>
   <si>
     <t xml:space="preserve">0.129673570394516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356128931046</t>
+    <t xml:space="preserve">0.128356143832207</t>
   </si>
   <si>
     <t xml:space="preserve">0.132496640086174</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">0.135633394122124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137891873717308</t>
+    <t xml:space="preserve">0.137891858816147</t>
   </si>
   <si>
     <t xml:space="preserve">0.13770367205143</t>
@@ -812,19 +812,19 @@
     <t xml:space="preserve">0.13205748796463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134504169225693</t>
+    <t xml:space="preserve">0.134504154324532</t>
   </si>
   <si>
     <t xml:space="preserve">0.134502410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13298973441124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131729170680046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130720719695091</t>
+    <t xml:space="preserve">0.132989749312401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131729185581207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13072070479393</t>
   </si>
   <si>
     <t xml:space="preserve">0.133178815245628</t>
@@ -833,82 +833,82 @@
     <t xml:space="preserve">0.134565442800522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134943619370461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131792187690735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131477043032646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132359430193901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130909785628319</t>
+    <t xml:space="preserve">0.134943604469299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131792217493057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131477057933807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132359459996223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130909815430641</t>
   </si>
   <si>
     <t xml:space="preserve">0.130468606948853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129964396357536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127506271004677</t>
+    <t xml:space="preserve">0.129964381456375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127506285905838</t>
   </si>
   <si>
     <t xml:space="preserve">0.129586204886436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127002030611038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127947479486465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128199577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12870380282402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371741294861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125930562615395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127128109335899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056641340256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479605525732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124669998884201</t>
+    <t xml:space="preserve">0.127002060413361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127947464585304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128199592232704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128703817725182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371756196022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125930547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127128094434738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056626439095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12479604780674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12466999143362</t>
   </si>
   <si>
     <t xml:space="preserve">0.124165765941143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125174224376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125237256288528</t>
+    <t xml:space="preserve">0.12517423927784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125237241387367</t>
   </si>
   <si>
     <t xml:space="preserve">0.129018932580948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127380207180977</t>
+    <t xml:space="preserve">0.127380236983299</t>
   </si>
   <si>
     <t xml:space="preserve">0.128451690077782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128136530518532</t>
+    <t xml:space="preserve">0.128136560320854</t>
   </si>
   <si>
     <t xml:space="preserve">0.127884447574615</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">0.128262609243393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126875981688499</t>
+    <t xml:space="preserve">0.126875966787338</t>
   </si>
   <si>
     <t xml:space="preserve">0.126497820019722</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">0.126308739185333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430942893028</t>
+    <t xml:space="preserve">0.133430927991867</t>
   </si>
   <si>
     <t xml:space="preserve">0.135573893785477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135762989521027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136456280946732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135636940598488</t>
+    <t xml:space="preserve">0.135762974619865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136456310749054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135636910796165</t>
   </si>
   <si>
     <t xml:space="preserve">0.134061217308044</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">0.137464746832848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137716859579086</t>
+    <t xml:space="preserve">0.137716874480247</t>
   </si>
   <si>
     <t xml:space="preserve">0.138221085071564</t>
@@ -977,115 +977,115 @@
     <t xml:space="preserve">0.137842908501625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136330232024193</t>
+    <t xml:space="preserve">0.136330217123032</t>
   </si>
   <si>
     <t xml:space="preserve">0.13708658516407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136771410703659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136204212903976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006636381149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134754538536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13506968319416</t>
+    <t xml:space="preserve">0.13677142560482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136204198002815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13500665128231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134754523634911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135069668292999</t>
   </si>
   <si>
     <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151141881942749</t>
+    <t xml:space="preserve">0.15114189684391</t>
   </si>
   <si>
     <t xml:space="preserve">0.153789073228836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15278060734272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15126796066761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145280256867409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147045060992241</t>
+    <t xml:space="preserve">0.152780622243881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267930865288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14528027176857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14704504609108</t>
   </si>
   <si>
     <t xml:space="preserve">0.157444715499878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159398585557938</t>
+    <t xml:space="preserve">0.159398600459099</t>
   </si>
   <si>
     <t xml:space="preserve">0.156625375151634</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570794224739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152843654155731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152654573321342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151898220181465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153095781803131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150259509682655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148746818304062</t>
+    <t xml:space="preserve">0.157570764422417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152843669056892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152654558420181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151898235082626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15309576690197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150259479880333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746803402901</t>
   </si>
   <si>
     <t xml:space="preserve">0.153347879648209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155805975198746</t>
+    <t xml:space="preserve">0.155805990099907</t>
   </si>
   <si>
     <t xml:space="preserve">0.154419362545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156940475106239</t>
+    <t xml:space="preserve">0.156940490007401</t>
   </si>
   <si>
     <t xml:space="preserve">0.15914648771286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167655304074287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050367712975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16721411049366</t>
+    <t xml:space="preserve">0.167655318975449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050382614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167214140295982</t>
   </si>
   <si>
     <t xml:space="preserve">0.172067284584045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.179945841431618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175218686461449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336314201355</t>
+    <t xml:space="preserve">0.179945811629295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811326622963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175218731164932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336299300194</t>
   </si>
   <si>
     <t xml:space="preserve">0.170176446437836</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">0.176479279994965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173643007874489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170365542173386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166205659508705</t>
+    <t xml:space="preserve">0.173642992973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170365512371063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166205674409866</t>
   </si>
   <si>
     <t xml:space="preserve">0.168222561478615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168600738048553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166520774364471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166394725441933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161730632185936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160091891884804</t>
+    <t xml:space="preserve">0.168600767850876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166520804166794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166394740343094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161730647087097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160091906785965</t>
   </si>
   <si>
     <t xml:space="preserve">0.156688392162323</t>
@@ -1130,40 +1130,40 @@
     <t xml:space="preserve">0.162487000226974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747534155846</t>
+    <t xml:space="preserve">0.163747519254684</t>
   </si>
   <si>
     <t xml:space="preserve">0.163873612880707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161037310957909</t>
+    <t xml:space="preserve">0.16103732585907</t>
   </si>
   <si>
     <t xml:space="preserve">0.158011972904205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157759860157967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970448732376</t>
+    <t xml:space="preserve">0.157759875059128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970433831215</t>
   </si>
   <si>
     <t xml:space="preserve">0.167718321084976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165260255336761</t>
+    <t xml:space="preserve">0.165260225534439</t>
   </si>
   <si>
     <t xml:space="preserve">0.163117289543152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163810580968857</t>
+    <t xml:space="preserve">0.163810595870018</t>
   </si>
   <si>
     <t xml:space="preserve">0.159461617469788</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147675335407257</t>
+    <t xml:space="preserve">0.147675320506096</t>
   </si>
   <si>
     <t xml:space="preserve">0.147486254572868</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">0.150007396936417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150448575615883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511592626572</t>
+    <t xml:space="preserve">0.150448590517044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511607527733</t>
   </si>
   <si>
     <t xml:space="preserve">0.15107886493206</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">0.148494705557823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150826752185822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151772171258926</t>
+    <t xml:space="preserve">0.15082673728466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151772156357765</t>
   </si>
   <si>
     <t xml:space="preserve">0.149881318211555</t>
@@ -1205,10 +1205,10 @@
     <t xml:space="preserve">0.149629205465317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151709139347076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151015818119049</t>
+    <t xml:space="preserve">0.151709154248238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151015847921371</t>
   </si>
   <si>
     <t xml:space="preserve">0.148935914039612</t>
@@ -1217,10 +1217,10 @@
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763720273972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150637671351433</t>
+    <t xml:space="preserve">0.15076370537281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150637656450272</t>
   </si>
   <si>
     <t xml:space="preserve">0.15120492875576</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">0.149944365024567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152213379740715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528509497643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377092719078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15725564956665</t>
+    <t xml:space="preserve">0.152213394641876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528494596481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1493771225214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157255634665489</t>
   </si>
   <si>
     <t xml:space="preserve">0.156310215592384</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">0.163243323564529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162613049149513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161982759833336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163558468222618</t>
+    <t xml:space="preserve">0.162613019347191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161982774734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163558453321457</t>
   </si>
   <si>
     <t xml:space="preserve">0.165764465928078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165449321269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079580783844</t>
+    <t xml:space="preserve">0.165449306368828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079625487328</t>
   </si>
   <si>
     <t xml:space="preserve">0.160722196102142</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">0.149061962962151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147171080112457</t>
+    <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540820598602</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">0.146225690841675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14275911450386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334822893143</t>
+    <t xml:space="preserve">0.142759129405022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334837794304</t>
   </si>
   <si>
     <t xml:space="preserve">0.140237987041473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139607697725296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138031989336014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139922842383385</t>
+    <t xml:space="preserve">0.139607712626457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138032004237175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139922857284546</t>
   </si>
   <si>
     <t xml:space="preserve">0.135826006531715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138347163796425</t>
+    <t xml:space="preserve">0.138347148895264</t>
   </si>
   <si>
     <t xml:space="preserve">0.141498565673828</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">0.141183435916901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13866226375103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135510861873627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250313043594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935183286667</t>
+    <t xml:space="preserve">0.138662293553352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135510891675949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134250298142433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935153484344</t>
   </si>
   <si>
     <t xml:space="preserve">0.132674589753151</t>
@@ -1340,52 +1340,52 @@
     <t xml:space="preserve">0.143074259161949</t>
   </si>
   <si>
+    <t xml:space="preserve">0.144965127110481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443984746933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575853228569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864416241646</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575838327408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864431142807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145609423518181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455096960068</t>
+    <t xml:space="preserve">0.145609393715858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455082058907</t>
   </si>
   <si>
     <t xml:space="preserve">0.142710089683533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141421556472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139166504144669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139488637447357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135622903704643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133690059185028</t>
+    <t xml:space="preserve">0.141421541571617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13916651904583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777245163918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13948866724968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135622918605804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133690044283867</t>
   </si>
   <si>
     <t xml:space="preserve">0.132723614573479</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">0.13207933306694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129824310541153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125765278935432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124992154538631</t>
+    <t xml:space="preserve">0.129824295639992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125765293836594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12499213963747</t>
   </si>
   <si>
     <t xml:space="preserve">0.126796141266823</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">0.131757184863091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125894144177437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126925006508827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125378727912903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128600150346756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127440452575684</t>
+    <t xml:space="preserve">0.125894159078598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126925021409988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125378713011742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128600165247917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127440437674522</t>
   </si>
   <si>
     <t xml:space="preserve">0.127955868840218</t>
@@ -1436,13 +1436,13 @@
     <t xml:space="preserve">0.127827018499374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126023024320602</t>
+    <t xml:space="preserve">0.126023009419441</t>
   </si>
   <si>
     <t xml:space="preserve">0.124347865581512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.123703561723232</t>
+    <t xml:space="preserve">0.123703569173813</t>
   </si>
   <si>
     <t xml:space="preserve">0.127311587333679</t>
@@ -1451,61 +1451,61 @@
     <t xml:space="preserve">0.127569288015366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12666729092598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126538440585136</t>
+    <t xml:space="preserve">0.126667305827141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126538425683975</t>
   </si>
   <si>
     <t xml:space="preserve">0.12872901558876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128342464566231</t>
+    <t xml:space="preserve">0.12834244966507</t>
   </si>
   <si>
     <t xml:space="preserve">0.129502177238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130146458745003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134012192487717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134656488895416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138522237539291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13820007443428</t>
+    <t xml:space="preserve">0.130146443843842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134012207388878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134656473994255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13852222263813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138200089335442</t>
   </si>
   <si>
     <t xml:space="preserve">0.135300755500793</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130790770053864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128084734082222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128857865929604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125249862670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122157268226147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123316988348961</t>
+    <t xml:space="preserve">0.130790755152702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128084719181061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128857880830765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125249847769737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122157253324986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12331698089838</t>
   </si>
   <si>
     <t xml:space="preserve">0.125507563352585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128213599324226</t>
+    <t xml:space="preserve">0.128213584423065</t>
   </si>
   <si>
     <t xml:space="preserve">0.126151859760284</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">0.127182736992836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12563644349575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120482131838799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122286133468151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122414983808994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260672152042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266050815582</t>
+    <t xml:space="preserve">0.125636428594589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120482116937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12228612601757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122414968907833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260649800301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266080617905</t>
   </si>
   <si>
     <t xml:space="preserve">0.113394923508167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111848644912243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112106338143349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114425800740719</t>
+    <t xml:space="preserve">0.111848630011082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112106345593929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114425793290138</t>
   </si>
   <si>
     <t xml:space="preserve">0.114683508872986</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">0.112235210835934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110817797482014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108240604400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565468013287</t>
+    <t xml:space="preserve">0.110817775130272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108240619301796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565453112125</t>
   </si>
   <si>
     <t xml:space="preserve">0.105921171605587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10192658752203</t>
+    <t xml:space="preserve">0.101926572620869</t>
   </si>
   <si>
     <t xml:space="preserve">0.105019174516201</t>
@@ -1571,19 +1571,19 @@
     <t xml:space="preserve">0.103086307644844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104374878108501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117169976234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105663456022739</t>
+    <t xml:space="preserve">0.104374885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105663470923901</t>
   </si>
   <si>
     <t xml:space="preserve">0.107982911169529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108627185225487</t>
+    <t xml:space="preserve">0.108627192676067</t>
   </si>
   <si>
     <t xml:space="preserve">0.108111761510372</t>
@@ -1592,46 +1592,46 @@
     <t xml:space="preserve">0.111462064087391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112750649452209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173493623734</t>
+    <t xml:space="preserve">0.112750642001629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10875603556633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173486173153</t>
   </si>
   <si>
     <t xml:space="preserve">0.109529197216034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106952026486397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103988319635391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699741721153</t>
+    <t xml:space="preserve">0.106952041387558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153448224068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103988312184811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699726819992</t>
   </si>
   <si>
     <t xml:space="preserve">0.105276882648468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111204348504543</t>
+    <t xml:space="preserve">0.111204355955124</t>
   </si>
   <si>
     <t xml:space="preserve">0.115585520863533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115843243896961</t>
+    <t xml:space="preserve">0.1158432289958</t>
   </si>
   <si>
     <t xml:space="preserve">0.115327805280685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113008365035057</t>
+    <t xml:space="preserve">0.113008357584476</t>
   </si>
   <si>
     <t xml:space="preserve">0.10940033942461</t>
@@ -1643,43 +1643,43 @@
     <t xml:space="preserve">0.107854045927525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103730581700802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1063077673316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103859439492226</t>
+    <t xml:space="preserve">0.103730589151382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106307737529278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103859454393387</t>
   </si>
   <si>
     <t xml:space="preserve">0.114554658532143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109142616391182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013766050339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884908258915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271481633186</t>
+    <t xml:space="preserve">0.109142631292343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013758599758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884915709496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271474182606</t>
   </si>
   <si>
     <t xml:space="preserve">0.107338614761829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102442011237144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411156356335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055437862873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100251421332359</t>
+    <t xml:space="preserve">0.102442018687725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411148905754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055452764034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10025142878294</t>
   </si>
   <si>
     <t xml:space="preserve">0.0999937206506729</t>
@@ -1688,25 +1688,25 @@
     <t xml:space="preserve">0.10128228366375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101797722280025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100766859948635</t>
+    <t xml:space="preserve">0.101797729730606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100766852498055</t>
   </si>
   <si>
     <t xml:space="preserve">0.105148032307625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109915763139725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11107549071312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112621791660786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302336513996</t>
+    <t xml:space="preserve">0.109915770590305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111075483262539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112621776759624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302351415157</t>
   </si>
   <si>
     <t xml:space="preserve">0.110688924789429</t>
@@ -1715,40 +1715,40 @@
     <t xml:space="preserve">0.104761451482773</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105534590780735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467494904995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108498327434063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107080891728401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503743350506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792321264744</t>
+    <t xml:space="preserve">0.105534598231316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467472553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108498334884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107080906629562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503735899925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792313814163</t>
   </si>
   <si>
     <t xml:space="preserve">0.106436602771282</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105341322720051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596330344677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562774956226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110185049474239</t>
+    <t xml:space="preserve">0.105341300368309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596322894096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562767505646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207049012184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185064375401</t>
   </si>
   <si>
     <t xml:space="preserve">0.109857134521008</t>
@@ -1757,142 +1757,142 @@
     <t xml:space="preserve">0.11116885393858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110513016581535</t>
+    <t xml:space="preserve">0.110512994229794</t>
   </si>
   <si>
     <t xml:space="preserve">0.107889540493488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106905743479729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10592196136713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103954374790192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104282297194004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105594009160995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217485249043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104938149452209</t>
+    <t xml:space="preserve">0.106905750930309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921968817711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103954344987869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104282289743423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105594016611576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217462897301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266101658344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10493815690279</t>
   </si>
   <si>
     <t xml:space="preserve">0.102970570325851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103626430034637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103298500180244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101658843457699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100347101688385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101330906152725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0970677956938744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0977236554026604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957255482674</t>
+    <t xml:space="preserve">0.103626437485218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103298492729664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101658821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100347116589546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101330891251564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0970677882432938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0977236703038216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957106471062</t>
   </si>
   <si>
     <t xml:space="preserve">0.0951002016663551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0980515852570534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0964119359850883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0987074598670006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099363312125206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100019186735153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002983748913</t>
+    <t xml:space="preserve">0.098051592707634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0964119285345078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09870745241642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0993633195757866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100019179284573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002991199493</t>
   </si>
   <si>
     <t xml:space="preserve">0.10067505389452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102642640471458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.098379522562027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0996912568807602</t>
+    <t xml:space="preserve">0.102642647922039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0983795300126076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099691241979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.0990353748202324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104610212147236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107561610639095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108873322606087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545407652855</t>
+    <t xml:space="preserve">0.104610227048397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107561625540257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108873337507248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545422554016</t>
   </si>
   <si>
     <t xml:space="preserve">0.109201282262802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107233673334122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106249876320362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11215265840292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114448167383671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111824713647366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808525562286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113136455416679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112480588257313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496791243553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130516842007637</t>
+    <t xml:space="preserve">0.107233665883541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106249883770943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112152650952339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114448182284832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111824721097946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808518111706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113136447966099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112480595707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496798694134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130516827106476</t>
   </si>
   <si>
     <t xml:space="preserve">0.139698907732964</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">0.160686567425728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173803806304932</t>
+    <t xml:space="preserve">0.173803821206093</t>
   </si>
   <si>
     <t xml:space="preserve">0.167245179414749</t>
@@ -1922,22 +1922,22 @@
     <t xml:space="preserve">0.154127910733223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157407239079475</t>
+    <t xml:space="preserve">0.157407224178314</t>
   </si>
   <si>
     <t xml:space="preserve">0.156751364469528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15281617641449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148880988359451</t>
+    <t xml:space="preserve">0.152816191315651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148881018161774</t>
   </si>
   <si>
     <t xml:space="preserve">0.145601689815521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146257564425468</t>
+    <t xml:space="preserve">0.146257549524307</t>
   </si>
   <si>
     <t xml:space="preserve">0.146913424134254</t>
@@ -1955,37 +1955,37 @@
     <t xml:space="preserve">0.147569268941879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148225158452988</t>
+    <t xml:space="preserve">0.148225143551826</t>
   </si>
   <si>
     <t xml:space="preserve">0.162654146552086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161342442035675</t>
+    <t xml:space="preserve">0.161342427134514</t>
   </si>
   <si>
     <t xml:space="preserve">0.141666516661644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139043048024178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135107859969139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133140295743942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137731328606606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15478378534317</t>
+    <t xml:space="preserve">0.1390430778265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135107889771461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133140280842781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137731313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154783800244331</t>
   </si>
   <si>
     <t xml:space="preserve">0.156095519661903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153472051024437</t>
+    <t xml:space="preserve">0.153472036123276</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
@@ -1997,34 +1997,34 @@
     <t xml:space="preserve">0.137075453996658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125597849488258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126581653952599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123958200216293</t>
+    <t xml:space="preserve">0.12559786438942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12658166885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123958192765713</t>
   </si>
   <si>
     <t xml:space="preserve">0.118711277842522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110840924084187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0967398434877396</t>
+    <t xml:space="preserve">0.110840931534767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0967398509383202</t>
   </si>
   <si>
     <t xml:space="preserve">0.0826388001441956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.087885707616806</t>
+    <t xml:space="preserve">0.0878857150673866</t>
   </si>
   <si>
     <t xml:space="preserve">0.08722984790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0885415747761726</t>
+    <t xml:space="preserve">0.0885415598750114</t>
   </si>
   <si>
     <t xml:space="preserve">0.0911650210618973</t>
@@ -2033,97 +2033,97 @@
     <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0928046777844429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0944443494081497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0960840061306953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0931326150894165</t>
+    <t xml:space="preserve">0.0928046852350235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0944443345069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0960839986801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0931326076388359</t>
   </si>
   <si>
     <t xml:space="preserve">0.0957560688257217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0937884747982025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0965431034564972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0969366133213043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0978548303246498</t>
+    <t xml:space="preserve">0.0937884822487831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0965431109070778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0969366207718849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0978548377752304</t>
   </si>
   <si>
     <t xml:space="preserve">0.0971989706158638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0924767553806305</t>
+    <t xml:space="preserve">0.0924767479300499</t>
   </si>
   <si>
     <t xml:space="preserve">0.0940508171916008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.093919649720192</t>
+    <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
     <t xml:space="preserve">0.0941819921135902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0949690416455269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937189817429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483476400375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740633904934</t>
+    <t xml:space="preserve">0.0949690341949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937264323235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483550906181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740626454353</t>
   </si>
   <si>
     <t xml:space="preserve">0.0968054458498955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0966742932796478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709749162197</t>
+    <t xml:space="preserve">0.096674270927906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709741711617</t>
   </si>
   <si>
     <t xml:space="preserve">0.0979860052466393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0991665497422218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0936572998762131</t>
+    <t xml:space="preserve">0.0991665571928024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
     <t xml:space="preserve">0.0948378592729568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100084774196148</t>
+    <t xml:space="preserve">0.100084781646729</t>
   </si>
   <si>
     <t xml:space="preserve">0.102183528244495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0999535992741585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10323292016983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104806981980801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14035476744175</t>
+    <t xml:space="preserve">0.0999535918235779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10323291271925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10480697453022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
     <t xml:space="preserve">0.125925794243813</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">0.142322361469269</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137403413653374</t>
+    <t xml:space="preserve">0.137403398752213</t>
   </si>
   <si>
     <t xml:space="preserve">0.135435804724693</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">0.131041511893272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127893388271332</t>
+    <t xml:space="preserve">0.127893358469009</t>
   </si>
   <si>
     <t xml:space="preserve">0.134779959917068</t>
@@ -2168,40 +2168,40 @@
     <t xml:space="preserve">0.130123317241669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129336282610893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130385637283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131500616669655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130910336971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133468210697174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129992127418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975178718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127631038427353</t>
+    <t xml:space="preserve">0.129336267709732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130385667085648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131500631570816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130910366773605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133468225598335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129992142319679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975163817406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127631023526192</t>
   </si>
   <si>
     <t xml:space="preserve">0.128549233078957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133796155452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132156491279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130648002028465</t>
+    <t xml:space="preserve">0.133796140551567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132156476378441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130648016929626</t>
   </si>
   <si>
     <t xml:space="preserve">0.129205107688904</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">0.129598617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140026852488518</t>
+    <t xml:space="preserve">0.140026837587357</t>
   </si>
   <si>
     <t xml:space="preserve">0.1297297924757</t>
@@ -2228,13 +2228,13 @@
     <t xml:space="preserve">0.125138744711876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12461406737566</t>
+    <t xml:space="preserve">0.124614045023918</t>
   </si>
   <si>
     <t xml:space="preserve">0.143634095788002</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143962040543556</t>
+    <t xml:space="preserve">0.143962055444717</t>
   </si>
   <si>
     <t xml:space="preserve">0.139370992779732</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">0.136091664433479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13805927336216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136747524142265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140682712197304</t>
+    <t xml:space="preserve">0.138059258460999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136747539043427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140682727098465</t>
   </si>
   <si>
     <t xml:space="preserve">0.144945830106735</t>
@@ -2267,19 +2267,19 @@
     <t xml:space="preserve">0.153799995779991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152488246560097</t>
+    <t xml:space="preserve">0.152488261461258</t>
   </si>
   <si>
     <t xml:space="preserve">0.157079309225082</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152160316705704</t>
+    <t xml:space="preserve">0.152160346508026</t>
   </si>
   <si>
     <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155111715197563</t>
+    <t xml:space="preserve">0.155111700296402</t>
   </si>
   <si>
     <t xml:space="preserve">0.155767560005188</t>
@@ -2288,22 +2288,22 @@
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702733159065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162982076406479</t>
+    <t xml:space="preserve">0.159702748060226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162982061505318</t>
   </si>
   <si>
     <t xml:space="preserve">0.166917264461517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163309991359711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162326201796532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161014467477798</t>
+    <t xml:space="preserve">0.163310006260872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162326216697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16101448237896</t>
   </si>
   <si>
     <t xml:space="preserve">0.15904688835144</t>
@@ -2327,10 +2327,10 @@
     <t xml:space="preserve">0.165341436862946</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163571178913116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162863090634346</t>
+    <t xml:space="preserve">0.163571193814278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162863075733185</t>
   </si>
   <si>
     <t xml:space="preserve">0.16250903904438</t>
@@ -2342,19 +2342,19 @@
     <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157198294997215</t>
+    <t xml:space="preserve">0.157198280096054</t>
   </si>
   <si>
     <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162154987454414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158968523144722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160384744405746</t>
+    <t xml:space="preserve">0.162154972553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158968538045883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160384729504585</t>
   </si>
   <si>
     <t xml:space="preserve">0.159322574734688</t>
@@ -2372,34 +2372,34 @@
     <t xml:space="preserve">0.153303727507591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155782073736191</t>
+    <t xml:space="preserve">0.155782088637352</t>
   </si>
   <si>
     <t xml:space="preserve">0.151533484458923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15259562432766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154719933867455</t>
+    <t xml:space="preserve">0.152595639228821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154719948768616</t>
   </si>
   <si>
     <t xml:space="preserve">0.155428051948547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156844243407249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156490162014961</t>
+    <t xml:space="preserve">0.156844213604927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156490176916122</t>
   </si>
   <si>
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011830687523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156136140227318</t>
+    <t xml:space="preserve">0.154011815786362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156136125326157</t>
   </si>
   <si>
     <t xml:space="preserve">0.152241587638855</t>
@@ -2408,16 +2408,16 @@
     <t xml:space="preserve">0.154365882277489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151887521147728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151179432868958</t>
+    <t xml:space="preserve">0.151887536048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151179417967796</t>
   </si>
   <si>
     <t xml:space="preserve">0.150117293000221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150825381278992</t>
+    <t xml:space="preserve">0.150825366377831</t>
   </si>
   <si>
     <t xml:space="preserve">0.149763226509094</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149055108428001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146222725510597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147284895181656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1426822245121</t>
+    <t xml:space="preserve">0.149055138230324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146222710609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147284880280495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142682209610939</t>
   </si>
   <si>
     <t xml:space="preserve">0.143390327692032</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152949675917625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1451605707407</t>
+    <t xml:space="preserve">0.152949690818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145160585641861</t>
   </si>
   <si>
     <t xml:space="preserve">0.147638931870461</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">0.144452467560768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143744379281998</t>
+    <t xml:space="preserve">0.143744364380836</t>
   </si>
   <si>
     <t xml:space="preserve">0.144806519150734</t>
@@ -2477,7 +2477,7 @@
     <t xml:space="preserve">0.144098430871964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14586865901947</t>
+    <t xml:space="preserve">0.145868673920631</t>
   </si>
   <si>
     <t xml:space="preserve">0.147992968559265</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">0.16569547355175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168527901172638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167111694812775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16746574640274</t>
+    <t xml:space="preserve">0.168527886271477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167111709713936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167465716600418</t>
   </si>
   <si>
     <t xml:space="preserve">0.16498738527298</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">0.167021751403809</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161695286631584</t>
+    <t xml:space="preserve">0.161695301532745</t>
   </si>
   <si>
     <t xml:space="preserve">0.161314845085144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159793004393578</t>
+    <t xml:space="preserve">0.159792989492416</t>
   </si>
   <si>
     <t xml:space="preserve">0.163978055119514</t>
@@ -2528,13 +2528,13 @@
     <t xml:space="preserve">0.16055391728878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158271163702011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160934388637543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162836685776711</t>
+    <t xml:space="preserve">0.158271178603172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160934373736382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2549,10 +2549,10 @@
     <t xml:space="preserve">0.159032076597214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159412547945976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160173445940018</t>
+    <t xml:space="preserve">0.159412533044815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16017347574234</t>
   </si>
   <si>
     <t xml:space="preserve">0.165880352258682</t>
@@ -2564,40 +2564,40 @@
     <t xml:space="preserve">0.169684946537018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170826330780983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171967715024948</t>
+    <t xml:space="preserve">0.170826315879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171967700123787</t>
   </si>
   <si>
     <t xml:space="preserve">0.170065402984619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157129779458046</t>
+    <t xml:space="preserve">0.157129764556885</t>
   </si>
   <si>
     <t xml:space="preserve">0.15789070725441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153705641627312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144270271062851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147770464420319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155227467417717</t>
+    <t xml:space="preserve">0.153705656528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14427025616169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14777047932148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155227482318878</t>
   </si>
   <si>
     <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157510235905647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164738968014717</t>
+    <t xml:space="preserve">0.157510250806808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164738982915878</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
@@ -2606,37 +2606,37 @@
     <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166641250252724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16816309094429</t>
+    <t xml:space="preserve">0.166641265153885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168163105845451</t>
   </si>
   <si>
     <t xml:space="preserve">0.167402192950249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168543577194214</t>
+    <t xml:space="preserve">0.168543562293053</t>
   </si>
   <si>
     <t xml:space="preserve">0.173869997262955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174277201294899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173462823033333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171426862478256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168983712792397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166133403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170612469315529</t>
+    <t xml:space="preserve">0.174277186393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173462808132172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171426877379417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168983727693558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166133388876915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17061248421669</t>
   </si>
   <si>
     <t xml:space="preserve">0.16816933453083</t>
@@ -2645,10 +2645,10 @@
     <t xml:space="preserve">0.167354971170425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165319010615349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166540592908859</t>
+    <t xml:space="preserve">0.16531902551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16654060781002</t>
   </si>
   <si>
     <t xml:space="preserve">0.166947782039642</t>
@@ -2660,31 +2660,31 @@
     <t xml:space="preserve">0.168576538562775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169390916824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16287587583065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15196318924427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155709341168404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157175213098526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15636083483696</t>
+    <t xml:space="preserve">0.169390931725502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162875890731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151963204145432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155709356069565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157175242900848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156360849738121</t>
   </si>
   <si>
     <t xml:space="preserve">0.157338097691536</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155546456575394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15424345433712</t>
+    <t xml:space="preserve">0.155546471476555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154243469238281</t>
   </si>
   <si>
     <t xml:space="preserve">0.150660187005997</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">0.163690254092216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162387236952782</t>
+    <t xml:space="preserve">0.162387251853943</t>
   </si>
   <si>
     <t xml:space="preserve">0.158478230237961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160432741045952</t>
+    <t xml:space="preserve">0.160432755947113</t>
   </si>
   <si>
     <t xml:space="preserve">0.157012343406677</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">0.161247119307518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161735728383064</t>
+    <t xml:space="preserve">0.161735743284225</t>
   </si>
   <si>
     <t xml:space="preserve">0.161572873592377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157500967383385</t>
+    <t xml:space="preserve">0.157500982284546</t>
   </si>
   <si>
     <t xml:space="preserve">0.160269856452942</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">0.159129723906517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160595625638962</t>
+    <t xml:space="preserve">0.160595610737801</t>
   </si>
   <si>
     <t xml:space="preserve">0.159781232476234</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">0.161410003900528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159944102168083</t>
+    <t xml:space="preserve">0.159944117069244</t>
   </si>
   <si>
     <t xml:space="preserve">0.154732078313828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966839313507</t>
+    <t xml:space="preserve">0.158966869115829</t>
   </si>
   <si>
     <t xml:space="preserve">0.15652371942997</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">0.156197965145111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156035080552101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157663851976395</t>
+    <t xml:space="preserve">0.156035095453262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157663837075233</t>
   </si>
   <si>
     <t xml:space="preserve">0.155383586883545</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">0.157826736569405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158152461051941</t>
+    <t xml:space="preserve">0.158152475953102</t>
   </si>
   <si>
     <t xml:space="preserve">0.156686589121819</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">0.153103321790695</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152288943529129</t>
+    <t xml:space="preserve">0.15228895843029</t>
   </si>
   <si>
     <t xml:space="preserve">0.154894962906837</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">0.160921365022659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159292608499527</t>
+    <t xml:space="preserve">0.159292623400688</t>
   </si>
   <si>
     <t xml:space="preserve">0.158641114830971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164911836385727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164504632353783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163283064961433</t>
+    <t xml:space="preserve">0.164911821484566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164504647254944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163283079862595</t>
   </si>
   <si>
     <t xml:space="preserve">0.164097443223</t>
@@ -2828,19 +2828,19 @@
     <t xml:space="preserve">0.162550121545792</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161084234714508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15880398452282</t>
+    <t xml:space="preserve">0.161084249615669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158803969621658</t>
   </si>
   <si>
     <t xml:space="preserve">0.159618362784386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159455493092537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16271299123764</t>
+    <t xml:space="preserve">0.159455478191376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162713006138802</t>
   </si>
   <si>
     <t xml:space="preserve">0.165726214647293</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">0.17305563390255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176720336079597</t>
+    <t xml:space="preserve">0.176720321178436</t>
   </si>
   <si>
     <t xml:space="preserve">0.177534714341164</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">0.175091579556465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171019673347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172241255640984</t>
+    <t xml:space="preserve">0.171019658446312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172241240739822</t>
   </si>
   <si>
     <t xml:space="preserve">0.172648444771767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171834066510201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169798091053963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.183235362172127</t>
+    <t xml:space="preserve">0.171834051609039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.169798105955124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183235347270966</t>
   </si>
   <si>
     <t xml:space="preserve">0.181606605648994</t>
@@ -2891,40 +2891,43 @@
     <t xml:space="preserve">0.184049740433693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182420983910561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.184864118695259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.185678511857986</t>
+    <t xml:space="preserve">0.182420998811722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18486413359642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.185678496956825</t>
   </si>
   <si>
     <t xml:space="preserve">0.188121646642685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182920128107071</t>
+    <t xml:space="preserve">0.18292011320591</t>
   </si>
   <si>
     <t xml:space="preserve">0.186387807130814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187254726886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189855486154556</t>
+    <t xml:space="preserve">0.18725474178791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189855471253395</t>
   </si>
   <si>
     <t xml:space="preserve">0.190722405910492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188988566398621</t>
+    <t xml:space="preserve">0.188988551497459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188121631741524</t>
   </si>
   <si>
     <t xml:space="preserve">0.185520887374878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183787047863007</t>
+    <t xml:space="preserve">0.183787032961845</t>
   </si>
   <si>
     <t xml:space="preserve">0.182053208351135</t>
@@ -2942,25 +2945,25 @@
     <t xml:space="preserve">0.179452449083328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177718609571457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176851689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175984755158424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175117835402489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174250915646553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173383995890617</t>
+    <t xml:space="preserve">0.178585514426231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177718594670296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17685167491436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175984770059586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17511785030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174250930547714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173384010791779</t>
   </si>
   <si>
     <t xml:space="preserve">0.191589325666428</t>
@@ -52379,7 +52382,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1873" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52431,7 +52434,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1875" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52457,7 +52460,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1876" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52483,7 +52486,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1877" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52509,7 +52512,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1878" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52561,7 +52564,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1880" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52639,7 +52642,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1883" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52665,7 +52668,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1884" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52691,7 +52694,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1885" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52769,7 +52772,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1888" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52795,7 +52798,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1889" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52821,7 +52824,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1890" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52847,7 +52850,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1891" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52873,7 +52876,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1892" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52899,7 +52902,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1893" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52925,7 +52928,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1894" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52951,7 +52954,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1895" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52977,7 +52980,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1896" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53029,7 +53032,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1898" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53055,7 +53058,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1899" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53081,7 +53084,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1900" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53107,7 +53110,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1901" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53133,7 +53136,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1902" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53185,7 +53188,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1904" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53211,7 +53214,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1905" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53289,7 +53292,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1908" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53315,7 +53318,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1909" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53341,7 +53344,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1910" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53367,7 +53370,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1911" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53419,7 +53422,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1913" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53445,7 +53448,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1914" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53497,7 +53500,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1916" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53523,7 +53526,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1917" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53549,7 +53552,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1918" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53575,7 +53578,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1919" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53601,7 +53604,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1920" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53627,7 +53630,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1921" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53653,7 +53656,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1922" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53679,7 +53682,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1923" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53705,7 +53708,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1924" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53731,7 +53734,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1925" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53757,7 +53760,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1926" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53783,7 +53786,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1927" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53835,7 +53838,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1929" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53887,7 +53890,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1931" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53913,7 +53916,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1932" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53939,7 +53942,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1933" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53965,7 +53968,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1934" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53991,7 +53994,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1935" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54017,7 +54020,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1936" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54043,7 +54046,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54069,7 +54072,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1938" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54095,7 +54098,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1939" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54121,7 +54124,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1940" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54147,7 +54150,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1941" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54173,7 +54176,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1942" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54199,7 +54202,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54225,7 +54228,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54251,7 +54254,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1945" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54277,7 +54280,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1946" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54303,7 +54306,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54329,7 +54332,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1948" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54355,7 +54358,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54381,7 +54384,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1950" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54407,7 +54410,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54433,7 +54436,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1952" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54459,7 +54462,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1953" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54485,7 +54488,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1954" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54511,7 +54514,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1955" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54537,7 +54540,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1956" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54563,7 +54566,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1957" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54589,7 +54592,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1958" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54615,7 +54618,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1959" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54641,7 +54644,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1960" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54667,7 +54670,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1961" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54693,7 +54696,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1962" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54719,7 +54722,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54745,7 +54748,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54771,7 +54774,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1965" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54823,7 +54826,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1967" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54849,7 +54852,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1968" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54875,7 +54878,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1969" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54901,7 +54904,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1970" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54927,7 +54930,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1971" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54953,7 +54956,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1972" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54979,7 +54982,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1973" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55005,7 +55008,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1974" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55031,7 +55034,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1975" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55057,7 +55060,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55083,7 +55086,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1977" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55109,7 +55112,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1978" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55135,7 +55138,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55161,7 +55164,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1980" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55187,7 +55190,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1981" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55213,7 +55216,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1982" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55239,7 +55242,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1983" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55265,7 +55268,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1984" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55291,7 +55294,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1985" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55317,7 +55320,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1986" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55343,7 +55346,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1987" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55369,7 +55372,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55395,7 +55398,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1989" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55421,7 +55424,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55447,7 +55450,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1991" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55473,7 +55476,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1992" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55499,7 +55502,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1993" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55525,7 +55528,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1994" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55551,7 +55554,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1995" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55577,7 +55580,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1996" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55603,7 +55606,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1997" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55629,7 +55632,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1998" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55655,7 +55658,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1999" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55681,7 +55684,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2000" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55707,7 +55710,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55733,7 +55736,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2002" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55759,7 +55762,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2003" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55785,7 +55788,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2004" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55811,7 +55814,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55837,7 +55840,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2006" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55863,7 +55866,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2007" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55889,7 +55892,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2008" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55915,7 +55918,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2009" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55941,7 +55944,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2010" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55967,7 +55970,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2011" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55993,7 +55996,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2012" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56019,7 +56022,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2013" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56045,7 +56048,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2014" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56071,7 +56074,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2015" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56097,7 +56100,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2016" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56123,7 +56126,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2017" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56149,7 +56152,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2018" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56175,7 +56178,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2019" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56201,7 +56204,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2020" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56227,7 +56230,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2021" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56253,7 +56256,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56279,7 +56282,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2023" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56305,7 +56308,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2024" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56331,7 +56334,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2025" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56357,7 +56360,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56383,7 +56386,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2027" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56409,7 +56412,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56435,7 +56438,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2029" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56461,7 +56464,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2030" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56487,7 +56490,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2031" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56513,7 +56516,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2032" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56539,7 +56542,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56565,7 +56568,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2034" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56591,7 +56594,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2035" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56617,7 +56620,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2036" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56643,7 +56646,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2037" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56669,7 +56672,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2038" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56695,7 +56698,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2039" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56721,7 +56724,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56747,7 +56750,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2041" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56773,7 +56776,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2042" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56799,7 +56802,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2043" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56825,7 +56828,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2044" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56851,7 +56854,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2045" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56877,7 +56880,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2046" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56903,7 +56906,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2047" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56929,7 +56932,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2048" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56955,7 +56958,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2049" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56981,7 +56984,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2050" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57007,7 +57010,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2051" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57033,7 +57036,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2052" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57059,7 +57062,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2053" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57085,7 +57088,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2054" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57111,7 +57114,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2055" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57137,7 +57140,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2056" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57163,7 +57166,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2057" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57189,7 +57192,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2058" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57215,7 +57218,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2059" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57241,7 +57244,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2060" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57267,7 +57270,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2061" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57293,7 +57296,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2062" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57319,7 +57322,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2063" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57345,7 +57348,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2064" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57371,7 +57374,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2065" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57397,7 +57400,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57423,7 +57426,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57449,7 +57452,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2068" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57475,7 +57478,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57501,7 +57504,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57527,7 +57530,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57553,7 +57556,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57579,7 +57582,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57605,7 +57608,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2074" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57631,7 +57634,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2075" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57657,7 +57660,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2076" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57683,7 +57686,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2077" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57709,7 +57712,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2078" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57735,7 +57738,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2079" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57761,7 +57764,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2080" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57787,7 +57790,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2081" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57813,7 +57816,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2082" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57839,7 +57842,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2083" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57865,7 +57868,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2084" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57891,7 +57894,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2085" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57917,7 +57920,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2086" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57943,7 +57946,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2087" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57969,7 +57972,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2088" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57995,7 +57998,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2089" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58021,7 +58024,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2090" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58047,7 +58050,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2091" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58073,7 +58076,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2092" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58099,7 +58102,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2093" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58125,7 +58128,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2094" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58151,7 +58154,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2095" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58229,7 +58232,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2098" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58307,7 +58310,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2101" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58333,7 +58336,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2102" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58359,7 +58362,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2103" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58385,7 +58388,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2104" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58437,7 +58440,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2106" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58489,7 +58492,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2108" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58541,7 +58544,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2110" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58567,7 +58570,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2111" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58593,7 +58596,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2112" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58619,7 +58622,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2113" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58645,7 +58648,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2114" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58671,7 +58674,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2115" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58697,7 +58700,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2116" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58749,7 +58752,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2118" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58775,7 +58778,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2119" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58801,7 +58804,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2120" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58827,7 +58830,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2121" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58853,7 +58856,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2122" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58879,7 +58882,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2123" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58905,7 +58908,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2124" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58931,7 +58934,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2125" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58957,7 +58960,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2126" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58983,7 +58986,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2127" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59009,7 +59012,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2128" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59035,7 +59038,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2129" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59061,7 +59064,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2130" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59087,7 +59090,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2131" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59113,7 +59116,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2132" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59139,7 +59142,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2133" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59165,7 +59168,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2134" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59191,7 +59194,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2135" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59217,7 +59220,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2136" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59243,7 +59246,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2137" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59269,7 +59272,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2138" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59295,7 +59298,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2139" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59321,7 +59324,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2140" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59347,7 +59350,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2141" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59373,7 +59376,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2142" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59399,7 +59402,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2143" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59425,7 +59428,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2144" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59451,7 +59454,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2145" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59477,7 +59480,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2146" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59503,7 +59506,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2147" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59529,7 +59532,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2148" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59555,7 +59558,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2149" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59581,7 +59584,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2150" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59607,7 +59610,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2151" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59633,7 +59636,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2152" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59659,7 +59662,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2153" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59685,7 +59688,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2154" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59711,7 +59714,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2155" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59737,7 +59740,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2156" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59763,7 +59766,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2157" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59789,7 +59792,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2158" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59815,7 +59818,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2159" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59841,7 +59844,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2160" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59867,7 +59870,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2161" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59893,7 +59896,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2162" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59919,7 +59922,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2163" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59945,7 +59948,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2164" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59971,7 +59974,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2165" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59997,7 +60000,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G2166" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60023,7 +60026,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2167" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60049,7 +60052,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2168" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60075,7 +60078,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2169" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60101,7 +60104,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2170" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60127,7 +60130,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2171" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60153,7 +60156,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2172" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60179,7 +60182,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2173" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60205,7 +60208,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2174" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60231,7 +60234,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2175" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60257,7 +60260,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2176" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60283,7 +60286,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2177" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60309,7 +60312,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2178" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60335,7 +60338,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2179" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60361,7 +60364,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2180" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60387,7 +60390,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G2181" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60413,7 +60416,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2182" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60439,7 +60442,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2183" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60465,7 +60468,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2184" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60491,7 +60494,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2185" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60517,7 +60520,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2186" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60543,7 +60546,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2187" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60569,7 +60572,7 @@
         <v>0.195500001311302</v>
       </c>
       <c r="G2188" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60595,7 +60598,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2189" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60621,7 +60624,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2190" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60647,7 +60650,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2191" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60673,7 +60676,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2192" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60699,7 +60702,7 @@
         <v>0.194499999284744</v>
       </c>
       <c r="G2193" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60725,7 +60728,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2194" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60751,7 +60754,7 @@
         <v>0.195999994874001</v>
       </c>
       <c r="G2195" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60777,7 +60780,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2196" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60803,7 +60806,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2197" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60829,7 +60832,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2198" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60855,7 +60858,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2199" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60881,7 +60884,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2200" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60907,7 +60910,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2201" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60933,7 +60936,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2202" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60959,7 +60962,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2203" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60985,7 +60988,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2204" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61011,7 +61014,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2205" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61037,7 +61040,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2206" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61063,7 +61066,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2207" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61089,7 +61092,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2208" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61115,7 +61118,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2209" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61141,7 +61144,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2210" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61167,7 +61170,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2211" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61193,7 +61196,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2212" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61219,7 +61222,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2213" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61245,7 +61248,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2214" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61271,7 +61274,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2215" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61297,7 +61300,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2216" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61323,7 +61326,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2217" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61349,7 +61352,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2218" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61375,7 +61378,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2219" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61401,7 +61404,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2220" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61427,7 +61430,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2221" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61453,7 +61456,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2222" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61479,7 +61482,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2223" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61505,7 +61508,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2224" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61531,7 +61534,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2225" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61557,7 +61560,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2226" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61583,7 +61586,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2227" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61609,7 +61612,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2228" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61635,7 +61638,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2229" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61661,7 +61664,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2230" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61687,7 +61690,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2231" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61713,7 +61716,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2232" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61739,7 +61742,7 @@
         <v>0.197500005364418</v>
       </c>
       <c r="G2233" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61765,7 +61768,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2234" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61791,7 +61794,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2235" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61817,7 +61820,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2236" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61843,7 +61846,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2237" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61869,7 +61872,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2238" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61895,7 +61898,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2239" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61921,7 +61924,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2240" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61947,7 +61950,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2241" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61973,7 +61976,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2242" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61999,7 +62002,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2243" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62025,7 +62028,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2244" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62051,7 +62054,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2245" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62077,7 +62080,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2246" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62103,7 +62106,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2247" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62129,7 +62132,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2248" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62155,7 +62158,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62181,7 +62184,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G2250" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62207,7 +62210,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2251" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62233,7 +62236,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2252" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62259,7 +62262,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2253" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62285,7 +62288,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2254" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62311,7 +62314,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2255" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62337,7 +62340,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62363,7 +62366,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2257" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62389,7 +62392,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2258" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62415,7 +62418,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2259" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62441,7 +62444,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2260" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62467,7 +62470,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2261" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62493,7 +62496,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2262" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62519,7 +62522,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2263" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62545,7 +62548,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2264" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62571,7 +62574,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2265" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62597,7 +62600,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2266" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62623,7 +62626,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2267" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62649,7 +62652,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2268" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62675,7 +62678,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2269" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62701,7 +62704,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2270" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62727,7 +62730,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2271" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62753,7 +62756,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2272" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62779,7 +62782,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2273" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62805,7 +62808,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2274" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62831,7 +62834,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2275" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62857,7 +62860,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2276" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62883,7 +62886,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2277" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62909,7 +62912,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2278" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62935,7 +62938,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2279" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62961,7 +62964,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2280" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62987,7 +62990,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2281" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63013,7 +63016,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G2282" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63039,7 +63042,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2283" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63065,7 +63068,7 @@
         <v>0.19149999320507</v>
       </c>
       <c r="G2284" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63091,7 +63094,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2285" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63117,7 +63120,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2286" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63143,7 +63146,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2287" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63169,7 +63172,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2288" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63195,7 +63198,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2289" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63221,7 +63224,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2290" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63247,7 +63250,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G2291" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63273,7 +63276,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2292" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63299,7 +63302,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G2293" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63325,7 +63328,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2294" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63351,7 +63354,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2295" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63377,7 +63380,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2296" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63403,7 +63406,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2297" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63429,7 +63432,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2298" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63455,7 +63458,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2299" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63481,7 +63484,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2300" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63507,7 +63510,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2301" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63533,7 +63536,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2302" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63559,7 +63562,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2303" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63585,7 +63588,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2304" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63611,7 +63614,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2305" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63637,7 +63640,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2306" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63663,7 +63666,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2307" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63689,7 +63692,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2308" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63715,7 +63718,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2309" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63741,7 +63744,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2310" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63767,7 +63770,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2311" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63793,7 +63796,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2312" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63819,7 +63822,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2313" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63845,7 +63848,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2314" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63871,7 +63874,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2315" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63897,7 +63900,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2316" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63923,7 +63926,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2317" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63949,7 +63952,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2318" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63975,7 +63978,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2319" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64001,7 +64004,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2320" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64027,7 +64030,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2321" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64053,7 +64056,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2322" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64079,7 +64082,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2323" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64105,7 +64108,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2324" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64131,7 +64134,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2325" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64157,7 +64160,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2326" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64183,7 +64186,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2327" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64209,7 +64212,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2328" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64235,7 +64238,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2329" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64261,7 +64264,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2330" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64287,7 +64290,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2331" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64313,7 +64316,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2332" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64339,7 +64342,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2333" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64365,7 +64368,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2334" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64391,7 +64394,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2335" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64417,7 +64420,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2336" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64443,7 +64446,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2337" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64469,7 +64472,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2338" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64495,7 +64498,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64521,7 +64524,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2340" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64547,7 +64550,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2341" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64573,7 +64576,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2342" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64599,7 +64602,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2343" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64625,7 +64628,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2344" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64651,7 +64654,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2345" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64677,7 +64680,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2346" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64703,7 +64706,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2347" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64729,7 +64732,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64755,7 +64758,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2349" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64781,7 +64784,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2350" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64807,7 +64810,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2351" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64833,7 +64836,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2352" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64859,7 +64862,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2353" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64885,7 +64888,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G2354" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64911,7 +64914,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2355" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64937,7 +64940,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2356" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64963,7 +64966,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2357" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64989,7 +64992,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2358" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65015,7 +65018,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2359" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65041,7 +65044,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2360" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65067,7 +65070,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2361" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65093,7 +65096,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65119,7 +65122,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2363" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65145,7 +65148,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G2364" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65171,7 +65174,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2365" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65197,7 +65200,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2366" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65223,7 +65226,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2367" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65249,7 +65252,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2368" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65275,7 +65278,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2369" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65301,7 +65304,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2370" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65327,7 +65330,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2371" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65353,7 +65356,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2372" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65379,7 +65382,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2373" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65405,7 +65408,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2374" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65431,7 +65434,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2375" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65457,7 +65460,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2376" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65483,7 +65486,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2377" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65509,7 +65512,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2378" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65535,7 +65538,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2379" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65561,7 +65564,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2380" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65587,7 +65590,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2381" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65613,7 +65616,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2382" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65639,7 +65642,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2383" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65665,7 +65668,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65691,7 +65694,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2385" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65717,7 +65720,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2386" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65743,7 +65746,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2387" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65769,7 +65772,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2388" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65795,7 +65798,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2389" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65821,7 +65824,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2390" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65847,7 +65850,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2391" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65873,7 +65876,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2392" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65899,7 +65902,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2393" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65925,7 +65928,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2394" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65951,7 +65954,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2395" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65977,7 +65980,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2396" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66003,7 +66006,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2397" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66029,7 +66032,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2398" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66055,7 +66058,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2399" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66081,7 +66084,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2400" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66107,7 +66110,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2401" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66133,7 +66136,7 @@
         <v>0.172499999403954</v>
       </c>
       <c r="G2402" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66159,7 +66162,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2403" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66185,7 +66188,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2404" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66211,7 +66214,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2405" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66237,7 +66240,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2406" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66263,7 +66266,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2407" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66289,7 +66292,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2408" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66315,7 +66318,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2409" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66341,7 +66344,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2410" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66367,7 +66370,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2411" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66393,7 +66396,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2412" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66419,7 +66422,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2413" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66445,7 +66448,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2414" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66471,7 +66474,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2415" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66497,7 +66500,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2416" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66523,7 +66526,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2417" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66549,7 +66552,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2418" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66575,7 +66578,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2419" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66601,7 +66604,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2420" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66627,7 +66630,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2421" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66653,7 +66656,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2422" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66679,7 +66682,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2423" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66705,7 +66708,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2424" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66731,7 +66734,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2425" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66757,7 +66760,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2426" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66783,7 +66786,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66809,7 +66812,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2428" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66835,7 +66838,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2429" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66861,7 +66864,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2430" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66887,7 +66890,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2431" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66913,7 +66916,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2432" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66939,7 +66942,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2433" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66965,7 +66968,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66991,7 +66994,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2435" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67017,7 +67020,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2436" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67043,7 +67046,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2437" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67069,7 +67072,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2438" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67095,7 +67098,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2439" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67121,7 +67124,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2440" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67147,7 +67150,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2441" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67173,7 +67176,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2442" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67199,7 +67202,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2443" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67225,7 +67228,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67251,7 +67254,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2445" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67277,7 +67280,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2446" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67303,7 +67306,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2447" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67329,7 +67332,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2448" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67355,7 +67358,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2449" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67381,7 +67384,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2450" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67407,7 +67410,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67433,7 +67436,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2452" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67459,7 +67462,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2453" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67485,7 +67488,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2454" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67511,7 +67514,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2455" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67537,7 +67540,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2456" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67563,7 +67566,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2457" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67589,7 +67592,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2458" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67615,7 +67618,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67641,7 +67644,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2460" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67667,7 +67670,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2461" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67693,7 +67696,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2462" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67719,7 +67722,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2463" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67745,7 +67748,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2464" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67771,7 +67774,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2465" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67797,7 +67800,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2466" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67823,7 +67826,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2467" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67849,7 +67852,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2468" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67875,7 +67878,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67901,7 +67904,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2470" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67927,7 +67930,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2471" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67953,7 +67956,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2472" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67979,7 +67982,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2473" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68005,7 +68008,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2474" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68031,7 +68034,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2475" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68057,7 +68060,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2476" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68083,7 +68086,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2477" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68109,7 +68112,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2478" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68135,7 +68138,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2479" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68161,7 +68164,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2480" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68187,7 +68190,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68213,7 +68216,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2482" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68239,7 +68242,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2483" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68265,7 +68268,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2484" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68291,7 +68294,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2485" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68317,7 +68320,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2486" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68343,7 +68346,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2487" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68369,7 +68372,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68395,7 +68398,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2489" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68421,7 +68424,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2490" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68447,7 +68450,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2491" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68473,7 +68476,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2492" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68499,7 +68502,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2493" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68525,7 +68528,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2494" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68551,7 +68554,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2495" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68577,7 +68580,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68603,7 +68606,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2497" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68629,7 +68632,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2498" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68655,7 +68658,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2499" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68681,7 +68684,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2500" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68707,7 +68710,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2501" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68733,7 +68736,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2502" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68759,7 +68762,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2503" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68785,7 +68788,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2504" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68811,7 +68814,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2505" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68837,7 +68840,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G2506" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68863,7 +68866,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2507" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68889,7 +68892,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2508" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68915,7 +68918,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2509" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68941,7 +68944,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2510" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68967,7 +68970,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2511" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68993,7 +68996,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G2512" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -69019,7 +69022,7 @@
         <v>0.157499998807907</v>
       </c>
       <c r="G2513" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -69045,7 +69048,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2514" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -69071,7 +69074,7 @@
         <v>0.156000003218651</v>
       </c>
       <c r="G2515" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -69097,7 +69100,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G2516" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -69123,7 +69126,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G2517" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -69149,7 +69152,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G2518" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -69175,7 +69178,7 @@
         <v>0.152500003576279</v>
       </c>
       <c r="G2519" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -69201,7 +69204,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G2520" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -69227,7 +69230,7 @@
         <v>0.150999993085861</v>
       </c>
       <c r="G2521" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -69253,7 +69256,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G2522" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -69279,7 +69282,7 @@
         <v>0.149499997496605</v>
       </c>
       <c r="G2523" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -69305,7 +69308,7 @@
         <v>0.150000005960464</v>
       </c>
       <c r="G2524" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -69331,7 +69334,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G2525" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -69357,7 +69360,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G2526" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -69383,7 +69386,7 @@
         <v>0.156000003218651</v>
       </c>
       <c r="G2527" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -69409,7 +69412,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G2528" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -69435,7 +69438,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2529" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -69461,7 +69464,7 @@
         <v>0.155000001192093</v>
       </c>
       <c r="G2530" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -69487,7 +69490,7 @@
         <v>0.156000003218651</v>
       </c>
       <c r="G2531" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -69513,7 +69516,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2532" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -69539,7 +69542,7 @@
         <v>0.157000005245209</v>
       </c>
       <c r="G2533" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -69565,7 +69568,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2534" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -69591,7 +69594,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2535" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -69617,7 +69620,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2536" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -69643,7 +69646,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2537" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -69669,7 +69672,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2538" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -69695,7 +69698,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2539" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -69721,7 +69724,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2540" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -69747,7 +69750,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2541" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -69773,7 +69776,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2542" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -69799,7 +69802,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2543" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -69825,7 +69828,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2544" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2544" t="s">
         <v>9</v>
@@ -69851,7 +69854,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2545" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2545" t="s">
         <v>9</v>
@@ -69877,7 +69880,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2546" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2546" t="s">
         <v>9</v>
@@ -69903,7 +69906,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2547" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2547" t="s">
         <v>9</v>
@@ -69929,7 +69932,7 @@
         <v>0.174999997019768</v>
       </c>
       <c r="G2548" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2548" t="s">
         <v>9</v>
@@ -69955,7 +69958,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2549" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2549" t="s">
         <v>9</v>
@@ -69981,7 +69984,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2550" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2550" t="s">
         <v>9</v>
@@ -70007,7 +70010,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2551" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H2551" t="s">
         <v>9</v>
@@ -70033,7 +70036,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2552" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2552" t="s">
         <v>9</v>
@@ -70059,7 +70062,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2553" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2553" t="s">
         <v>9</v>
@@ -70085,7 +70088,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2554" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2554" t="s">
         <v>9</v>
@@ -70093,7 +70096,7 @@
     </row>
     <row r="2555">
       <c r="A2555" s="1" t="n">
-        <v>46043.6911111111</v>
+        <v>46043.3333333333</v>
       </c>
       <c r="B2555" t="n">
         <v>253540</v>
@@ -70111,9 +70114,35 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2555" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2555" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2556">
+      <c r="A2556" s="1" t="n">
+        <v>46044.6911805556</v>
+      </c>
+      <c r="B2556" t="n">
+        <v>1772272</v>
+      </c>
+      <c r="C2556" t="n">
+        <v>0.185000002384186</v>
+      </c>
+      <c r="D2556" t="n">
+        <v>0.180999994277954</v>
+      </c>
+      <c r="E2556" t="n">
+        <v>0.181999996304512</v>
+      </c>
+      <c r="F2556" t="n">
+        <v>0.180999994277954</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H2556" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">0.158481389284134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155000314116478</t>
+    <t xml:space="preserve">0.155000299215317</t>
   </si>
   <si>
     <t xml:space="preserve">0.153229221701622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150542065501213</t>
+    <t xml:space="preserve">0.150542050600052</t>
   </si>
   <si>
     <t xml:space="preserve">0.148099169135094</t>
@@ -65,22 +65,22 @@
     <t xml:space="preserve">0.151580274105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14736633002758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358437180519</t>
+    <t xml:space="preserve">0.147366315126419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142358407378197</t>
   </si>
   <si>
     <t xml:space="preserve">0.132831215858459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134541258215904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125319391489029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131121203303337</t>
+    <t xml:space="preserve">0.134541243314743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12531940639019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131121218204498</t>
   </si>
   <si>
     <t xml:space="preserve">0.134358018636703</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">0.134419098496437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143335595726967</t>
+    <t xml:space="preserve">0.143335565924644</t>
   </si>
   <si>
     <t xml:space="preserve">0.13802233338356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137778043746948</t>
+    <t xml:space="preserve">0.137778058648109</t>
   </si>
   <si>
     <t xml:space="preserve">0.140465199947357</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">0.136190190911293</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131793007254601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129166901111603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12928906083107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967935442924</t>
+    <t xml:space="preserve">0.131793022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129166916012764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129289075732231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967920541763</t>
   </si>
   <si>
     <t xml:space="preserve">0.122754380106926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11615863442421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118479356169701</t>
+    <t xml:space="preserve">0.116158619523048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479363620281</t>
   </si>
   <si>
     <t xml:space="preserve">0.125807970762253</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">0.129960849881172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125014021992683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130999073386192</t>
+    <t xml:space="preserve">0.127029404044151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125014036893845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130999058485031</t>
   </si>
   <si>
     <t xml:space="preserve">0.129105851054192</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">0.128617271780968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130205124616623</t>
+    <t xml:space="preserve">0.130205139517784</t>
   </si>
   <si>
     <t xml:space="preserve">0.130510494112968</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133808359503746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138755202293396</t>
+    <t xml:space="preserve">0.133808374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138755187392235</t>
   </si>
   <si>
     <t xml:space="preserve">0.139671266078949</t>
@@ -179,37 +179,37 @@
     <t xml:space="preserve">0.140159845352173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14174772799015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147122025489807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14901527762413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146572381258011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14571738243103</t>
+    <t xml:space="preserve">0.141747713088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147122040390968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149015262722969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146572396159172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145717397332191</t>
   </si>
   <si>
     <t xml:space="preserve">0.1432134360075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144129544496536</t>
+    <t xml:space="preserve">0.144129499793053</t>
   </si>
   <si>
     <t xml:space="preserve">0.140892699360847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139793410897255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968727827072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068031191826</t>
+    <t xml:space="preserve">0.139793425798416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968742728233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068046092987</t>
   </si>
   <si>
     <t xml:space="preserve">0.13594588637352</t>
@@ -218,10 +218,10 @@
     <t xml:space="preserve">0.135823741555214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133136600255966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130693703889847</t>
+    <t xml:space="preserve">0.133136570453644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130693688988686</t>
   </si>
   <si>
     <t xml:space="preserve">0.12886156141758</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">0.133930519223213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137472689151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142480552196503</t>
+    <t xml:space="preserve">0.137472674250603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142480581998825</t>
   </si>
   <si>
     <t xml:space="preserve">0.142114147543907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141320213675499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14217521250248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138327687978745</t>
+    <t xml:space="preserve">0.14132022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142175227403641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138327673077583</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236292362213</t>
@@ -263,22 +263,22 @@
     <t xml:space="preserve">0.139899402856827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136135265231133</t>
+    <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
     <t xml:space="preserve">0.136637181043625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133876800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133814081549644</t>
+    <t xml:space="preserve">0.133876815438271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133814066648483</t>
   </si>
   <si>
     <t xml:space="preserve">0.132998526096344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129234418272972</t>
+    <t xml:space="preserve">0.129234433174133</t>
   </si>
   <si>
     <t xml:space="preserve">0.128732532262802</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.125156626105309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126662269234657</t>
+    <t xml:space="preserve">0.12666229903698</t>
   </si>
   <si>
     <t xml:space="preserve">0.126725018024445</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">0.127352356910706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127979710698128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126599550247192</t>
+    <t xml:space="preserve">0.127979725599289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126599535346031</t>
   </si>
   <si>
     <t xml:space="preserve">0.127916976809502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130489140748978</t>
+    <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
     <t xml:space="preserve">0.131743833422661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131116479635239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131555616855621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134065017104149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131179198622704</t>
+    <t xml:space="preserve">0.131116464734077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13155560195446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13406503200531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131179213523865</t>
   </si>
   <si>
     <t xml:space="preserve">0.133688613772392</t>
@@ -329,31 +329,31 @@
     <t xml:space="preserve">0.134880587458611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134190484881401</t>
+    <t xml:space="preserve">0.13419046998024</t>
   </si>
   <si>
     <t xml:space="preserve">0.130614593625069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132873073220253</t>
+    <t xml:space="preserve">0.132873058319092</t>
   </si>
   <si>
     <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121078841388226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12020055949688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831670403481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413864254951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233199179173</t>
+    <t xml:space="preserve">0.121078863739967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120200544595718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1218316629529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413886606693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233206629753</t>
   </si>
   <si>
     <t xml:space="preserve">0.114366181194782</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">0.111794047057629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114052511751652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395056307316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893192648888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041210591793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904478907585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354902386665</t>
+    <t xml:space="preserve">0.114052504301071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395063757896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893177747726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041225492954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904464006424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354887485504</t>
   </si>
   <si>
     <t xml:space="preserve">0.110727526247501</t>
@@ -386,61 +386,61 @@
     <t xml:space="preserve">0.107277117669582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102822914719582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501716136932</t>
+    <t xml:space="preserve">0.102822907269001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501708686352</t>
   </si>
   <si>
     <t xml:space="preserve">0.107716254889965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110790282487869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11292327195406</t>
+    <t xml:space="preserve">0.110790267586708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554390311241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923286855221</t>
   </si>
   <si>
     <t xml:space="preserve">0.114303454756737</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118632160127163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116561912000179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11637369543314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746363997459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432687103748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805333316326</t>
+    <t xml:space="preserve">0.118632167577744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116561897099018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116373710334301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746356546879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432672202587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805325865746</t>
   </si>
   <si>
     <t xml:space="preserve">0.116185508668423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118569441139698</t>
+    <t xml:space="preserve">0.118569448590279</t>
   </si>
   <si>
     <t xml:space="preserve">0.118820384144783</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115934580564499</t>
+    <t xml:space="preserve">0.115934558212757</t>
   </si>
   <si>
     <t xml:space="preserve">0.109159164130688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107088901102543</t>
+    <t xml:space="preserve">0.107088916003704</t>
   </si>
   <si>
     <t xml:space="preserve">0.10614787787199</t>
@@ -449,52 +449,52 @@
     <t xml:space="preserve">0.104140356183052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105646006762981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10746531188488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108531802892685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535589814186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10483043640852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092658221722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029924333096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849259257317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978484153748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11160584539175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11373882740736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864317536354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110288389027119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225662589073</t>
+    <t xml:space="preserve">0.10564599186182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107465304434299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108531810343266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590787112713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535582363605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1048304438591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092680573463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029931783676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10765352845192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849251806736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978491604328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111605823040009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113738834857941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864302635193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110288381576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225655138493</t>
   </si>
   <si>
     <t xml:space="preserve">0.108845494687557</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">0.109723784029484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107339859008789</t>
+    <t xml:space="preserve">0.107339844107628</t>
   </si>
   <si>
     <t xml:space="preserve">0.108406342566013</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">0.105018652975559</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10664975643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105834193527699</t>
+    <t xml:space="preserve">0.106649771332741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10583420842886</t>
   </si>
   <si>
     <t xml:space="preserve">0.106085143983364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109786510467529</t>
+    <t xml:space="preserve">0.10978651791811</t>
   </si>
   <si>
     <t xml:space="preserve">0.104391291737556</t>
@@ -533,91 +533,91 @@
     <t xml:space="preserve">0.107778996229172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107214391231537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11606003344059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114742577075958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11242138594389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425150513649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295925617218</t>
+    <t xml:space="preserve">0.107214368879795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060055792332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114742591977119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11242139339447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11342515796423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295918166637</t>
   </si>
   <si>
     <t xml:space="preserve">0.106022417545319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106712490320206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837965548038</t>
+    <t xml:space="preserve">0.106712505221367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
   </si>
   <si>
     <t xml:space="preserve">0.105520538985729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104265831410885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760180830956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101003594696522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104579508304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885670959949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889428079128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254552602768</t>
+    <t xml:space="preserve">0.104265823960304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760188281536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101003602147102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104579493403435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885663509369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889413177967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254537701607</t>
   </si>
   <si>
     <t xml:space="preserve">0.100564457476139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101066328585148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101630955934525</t>
+    <t xml:space="preserve">0.101066343486309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101630948483944</t>
   </si>
   <si>
     <t xml:space="preserve">0.106524296104908</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109911985695362</t>
+    <t xml:space="preserve">0.109911993145943</t>
   </si>
   <si>
     <t xml:space="preserve">0.110539346933365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110915757715702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657293021679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112609602510929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111292168498039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410114586353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108343623578548</t>
+    <t xml:space="preserve">0.110915750265121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657285571098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11260960996151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11129217594862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410107135773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108343616127968</t>
   </si>
   <si>
     <t xml:space="preserve">0.108280889689922</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">0.110351130366325</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128544330596924</t>
+    <t xml:space="preserve">0.128544315695763</t>
   </si>
   <si>
     <t xml:space="preserve">0.15370112657547</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">0.134692370891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135821610689163</t>
+    <t xml:space="preserve">0.135821625590324</t>
   </si>
   <si>
     <t xml:space="preserve">0.139836654067039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855454564095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143161624670029</t>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855484366417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143161609768867</t>
   </si>
   <si>
     <t xml:space="preserve">0.141781449317932</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">0.131681084632874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130112707614899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13074004650116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842964112759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097664237022</t>
+    <t xml:space="preserve">0.13011272251606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130740061402321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842941761017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097679138184</t>
   </si>
   <si>
     <t xml:space="preserve">0.126975953578949</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">0.127289637923241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127226904034615</t>
+    <t xml:space="preserve">0.127226889133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.126411348581314</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1254703104496</t>
+    <t xml:space="preserve">0.125470295548439</t>
   </si>
   <si>
     <t xml:space="preserve">0.126536816358566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215610325336</t>
+    <t xml:space="preserve">0.124215617775917</t>
   </si>
   <si>
     <t xml:space="preserve">0.12597219645977</t>
@@ -725,25 +725,25 @@
     <t xml:space="preserve">0.130551859736443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182970643044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171699285507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13224570453167</t>
+    <t xml:space="preserve">0.130677312612534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182985544205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171684384346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132245719432831</t>
   </si>
   <si>
     <t xml:space="preserve">0.135006040334702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133939549326897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127765893936</t>
+    <t xml:space="preserve">0.133939564228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127750992775</t>
   </si>
   <si>
     <t xml:space="preserve">0.136260762810707</t>
@@ -752,64 +752,64 @@
     <t xml:space="preserve">0.134943321347237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137766405940056</t>
+    <t xml:space="preserve">0.137766391038895</t>
   </si>
   <si>
     <t xml:space="preserve">0.13801734149456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140777707099915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145733758807182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14416541159153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143977180123329</t>
+    <t xml:space="preserve">0.140777692198753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145733743906021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165396690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977165222168</t>
   </si>
   <si>
     <t xml:space="preserve">0.14115409553051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137640908360481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136762648820877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629651904106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134002283215523</t>
+    <t xml:space="preserve">0.137640938162804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136762633919716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629637002945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134002313017845</t>
   </si>
   <si>
     <t xml:space="preserve">0.133437663316727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129673555493355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128356158733368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496654987335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135633409023285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137891873717308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13770367205143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433921098709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13205748796463</t>
+    <t xml:space="preserve">0.129673570394516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128356128931046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496640086174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135633394122124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137891843914986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137703657150269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433906197548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132057502865791</t>
   </si>
   <si>
     <t xml:space="preserve">0.134504169225693</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">0.131729170680046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130720719695091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13317883014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565442800522</t>
+    <t xml:space="preserve">0.130720734596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133178815245628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565457701683</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943619370461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792187690735</t>
+    <t xml:space="preserve">0.131792202591896</t>
   </si>
   <si>
     <t xml:space="preserve">0.131477057933807</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129964366555214</t>
+    <t xml:space="preserve">0.130468592047691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129964381456375</t>
   </si>
   <si>
     <t xml:space="preserve">0.127506271004677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129586189985275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127002045512199</t>
+    <t xml:space="preserve">0.129586219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127002060413361</t>
   </si>
   <si>
     <t xml:space="preserve">0.127947464585304</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">0.12870380282402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126371756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125930547714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127128124237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056626439095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479605525732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12466999143362</t>
+    <t xml:space="preserve">0.126371771097183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125930577516556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127128109335899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056611537933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124796062707901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12466998398304</t>
   </si>
   <si>
     <t xml:space="preserve">0.124165765941143</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">0.125174224376678</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125237256288528</t>
+    <t xml:space="preserve">0.12523727118969</t>
   </si>
   <si>
     <t xml:space="preserve">0.129018947482109</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">0.127380207180977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128451690077782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136545419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884462475777</t>
+    <t xml:space="preserve">0.128451704978943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136560320854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884447574615</t>
   </si>
   <si>
     <t xml:space="preserve">0.127443253993988</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">0.128262609243393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126875981688499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126497820019722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126308709383011</t>
+    <t xml:space="preserve">0.126875996589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126497805118561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126308739185333</t>
   </si>
   <si>
     <t xml:space="preserve">0.133430942893028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135573908686638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135762989521027</t>
+    <t xml:space="preserve">0.135573893785477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135762974619865</t>
   </si>
   <si>
     <t xml:space="preserve">0.136456295847893</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">0.134061202406883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132485508918762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133556976914406</t>
+    <t xml:space="preserve">0.132485523819923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133556991815567</t>
   </si>
   <si>
     <t xml:space="preserve">0.135195717215538</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">0.136141166090965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134439393877983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137464746832848</t>
+    <t xml:space="preserve">0.134439378976822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137464731931686</t>
   </si>
   <si>
     <t xml:space="preserve">0.137716859579086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138221070170403</t>
+    <t xml:space="preserve">0.138221085071564</t>
   </si>
   <si>
     <t xml:space="preserve">0.137842923402786</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">0.136330232024193</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137086570262909</t>
+    <t xml:space="preserve">0.13708658516407</t>
   </si>
   <si>
     <t xml:space="preserve">0.13677142560482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136204183101654</t>
+    <t xml:space="preserve">0.136204168200493</t>
   </si>
   <si>
     <t xml:space="preserve">0.13500665128231</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151141911745071</t>
+    <t xml:space="preserve">0.15114189684391</t>
   </si>
   <si>
     <t xml:space="preserve">0.153789088129997</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">0.151267945766449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145280256867409</t>
+    <t xml:space="preserve">0.145280241966248</t>
   </si>
   <si>
     <t xml:space="preserve">0.14704504609108</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">0.157444730401039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159398600459099</t>
+    <t xml:space="preserve">0.159398585557938</t>
   </si>
   <si>
     <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570779323578</t>
+    <t xml:space="preserve">0.157570749521255</t>
   </si>
   <si>
     <t xml:space="preserve">0.15284363925457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152654558420181</t>
+    <t xml:space="preserve">0.152654573321342</t>
   </si>
   <si>
     <t xml:space="preserve">0.151898220181465</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">0.153095781803131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150259494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148746818304062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153347879648209</t>
+    <t xml:space="preserve">0.150259479880333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746803402901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15334789454937</t>
   </si>
   <si>
     <t xml:space="preserve">0.155805975198746</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154419362545013</t>
+    <t xml:space="preserve">0.154419347643852</t>
   </si>
   <si>
     <t xml:space="preserve">0.156940504908562</t>
@@ -1064,37 +1064,37 @@
     <t xml:space="preserve">0.15914648771286</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167655318975449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050382614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167214125394821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172067314386368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945811629295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.178811341524124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17521870136261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336314201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176431536674</t>
+    <t xml:space="preserve">0.167655304074287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050397515297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167214140295982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172067284584045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945826530457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.178811326622963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175218716263771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336299300194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176446437836</t>
   </si>
   <si>
     <t xml:space="preserve">0.176479279994965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173643007874489</t>
+    <t xml:space="preserve">0.173642978072166</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365527272224</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">0.168222546577454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168600738048553</t>
+    <t xml:space="preserve">0.168600752949715</t>
   </si>
   <si>
     <t xml:space="preserve">0.166520804166794</t>
@@ -1115,37 +1115,37 @@
     <t xml:space="preserve">0.166394740343094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161730632185936</t>
+    <t xml:space="preserve">0.161730647087097</t>
   </si>
   <si>
     <t xml:space="preserve">0.160091906785965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156688377261162</t>
+    <t xml:space="preserve">0.156688362360001</t>
   </si>
   <si>
     <t xml:space="preserve">0.16122642159462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162487000226974</t>
+    <t xml:space="preserve">0.162487015128136</t>
   </si>
   <si>
     <t xml:space="preserve">0.163747534155846</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163873597979546</t>
+    <t xml:space="preserve">0.163873612880707</t>
   </si>
   <si>
     <t xml:space="preserve">0.16103732585907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158011972904205</t>
+    <t xml:space="preserve">0.158011958003044</t>
   </si>
   <si>
     <t xml:space="preserve">0.157759860157967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167970433831215</t>
+    <t xml:space="preserve">0.167970448732376</t>
   </si>
   <si>
     <t xml:space="preserve">0.167718321084976</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">0.163810595870018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159461602568626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147675335407257</t>
+    <t xml:space="preserve">0.159461617469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147675350308418</t>
   </si>
   <si>
     <t xml:space="preserve">0.147486254572868</t>
@@ -1172,28 +1172,28 @@
     <t xml:space="preserve">0.150007382035255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150448590517044</t>
+    <t xml:space="preserve">0.150448575615883</t>
   </si>
   <si>
     <t xml:space="preserve">0.150511607527733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151078850030899</t>
+    <t xml:space="preserve">0.151078879833221</t>
   </si>
   <si>
     <t xml:space="preserve">0.151646122336388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150322541594505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494720458984</t>
+    <t xml:space="preserve">0.150322511792183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494690656662</t>
   </si>
   <si>
     <t xml:space="preserve">0.150826752185822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151772186160088</t>
+    <t xml:space="preserve">0.151772171258926</t>
   </si>
   <si>
     <t xml:space="preserve">0.149881318211555</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">0.151583090424538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149629205465317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709124445915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151015818119049</t>
+    <t xml:space="preserve">0.149629190564156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709154248238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15101583302021</t>
   </si>
   <si>
     <t xml:space="preserve">0.148935899138451</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763735175133</t>
+    <t xml:space="preserve">0.15076370537281</t>
   </si>
   <si>
     <t xml:space="preserve">0.150637671351433</t>
@@ -1226,16 +1226,16 @@
     <t xml:space="preserve">0.151204913854599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149944350123405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213379740715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528524398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377092719078</t>
+    <t xml:space="preserve">0.149944365024567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213394641876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528509497643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149377107620239</t>
   </si>
   <si>
     <t xml:space="preserve">0.157255634665489</t>
@@ -1244,28 +1244,28 @@
     <t xml:space="preserve">0.156310215592384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164503887295723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163243323564529</t>
+    <t xml:space="preserve">0.164503902196884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163243308663368</t>
   </si>
   <si>
     <t xml:space="preserve">0.162613034248352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161982774734497</t>
+    <t xml:space="preserve">0.161982759833336</t>
   </si>
   <si>
     <t xml:space="preserve">0.163558468222618</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165764451026917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165449321269989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079595685005</t>
+    <t xml:space="preserve">0.165764465928078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16544933617115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079625487328</t>
   </si>
   <si>
     <t xml:space="preserve">0.160722196102142</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">0.162297889590263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149061948060989</t>
+    <t xml:space="preserve">0.149061962962151</t>
   </si>
   <si>
     <t xml:space="preserve">0.14717110991478</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146540820598602</t>
+    <t xml:space="preserve">0.146540835499763</t>
   </si>
   <si>
     <t xml:space="preserve">0.146225690841675</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">0.140237987041473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139607712626457</t>
+    <t xml:space="preserve">0.139607682824135</t>
   </si>
   <si>
     <t xml:space="preserve">0.138031989336014</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">0.135826006531715</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138347148895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498550772667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813695430756</t>
+    <t xml:space="preserve">0.138347133994102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498580574989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813710331917</t>
   </si>
   <si>
     <t xml:space="preserve">0.140553146600723</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">0.141183406114578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138662278652191</t>
+    <t xml:space="preserve">0.138662293553352</t>
   </si>
   <si>
     <t xml:space="preserve">0.135510876774788</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">0.134880572557449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134250298142433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935168385506</t>
+    <t xml:space="preserve">0.134250313043594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935153484344</t>
   </si>
   <si>
     <t xml:space="preserve">0.132674589753151</t>
@@ -1343,40 +1343,43 @@
     <t xml:space="preserve">0.14307427406311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144965097308159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143389403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
+    <t xml:space="preserve">0.144965127110481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389418721199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443969845772</t>
   </si>
   <si>
     <t xml:space="preserve">0.146575853228569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147864416241646</t>
+    <t xml:space="preserve">0.147864401340485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
     <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14560940861702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455082058907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142710104584694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141421541571617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13916651904583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
+    <t xml:space="preserve">0.145609393715858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455096960068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142710089683533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141421511769295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139166504144669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777245163918</t>
   </si>
   <si>
     <t xml:space="preserve">0.139488652348518</t>
@@ -1385,28 +1388,28 @@
     <t xml:space="preserve">0.135622903704643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133690029382706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13272362947464</t>
+    <t xml:space="preserve">0.133690059185028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132723599672318</t>
   </si>
   <si>
     <t xml:space="preserve">0.13207933306694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129824295639992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125765278935432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12499213963747</t>
+    <t xml:space="preserve">0.129824310541153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125765293836594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12499213218689</t>
   </si>
   <si>
     <t xml:space="preserve">0.126796156167984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129180043935776</t>
+    <t xml:space="preserve">0.129180014133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.133367910981178</t>
@@ -1427,31 +1430,28 @@
     <t xml:space="preserve">0.128600150346756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468592047691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127440437674522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127955868840218</t>
+    <t xml:space="preserve">0.127440452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127955853939056</t>
   </si>
   <si>
     <t xml:space="preserve">0.127827018499374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12602299451828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12434783577919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703561723232</t>
+    <t xml:space="preserve">0.126023009419441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124347850680351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703576624393</t>
   </si>
   <si>
     <t xml:space="preserve">0.127311587333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127569288015366</t>
+    <t xml:space="preserve">0.127569302916527</t>
   </si>
   <si>
     <t xml:space="preserve">0.126667305827141</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">0.129502177238464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130146443843842</t>
+    <t xml:space="preserve">0.130146458745003</t>
   </si>
   <si>
     <t xml:space="preserve">0.134012192487717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134656488895416</t>
+    <t xml:space="preserve">0.134656473994255</t>
   </si>
   <si>
     <t xml:space="preserve">0.138522237539291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138200059533119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300770401955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130790740251541</t>
+    <t xml:space="preserve">0.13820007443428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300785303116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13079072535038</t>
   </si>
   <si>
     <t xml:space="preserve">0.128084734082222</t>
@@ -1499,118 +1499,118 @@
     <t xml:space="preserve">0.125249862670898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122157253324986</t>
+    <t xml:space="preserve">0.122157275676727</t>
   </si>
   <si>
     <t xml:space="preserve">0.123317003250122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125507593154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128213599324226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126151874661446</t>
+    <t xml:space="preserve">0.125507563352585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128213584423065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126151859760284</t>
   </si>
   <si>
     <t xml:space="preserve">0.127182707190514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125636428594589</t>
+    <t xml:space="preserve">0.12563644349575</t>
   </si>
   <si>
     <t xml:space="preserve">0.120482116937637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.122286133468151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122414998710155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.117260664701462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113266065716743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113394930958748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848644912243</t>
+    <t xml:space="preserve">0.122286111116409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122414976358414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.117260687053204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113266073167324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113394923508167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848637461662</t>
   </si>
   <si>
     <t xml:space="preserve">0.11210636049509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114425793290138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683508872986</t>
+    <t xml:space="preserve">0.11442581564188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683516323566</t>
   </si>
   <si>
     <t xml:space="preserve">0.112235210835934</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110817797482014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108240619301796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106565468013287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921179056168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101926580071449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105019174516201</t>
+    <t xml:space="preserve">0.110817790031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108240611851215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106565475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921171605587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10192659497261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10501915961504</t>
   </si>
   <si>
     <t xml:space="preserve">0.103086300194263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104374885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104117162525654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105663470923901</t>
+    <t xml:space="preserve">0.104374878108501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104117155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105663478374481</t>
   </si>
   <si>
     <t xml:space="preserve">0.107982903718948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108627192676067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108111768960953</t>
+    <t xml:space="preserve">0.108627185225487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108111754059792</t>
   </si>
   <si>
     <t xml:space="preserve">0.11146205663681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11275065690279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756050467491</t>
+    <t xml:space="preserve">0.112750642001629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756043016911</t>
   </si>
   <si>
     <t xml:space="preserve">0.110173493623734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109529197216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106952026486397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153425872326</t>
+    <t xml:space="preserve">0.109529189765453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106952033936977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153448224068</t>
   </si>
   <si>
     <t xml:space="preserve">0.10398830473423</t>
@@ -1619,67 +1619,67 @@
     <t xml:space="preserve">0.102699734270573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105276882648468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111204355955124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115585513412952</t>
+    <t xml:space="preserve">0.105276875197887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111204363405704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115585505962372</t>
   </si>
   <si>
     <t xml:space="preserve">0.115843236446381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115327805280685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113008365035057</t>
+    <t xml:space="preserve">0.115327812731266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113008379936218</t>
   </si>
   <si>
     <t xml:space="preserve">0.10940033942461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110431201756001</t>
+    <t xml:space="preserve">0.110431186854839</t>
   </si>
   <si>
     <t xml:space="preserve">0.107854045927525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103730589151382</t>
+    <t xml:space="preserve">0.103730604052544</t>
   </si>
   <si>
     <t xml:space="preserve">0.106307752430439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103859439492226</t>
+    <t xml:space="preserve">0.103859454393387</t>
   </si>
   <si>
     <t xml:space="preserve">0.114554658532143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109142616391182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013773500919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884908258915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271481633186</t>
+    <t xml:space="preserve">0.109142623841763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013758599758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884900808334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271489083767</t>
   </si>
   <si>
     <t xml:space="preserve">0.10733862221241</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102442011237144</t>
+    <t xml:space="preserve">0.102441996335983</t>
   </si>
   <si>
     <t xml:space="preserve">0.101411141455173</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102055445313454</t>
+    <t xml:space="preserve">0.102055452764034</t>
   </si>
   <si>
     <t xml:space="preserve">0.10025142878294</t>
@@ -1697,28 +1697,28 @@
     <t xml:space="preserve">0.100766852498055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105148024857044</t>
+    <t xml:space="preserve">0.105148032307625</t>
   </si>
   <si>
     <t xml:space="preserve">0.109915770590305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11107549071312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112621776759624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302351415157</t>
+    <t xml:space="preserve">0.1110754981637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112621784210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302358865738</t>
   </si>
   <si>
     <t xml:space="preserve">0.110688917338848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104761444032192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534598231316</t>
+    <t xml:space="preserve">0.104761466383934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534605681896</t>
   </si>
   <si>
     <t xml:space="preserve">0.107467480003834</t>
@@ -1727,52 +1727,52 @@
     <t xml:space="preserve">0.108498349785805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107080906629562</t>
+    <t xml:space="preserve">0.107080899178982</t>
   </si>
   <si>
     <t xml:space="preserve">0.104503743350506</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105792313814163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436610221863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105341322720051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596322894096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562767505646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207041561604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11018505692482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857134521008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111168846487999</t>
+    <t xml:space="preserve">0.105792321264744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436617672443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105341330170631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596330344677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562752604485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207049012184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185049474239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857141971588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11116885393858</t>
   </si>
   <si>
     <t xml:space="preserve">0.110513016581535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107889540493488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106905736029148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10592195391655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103954367339611</t>
+    <t xml:space="preserve">0.107889533042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106905743479729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10592196136713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103954374790192</t>
   </si>
   <si>
     <t xml:space="preserve">0.104282289743423</t>
@@ -1784,40 +1784,40 @@
     <t xml:space="preserve">0.108217477798462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105266086757183</t>
+    <t xml:space="preserve">0.105266094207764</t>
   </si>
   <si>
     <t xml:space="preserve">0.10493815690279</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102970562875271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103626422584057</t>
+    <t xml:space="preserve">0.102970577776432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103626430034637</t>
   </si>
   <si>
     <t xml:space="preserve">0.103298485279083</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101658836007118</t>
+    <t xml:space="preserve">0.101658843457699</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347109138966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330906152725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0970677956938744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0977236554026604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957255482674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951002016663551</t>
+    <t xml:space="preserve">0.101330898702145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0970677882432938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0977236703038216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.097395732998848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951002091169357</t>
   </si>
   <si>
     <t xml:space="preserve">0.098051592707634</t>
@@ -1826,49 +1826,49 @@
     <t xml:space="preserve">0.0964119359850883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0987074449658394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0993633195757866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100019179284573</t>
+    <t xml:space="preserve">0.09870745241642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0993633046746254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100019186735153</t>
   </si>
   <si>
     <t xml:space="preserve">0.101002968847752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100675046443939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102642633020878</t>
+    <t xml:space="preserve">0.100675038993359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102642640471458</t>
   </si>
   <si>
     <t xml:space="preserve">0.0983795300126076</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0996912494301796</t>
+    <t xml:space="preserve">0.099691241979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.099035382270813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104610234498978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107561618089676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108873344957829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545407652855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10920125991106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107233673334122</t>
+    <t xml:space="preserve">0.104610227048397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107561610639095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108873330056667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545400202274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109201274812222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107233680784702</t>
   </si>
   <si>
     <t xml:space="preserve">0.106249891221523</t>
@@ -1877,22 +1877,22 @@
     <t xml:space="preserve">0.11215265840292</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114448174834251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111824713647366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808525562286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113136447966099</t>
+    <t xml:space="preserve">0.114448182284832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111824721097946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808533012867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11313646286726</t>
   </si>
   <si>
     <t xml:space="preserve">0.112480580806732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111496791243553</t>
+    <t xml:space="preserve">0.111496806144714</t>
   </si>
   <si>
     <t xml:space="preserve">0.130516842007637</t>
@@ -1907,16 +1907,16 @@
     <t xml:space="preserve">0.141010642051697</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160686567425728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17380379140377</t>
+    <t xml:space="preserve">0.160686552524567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173803806304932</t>
   </si>
   <si>
     <t xml:space="preserve">0.167245179414749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155439645051956</t>
+    <t xml:space="preserve">0.155439630150795</t>
   </si>
   <si>
     <t xml:space="preserve">0.150848597288132</t>
@@ -1925,22 +1925,22 @@
     <t xml:space="preserve">0.154127925634384</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157407224178314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156751379370689</t>
+    <t xml:space="preserve">0.157407239079475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156751364469528</t>
   </si>
   <si>
     <t xml:space="preserve">0.15281617641449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148881003260612</t>
+    <t xml:space="preserve">0.148881018161774</t>
   </si>
   <si>
     <t xml:space="preserve">0.145601689815521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146257564425468</t>
+    <t xml:space="preserve">0.146257549524307</t>
   </si>
   <si>
     <t xml:space="preserve">0.146913424134254</t>
@@ -1955,40 +1955,40 @@
     <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147569268941879</t>
+    <t xml:space="preserve">0.14756928384304</t>
   </si>
   <si>
     <t xml:space="preserve">0.148225158452988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162654146552086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161342412233353</t>
+    <t xml:space="preserve">0.162654131650925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161342427134514</t>
   </si>
   <si>
     <t xml:space="preserve">0.141666516661644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139043062925339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1351078748703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133140280842781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137731328606606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154783770442009</t>
+    <t xml:space="preserve">0.139043048024178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135107859969139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133140295743942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137731313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15478378534317</t>
   </si>
   <si>
     <t xml:space="preserve">0.156095519661903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153472051024437</t>
+    <t xml:space="preserve">0.153472036123276</t>
   </si>
   <si>
     <t xml:space="preserve">0.131828561425209</t>
@@ -2000,58 +2000,58 @@
     <t xml:space="preserve">0.13707546889782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12559786438942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126581653952599</t>
+    <t xml:space="preserve">0.125597849488258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12658166885376</t>
   </si>
   <si>
     <t xml:space="preserve">0.123958185315132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118711292743683</t>
+    <t xml:space="preserve">0.118711270391941</t>
   </si>
   <si>
     <t xml:space="preserve">0.110840916633606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0967398509383202</t>
+    <t xml:space="preserve">0.0967398658394814</t>
   </si>
   <si>
     <t xml:space="preserve">0.082638792693615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.087885707616806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.08722984790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.088541567325592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0911650285124779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0918208807706833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0928046777844429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0944443494081497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0960840135812759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0931326150894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0957560762763023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0937884896993637</t>
+    <t xml:space="preserve">0.0878857150673866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0872298404574394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0885415822267532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0911650210618973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0918208882212639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0928046703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0944443270564079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0960839986801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0931326225399971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0957560613751411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0937884822487831</t>
   </si>
   <si>
     <t xml:space="preserve">0.0965431034564972</t>
@@ -2069,49 +2069,49 @@
     <t xml:space="preserve">0.0924767479300499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0940508171916008</t>
+    <t xml:space="preserve">0.0940508246421814</t>
   </si>
   <si>
     <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0941819921135902</t>
+    <t xml:space="preserve">0.0941819995641708</t>
   </si>
   <si>
     <t xml:space="preserve">0.0949690341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0954937189817429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483476400375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740641355515</t>
+    <t xml:space="preserve">0.0954937264323235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483550906181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740633904934</t>
   </si>
   <si>
     <t xml:space="preserve">0.0968054458498955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0966742783784866</t>
+    <t xml:space="preserve">0.0966742858290672</t>
   </si>
   <si>
     <t xml:space="preserve">0.110709749162197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0979860052466393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.099166564643383</t>
+    <t xml:space="preserve">0.0979859977960587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0991665571928024</t>
   </si>
   <si>
     <t xml:space="preserve">0.0936573073267937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0948378518223763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084766745567</t>
+    <t xml:space="preserve">0.0948378667235374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084781646729</t>
   </si>
   <si>
     <t xml:space="preserve">0.102183535695076</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">0.0999536067247391</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103232905268669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104806967079639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14035476744175</t>
+    <t xml:space="preserve">0.10323292016983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104806981980801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140354782342911</t>
   </si>
   <si>
     <t xml:space="preserve">0.125925779342651</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">0.13838717341423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142322361469269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137403413653374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135435819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136419609189034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134452000260353</t>
+    <t xml:space="preserve">0.14232237637043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137403398752213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135435804724693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136419594287872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134452015161514</t>
   </si>
   <si>
     <t xml:space="preserve">0.134124085307121</t>
@@ -2156,73 +2156,73 @@
     <t xml:space="preserve">0.131041511893272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127893358469009</t>
+    <t xml:space="preserve">0.127893373370171</t>
   </si>
   <si>
     <t xml:space="preserve">0.134779945015907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131172686815262</t>
+    <t xml:space="preserve">0.131172701716423</t>
   </si>
   <si>
     <t xml:space="preserve">0.130779176950455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130123317241669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129336282610893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130385667085648</t>
+    <t xml:space="preserve">0.130123302340508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129336267709732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130385652184486</t>
   </si>
   <si>
     <t xml:space="preserve">0.131500631570816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130910336971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133468210697174</t>
+    <t xml:space="preserve">0.130910351872444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133468225598335</t>
   </si>
   <si>
     <t xml:space="preserve">0.129992142319679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975178718567</t>
+    <t xml:space="preserve">0.126975163817406</t>
   </si>
   <si>
     <t xml:space="preserve">0.127631038427353</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128549233078957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133796155452728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132156491279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130648016929626</t>
+    <t xml:space="preserve">0.128549218177795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133796140551567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132156506180763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130648002028465</t>
   </si>
   <si>
     <t xml:space="preserve">0.129205092787743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129598617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140026852488518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129729777574539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12986096739769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130254492163658</t>
+    <t xml:space="preserve">0.129598647356033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140026837587357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129729807376862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129860982298851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130254477262497</t>
   </si>
   <si>
     <t xml:space="preserve">0.129073917865753</t>
@@ -2231,55 +2231,55 @@
     <t xml:space="preserve">0.125138744711876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12461406737566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143634110689163</t>
+    <t xml:space="preserve">0.124614059925079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143634080886841</t>
   </si>
   <si>
     <t xml:space="preserve">0.143962040543556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370992779732</t>
+    <t xml:space="preserve">0.139370977878571</t>
   </si>
   <si>
     <t xml:space="preserve">0.136091649532318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138059258460999</t>
+    <t xml:space="preserve">0.13805927336216</t>
   </si>
   <si>
     <t xml:space="preserve">0.136747524142265</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140682712197304</t>
+    <t xml:space="preserve">0.140682727098465</t>
   </si>
   <si>
     <t xml:space="preserve">0.144945830106735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142650291323662</t>
+    <t xml:space="preserve">0.142650306224823</t>
   </si>
   <si>
     <t xml:space="preserve">0.141994446516037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144289955496788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153799995779991</t>
+    <t xml:space="preserve">0.144289970397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15379998087883</t>
   </si>
   <si>
     <t xml:space="preserve">0.152488261461258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157079294323921</t>
+    <t xml:space="preserve">0.157079309225082</t>
   </si>
   <si>
     <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153144136071205</t>
+    <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
     <t xml:space="preserve">0.155111715197563</t>
@@ -2291,7 +2291,7 @@
     <t xml:space="preserve">0.160358622670174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159702748060226</t>
+    <t xml:space="preserve">0.159702762961388</t>
   </si>
   <si>
     <t xml:space="preserve">0.162982076406479</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">0.166917249560356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163310006260872</t>
+    <t xml:space="preserve">0.163310021162033</t>
   </si>
   <si>
     <t xml:space="preserve">0.162326216697693</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">0.15904688835144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159374818205833</t>
+    <t xml:space="preserve">0.159374833106995</t>
   </si>
   <si>
     <t xml:space="preserve">0.158718973398209</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">0.163571193814278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162509024143219</t>
+    <t xml:space="preserve">0.162863090634346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16250903904438</t>
   </si>
   <si>
     <t xml:space="preserve">0.161092847585678</t>
@@ -2345,40 +2345,40 @@
     <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157198294997215</t>
+    <t xml:space="preserve">0.157198280096054</t>
   </si>
   <si>
     <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162154987454414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158968523144722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160384729504585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159322574734688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15755233168602</t>
+    <t xml:space="preserve">0.162154972553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158968552947044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160384744405746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159322589635849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157552316784859</t>
   </si>
   <si>
     <t xml:space="preserve">0.161800935864449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15507398545742</t>
+    <t xml:space="preserve">0.155073970556259</t>
   </si>
   <si>
     <t xml:space="preserve">0.153303727507591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15578205883503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151533469557762</t>
+    <t xml:space="preserve">0.155782073736191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151533484458923</t>
   </si>
   <si>
     <t xml:space="preserve">0.15259562432766</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">0.156490176916122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153657779097557</t>
+    <t xml:space="preserve">0.153657793998718</t>
   </si>
   <si>
     <t xml:space="preserve">0.154011815786362</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">0.156136140227318</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152241572737694</t>
+    <t xml:space="preserve">0.152241587638855</t>
   </si>
   <si>
     <t xml:space="preserve">0.154365882277489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151887521147728</t>
+    <t xml:space="preserve">0.151887536048889</t>
   </si>
   <si>
     <t xml:space="preserve">0.151179432868958</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">0.15011727809906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150825396180153</t>
+    <t xml:space="preserve">0.150825381278992</t>
   </si>
   <si>
     <t xml:space="preserve">0.149763226509094</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">0.150471329689026</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149055123329163</t>
+    <t xml:space="preserve">0.149055138230324</t>
   </si>
   <si>
     <t xml:space="preserve">0.146222725510597</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147284895181656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142682209610939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143390327692032</t>
+    <t xml:space="preserve">0.147284880280495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142682239413261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143390312790871</t>
   </si>
   <si>
     <t xml:space="preserve">0.145514622330666</t>
@@ -2450,13 +2450,13 @@
     <t xml:space="preserve">0.148347035050392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149409160017967</t>
+    <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
     <t xml:space="preserve">0.152949675917625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145160555839539</t>
+    <t xml:space="preserve">0.1451605707407</t>
   </si>
   <si>
     <t xml:space="preserve">0.147638916969299</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">0.146576792001724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144452482461929</t>
+    <t xml:space="preserve">0.144452467560768</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">0.144806534051895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144098430871964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145868673920631</t>
+    <t xml:space="preserve">0.144098415970802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14586865901947</t>
   </si>
   <si>
     <t xml:space="preserve">0.147992983460426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16569547355175</t>
+    <t xml:space="preserve">0.165695488452911</t>
   </si>
   <si>
     <t xml:space="preserve">0.168527901172638</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16746574640274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16498738527298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163217127323151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164358526468277</t>
+    <t xml:space="preserve">0.167465731501579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164987370371819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163217142224312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164358511567116</t>
   </si>
   <si>
     <t xml:space="preserve">0.162075757980347</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167021751403809</t>
+    <t xml:space="preserve">0.167021736502647</t>
   </si>
   <si>
     <t xml:space="preserve">0.161695286631584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161314845085144</t>
+    <t xml:space="preserve">0.161314830183983</t>
   </si>
   <si>
     <t xml:space="preserve">0.159793004393578</t>
@@ -2531,13 +2531,13 @@
     <t xml:space="preserve">0.16055391728878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158271163702011</t>
+    <t xml:space="preserve">0.158271178603172</t>
   </si>
   <si>
     <t xml:space="preserve">0.160934388637543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162836685776711</t>
+    <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">0.159412547945976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160173445940018</t>
+    <t xml:space="preserve">0.160173460841179</t>
   </si>
   <si>
     <t xml:space="preserve">0.165880352258682</t>
@@ -2564,34 +2564,34 @@
     <t xml:space="preserve">0.170445874333382</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169684946537018</t>
+    <t xml:space="preserve">0.169684961438179</t>
   </si>
   <si>
     <t xml:space="preserve">0.170826330780983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171967715024948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170065402984619</t>
+    <t xml:space="preserve">0.171967700123787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17006541788578</t>
   </si>
   <si>
     <t xml:space="preserve">0.157129779458046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15789070725441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153705641627312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144270271062851</t>
+    <t xml:space="preserve">0.157890692353249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153705656528473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14427025616169</t>
   </si>
   <si>
     <t xml:space="preserve">0.147770464420319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155227467417717</t>
+    <t xml:space="preserve">0.155227482318878</t>
   </si>
   <si>
     <t xml:space="preserve">0.155988410115242</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">0.157510235905647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164738968014717</t>
+    <t xml:space="preserve">0.164738982915878</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">0.166641250252724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16816309094429</t>
+    <t xml:space="preserve">0.168163105845451</t>
   </si>
   <si>
     <t xml:space="preserve">0.167402192950249</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">0.173869997262955</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174277201294899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173462823033333</t>
+    <t xml:space="preserve">0.174277186393738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173462808132172</t>
   </si>
   <si>
     <t xml:space="preserve">0.171426862478256</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">0.167354971170425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165319010615349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166540592908859</t>
+    <t xml:space="preserve">0.16531902551651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16654060781002</t>
   </si>
   <si>
     <t xml:space="preserve">0.166947782039642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167762160301208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168576538562775</t>
+    <t xml:space="preserve">0.167762145400047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168576523661613</t>
   </si>
   <si>
     <t xml:space="preserve">0.169390916824341</t>
@@ -2669,19 +2669,19 @@
     <t xml:space="preserve">0.16287587583065</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15196318924427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155709341168404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157175213098526</t>
+    <t xml:space="preserve">0.151963204145432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155709356069565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157175227999687</t>
   </si>
   <si>
     <t xml:space="preserve">0.15636083483696</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157338097691536</t>
+    <t xml:space="preserve">0.157338112592697</t>
   </si>
   <si>
     <t xml:space="preserve">0.155546456575394</t>
@@ -2699,10 +2699,10 @@
     <t xml:space="preserve">0.152614697813988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163690254092216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162387236952782</t>
+    <t xml:space="preserve">0.163690268993378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162387251853943</t>
   </si>
   <si>
     <t xml:space="preserve">0.158478230237961</t>
@@ -2717,22 +2717,22 @@
     <t xml:space="preserve">0.161247119307518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161735728383064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161572873592377</t>
+    <t xml:space="preserve">0.161735743284225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161572888493538</t>
   </si>
   <si>
     <t xml:space="preserve">0.157500967383385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160269856452942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159129723906517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160595625638962</t>
+    <t xml:space="preserve">0.160269871354103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159129738807678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160595610737801</t>
   </si>
   <si>
     <t xml:space="preserve">0.159781232476234</t>
@@ -2750,16 +2750,16 @@
     <t xml:space="preserve">0.161410003900528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159944102168083</t>
+    <t xml:space="preserve">0.159944117069244</t>
   </si>
   <si>
     <t xml:space="preserve">0.154732078313828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966839313507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15652371942997</t>
+    <t xml:space="preserve">0.158966854214668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156523734331131</t>
   </si>
   <si>
     <t xml:space="preserve">0.155220702290535</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">0.156197965145111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156035080552101</t>
+    <t xml:space="preserve">0.156035095453262</t>
   </si>
   <si>
     <t xml:space="preserve">0.157663851976395</t>
@@ -2783,22 +2783,22 @@
     <t xml:space="preserve">0.157826736569405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158152461051941</t>
+    <t xml:space="preserve">0.158152475953102</t>
   </si>
   <si>
     <t xml:space="preserve">0.156686589121819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153103321790695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152288943529129</t>
+    <t xml:space="preserve">0.153103336691856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15228895843029</t>
   </si>
   <si>
     <t xml:space="preserve">0.154894962906837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153917700052261</t>
+    <t xml:space="preserve">0.153917714953423</t>
   </si>
   <si>
     <t xml:space="preserve">0.15440633893013</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">0.164911836385727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164504632353783</t>
+    <t xml:space="preserve">0.164504647254944</t>
   </si>
   <si>
     <t xml:space="preserve">0.163283064961433</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">0.162224382162094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162550121545792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161084234714508</t>
+    <t xml:space="preserve">0.162550136446953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161084249615669</t>
   </si>
   <si>
     <t xml:space="preserve">0.15880398452282</t>
@@ -2876,10 +2876,10 @@
     <t xml:space="preserve">0.172241255640984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172648444771767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171834066510201</t>
+    <t xml:space="preserve">0.172648429870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171834051609039</t>
   </si>
   <si>
     <t xml:space="preserve">0.169798091053963</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">0.184864118695259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.185678511857986</t>
+    <t xml:space="preserve">0.185678496956825</t>
   </si>
   <si>
     <t xml:space="preserve">0.188121646642685</t>
@@ -19183,7 +19183,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19209,7 +19209,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G597" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19235,7 +19235,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G598" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19261,7 +19261,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G599" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19287,7 +19287,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G600" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19313,7 +19313,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G601" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19339,7 +19339,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G602" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19365,7 +19365,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G603" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19391,7 +19391,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G604" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19417,7 +19417,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G605" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19443,7 +19443,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G606" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19469,7 +19469,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19495,7 +19495,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G608" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19521,7 +19521,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G609" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19547,7 +19547,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G610" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19573,7 +19573,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G611" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19599,7 +19599,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G612" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19625,7 +19625,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G613" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19651,7 +19651,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19677,7 +19677,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G615" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19703,7 +19703,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G616" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19729,7 +19729,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G617" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19755,7 +19755,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G618" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19781,7 +19781,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G619" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19807,7 +19807,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G620" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19833,7 +19833,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G621" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19859,7 +19859,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G622" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19885,7 +19885,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G623" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19911,7 +19911,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G624" t="s">
-        <v>471</v>
+        <v>278</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19937,7 +19937,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G625" t="s">
-        <v>471</v>
+        <v>278</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19963,7 +19963,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G626" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19989,7 +19989,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G627" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20041,7 +20041,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G629" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20093,7 +20093,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G631" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20327,7 +20327,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G640" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20457,7 +20457,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G645" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20639,7 +20639,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G652" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20691,7 +20691,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G654" t="s">
-        <v>471</v>
+        <v>278</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20743,7 +20743,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G656" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20899,7 +20899,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G662" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20951,7 +20951,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G664" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20977,7 +20977,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G665" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21003,7 +21003,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G666" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21185,7 +21185,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G673" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21237,7 +21237,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G675" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21263,7 +21263,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G676" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21549,7 +21549,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G687" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21601,7 +21601,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G689" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21705,7 +21705,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G693" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21731,7 +21731,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G694" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21835,7 +21835,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G698" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -70255,7 +70255,7 @@
     </row>
     <row r="2561">
       <c r="A2561" s="1" t="n">
-        <v>46051.6910069444</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2561" t="n">
         <v>330674</v>
@@ -70264,7 +70264,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="D2561" t="n">
-        <v>0.179499998688698</v>
+        <v>0.179000005125999</v>
       </c>
       <c r="E2561" t="n">
         <v>0.180000007152557</v>
@@ -70276,6 +70276,32 @@
         <v>1114</v>
       </c>
       <c r="H2561" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2562">
+      <c r="A2562" s="1" t="n">
+        <v>46052.635150463</v>
+      </c>
+      <c r="B2562" t="n">
+        <v>143684</v>
+      </c>
+      <c r="C2562" t="n">
+        <v>0.180999994277954</v>
+      </c>
+      <c r="D2562" t="n">
+        <v>0.179000005125999</v>
+      </c>
+      <c r="E2562" t="n">
+        <v>0.179499998688698</v>
+      </c>
+      <c r="F2562" t="n">
+        <v>0.180500000715256</v>
+      </c>
+      <c r="G2562" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H2562" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="1115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="1116">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158053904771805</t>
+    <t xml:space="preserve">0.158053889870644</t>
   </si>
   <si>
     <t xml:space="preserve">PRO.MI</t>
@@ -47,106 +47,106 @@
     <t xml:space="preserve">0.158481404185295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155000314116478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153229236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150542065501213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148099198937416</t>
+    <t xml:space="preserve">0.155000299215317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153229221701622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150542035698891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148099184036255</t>
   </si>
   <si>
     <t xml:space="preserve">0.150297775864601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151580289006233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147366344928741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358422279358</t>
+    <t xml:space="preserve">0.151580274105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147366315126419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14235845208168</t>
   </si>
   <si>
     <t xml:space="preserve">0.132831230759621</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134541228413582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125319391489029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131121203303337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134358018636703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419098496437</t>
+    <t xml:space="preserve">0.134541243314743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12531940639019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131121218204498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134358033537865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419083595276</t>
   </si>
   <si>
     <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138022318482399</t>
+    <t xml:space="preserve">0.13802233338356</t>
   </si>
   <si>
     <t xml:space="preserve">0.137778058648109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140465199947357</t>
+    <t xml:space="preserve">0.140465214848518</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136190190911293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131793022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129166930913925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129289090633392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118967935442924</t>
+    <t xml:space="preserve">0.136190176010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131793007254601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129166916012764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129289045929909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118967942893505</t>
   </si>
   <si>
     <t xml:space="preserve">0.122754372656345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116158626973629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11847934871912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125807970762253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125197261571884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960849881172</t>
+    <t xml:space="preserve">0.11615863442421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479363620281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125807955861092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125197246670723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960834980011</t>
   </si>
   <si>
     <t xml:space="preserve">0.127029404044151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125014036893845</t>
+    <t xml:space="preserve">0.125014021992683</t>
   </si>
   <si>
     <t xml:space="preserve">0.130999073386192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129105851054192</t>
+    <t xml:space="preserve">0.129105821251869</t>
   </si>
   <si>
     <t xml:space="preserve">0.128617271780968</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">0.130205139517784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13051050901413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129533350467682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133808359503746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138755187392235</t>
+    <t xml:space="preserve">0.130510494112968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129533335566521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133808374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138755217194557</t>
   </si>
   <si>
     <t xml:space="preserve">0.139671266078949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136739820241928</t>
+    <t xml:space="preserve">0.136739835143089</t>
   </si>
   <si>
     <t xml:space="preserve">0.136495530605316</t>
@@ -179,37 +179,37 @@
     <t xml:space="preserve">0.140159830451012</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141747713088989</t>
+    <t xml:space="preserve">0.14174772799015</t>
   </si>
   <si>
     <t xml:space="preserve">0.147122025489807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149015262722969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146572396159172</t>
+    <t xml:space="preserve">0.14901527762413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146572381258011</t>
   </si>
   <si>
     <t xml:space="preserve">0.14571738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1432134360075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144129514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140892699360847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139793440699577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968757629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068031191826</t>
+    <t xml:space="preserve">0.143213450908661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144129529595375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140892714262009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139793410897255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968742728233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068046092987</t>
   </si>
   <si>
     <t xml:space="preserve">0.13594588637352</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">0.135823741555214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133136585354805</t>
+    <t xml:space="preserve">0.133136600255966</t>
   </si>
   <si>
     <t xml:space="preserve">0.130693718791008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12886156141758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125258311629295</t>
+    <t xml:space="preserve">0.128861576318741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125258326530457</t>
   </si>
   <si>
     <t xml:space="preserve">0.133930519223213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137472689151764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142480581998825</t>
+    <t xml:space="preserve">0.137472674250603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142480552196503</t>
   </si>
   <si>
     <t xml:space="preserve">0.142114147543907</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">0.142175227403641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138327702879906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142236277461052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138205543160439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140526741743088</t>
+    <t xml:space="preserve">0.138327687978745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142236262559891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1382055580616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14052677154541</t>
   </si>
   <si>
     <t xml:space="preserve">0.139899387955666</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136637151241302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133876800537109</t>
+    <t xml:space="preserve">0.136637181043625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133876830339432</t>
   </si>
   <si>
     <t xml:space="preserve">0.133814081549644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132998526096344</t>
+    <t xml:space="preserve">0.132998540997505</t>
   </si>
   <si>
     <t xml:space="preserve">0.129234418272972</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.12515664100647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126662284135818</t>
+    <t xml:space="preserve">0.126662269234657</t>
   </si>
   <si>
     <t xml:space="preserve">0.126725018024445</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">0.127352356910706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127979695796967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126599550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127916976809502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130489110946655</t>
+    <t xml:space="preserve">0.127979710698128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126599535346031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127916991710663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
     <t xml:space="preserve">0.1317438185215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1311164945364</t>
+    <t xml:space="preserve">0.131116479635239</t>
   </si>
   <si>
     <t xml:space="preserve">0.131555616855621</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">0.131179213523865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133688613772392</t>
+    <t xml:space="preserve">0.133688628673553</t>
   </si>
   <si>
     <t xml:space="preserve">0.134880587458611</t>
@@ -332,43 +332,43 @@
     <t xml:space="preserve">0.134190499782562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130614593625069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132873073220253</t>
+    <t xml:space="preserve">0.130614578723907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132873043417931</t>
   </si>
   <si>
     <t xml:space="preserve">0.128481596708298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121078841388226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120200537145138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121831670403481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413879156113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233191728592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366181194782</t>
+    <t xml:space="preserve">0.121078848838806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120200552046299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831648051739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413864254951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233199179173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366188645363</t>
   </si>
   <si>
     <t xml:space="preserve">0.111794047057629</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114052511751652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395056307316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893185198307</t>
+    <t xml:space="preserve">0.11405248939991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395063757896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893177747726</t>
   </si>
   <si>
     <t xml:space="preserve">0.111041218042374</t>
@@ -380,208 +380,208 @@
     <t xml:space="preserve">0.111354902386665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110727541148663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277110219002</t>
+    <t xml:space="preserve">0.110727533698082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277117669582</t>
   </si>
   <si>
     <t xml:space="preserve">0.102822922170162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100501708686352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716247439384</t>
+    <t xml:space="preserve">0.100501701235771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
   </si>
   <si>
     <t xml:space="preserve">0.110790267586708</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11455437541008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303454756737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632182478905</t>
+    <t xml:space="preserve">0.114554397761822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923286855221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303439855576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632189929485</t>
   </si>
   <si>
     <t xml:space="preserve">0.116561912000179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116373717784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746356546879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432687103748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805340766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185508668423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569448590279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820384144783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934543311596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159179031849</t>
+    <t xml:space="preserve">0.116373710334301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746349096298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432694554329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805348217487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185516119003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569426238537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820369243622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934573113918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159171581268</t>
   </si>
   <si>
     <t xml:space="preserve">0.107088901102543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106147900223732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104140371084213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10564599186182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107465326786041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108531825244427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590772211552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535574913025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1048304438591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092665672302</t>
+    <t xml:space="preserve">0.106147885322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104140363633633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105646006762981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107465319335461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108531810343266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590802013874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535582363605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104830451309681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092673122883</t>
   </si>
   <si>
     <t xml:space="preserve">0.108029931783676</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107653521001339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109849259257317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110978491604328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11160584539175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738834857941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864317536354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110288381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110225655138493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108845502138138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723769128323</t>
+    <t xml:space="preserve">0.10765352845192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109849251806736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110978499054909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11160583794117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113738819956779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864310085773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11028841137886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110225662589073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108845494687557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723776578903</t>
   </si>
   <si>
     <t xml:space="preserve">0.107339851558208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108406364917755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10451678186655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105018630623817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10664975643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10583420842886</t>
+    <t xml:space="preserve">0.108406357467175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10451677441597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10501866042614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106649771332741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10583421587944</t>
   </si>
   <si>
     <t xml:space="preserve">0.106085143983364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10978651791811</t>
+    <t xml:space="preserve">0.109786503016949</t>
   </si>
   <si>
     <t xml:space="preserve">0.104391291737556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107779003679752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214376330376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11606003344059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1147425994277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112421378493309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11342515796423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295933067799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022395193577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712512671947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106837965548038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520531535149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265816509724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760180830956</t>
+    <t xml:space="preserve">0.107778988778591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214383780956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116060048341751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114742591977119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11242138594389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113425143063068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295925617218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022402644157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712505221367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520516633987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265823960304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760188281536</t>
   </si>
   <si>
     <t xml:space="preserve">0.101003602147102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104579500854015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885656058788</t>
+    <t xml:space="preserve">0.104579508304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10288567841053</t>
   </si>
   <si>
     <t xml:space="preserve">0.103889420628548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101254552602768</t>
+    <t xml:space="preserve">0.101254530251026</t>
   </si>
   <si>
     <t xml:space="preserve">0.10056446492672</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">0.101066328585148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101630941033363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106524281203747</t>
+    <t xml:space="preserve">0.101630948483944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106524296104908</t>
   </si>
   <si>
     <t xml:space="preserve">0.109911993145943</t>
@@ -602,37 +602,37 @@
     <t xml:space="preserve">0.110539354383945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110915742814541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657278120518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112609587609768</t>
+    <t xml:space="preserve">0.110915765166283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657293021679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11260960996151</t>
   </si>
   <si>
     <t xml:space="preserve">0.111292161047459</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109410099685192</t>
+    <t xml:space="preserve">0.109410114586353</t>
   </si>
   <si>
     <t xml:space="preserve">0.108343616127968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108280889689922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033711254597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351130366325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544315695763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153701141476631</t>
+    <t xml:space="preserve">0.108280874788761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033703804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351145267487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544345498085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
     <t xml:space="preserve">0.144918218255043</t>
@@ -641,19 +641,19 @@
     <t xml:space="preserve">0.142408803105354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132371172308922</t>
+    <t xml:space="preserve">0.132371202111244</t>
   </si>
   <si>
     <t xml:space="preserve">0.132684856653214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134253233671188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304681301117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134692385792732</t>
+    <t xml:space="preserve">0.13425324857235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304666399956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134692370891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.135821610689163</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">0.142659738659859</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144855484366417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14316163957119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141781434416771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133500412106514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129861772060394</t>
+    <t xml:space="preserve">0.144855469465256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143161624670029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141781449317932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133500382304192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129861757159233</t>
   </si>
   <si>
     <t xml:space="preserve">0.130175441503525</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">0.131681099534035</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130112692713737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130740076303482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842956662178</t>
+    <t xml:space="preserve">0.130112707614899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130740061402321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842964112759</t>
   </si>
   <si>
     <t xml:space="preserve">0.126097664237022</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">0.126536801457405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215602874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12597219645977</t>
+    <t xml:space="preserve">0.124215625226498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125972211360931</t>
   </si>
   <si>
     <t xml:space="preserve">0.130551859736443</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182955741882</t>
+    <t xml:space="preserve">0.130677342414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182970643044</t>
   </si>
   <si>
     <t xml:space="preserve">0.129171684384346</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">0.135006070137024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133939534425735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127750992775</t>
+    <t xml:space="preserve">0.133939549326897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127765893936</t>
   </si>
   <si>
     <t xml:space="preserve">0.136260747909546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134943336248398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766405940056</t>
+    <t xml:space="preserve">0.134943321347237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766391038895</t>
   </si>
   <si>
     <t xml:space="preserve">0.13801734149456</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145733788609505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144165366888046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14397719502449</t>
+    <t xml:space="preserve">0.145733758807182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144165381789207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977180123329</t>
   </si>
   <si>
     <t xml:space="preserve">0.14115409553051</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137640938162804</t>
+    <t xml:space="preserve">0.137640923261642</t>
   </si>
   <si>
     <t xml:space="preserve">0.136762648820877</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">0.134629637002945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134002268314362</t>
+    <t xml:space="preserve">0.134002298116684</t>
   </si>
   <si>
     <t xml:space="preserve">0.133437678217888</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">0.129673555493355</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356143832207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496640086174</t>
+    <t xml:space="preserve">0.128356099128723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496669888496</t>
   </si>
   <si>
     <t xml:space="preserve">0.135633394122124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137891858816147</t>
+    <t xml:space="preserve">0.137891873717308</t>
   </si>
   <si>
     <t xml:space="preserve">0.13770367205143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132433891296387</t>
+    <t xml:space="preserve">0.132433921098709</t>
   </si>
   <si>
     <t xml:space="preserve">0.132057502865791</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">0.134504154324532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134502410888672</t>
+    <t xml:space="preserve">0.134502425789833</t>
   </si>
   <si>
     <t xml:space="preserve">0.132989749312401</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">0.131729170680046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13072070479393</t>
+    <t xml:space="preserve">0.130720719695091</t>
   </si>
   <si>
     <t xml:space="preserve">0.13317883014679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134565427899361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943634271622</t>
+    <t xml:space="preserve">0.134565442800522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943619370461</t>
   </si>
   <si>
     <t xml:space="preserve">0.131792202591896</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">0.132359445095062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130909785628319</t>
+    <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
     <t xml:space="preserve">0.130468606948853</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">0.127002045512199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127947464585304</t>
+    <t xml:space="preserve">0.127947479486465</t>
   </si>
   <si>
     <t xml:space="preserve">0.128199592232704</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">0.128703817725182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126371785998344</t>
+    <t xml:space="preserve">0.126371756196022</t>
   </si>
   <si>
     <t xml:space="preserve">0.125930562615395</t>
@@ -881,64 +881,64 @@
     <t xml:space="preserve">0.127128094434738</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126056626439095</t>
+    <t xml:space="preserve">0.126056611537933</t>
   </si>
   <si>
     <t xml:space="preserve">0.124796062707901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124670006334782</t>
+    <t xml:space="preserve">0.124669998884201</t>
   </si>
   <si>
     <t xml:space="preserve">0.124165765941143</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12517423927784</t>
+    <t xml:space="preserve">0.125174209475517</t>
   </si>
   <si>
     <t xml:space="preserve">0.125237256288528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129018947482109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127380222082138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128451690077782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136545419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884447574615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443253993988</t>
+    <t xml:space="preserve">0.129018932580948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127380207180977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128451704978943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136530518532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884432673454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443239092827</t>
   </si>
   <si>
     <t xml:space="preserve">0.126939013600349</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128262624144554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126875981688499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126497820019722</t>
+    <t xml:space="preserve">0.128262609243393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126875996589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126497834920883</t>
   </si>
   <si>
     <t xml:space="preserve">0.126308739185333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133430942893028</t>
+    <t xml:space="preserve">0.133430913090706</t>
   </si>
   <si>
     <t xml:space="preserve">0.135573893785477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135762974619865</t>
+    <t xml:space="preserve">0.135762989521027</t>
   </si>
   <si>
     <t xml:space="preserve">0.136456295847893</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">0.135195732116699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136141151189804</t>
+    <t xml:space="preserve">0.136141166090965</t>
   </si>
   <si>
     <t xml:space="preserve">0.134439393877983</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">0.137464746832848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137716874480247</t>
+    <t xml:space="preserve">0.137716844677925</t>
   </si>
   <si>
     <t xml:space="preserve">0.138221085071564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137842923402786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136330217123032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13708658516407</t>
+    <t xml:space="preserve">0.137842908501625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136330246925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137086570262909</t>
   </si>
   <si>
     <t xml:space="preserve">0.13677142560482</t>
@@ -989,19 +989,19 @@
     <t xml:space="preserve">0.136204183101654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135006636381149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134754538536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135069653391838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137401714920998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151141911745071</t>
+    <t xml:space="preserve">0.13500665128231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134754523634911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13506968319416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137401729822159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151141881942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.153789088129997</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">0.145280241966248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14704504609108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157444700598717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15939861536026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156625360250473</t>
+    <t xml:space="preserve">0.147045031189919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157444715499878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159398600459099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156625345349312</t>
   </si>
   <si>
     <t xml:space="preserve">0.157570779323578</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">0.152843654155731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152654573321342</t>
+    <t xml:space="preserve">0.152654558420181</t>
   </si>
   <si>
     <t xml:space="preserve">0.151898220181465</t>
@@ -1043,19 +1043,19 @@
     <t xml:space="preserve">0.15309576690197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150259479880333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148746803402901</t>
+    <t xml:space="preserve">0.150259509682655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746833205223</t>
   </si>
   <si>
     <t xml:space="preserve">0.15334789454937</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155805975198746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154419377446175</t>
+    <t xml:space="preserve">0.155805990099907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154419347643852</t>
   </si>
   <si>
     <t xml:space="preserve">0.156940504908562</t>
@@ -1073,28 +1073,28 @@
     <t xml:space="preserve">0.16721411049366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172067284584045</t>
+    <t xml:space="preserve">0.172067299485207</t>
   </si>
   <si>
     <t xml:space="preserve">0.179945826530457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178811326622963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175218716263771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174336314201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176461338997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176479265093803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173642992973328</t>
+    <t xml:space="preserve">0.178811311721802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17521870136261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174336329102516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176446437836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176479279994965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17364302277565</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365512371063</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">0.166205659508705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.168222546577454</t>
+    <t xml:space="preserve">0.168222561478615</t>
   </si>
   <si>
     <t xml:space="preserve">0.168600738048553</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">0.166394740343094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161730632185936</t>
+    <t xml:space="preserve">0.161730647087097</t>
   </si>
   <si>
     <t xml:space="preserve">0.160091921687126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156688392162323</t>
+    <t xml:space="preserve">0.156688377261162</t>
   </si>
   <si>
     <t xml:space="preserve">0.16122642159462</t>
@@ -1130,37 +1130,37 @@
     <t xml:space="preserve">0.162487000226974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873612880707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161037310957909</t>
+    <t xml:space="preserve">0.163747519254684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873583078384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16103732585907</t>
   </si>
   <si>
     <t xml:space="preserve">0.158011972904205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157759860157967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970448732376</t>
+    <t xml:space="preserve">0.157759845256805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970433831215</t>
   </si>
   <si>
     <t xml:space="preserve">0.167718321084976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1652602404356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163117274641991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163810566067696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159461617469788</t>
+    <t xml:space="preserve">0.165260225534439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163117259740829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163810595870018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159461632370949</t>
   </si>
   <si>
     <t xml:space="preserve">0.147675335407257</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">0.147486254572868</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150007382035255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150448590517044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511607527733</t>
+    <t xml:space="preserve">0.150007396936417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150448575615883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511622428894</t>
   </si>
   <si>
     <t xml:space="preserve">0.151078850030899</t>
@@ -1184,22 +1184,22 @@
     <t xml:space="preserve">0.151646107435226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150322526693344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494690656662</t>
+    <t xml:space="preserve">0.150322511792183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494705557823</t>
   </si>
   <si>
     <t xml:space="preserve">0.150826752185822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151772156357765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881318211555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583090424538</t>
+    <t xml:space="preserve">0.151772171258926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881333112717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583105325699</t>
   </si>
   <si>
     <t xml:space="preserve">0.149629220366478</t>
@@ -1211,40 +1211,40 @@
     <t xml:space="preserve">0.15101583302021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148935884237289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148116528987885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150763720273972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150637656450272</t>
+    <t xml:space="preserve">0.148935899138451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148116514086723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150763735175133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150637671351433</t>
   </si>
   <si>
     <t xml:space="preserve">0.15120492875576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149944365024567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213394641876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528509497643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149377107620239</t>
+    <t xml:space="preserve">0.149944350123405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213379740715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528524398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149377092719078</t>
   </si>
   <si>
     <t xml:space="preserve">0.157255634665489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156310215592384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164503887295723</t>
+    <t xml:space="preserve">0.156310185790062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164503902196884</t>
   </si>
   <si>
     <t xml:space="preserve">0.163243323564529</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">0.161982774734497</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163558468222618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165764480829239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165449306368828</t>
+    <t xml:space="preserve">0.163558483123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165764451026917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165449321269989</t>
   </si>
   <si>
     <t xml:space="preserve">0.166079595685005</t>
@@ -1274,10 +1274,10 @@
     <t xml:space="preserve">0.162297889590263</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149061962962151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14717110991478</t>
+    <t xml:space="preserve">0.149061933159828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147171095013618</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540820598602</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">0.146225675940514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142759129405022</t>
+    <t xml:space="preserve">0.14275911450386</t>
   </si>
   <si>
     <t xml:space="preserve">0.144334822893143</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">0.140237987041473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139607697725296</t>
+    <t xml:space="preserve">0.139607712626457</t>
   </si>
   <si>
     <t xml:space="preserve">0.138032004237175</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">0.139922857284546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135826006531715</t>
+    <t xml:space="preserve">0.135826021432877</t>
   </si>
   <si>
     <t xml:space="preserve">0.138347148895264</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">0.141813695430756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140553131699562</t>
+    <t xml:space="preserve">0.140553146600723</t>
   </si>
   <si>
     <t xml:space="preserve">0.141183421015739</t>
@@ -1328,37 +1328,37 @@
     <t xml:space="preserve">0.135510861873627</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134880602359772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250313043594</t>
+    <t xml:space="preserve">0.134250283241272</t>
   </si>
   <si>
     <t xml:space="preserve">0.133935183286667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132674604654312</t>
+    <t xml:space="preserve">0.132674589753151</t>
   </si>
   <si>
     <t xml:space="preserve">0.143074259161949</t>
   </si>
   <si>
+    <t xml:space="preserve">0.144965127110481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443969845772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575838327408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864416241646</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143389403820038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575838327408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864416241646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146253690123558</t>
+    <t xml:space="preserve">0.146253705024719</t>
   </si>
   <si>
     <t xml:space="preserve">0.145609393715858</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">0.142710104584694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141421526670456</t>
+    <t xml:space="preserve">0.141421541571617</t>
   </si>
   <si>
     <t xml:space="preserve">0.13916651904583</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">0.140777230262756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139488652348518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135622933506966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133690044283867</t>
+    <t xml:space="preserve">0.139488637447357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135622903704643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133690059185028</t>
   </si>
   <si>
     <t xml:space="preserve">0.132723614573479</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">0.13207933306694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129824310541153</t>
+    <t xml:space="preserve">0.129824325442314</t>
   </si>
   <si>
     <t xml:space="preserve">0.125765278935432</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">0.131757184863091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125894159078598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126925021409988</t>
+    <t xml:space="preserve">0.125894129276276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126925006508827</t>
   </si>
   <si>
     <t xml:space="preserve">0.125378727912903</t>
@@ -1430,19 +1430,19 @@
     <t xml:space="preserve">0.127440437674522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127955868840218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127827018499374</t>
+    <t xml:space="preserve">0.127955853939056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127827033400536</t>
   </si>
   <si>
     <t xml:space="preserve">0.126023009419441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124347843229771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123703554272652</t>
+    <t xml:space="preserve">0.124347850680351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123703569173813</t>
   </si>
   <si>
     <t xml:space="preserve">0.127311587333679</t>
@@ -1451,22 +1451,22 @@
     <t xml:space="preserve">0.127569302916527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126667305827141</t>
+    <t xml:space="preserve">0.12666729092598</t>
   </si>
   <si>
     <t xml:space="preserve">0.126538440585136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128729000687599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12834244966507</t>
+    <t xml:space="preserve">0.128729030489922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128342464566231</t>
   </si>
   <si>
     <t xml:space="preserve">0.129502162337303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130146443843842</t>
+    <t xml:space="preserve">0.130146458745003</t>
   </si>
   <si>
     <t xml:space="preserve">0.134012192487717</t>
@@ -1475,34 +1475,34 @@
     <t xml:space="preserve">0.134656488895416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138522207736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138200059533119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300755500793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130790755152702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128084719181061</t>
+    <t xml:space="preserve">0.13852222263813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13820007443428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300785303116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130790740251541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128084734082222</t>
   </si>
   <si>
     <t xml:space="preserve">0.128857880830765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125249847769737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122157283127308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12331698089838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125507563352585</t>
+    <t xml:space="preserve">0.12524987757206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122157268226147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123316988348961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125507578253746</t>
   </si>
   <si>
     <t xml:space="preserve">0.128213599324226</t>
@@ -1511,76 +1511,76 @@
     <t xml:space="preserve">0.126151859760284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127182722091675</t>
+    <t xml:space="preserve">0.127182736992836</t>
   </si>
   <si>
     <t xml:space="preserve">0.125636428594589</t>
   </si>
   <si>
-    <t xml:space="preserve">0.120482131838799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122286140918732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122414983808994</t>
+    <t xml:space="preserve">0.120482116937637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122286148369312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122414998710155</t>
   </si>
   <si>
     <t xml:space="preserve">0.117260672152042</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113266058266163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113394938409328</t>
+    <t xml:space="preserve">0.113266073167324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113394930958748</t>
   </si>
   <si>
     <t xml:space="preserve">0.111848644912243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112106367945671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114425808191299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683493971825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112235210835934</t>
+    <t xml:space="preserve">0.11210636049509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114425800740719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683516323566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112235195934772</t>
   </si>
   <si>
     <t xml:space="preserve">0.110817782580853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108240626752377</t>
+    <t xml:space="preserve">0.108240619301796</t>
   </si>
   <si>
     <t xml:space="preserve">0.106565460562706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105921179056168</t>
+    <t xml:space="preserve">0.105921193957329</t>
   </si>
   <si>
     <t xml:space="preserve">0.101926580071449</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105019174516201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103086300194263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104374878108501</t>
+    <t xml:space="preserve">0.105019181966782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103086292743683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104374893009663</t>
   </si>
   <si>
     <t xml:space="preserve">0.104117162525654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10566346347332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107982896268368</t>
+    <t xml:space="preserve">0.105663478374481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10798291862011</t>
   </si>
   <si>
     <t xml:space="preserve">0.108627185225487</t>
@@ -1589,106 +1589,106 @@
     <t xml:space="preserve">0.108111761510372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111462071537971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112750642001629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108756043016911</t>
+    <t xml:space="preserve">0.111462064087391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112750634551048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108756050467491</t>
   </si>
   <si>
     <t xml:space="preserve">0.110173478722572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109529197216034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106952041387558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153448224068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103988319635391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699711918831</t>
+    <t xml:space="preserve">0.109529212117195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106952033936977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153433322906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103988297283649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699734270573</t>
   </si>
   <si>
     <t xml:space="preserve">0.105276882648468</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111204363405704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115585520863533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115843243896961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327790379524</t>
+    <t xml:space="preserve">0.111204355955124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115585513412952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843236446381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327797830105</t>
   </si>
   <si>
     <t xml:space="preserve">0.113008357584476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10940033942461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110431209206581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107854038476944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730596601963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106307744979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103859454393387</t>
+    <t xml:space="preserve">0.109400346875191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110431201756001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107854053378105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730589151382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106307752430439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103859461843967</t>
   </si>
   <si>
     <t xml:space="preserve">0.114554636180401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109142638742924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1090137809515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884900808334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109271474182606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107338614761829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442018687725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411141455173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102055430412292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10025142878294</t>
+    <t xml:space="preserve">0.109142623841763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013773500919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884908258915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109271481633186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10733862221241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442011237144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411134004593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102055445313454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100251436233521</t>
   </si>
   <si>
     <t xml:space="preserve">0.0999937206506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10128228366375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797722280025</t>
+    <t xml:space="preserve">0.101282298564911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797737181187</t>
   </si>
   <si>
     <t xml:space="preserve">0.100766859948635</t>
@@ -1697,91 +1697,91 @@
     <t xml:space="preserve">0.105148032307625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109915778040886</t>
+    <t xml:space="preserve">0.109915770590305</t>
   </si>
   <si>
     <t xml:space="preserve">0.11107549071312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112621784210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110302351415157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11068893969059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761466383934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534605681896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467472553253</t>
+    <t xml:space="preserve">0.112621799111366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110302343964577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688902437687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761451482773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534613132477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467480003834</t>
   </si>
   <si>
     <t xml:space="preserve">0.108498334884644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107080891728401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104503743350506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105792306363583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106436595320702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10534131526947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107596322894096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108562767505646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207049012184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110185064375401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857119619846</t>
+    <t xml:space="preserve">0.107080899178982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104503728449345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105792313814163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106436617672443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10534130781889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107596315443516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108562760055065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207041561604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11018505692482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857141971588</t>
   </si>
   <si>
     <t xml:space="preserve">0.11116885393858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110513001680374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889533042908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106905750930309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10592195391655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10395435988903</t>
+    <t xml:space="preserve">0.110512994229794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889540493488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10690575838089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10592196136713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103954367339611</t>
   </si>
   <si>
     <t xml:space="preserve">0.104282297194004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105594024062157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108217470347881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266086757183</t>
+    <t xml:space="preserve">0.105594016611576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108217477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266101658344</t>
   </si>
   <si>
     <t xml:space="preserve">0.104938149452209</t>
@@ -1790,61 +1790,61 @@
     <t xml:space="preserve">0.102970570325851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103626430034637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103298492729664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101658843457699</t>
+    <t xml:space="preserve">0.103626437485218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103298500180244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101658836007118</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347109138966</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330906152725</t>
+    <t xml:space="preserve">0.101330891251564</t>
   </si>
   <si>
     <t xml:space="preserve">0.0970677956938744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.097723662853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0973957255482674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951002016663551</t>
+    <t xml:space="preserve">0.0977236703038216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957180976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951001942157745</t>
   </si>
   <si>
     <t xml:space="preserve">0.0980515852570534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0964119285345078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0987074449658394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0993633195757866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100019179284573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002968847752</t>
+    <t xml:space="preserve">0.0964119359850883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0987074598670006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099363312125206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100019186735153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002983748913</t>
   </si>
   <si>
     <t xml:space="preserve">0.10067505389452</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102642633020878</t>
+    <t xml:space="preserve">0.102642625570297</t>
   </si>
   <si>
     <t xml:space="preserve">0.098379522562027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0996912494301796</t>
+    <t xml:space="preserve">0.099691241979599</t>
   </si>
   <si>
     <t xml:space="preserve">0.099035382270813</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">0.107561610639095</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108873337507248</t>
+    <t xml:space="preserve">0.108873322606087</t>
   </si>
   <si>
     <t xml:space="preserve">0.108545407652855</t>
@@ -1868,73 +1868,73 @@
     <t xml:space="preserve">0.107233673334122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106249883770943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112152650952339</t>
+    <t xml:space="preserve">0.106249891221523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11215265840292</t>
   </si>
   <si>
     <t xml:space="preserve">0.114448174834251</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111824721097946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808518111706</t>
+    <t xml:space="preserve">0.111824728548527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808533012867</t>
   </si>
   <si>
     <t xml:space="preserve">0.113136433064938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112480580806732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111496798694134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130516827106476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139698907732964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132484421133995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141010656952858</t>
+    <t xml:space="preserve">0.112480603158474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111496783792973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130516812205315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139698937535286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132484436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141010642051697</t>
   </si>
   <si>
     <t xml:space="preserve">0.160686567425728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173803806304932</t>
+    <t xml:space="preserve">0.173803821206093</t>
   </si>
   <si>
     <t xml:space="preserve">0.16724519431591</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155439630150795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150848612189293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154127925634384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157407224178314</t>
+    <t xml:space="preserve">0.155439659953117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150848597288132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154127910733223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157407239079475</t>
   </si>
   <si>
     <t xml:space="preserve">0.156751364469528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152816206216812</t>
+    <t xml:space="preserve">0.15281617641449</t>
   </si>
   <si>
     <t xml:space="preserve">0.148881018161774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.145601689815521</t>
+    <t xml:space="preserve">0.145601704716682</t>
   </si>
   <si>
     <t xml:space="preserve">0.146257549524307</t>
@@ -1943,22 +1943,22 @@
     <t xml:space="preserve">0.146913424134254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150192752480507</t>
+    <t xml:space="preserve">0.150192737579346</t>
   </si>
   <si>
     <t xml:space="preserve">0.149536862969398</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142978250980377</t>
+    <t xml:space="preserve">0.142978236079216</t>
   </si>
   <si>
     <t xml:space="preserve">0.147569268941879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148225128650665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162654146552086</t>
+    <t xml:space="preserve">0.148225143551826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162654131650925</t>
   </si>
   <si>
     <t xml:space="preserve">0.161342427134514</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">0.141666516661644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139043048024178</t>
+    <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
     <t xml:space="preserve">0.1351078748703</t>
@@ -2000,22 +2000,22 @@
     <t xml:space="preserve">0.125597849488258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126581639051437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123958207666874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118711292743683</t>
+    <t xml:space="preserve">0.12658166885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123958192765713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118711285293102</t>
   </si>
   <si>
     <t xml:space="preserve">0.110840924084187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0967398583889008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0826387852430344</t>
+    <t xml:space="preserve">0.0967398509383202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0826388001441956</t>
   </si>
   <si>
     <t xml:space="preserve">0.087885707616806</t>
@@ -2024,16 +2024,16 @@
     <t xml:space="preserve">0.08722984790802</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0885415747761726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0911650210618973</t>
+    <t xml:space="preserve">0.088541567325592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0911650285124779</t>
   </si>
   <si>
     <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0928046777844429</t>
+    <t xml:space="preserve">0.0928046852350235</t>
   </si>
   <si>
     <t xml:space="preserve">0.0944443419575691</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">0.0960840061306953</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0931326076388359</t>
+    <t xml:space="preserve">0.0931326150894165</t>
   </si>
   <si>
     <t xml:space="preserve">0.0957560688257217</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">0.0969366207718849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0978548303246498</t>
+    <t xml:space="preserve">0.0978548377752304</t>
   </si>
   <si>
     <t xml:space="preserve">0.0971989706158638</t>
@@ -2066,34 +2066,34 @@
     <t xml:space="preserve">0.0924767479300499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0940508171916008</t>
+    <t xml:space="preserve">0.0940508246421814</t>
   </si>
   <si>
     <t xml:space="preserve">0.0939196422696114</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0941819995641708</t>
+    <t xml:space="preserve">0.0941819921135902</t>
   </si>
   <si>
     <t xml:space="preserve">0.0949690341949463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0954937338829041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483550906181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740641355515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0968054383993149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0966742932796478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110709741711617</t>
+    <t xml:space="preserve">0.0954937264323235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483476400375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740626454353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0968054533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0966742858290672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110709756612778</t>
   </si>
   <si>
     <t xml:space="preserve">0.0979859977960587</t>
@@ -2102,37 +2102,37 @@
     <t xml:space="preserve">0.0991665571928024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0936573147773743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0948378667235374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100084766745567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102183528244495</t>
+    <t xml:space="preserve">0.0936573073267937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0948378518223763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100084759294987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102183535695076</t>
   </si>
   <si>
     <t xml:space="preserve">0.0999535992741585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103232897818089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10480697453022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140354797244072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125925779342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138387188315392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14232237637043</t>
+    <t xml:space="preserve">0.10323292016983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104806981980801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140354782342911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125925794243813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138387203216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142322361469269</t>
   </si>
   <si>
     <t xml:space="preserve">0.137403398752213</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">0.135435804724693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136419594287872</t>
+    <t xml:space="preserve">0.136419609189034</t>
   </si>
   <si>
     <t xml:space="preserve">0.134452015161514</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">0.134124085307121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131041511893272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127893358469009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134779959917068</t>
+    <t xml:space="preserve">0.131041541695595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127893373370171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134779945015907</t>
   </si>
   <si>
     <t xml:space="preserve">0.131172701716423</t>
@@ -2171,52 +2171,52 @@
     <t xml:space="preserve">0.129336267709732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130385667085648</t>
+    <t xml:space="preserve">0.130385652184486</t>
   </si>
   <si>
     <t xml:space="preserve">0.131500631570816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130910351872444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133468225598335</t>
+    <t xml:space="preserve">0.130910336971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133468210697174</t>
   </si>
   <si>
     <t xml:space="preserve">0.129992142319679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975178718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127631038427353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128549233078957</t>
+    <t xml:space="preserve">0.126975163817406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127631023526192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128549247980118</t>
   </si>
   <si>
     <t xml:space="preserve">0.133796140551567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132156491279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130648016929626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129205107688904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129598617553711</t>
+    <t xml:space="preserve">0.132156476378441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130648002028465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129205092787743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129598632454872</t>
   </si>
   <si>
     <t xml:space="preserve">0.140026852488518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1297297924757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12986096739769</t>
+    <t xml:space="preserve">0.129729807376862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129860982298851</t>
   </si>
   <si>
     <t xml:space="preserve">0.130254477262497</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">0.129073932766914</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125138729810715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124614059925079</t>
+    <t xml:space="preserve">0.125138744711876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124614052474499</t>
   </si>
   <si>
     <t xml:space="preserve">0.143634095788002</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">0.143962040543556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139370992779732</t>
+    <t xml:space="preserve">0.139370977878571</t>
   </si>
   <si>
     <t xml:space="preserve">0.136091664433479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13805927336216</t>
+    <t xml:space="preserve">0.138059258460999</t>
   </si>
   <si>
     <t xml:space="preserve">0.136747539043427</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">0.144945830106735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142650321125984</t>
+    <t xml:space="preserve">0.142650306224823</t>
   </si>
   <si>
     <t xml:space="preserve">0.141994446516037</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">0.144289970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153799995779991</t>
+    <t xml:space="preserve">0.15379998087883</t>
   </si>
   <si>
     <t xml:space="preserve">0.152488261461258</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">0.157079294323921</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152160331606865</t>
+    <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
     <t xml:space="preserve">0.153144121170044</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">0.155111700296402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155767560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160358607769012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159702762961388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162982061505318</t>
+    <t xml:space="preserve">0.155767574906349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160358622670174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159702748060226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162982076406479</t>
   </si>
   <si>
     <t xml:space="preserve">0.166917249560356</t>
@@ -2300,46 +2300,46 @@
     <t xml:space="preserve">0.163310006260872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162326216697693</t>
+    <t xml:space="preserve">0.162326201796532</t>
   </si>
   <si>
     <t xml:space="preserve">0.161014467477798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159046903252602</t>
+    <t xml:space="preserve">0.15904688835144</t>
   </si>
   <si>
     <t xml:space="preserve">0.159374818205833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158718973398209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158391043543816</t>
+    <t xml:space="preserve">0.158718958497047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158391028642654</t>
   </si>
   <si>
     <t xml:space="preserve">0.160030692815781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158063098788261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165341436862946</t>
+    <t xml:space="preserve">0.1580630838871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165341451764107</t>
   </si>
   <si>
     <t xml:space="preserve">0.163571193814278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162863075733185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16250903904438</t>
+    <t xml:space="preserve">0.162863090634346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162509024143219</t>
   </si>
   <si>
     <t xml:space="preserve">0.161092832684517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158614471554756</t>
+    <t xml:space="preserve">0.158614486455917</t>
   </si>
   <si>
     <t xml:space="preserve">0.157198280096054</t>
@@ -2348,61 +2348,61 @@
     <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162154987454414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158968552947044</t>
+    <t xml:space="preserve">0.162154972553253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158968523144722</t>
   </si>
   <si>
     <t xml:space="preserve">0.160384729504585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159322589635849</t>
+    <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
     <t xml:space="preserve">0.15755233168602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161800920963287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15507398545742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153303727507591</t>
+    <t xml:space="preserve">0.161800935864449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155073970556259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153303742408752</t>
   </si>
   <si>
     <t xml:space="preserve">0.155782088637352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151533484458923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152595639228821</t>
+    <t xml:space="preserve">0.151533469557762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15259562432766</t>
   </si>
   <si>
     <t xml:space="preserve">0.154719933867455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155428037047386</t>
+    <t xml:space="preserve">0.155428051948547</t>
   </si>
   <si>
     <t xml:space="preserve">0.156844228506088</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156490191817284</t>
+    <t xml:space="preserve">0.156490176916122</t>
   </si>
   <si>
     <t xml:space="preserve">0.153657779097557</t>
   </si>
   <si>
-    <t xml:space="preserve">0.154011830687523</t>
+    <t xml:space="preserve">0.154011815786362</t>
   </si>
   <si>
     <t xml:space="preserve">0.156136125326157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152241572737694</t>
+    <t xml:space="preserve">0.152241587638855</t>
   </si>
   <si>
     <t xml:space="preserve">0.154365882277489</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">0.151887521147728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151179417967796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150117293000221</t>
+    <t xml:space="preserve">0.151179432868958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15011727809906</t>
   </si>
   <si>
     <t xml:space="preserve">0.150825381278992</t>
@@ -2432,16 +2432,16 @@
     <t xml:space="preserve">0.146222710609436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147284880280495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142682209610939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143390342593193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145514637231827</t>
+    <t xml:space="preserve">0.147284895181656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1426822245121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143390312790871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145514622330666</t>
   </si>
   <si>
     <t xml:space="preserve">0.148347020149231</t>
@@ -2450,10 +2450,10 @@
     <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152949675917625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.145160555839539</t>
+    <t xml:space="preserve">0.152949690818787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145160585641861</t>
   </si>
   <si>
     <t xml:space="preserve">0.147638931870461</t>
@@ -2465,13 +2465,13 @@
     <t xml:space="preserve">0.146576777100563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144452482461929</t>
+    <t xml:space="preserve">0.144452467560768</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144806534051895</t>
+    <t xml:space="preserve">0.144806548953056</t>
   </si>
   <si>
     <t xml:space="preserve">0.144098430871964</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">0.145868673920631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147992983460426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165695488452911</t>
+    <t xml:space="preserve">0.147992968559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16569547355175</t>
   </si>
   <si>
     <t xml:space="preserve">0.168527886271477</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167465716600418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16498738527298</t>
+    <t xml:space="preserve">0.167465731501579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164987370371819</t>
   </si>
   <si>
     <t xml:space="preserve">0.163217127323151</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">0.162075757980347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167782664299011</t>
+    <t xml:space="preserve">0.16778264939785</t>
   </si>
   <si>
     <t xml:space="preserve">0.167021751403809</t>
@@ -2516,28 +2516,28 @@
     <t xml:space="preserve">0.161695301532745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161314830183983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159793004393578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163978040218353</t>
+    <t xml:space="preserve">0.161314845085144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159792989492416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163978055119514</t>
   </si>
   <si>
     <t xml:space="preserve">0.16055391728878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158271163702011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160934388637543</t>
+    <t xml:space="preserve">0.158271178603172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160934373736382</t>
   </si>
   <si>
     <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16511943936348</t>
+    <t xml:space="preserve">0.165119424462318</t>
   </si>
   <si>
     <t xml:space="preserve">0.163597598671913</t>
@@ -2552,13 +2552,13 @@
     <t xml:space="preserve">0.159412533044815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160173460841179</t>
+    <t xml:space="preserve">0.16017347574234</t>
   </si>
   <si>
     <t xml:space="preserve">0.165880352258682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.17044585943222</t>
+    <t xml:space="preserve">0.170445874333382</t>
   </si>
   <si>
     <t xml:space="preserve">0.169684946537018</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">0.171967700123787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170065388083458</t>
+    <t xml:space="preserve">0.170065402984619</t>
   </si>
   <si>
     <t xml:space="preserve">0.157129764556885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157890692353249</t>
+    <t xml:space="preserve">0.15789070725441</t>
   </si>
   <si>
     <t xml:space="preserve">0.153705656528473</t>
@@ -2588,16 +2588,16 @@
     <t xml:space="preserve">0.14777047932148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155227497220039</t>
+    <t xml:space="preserve">0.155227482318878</t>
   </si>
   <si>
     <t xml:space="preserve">0.155988410115242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157510235905647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164738968014717</t>
+    <t xml:space="preserve">0.157510250806808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164738982915878</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
@@ -2606,7 +2606,7 @@
     <t xml:space="preserve">0.168924033641815</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166641280055046</t>
+    <t xml:space="preserve">0.166641265153885</t>
   </si>
   <si>
     <t xml:space="preserve">0.168163105845451</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">0.173462808132172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171426862478256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168983712792397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166133403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170612469315529</t>
+    <t xml:space="preserve">0.171426877379417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168983727693558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166133388876915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17061248421669</t>
   </si>
   <si>
     <t xml:space="preserve">0.16816933453083</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">0.166947782039642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167762145400047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168576523661613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.169390916824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16287587583065</t>
+    <t xml:space="preserve">0.167762160301208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168576538562775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.169390931725502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162875890731812</t>
   </si>
   <si>
     <t xml:space="preserve">0.151963204145432</t>
@@ -2672,19 +2672,19 @@
     <t xml:space="preserve">0.155709356069565</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157175227999687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15636083483696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157338112592697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155546456575394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15424345433712</t>
+    <t xml:space="preserve">0.157175242900848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156360849738121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157338097691536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155546471476555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154243469238281</t>
   </si>
   <si>
     <t xml:space="preserve">0.150660187005997</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">0.152614697813988</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163690268993378</t>
+    <t xml:space="preserve">0.163690254092216</t>
   </si>
   <si>
     <t xml:space="preserve">0.162387251853943</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">0.158478230237961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.160432741045952</t>
+    <t xml:space="preserve">0.160432755947113</t>
   </si>
   <si>
     <t xml:space="preserve">0.157012343406677</t>
@@ -2717,16 +2717,16 @@
     <t xml:space="preserve">0.161735743284225</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161572888493538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157500967383385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160269871354103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159129738807678</t>
+    <t xml:space="preserve">0.161572873592377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157500982284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160269856452942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159129723906517</t>
   </si>
   <si>
     <t xml:space="preserve">0.160595610737801</t>
@@ -2753,10 +2753,10 @@
     <t xml:space="preserve">0.154732078313828</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158966854214668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156523734331131</t>
+    <t xml:space="preserve">0.158966869115829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15652371942997</t>
   </si>
   <si>
     <t xml:space="preserve">0.155220702290535</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">0.156035095453262</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157663851976395</t>
+    <t xml:space="preserve">0.157663837075233</t>
   </si>
   <si>
     <t xml:space="preserve">0.155383586883545</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">0.156686589121819</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153103336691856</t>
+    <t xml:space="preserve">0.153103321790695</t>
   </si>
   <si>
     <t xml:space="preserve">0.15228895843029</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">0.154894962906837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153917714953423</t>
+    <t xml:space="preserve">0.153917700052261</t>
   </si>
   <si>
     <t xml:space="preserve">0.15440633893013</t>
@@ -2804,19 +2804,19 @@
     <t xml:space="preserve">0.160921365022659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159292608499527</t>
+    <t xml:space="preserve">0.159292623400688</t>
   </si>
   <si>
     <t xml:space="preserve">0.158641114830971</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164911836385727</t>
+    <t xml:space="preserve">0.164911821484566</t>
   </si>
   <si>
     <t xml:space="preserve">0.164504647254944</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163283064961433</t>
+    <t xml:space="preserve">0.163283079862595</t>
   </si>
   <si>
     <t xml:space="preserve">0.164097443223</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">0.162224382162094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162550136446953</t>
+    <t xml:space="preserve">0.162550121545792</t>
   </si>
   <si>
     <t xml:space="preserve">0.161084249615669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15880398452282</t>
+    <t xml:space="preserve">0.158803969621658</t>
   </si>
   <si>
     <t xml:space="preserve">0.159618362784386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159455493092537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16271299123764</t>
+    <t xml:space="preserve">0.159455478191376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162713006138802</t>
   </si>
   <si>
     <t xml:space="preserve">0.165726214647293</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">0.17305563390255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176720336079597</t>
+    <t xml:space="preserve">0.176720321178436</t>
   </si>
   <si>
     <t xml:space="preserve">0.177534714341164</t>
@@ -2867,22 +2867,22 @@
     <t xml:space="preserve">0.175091579556465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.171019673347473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172241255640984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.172648429870605</t>
+    <t xml:space="preserve">0.171019658446312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172241240739822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.172648444771767</t>
   </si>
   <si>
     <t xml:space="preserve">0.171834051609039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.169798091053963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.183235362172127</t>
+    <t xml:space="preserve">0.169798105955124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.183235347270966</t>
   </si>
   <si>
     <t xml:space="preserve">0.181606605648994</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">0.184049740433693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182420983910561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.184864118695259</t>
+    <t xml:space="preserve">0.182420998811722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18486413359642</t>
   </si>
   <si>
     <t xml:space="preserve">0.185678496956825</t>
@@ -2903,28 +2903,31 @@
     <t xml:space="preserve">0.188121646642685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.182920128107071</t>
+    <t xml:space="preserve">0.18292011320591</t>
   </si>
   <si>
     <t xml:space="preserve">0.186387807130814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.187254726886749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.189855486154556</t>
+    <t xml:space="preserve">0.18725474178791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.189855471253395</t>
   </si>
   <si>
     <t xml:space="preserve">0.190722405910492</t>
   </si>
   <si>
-    <t xml:space="preserve">0.188988566398621</t>
+    <t xml:space="preserve">0.188988551497459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.188121631741524</t>
   </si>
   <si>
     <t xml:space="preserve">0.185520887374878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.183787047863007</t>
+    <t xml:space="preserve">0.183787032961845</t>
   </si>
   <si>
     <t xml:space="preserve">0.182053208351135</t>
@@ -2942,25 +2945,25 @@
     <t xml:space="preserve">0.179452449083328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178585529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.177718609571457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176851689815521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175984755158424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.175117835402489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.174250915646553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173383995890617</t>
+    <t xml:space="preserve">0.178585514426231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.177718594670296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17685167491436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175984770059586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17511785030365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.174250930547714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173384010791779</t>
   </si>
   <si>
     <t xml:space="preserve">0.191589325666428</t>
@@ -18533,7 +18536,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G571" t="s">
-        <v>438</v>
+        <v>104</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -18559,7 +18562,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G572" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -18585,7 +18588,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G573" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -18611,7 +18614,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G574" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -18637,7 +18640,7 @@
         <v>0.212500005960464</v>
       </c>
       <c r="G575" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -18663,7 +18666,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G576" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -18897,7 +18900,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G585" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -18923,7 +18926,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G586" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -18975,7 +18978,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G588" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -19079,7 +19082,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G592" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -19105,7 +19108,7 @@
         <v>0.230000004172325</v>
       </c>
       <c r="G593" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -19131,7 +19134,7 @@
         <v>0.227500006556511</v>
       </c>
       <c r="G594" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -19157,7 +19160,7 @@
         <v>0.229499995708466</v>
       </c>
       <c r="G595" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -19183,7 +19186,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -52385,7 +52388,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G1873" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -52437,7 +52440,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1875" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -52463,7 +52466,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1876" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -52489,7 +52492,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1877" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52515,7 +52518,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1878" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -52567,7 +52570,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1880" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52645,7 +52648,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1883" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52671,7 +52674,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1884" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52697,7 +52700,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1885" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52775,7 +52778,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1888" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52801,7 +52804,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1889" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52827,7 +52830,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1890" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52853,7 +52856,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1891" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52879,7 +52882,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1892" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52905,7 +52908,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1893" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52931,7 +52934,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1894" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52957,7 +52960,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1895" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52983,7 +52986,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1896" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -53035,7 +53038,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1898" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -53061,7 +53064,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1899" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -53087,7 +53090,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1900" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -53113,7 +53116,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1901" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -53139,7 +53142,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1902" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -53191,7 +53194,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1904" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -53217,7 +53220,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1905" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -53295,7 +53298,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1908" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -53321,7 +53324,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1909" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53347,7 +53350,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1910" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53373,7 +53376,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1911" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53425,7 +53428,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1913" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53451,7 +53454,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1914" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53503,7 +53506,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1916" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53529,7 +53532,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1917" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53555,7 +53558,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1918" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53581,7 +53584,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1919" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53607,7 +53610,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1920" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53633,7 +53636,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1921" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53659,7 +53662,7 @@
         <v>0.212999999523163</v>
       </c>
       <c r="G1922" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53685,7 +53688,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1923" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53711,7 +53714,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1924" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53737,7 +53740,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1925" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53763,7 +53766,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1926" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53789,7 +53792,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1927" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53841,7 +53844,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1929" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53893,7 +53896,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1931" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53919,7 +53922,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G1932" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53945,7 +53948,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1933" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53971,7 +53974,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1934" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53997,7 +54000,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1935" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -54023,7 +54026,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1936" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -54049,7 +54052,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -54075,7 +54078,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1938" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -54101,7 +54104,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1939" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -54127,7 +54130,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1940" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -54153,7 +54156,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1941" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -54179,7 +54182,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1942" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -54205,7 +54208,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -54231,7 +54234,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -54257,7 +54260,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1945" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -54283,7 +54286,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1946" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54309,7 +54312,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54335,7 +54338,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1948" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54361,7 +54364,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1949" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54387,7 +54390,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1950" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54413,7 +54416,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54439,7 +54442,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1952" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54465,7 +54468,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1953" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54491,7 +54494,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1954" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54517,7 +54520,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1955" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54543,7 +54546,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G1956" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54569,7 +54572,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1957" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54595,7 +54598,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1958" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54621,7 +54624,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1959" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54647,7 +54650,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1960" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54673,7 +54676,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1961" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54699,7 +54702,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1962" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54725,7 +54728,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1963" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54751,7 +54754,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1964" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54777,7 +54780,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1965" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54829,7 +54832,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1967" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54855,7 +54858,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G1968" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54881,7 +54884,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G1969" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54907,7 +54910,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1970" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54933,7 +54936,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G1971" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54959,7 +54962,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1972" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54985,7 +54988,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1973" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -55011,7 +55014,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1974" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -55037,7 +55040,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1975" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -55063,7 +55066,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -55089,7 +55092,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1977" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -55115,7 +55118,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G1978" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -55141,7 +55144,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1979" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -55167,7 +55170,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1980" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -55193,7 +55196,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1981" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -55219,7 +55222,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1982" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -55245,7 +55248,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1983" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -55271,7 +55274,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1984" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -55297,7 +55300,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1985" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -55323,7 +55326,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1986" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55349,7 +55352,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1987" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55375,7 +55378,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55401,7 +55404,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1989" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55427,7 +55430,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55453,7 +55456,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G1991" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55479,7 +55482,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1992" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55505,7 +55508,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G1993" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55531,7 +55534,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1994" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55557,7 +55560,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G1995" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55583,7 +55586,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G1996" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55609,7 +55612,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G1997" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55635,7 +55638,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G1998" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55661,7 +55664,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G1999" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55687,7 +55690,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2000" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55713,7 +55716,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55739,7 +55742,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2002" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55765,7 +55768,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2003" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55791,7 +55794,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2004" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55817,7 +55820,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2005" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55843,7 +55846,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2006" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55869,7 +55872,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2007" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55895,7 +55898,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2008" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55921,7 +55924,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2009" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55947,7 +55950,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2010" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55973,7 +55976,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2011" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55999,7 +56002,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2012" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -56025,7 +56028,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2013" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -56051,7 +56054,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2014" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -56077,7 +56080,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2015" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -56103,7 +56106,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2016" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -56129,7 +56132,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2017" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -56155,7 +56158,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2018" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -56181,7 +56184,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2019" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -56207,7 +56210,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2020" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -56233,7 +56236,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2021" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -56259,7 +56262,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2022" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -56285,7 +56288,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2023" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -56311,7 +56314,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2024" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56337,7 +56340,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2025" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56363,7 +56366,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56389,7 +56392,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2027" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56415,7 +56418,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2028" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56441,7 +56444,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2029" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56467,7 +56470,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2030" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56493,7 +56496,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2031" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56519,7 +56522,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2032" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56545,7 +56548,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2033" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56571,7 +56574,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2034" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56597,7 +56600,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2035" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56623,7 +56626,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2036" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56649,7 +56652,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2037" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56675,7 +56678,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2038" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56701,7 +56704,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2039" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56727,7 +56730,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2040" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56753,7 +56756,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2041" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56779,7 +56782,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2042" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56805,7 +56808,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2043" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56831,7 +56834,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2044" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56857,7 +56860,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2045" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56883,7 +56886,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2046" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56909,7 +56912,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2047" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56935,7 +56938,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2048" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56961,7 +56964,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2049" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56987,7 +56990,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2050" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -57013,7 +57016,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2051" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -57039,7 +57042,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2052" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -57065,7 +57068,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2053" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -57091,7 +57094,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2054" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -57117,7 +57120,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2055" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -57143,7 +57146,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2056" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -57169,7 +57172,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2057" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -57195,7 +57198,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2058" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -57221,7 +57224,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2059" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -57247,7 +57250,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2060" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -57273,7 +57276,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2061" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -57299,7 +57302,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2062" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -57325,7 +57328,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2063" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57351,7 +57354,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2064" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57377,7 +57380,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2065" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57403,7 +57406,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57429,7 +57432,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57455,7 +57458,7 @@
         <v>0.202999994158745</v>
       </c>
       <c r="G2068" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57481,7 +57484,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57507,7 +57510,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57533,7 +57536,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2071" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57559,7 +57562,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57585,7 +57588,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2073" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57611,7 +57614,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2074" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57637,7 +57640,7 @@
         <v>0.203999996185303</v>
       </c>
       <c r="G2075" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57663,7 +57666,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2076" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57689,7 +57692,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2077" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57715,7 +57718,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2078" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57741,7 +57744,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2079" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57767,7 +57770,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2080" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57793,7 +57796,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2081" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57819,7 +57822,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2082" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57845,7 +57848,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2083" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57871,7 +57874,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2084" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57897,7 +57900,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2085" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57923,7 +57926,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2086" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57949,7 +57952,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2087" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57975,7 +57978,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2088" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -58001,7 +58004,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2089" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -58027,7 +58030,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2090" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -58053,7 +58056,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2091" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -58079,7 +58082,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2092" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -58105,7 +58108,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2093" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -58131,7 +58134,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2094" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -58157,7 +58160,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2095" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -58235,7 +58238,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2098" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -58313,7 +58316,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2101" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -58339,7 +58342,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2102" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58365,7 +58368,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2103" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58391,7 +58394,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2104" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58443,7 +58446,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2106" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58495,7 +58498,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2108" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58547,7 +58550,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2110" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58573,7 +58576,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2111" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58599,7 +58602,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2112" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58625,7 +58628,7 @@
         <v>0.223000004887581</v>
       </c>
       <c r="G2113" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58651,7 +58654,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2114" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58677,7 +58680,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2115" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58703,7 +58706,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2116" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58755,7 +58758,7 @@
         <v>0.221000000834465</v>
       </c>
       <c r="G2118" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58781,7 +58784,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2119" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58807,7 +58810,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2120" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58833,7 +58836,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2121" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58859,7 +58862,7 @@
         <v>0.224000006914139</v>
       </c>
       <c r="G2122" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58885,7 +58888,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2123" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58911,7 +58914,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2124" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58937,7 +58940,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2125" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58963,7 +58966,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2126" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58989,7 +58992,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2127" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -59015,7 +59018,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2128" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -59041,7 +59044,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2129" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -59067,7 +59070,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2130" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -59093,7 +59096,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2131" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -59119,7 +59122,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2132" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -59145,7 +59148,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2133" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -59171,7 +59174,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2134" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -59197,7 +59200,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2135" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -59223,7 +59226,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2136" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -59249,7 +59252,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2137" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -59275,7 +59278,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2138" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -59301,7 +59304,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2139" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -59327,7 +59330,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2140" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59353,7 +59356,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2141" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59379,7 +59382,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2142" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59405,7 +59408,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2143" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59431,7 +59434,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2144" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59457,7 +59460,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2145" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59483,7 +59486,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2146" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59509,7 +59512,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2147" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59535,7 +59538,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2148" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59561,7 +59564,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2149" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59587,7 +59590,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2150" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59613,7 +59616,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2151" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59639,7 +59642,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2152" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59665,7 +59668,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2153" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59691,7 +59694,7 @@
         <v>0.209000006318092</v>
       </c>
       <c r="G2154" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59717,7 +59720,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2155" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59743,7 +59746,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2156" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59769,7 +59772,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2157" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59795,7 +59798,7 @@
         <v>0.208000004291534</v>
       </c>
       <c r="G2158" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59821,7 +59824,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2159" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59847,7 +59850,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G2160" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59873,7 +59876,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2161" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59899,7 +59902,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2162" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59925,7 +59928,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G2163" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59951,7 +59954,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2164" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59977,7 +59980,7 @@
         <v>0.210999995470047</v>
       </c>
       <c r="G2165" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -60003,7 +60006,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G2166" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -60029,7 +60032,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2167" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -60055,7 +60058,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2168" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -60081,7 +60084,7 @@
         <v>0.222000002861023</v>
       </c>
       <c r="G2169" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -60107,7 +60110,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2170" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -60133,7 +60136,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2171" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -60159,7 +60162,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2172" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -60185,7 +60188,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2173" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -60211,7 +60214,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2174" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -60237,7 +60240,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2175" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -60263,7 +60266,7 @@
         <v>0.219999998807907</v>
       </c>
       <c r="G2176" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -60289,7 +60292,7 @@
         <v>0.218999996781349</v>
       </c>
       <c r="G2177" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -60315,7 +60318,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2178" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -60341,7 +60344,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2179" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60367,7 +60370,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2180" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60393,7 +60396,7 @@
         <v>0.215000003576279</v>
       </c>
       <c r="G2181" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60419,7 +60422,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G2182" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60445,7 +60448,7 @@
         <v>0.216999992728233</v>
       </c>
       <c r="G2183" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60471,7 +60474,7 @@
         <v>0.214000001549721</v>
       </c>
       <c r="G2184" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60497,7 +60500,7 @@
         <v>0.211999997496605</v>
       </c>
       <c r="G2185" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60523,7 +60526,7 @@
         <v>0.209999993443489</v>
       </c>
       <c r="G2186" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60549,7 +60552,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G2187" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60575,7 +60578,7 @@
         <v>0.195500001311302</v>
       </c>
       <c r="G2188" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60601,7 +60604,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2189" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60627,7 +60630,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2190" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60653,7 +60656,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2191" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60679,7 +60682,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2192" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60705,7 +60708,7 @@
         <v>0.194499999284744</v>
       </c>
       <c r="G2193" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60731,7 +60734,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2194" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60757,7 +60760,7 @@
         <v>0.195999994874001</v>
       </c>
       <c r="G2195" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60783,7 +60786,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2196" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60809,7 +60812,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2197" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60835,7 +60838,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2198" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60861,7 +60864,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2199" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60887,7 +60890,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2200" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60913,7 +60916,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2201" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60939,7 +60942,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2202" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60965,7 +60968,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2203" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60991,7 +60994,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2204" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -61017,7 +61020,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2205" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -61043,7 +61046,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2206" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -61069,7 +61072,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2207" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -61095,7 +61098,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2208" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -61121,7 +61124,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2209" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -61147,7 +61150,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2210" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -61173,7 +61176,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2211" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -61199,7 +61202,7 @@
         <v>0.202000007033348</v>
       </c>
       <c r="G2212" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -61225,7 +61228,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2213" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -61251,7 +61254,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2214" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -61277,7 +61280,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2215" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -61303,7 +61306,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2216" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -61329,7 +61332,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2217" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61355,7 +61358,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2218" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61381,7 +61384,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2219" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61407,7 +61410,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2220" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61433,7 +61436,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2221" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61459,7 +61462,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2222" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61485,7 +61488,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2223" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61511,7 +61514,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2224" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61537,7 +61540,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2225" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61563,7 +61566,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2226" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61589,7 +61592,7 @@
         <v>0.20100000500679</v>
       </c>
       <c r="G2227" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61615,7 +61618,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2228" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61641,7 +61644,7 @@
         <v>0.200000002980232</v>
       </c>
       <c r="G2229" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61667,7 +61670,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2230" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61693,7 +61696,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2231" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61719,7 +61722,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2232" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61745,7 +61748,7 @@
         <v>0.197500005364418</v>
       </c>
       <c r="G2233" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61771,7 +61774,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2234" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61797,7 +61800,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2235" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61823,7 +61826,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2236" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61849,7 +61852,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2237" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61875,7 +61878,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2238" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61901,7 +61904,7 @@
         <v>0.199499994516373</v>
       </c>
       <c r="G2239" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61927,7 +61930,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2240" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61953,7 +61956,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2241" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61979,7 +61982,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2242" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -62005,7 +62008,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2243" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -62031,7 +62034,7 @@
         <v>0.199000000953674</v>
       </c>
       <c r="G2244" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -62057,7 +62060,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2245" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -62083,7 +62086,7 @@
         <v>0.198500007390976</v>
       </c>
       <c r="G2246" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -62109,7 +62112,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2247" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -62135,7 +62138,7 @@
         <v>0.194999992847443</v>
       </c>
       <c r="G2248" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -62161,7 +62164,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2249" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -62187,7 +62190,7 @@
         <v>0.19200000166893</v>
       </c>
       <c r="G2250" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -62213,7 +62216,7 @@
         <v>0.193000003695488</v>
       </c>
       <c r="G2251" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -62239,7 +62242,7 @@
         <v>0.192499995231628</v>
       </c>
       <c r="G2252" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -62265,7 +62268,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2253" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -62291,7 +62294,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2254" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -62317,7 +62320,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2255" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -62343,7 +62346,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62369,7 +62372,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2257" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62395,7 +62398,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2258" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62421,7 +62424,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2259" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62447,7 +62450,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2260" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62473,7 +62476,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2261" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62499,7 +62502,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2262" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62525,7 +62528,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2263" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62551,7 +62554,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2264" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62577,7 +62580,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2265" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62603,7 +62606,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2266" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62629,7 +62632,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2267" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62655,7 +62658,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2268" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62681,7 +62684,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2269" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62707,7 +62710,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2270" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62733,7 +62736,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2271" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62759,7 +62762,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2272" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62785,7 +62788,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2273" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62811,7 +62814,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2274" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62837,7 +62840,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2275" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62863,7 +62866,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2276" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62889,7 +62892,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2277" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62915,7 +62918,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2278" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62941,7 +62944,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2279" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62967,7 +62970,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2280" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62993,7 +62996,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2281" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -63019,7 +63022,7 @@
         <v>0.190999999642372</v>
       </c>
       <c r="G2282" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -63045,7 +63048,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2283" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -63071,7 +63074,7 @@
         <v>0.19149999320507</v>
       </c>
       <c r="G2284" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -63097,7 +63100,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2285" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -63123,7 +63126,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2286" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -63149,7 +63152,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2287" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -63175,7 +63178,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2288" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -63201,7 +63204,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2289" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -63227,7 +63230,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2290" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -63253,7 +63256,7 @@
         <v>0.189999997615814</v>
       </c>
       <c r="G2291" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -63279,7 +63282,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2292" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -63305,7 +63308,7 @@
         <v>0.188999995589256</v>
       </c>
       <c r="G2293" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -63331,7 +63334,7 @@
         <v>0.187999993562698</v>
       </c>
       <c r="G2294" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63357,7 +63360,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2295" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63383,7 +63386,7 @@
         <v>0.1875</v>
       </c>
       <c r="G2296" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63409,7 +63412,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2297" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63435,7 +63438,7 @@
         <v>0.190500006079674</v>
       </c>
       <c r="G2298" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63461,7 +63464,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2299" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63487,7 +63490,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2300" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63513,7 +63516,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2301" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63539,7 +63542,7 @@
         <v>0.188500002026558</v>
       </c>
       <c r="G2302" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63565,7 +63568,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2303" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63591,7 +63594,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2304" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63617,7 +63620,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2305" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63643,7 +63646,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2306" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63669,7 +63672,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2307" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63695,7 +63698,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2308" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63721,7 +63724,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2309" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63747,7 +63750,7 @@
         <v>0.18299999833107</v>
       </c>
       <c r="G2310" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63773,7 +63776,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2311" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63799,7 +63802,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2312" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63825,7 +63828,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2313" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63851,7 +63854,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2314" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63877,7 +63880,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2315" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63903,7 +63906,7 @@
         <v>0.187000006437302</v>
       </c>
       <c r="G2316" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63929,7 +63932,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2317" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63955,7 +63958,7 @@
         <v>0.189500004053116</v>
       </c>
       <c r="G2318" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63981,7 +63984,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2319" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -64007,7 +64010,7 @@
         <v>0.186000004410744</v>
       </c>
       <c r="G2320" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -64033,7 +64036,7 @@
         <v>0.185000002384186</v>
       </c>
       <c r="G2321" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -64059,7 +64062,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2322" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -64085,7 +64088,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2323" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -64111,7 +64114,7 @@
         <v>0.185499995946884</v>
       </c>
       <c r="G2324" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -64137,7 +64140,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2325" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -64163,7 +64166,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2326" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -64189,7 +64192,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2327" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -64215,7 +64218,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2328" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -64241,7 +64244,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2329" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -64267,7 +64270,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2330" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -64293,7 +64296,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2331" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -64319,7 +64322,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2332" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -64345,7 +64348,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2333" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64371,7 +64374,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2334" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64397,7 +64400,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2335" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64423,7 +64426,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2336" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64449,7 +64452,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2337" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64475,7 +64478,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2338" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64501,7 +64504,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2339" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64527,7 +64530,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2340" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64553,7 +64556,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2341" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64579,7 +64582,7 @@
         <v>0.178000003099442</v>
       </c>
       <c r="G2342" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64605,7 +64608,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2343" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64631,7 +64634,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2344" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64657,7 +64660,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2345" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64683,7 +64686,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2346" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64709,7 +64712,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2347" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64735,7 +64738,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2348" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64761,7 +64764,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2349" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64787,7 +64790,7 @@
         <v>0.184000000357628</v>
       </c>
       <c r="G2350" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64813,7 +64816,7 @@
         <v>0.18350000679493</v>
       </c>
       <c r="G2351" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64839,7 +64842,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2352" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64865,7 +64868,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2353" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64891,7 +64894,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G2354" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64917,7 +64920,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2355" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64943,7 +64946,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2356" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64969,7 +64972,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2357" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64995,7 +64998,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2358" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -65021,7 +65024,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2359" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -65047,7 +65050,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2360" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -65073,7 +65076,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2361" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -65099,7 +65102,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2362" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -65125,7 +65128,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2363" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -65151,7 +65154,7 @@
         <v>0.172000005841255</v>
       </c>
       <c r="G2364" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -65177,7 +65180,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2365" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -65203,7 +65206,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2366" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -65229,7 +65232,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2367" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -65255,7 +65258,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2368" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -65281,7 +65284,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2369" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -65307,7 +65310,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2370" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -65333,7 +65336,7 @@
         <v>0.184499993920326</v>
       </c>
       <c r="G2371" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65359,7 +65362,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2372" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65385,7 +65388,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2373" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65411,7 +65414,7 @@
         <v>0.182500004768372</v>
       </c>
       <c r="G2374" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65437,7 +65440,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2375" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65463,7 +65466,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2376" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65489,7 +65492,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2377" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65515,7 +65518,7 @@
         <v>0.186499997973442</v>
       </c>
       <c r="G2378" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65541,7 +65544,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2379" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65567,7 +65570,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2380" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65593,7 +65596,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2381" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65619,7 +65622,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2382" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65645,7 +65648,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2383" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65671,7 +65674,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2384" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65697,7 +65700,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2385" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65723,7 +65726,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2386" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65749,7 +65752,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2387" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65775,7 +65778,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2388" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65801,7 +65804,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2389" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65827,7 +65830,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2390" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65853,7 +65856,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2391" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65879,7 +65882,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2392" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65905,7 +65908,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2393" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65931,7 +65934,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2394" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65957,7 +65960,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2395" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65983,7 +65986,7 @@
         <v>0.177499994635582</v>
       </c>
       <c r="G2396" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -66009,7 +66012,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2397" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -66035,7 +66038,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2398" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -66061,7 +66064,7 @@
         <v>0.175500005483627</v>
       </c>
       <c r="G2399" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -66087,7 +66090,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2400" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -66113,7 +66116,7 @@
         <v>0.174500003457069</v>
       </c>
       <c r="G2401" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -66139,7 +66142,7 @@
         <v>0.172499999403954</v>
       </c>
       <c r="G2402" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -66165,7 +66168,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2403" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -66191,7 +66194,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2404" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -66217,7 +66220,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2405" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -66243,7 +66246,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2406" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -66269,7 +66272,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2407" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -66295,7 +66298,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2408" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -66321,7 +66324,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2409" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -66347,7 +66350,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2410" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66373,7 +66376,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2411" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66399,7 +66402,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2412" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66425,7 +66428,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2413" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66451,7 +66454,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2414" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66477,7 +66480,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2415" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66503,7 +66506,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2416" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66529,7 +66532,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2417" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66555,7 +66558,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2418" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66581,7 +66584,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2419" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66607,7 +66610,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2420" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66633,7 +66636,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2421" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66659,7 +66662,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2422" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66685,7 +66688,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2423" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66711,7 +66714,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2424" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66737,7 +66740,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2425" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66763,7 +66766,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2426" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66789,7 +66792,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2427" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66815,7 +66818,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2428" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66841,7 +66844,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2429" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66867,7 +66870,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2430" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66893,7 +66896,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2431" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66919,7 +66922,7 @@
         <v>0.165500000119209</v>
       </c>
       <c r="G2432" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66945,7 +66948,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2433" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66971,7 +66974,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2434" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66997,7 +67000,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2435" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -67023,7 +67026,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2436" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -67049,7 +67052,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2437" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -67075,7 +67078,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2438" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -67101,7 +67104,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2439" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -67127,7 +67130,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2440" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -67153,7 +67156,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2441" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -67179,7 +67182,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2442" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -67205,7 +67208,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2443" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -67231,7 +67234,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2444" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -67257,7 +67260,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2445" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -67283,7 +67286,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2446" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -67309,7 +67312,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2447" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -67335,7 +67338,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2448" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67361,7 +67364,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2449" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67387,7 +67390,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2450" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67413,7 +67416,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2451" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67439,7 +67442,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2452" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67465,7 +67468,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2453" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67491,7 +67494,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2454" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67517,7 +67520,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2455" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67543,7 +67546,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2456" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67569,7 +67572,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2457" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67595,7 +67598,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2458" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67621,7 +67624,7 @@
         <v>0.171000003814697</v>
       </c>
       <c r="G2459" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67647,7 +67650,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2460" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67673,7 +67676,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2461" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67699,7 +67702,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2462" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67725,7 +67728,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2463" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67751,7 +67754,7 @@
         <v>0.168999999761581</v>
       </c>
       <c r="G2464" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67777,7 +67780,7 @@
         <v>0.168500006198883</v>
       </c>
       <c r="G2465" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67803,7 +67806,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2466" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67829,7 +67832,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2467" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67855,7 +67858,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2468" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67881,7 +67884,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2469" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67907,7 +67910,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2470" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67933,7 +67936,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2471" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67959,7 +67962,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2472" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67985,7 +67988,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2473" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -68011,7 +68014,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2474" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -68037,7 +68040,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2475" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -68063,7 +68066,7 @@
         <v>0.162499994039536</v>
       </c>
       <c r="G2476" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -68089,7 +68092,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2477" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -68115,7 +68118,7 @@
         <v>0.170000001788139</v>
       </c>
       <c r="G2478" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -68141,7 +68144,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2479" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -68167,7 +68170,7 @@
         <v>0.16949999332428</v>
       </c>
       <c r="G2480" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -68193,7 +68196,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2481" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -68219,7 +68222,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2482" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -68245,7 +68248,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2483" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -68271,7 +68274,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2484" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -68297,7 +68300,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2485" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -68323,7 +68326,7 @@
         <v>0.167500004172325</v>
       </c>
       <c r="G2486" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68349,7 +68352,7 @@
         <v>0.165000006556511</v>
       </c>
       <c r="G2487" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68375,7 +68378,7 @@
         <v>0.166999995708466</v>
       </c>
       <c r="G2488" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68401,7 +68404,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2489" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68427,7 +68430,7 @@
         <v>0.164000004529953</v>
       </c>
       <c r="G2490" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68453,7 +68456,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2491" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68479,7 +68482,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2492" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68505,7 +68508,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2493" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68531,7 +68534,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2494" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68557,7 +68560,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2495" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68583,7 +68586,7 @@
         <v>0.163000002503395</v>
       </c>
       <c r="G2496" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68609,7 +68612,7 @@
         <v>0.162000000476837</v>
       </c>
       <c r="G2497" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68635,7 +68638,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2498" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68661,7 +68664,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2499" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68687,7 +68690,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2500" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68713,7 +68716,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2501" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68739,7 +68742,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2502" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68765,7 +68768,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2503" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68791,7 +68794,7 @@
         <v>0.158999994397163</v>
       </c>
       <c r="G2504" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68817,7 +68820,7 @@
         <v>0.158500000834465</v>
       </c>
       <c r="G2505" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68843,7 +68846,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G2506" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68869,7 +68872,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2507" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68895,7 +68898,7 @@
         <v>0.160500004887581</v>
       </c>
       <c r="G2508" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68921,7 +68924,7 @@
         <v>0.160999998450279</v>
       </c>
       <c r="G2509" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68947,7 +68950,7 @@
         <v>0.161500006914139</v>
       </c>
       <c r="G2510" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68973,7 +68976,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2511" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68999,7 +69002,7 @@
         <v>0.158000007271767</v>
       </c>
       <c r="G2512" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -69025,7 +69028,7 @@
         <v>0.157499998807907</v>
       </c>
       <c r="G2513" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -69051,7 +69054,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2514" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -69077,7 +69080,7 @@
         <v>0.156000003218651</v>
       </c>
       <c r="G2515" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -69103,7 +69106,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G2516" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -69129,7 +69132,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G2517" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -69155,7 +69158,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G2518" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -69181,7 +69184,7 @@
         <v>0.152500003576279</v>
       </c>
       <c r="G2519" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -69207,7 +69210,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G2520" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -69233,7 +69236,7 @@
         <v>0.150999993085861</v>
       </c>
       <c r="G2521" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -69259,7 +69262,7 @@
         <v>0.151500001549721</v>
       </c>
       <c r="G2522" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -69285,7 +69288,7 @@
         <v>0.149499997496605</v>
       </c>
       <c r="G2523" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -69311,7 +69314,7 @@
         <v>0.150000005960464</v>
       </c>
       <c r="G2524" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -69337,7 +69340,7 @@
         <v>0.150499999523163</v>
       </c>
       <c r="G2525" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -69363,7 +69366,7 @@
         <v>0.151999995112419</v>
       </c>
       <c r="G2526" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -69389,7 +69392,7 @@
         <v>0.156000003218651</v>
       </c>
       <c r="G2527" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -69415,7 +69418,7 @@
         <v>0.152999997138977</v>
       </c>
       <c r="G2528" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -69441,7 +69444,7 @@
         <v>0.156499996781349</v>
       </c>
       <c r="G2529" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -69467,7 +69470,7 @@
         <v>0.155000001192093</v>
       </c>
       <c r="G2530" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -69493,7 +69496,7 @@
         <v>0.156000003218651</v>
       </c>
       <c r="G2531" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -69519,7 +69522,7 @@
         <v>0.159500002861023</v>
       </c>
       <c r="G2532" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -69545,7 +69548,7 @@
         <v>0.157000005245209</v>
       </c>
       <c r="G2533" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -69571,7 +69574,7 @@
         <v>0.159999996423721</v>
       </c>
       <c r="G2534" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="H2534" t="s">
         <v>9</v>
@@ -69597,7 +69600,7 @@
         <v>0.164499998092651</v>
       </c>
       <c r="G2535" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="H2535" t="s">
         <v>9</v>
@@ -69623,7 +69626,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2536" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2536" t="s">
         <v>9</v>
@@ -69649,7 +69652,7 @@
         <v>0.167999997735023</v>
       </c>
       <c r="G2537" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="H2537" t="s">
         <v>9</v>
@@ -69675,7 +69678,7 @@
         <v>0.166500002145767</v>
       </c>
       <c r="G2538" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H2538" t="s">
         <v>9</v>
@@ -69701,7 +69704,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2539" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2539" t="s">
         <v>9</v>
@@ -69727,7 +69730,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2540" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2540" t="s">
         <v>9</v>
@@ -69753,7 +69756,7 @@
         <v>0.165999993681908</v>
       </c>
       <c r="G2541" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="H2541" t="s">
         <v>9</v>
@@ -69779,7 +69782,7 @@
         <v>0.170499995350838</v>
       </c>
       <c r="G2542" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="H2542" t="s">
         <v>9</v>
@@ -69805,7 +69808,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2543" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2543" t="s">
         <v>9</v>
@@ -69831,7 +69834,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2544" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2544" t="s">
         <v>9</v>
@@ -69857,7 +69860,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2545" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2545" t="s">
         <v>9</v>
@@ -69883,7 +69886,7 @@
         <v>0.176499992609024</v>
       </c>
       <c r="G2546" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H2546" t="s">
         <v>9</v>
@@ -69909,7 +69912,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2547" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2547" t="s">
         <v>9</v>
@@ -69935,7 +69938,7 @@
         <v>0.174999997019768</v>
       </c>
       <c r="G2548" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2548" t="s">
         <v>9</v>
@@ -69961,7 +69964,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2549" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2549" t="s">
         <v>9</v>
@@ -69987,7 +69990,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2550" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2550" t="s">
         <v>9</v>
@@ -70013,7 +70016,7 @@
         <v>0.181999996304512</v>
       </c>
       <c r="G2551" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="H2551" t="s">
         <v>9</v>
@@ -70039,7 +70042,7 @@
         <v>0.180000007152557</v>
       </c>
       <c r="G2552" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="H2552" t="s">
         <v>9</v>
@@ -70065,7 +70068,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2553" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2553" t="s">
         <v>9</v>
@@ -70091,7 +70094,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2554" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2554" t="s">
         <v>9</v>
@@ -70117,7 +70120,7 @@
         <v>0.179499998688698</v>
       </c>
       <c r="G2555" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H2555" t="s">
         <v>9</v>
@@ -70143,7 +70146,7 @@
         <v>0.180999994277954</v>
       </c>
       <c r="G2556" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="H2556" t="s">
         <v>9</v>
@@ -70169,7 +70172,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2557" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2557" t="s">
         <v>9</v>
@@ -70195,7 +70198,7 @@
         <v>0.180500000715256</v>
       </c>
       <c r="G2558" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="H2558" t="s">
         <v>9</v>
@@ -70221,7 +70224,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2559" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2559" t="s">
         <v>9</v>
@@ -70247,7 +70250,7 @@
         <v>0.181500002741814</v>
       </c>
       <c r="G2560" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="H2560" t="s">
         <v>9</v>
@@ -70273,7 +70276,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2561" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2561" t="s">
         <v>9</v>
@@ -70299,7 +70302,7 @@
         <v>0.179000005125999</v>
       </c>
       <c r="G2562" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H2562" t="s">
         <v>9</v>
@@ -70325,7 +70328,7 @@
         <v>0.17849999666214</v>
       </c>
       <c r="G2563" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H2563" t="s">
         <v>9</v>
@@ -70351,7 +70354,7 @@
         <v>0.175999999046326</v>
       </c>
       <c r="G2564" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H2564" t="s">
         <v>9</v>
@@ -70377,7 +70380,7 @@
         <v>0.177000001072884</v>
       </c>
       <c r="G2565" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="H2565" t="s">
         <v>9</v>
@@ -70403,7 +70406,7 @@
         <v>0.173500001430511</v>
       </c>
       <c r="G2566" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H2566" t="s">
         <v>9</v>
@@ -70411,7 +70414,7 @@
     </row>
     <row r="2567">
       <c r="A2567" s="1" t="n">
-        <v>46059.6910648148</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2567" t="n">
         <v>731310</v>
@@ -70429,9 +70432,35 @@
         <v>0.174999997019768</v>
       </c>
       <c r="G2567" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.691099537</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>607313</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>0.177499994635582</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>0.172999992966652</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>0.177499994635582</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>0.173500001430511</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H2568" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -44,76 +44,76 @@
     <t xml:space="preserve">PRO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.158481404185295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155000314116478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153229236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150542035698891</t>
+    <t xml:space="preserve">0.158481389284134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155000299215317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1532291918993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150542050600052</t>
   </si>
   <si>
     <t xml:space="preserve">0.148099184036255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15029776096344</t>
+    <t xml:space="preserve">0.150297746062279</t>
   </si>
   <si>
     <t xml:space="preserve">0.151580274105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14736633002758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358437180519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132831230759621</t>
+    <t xml:space="preserve">0.147366315126419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142358422279358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132831215858459</t>
   </si>
   <si>
     <t xml:space="preserve">0.134541258215904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125319376587868</t>
+    <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
     <t xml:space="preserve">0.131121203303337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134358033537865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134419113397598</t>
+    <t xml:space="preserve">0.134358018636703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134419098496437</t>
   </si>
   <si>
     <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13802233338356</t>
+    <t xml:space="preserve">0.138022318482399</t>
   </si>
   <si>
     <t xml:space="preserve">0.137778043746948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140465185046196</t>
+    <t xml:space="preserve">0.140465214848518</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136190190911293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131793007254601</t>
+    <t xml:space="preserve">0.136190176010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131792992353439</t>
   </si>
   <si>
     <t xml:space="preserve">0.129166916012764</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12928906083107</t>
+    <t xml:space="preserve">0.129289075732231</t>
   </si>
   <si>
     <t xml:space="preserve">0.118967935442924</t>
@@ -122,19 +122,19 @@
     <t xml:space="preserve">0.122754380106926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116158626973629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118479341268539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12580794095993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125197261571884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960849881172</t>
+    <t xml:space="preserve">0.116158612072468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118479363620281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125807955861092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125197246670723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960834980011</t>
   </si>
   <si>
     <t xml:space="preserve">0.127029404044151</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">0.125014021992683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130999073386192</t>
+    <t xml:space="preserve">0.130999058485031</t>
   </si>
   <si>
     <t xml:space="preserve">0.129105851054192</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">0.128617271780968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130205139517784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13051050901413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129533365368843</t>
+    <t xml:space="preserve">0.130205154418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130510494112968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129533350467682</t>
   </si>
   <si>
     <t xml:space="preserve">0.133808389306068</t>
@@ -167,52 +167,52 @@
     <t xml:space="preserve">0.138755187392235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139671266078949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136739820241928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136495545506477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140159860253334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14174772799015</t>
+    <t xml:space="preserve">0.13967128098011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136739835143089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136495530605316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140159845352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141747713088989</t>
   </si>
   <si>
     <t xml:space="preserve">0.147122040390968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149015262722969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146572396159172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14571738243103</t>
+    <t xml:space="preserve">0.14901527762413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146572381258011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145717367529869</t>
   </si>
   <si>
     <t xml:space="preserve">0.1432134360075</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144129514694214</t>
+    <t xml:space="preserve">0.144129499793053</t>
   </si>
   <si>
     <t xml:space="preserve">0.140892714262009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.139793410897255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968727827072</t>
+    <t xml:space="preserve">0.139793425798416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968742728233</t>
   </si>
   <si>
     <t xml:space="preserve">0.136068016290665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13594588637352</t>
+    <t xml:space="preserve">0.135945871472359</t>
   </si>
   <si>
     <t xml:space="preserve">0.135823741555214</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">0.125258311629295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133930504322052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137472674250603</t>
+    <t xml:space="preserve">0.133930534124374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137472704052925</t>
   </si>
   <si>
     <t xml:space="preserve">0.142480567097664</t>
@@ -242,49 +242,49 @@
     <t xml:space="preserve">0.142114147543907</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141320213675499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142175227403641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138327702879906</t>
+    <t xml:space="preserve">0.14132022857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14217521250248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138327717781067</t>
   </si>
   <si>
     <t xml:space="preserve">0.142236277461052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138205528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140526726841927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139899402856827</t>
+    <t xml:space="preserve">0.1382055580616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140526741743088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139899417757988</t>
   </si>
   <si>
     <t xml:space="preserve">0.136135280132294</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136637181043625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133876815438271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133814066648483</t>
+    <t xml:space="preserve">0.136637151241302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133876800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133814081549644</t>
   </si>
   <si>
     <t xml:space="preserve">0.132998511195183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12923438847065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128732517361641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125156626105309</t>
+    <t xml:space="preserve">0.129234418272972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128732547163963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12515664100647</t>
   </si>
   <si>
     <t xml:space="preserve">0.126662269234657</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">0.127352371811867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127979695796967</t>
+    <t xml:space="preserve">0.127979710698128</t>
   </si>
   <si>
     <t xml:space="preserve">0.126599535346031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127916976809502</t>
+    <t xml:space="preserve">0.12791696190834</t>
   </si>
   <si>
     <t xml:space="preserve">0.130489125847816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1317438185215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131116479635239</t>
+    <t xml:space="preserve">0.131743803620338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131116464734077</t>
   </si>
   <si>
     <t xml:space="preserve">0.131555631756783</t>
@@ -320,55 +320,55 @@
     <t xml:space="preserve">0.13406503200531</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131179213523865</t>
+    <t xml:space="preserve">0.131179198622704</t>
   </si>
   <si>
     <t xml:space="preserve">0.133688613772392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134880587458611</t>
+    <t xml:space="preserve">0.134880572557449</t>
   </si>
   <si>
     <t xml:space="preserve">0.134190484881401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130614563822746</t>
+    <t xml:space="preserve">0.130614593625069</t>
   </si>
   <si>
     <t xml:space="preserve">0.132873058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128481581807137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.121078871190548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.120200544595718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1218316629529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110413864254951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112233176827431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366188645363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111794047057629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114052511751652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395056307316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893177747726</t>
+    <t xml:space="preserve">0.128481596708298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121078841388226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12020055949688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.121831670403481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110413871705532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112233206629753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366173744202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111794054508209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114052504301071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395048856735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893185198307</t>
   </si>
   <si>
     <t xml:space="preserve">0.111041232943535</t>
@@ -377,118 +377,118 @@
     <t xml:space="preserve">0.107904486358166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111354887485504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727526247501</t>
+    <t xml:space="preserve">0.111354909837246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727533698082</t>
   </si>
   <si>
     <t xml:space="preserve">0.107277132570744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102822907269001</t>
+    <t xml:space="preserve">0.102822914719582</t>
   </si>
   <si>
     <t xml:space="preserve">0.100501716136932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107716254889965</t>
+    <t xml:space="preserve">0.107716277241707</t>
   </si>
   <si>
     <t xml:space="preserve">0.110790275037289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114554397761822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114303439855576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118632189929485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116561904549599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116373717784882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115746341645718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432694554329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114805325865746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.116185501217842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118569448590279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.118820391595364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934573113918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159171581268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088923454285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106147885322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104140363633633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105645999312401</t>
+    <t xml:space="preserve">0.114554390311241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923286855221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114303447306156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118632175028324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11656192690134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116373710334301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746363997459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432672202587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114805333316326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116185508668423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118569426238537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.118820384144783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934565663338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159164130688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088930904865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106147892773151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104140348732471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10564599186182</t>
   </si>
   <si>
     <t xml:space="preserve">0.10746531188488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108531810343266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590802013874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535567462444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104830466210842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108092680573463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029931783676</t>
+    <t xml:space="preserve">0.108531802892685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590809464455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535574913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10483043640852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108092658221722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029946684837</t>
   </si>
   <si>
     <t xml:space="preserve">0.10765352845192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109849244356155</t>
+    <t xml:space="preserve">0.109849251806736</t>
   </si>
   <si>
     <t xml:space="preserve">0.110978491604328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.111605830490589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113738834857941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864310085773</t>
+    <t xml:space="preserve">0.111605852842331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11373882740736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864302635193</t>
   </si>
   <si>
     <t xml:space="preserve">0.110288389027119</t>
@@ -497,34 +497,34 @@
     <t xml:space="preserve">0.110225655138493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108845494687557</t>
+    <t xml:space="preserve">0.108845479786396</t>
   </si>
   <si>
     <t xml:space="preserve">0.109723784029484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107339851558208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406357467175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10451677441597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105018652975559</t>
+    <t xml:space="preserve">0.107339859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406335115433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104516766965389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105018638074398</t>
   </si>
   <si>
     <t xml:space="preserve">0.10664976388216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105834200978279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085158884525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109786532819271</t>
+    <t xml:space="preserve">0.10583420842886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085143983364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10978651791811</t>
   </si>
   <si>
     <t xml:space="preserve">0.104391299188137</t>
@@ -533,52 +533,52 @@
     <t xml:space="preserve">0.107778996229172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107214376330376</t>
+    <t xml:space="preserve">0.107214383780956</t>
   </si>
   <si>
     <t xml:space="preserve">0.116060040891171</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1147425994277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112421378493309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113425150513649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295933067799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022417545319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106712512671947</t>
+    <t xml:space="preserve">0.114742606878281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11242138594389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113425143063068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295940518379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022410094738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106712497770786</t>
   </si>
   <si>
     <t xml:space="preserve">0.106837972998619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105520538985729</t>
+    <t xml:space="preserve">0.105520531535149</t>
   </si>
   <si>
     <t xml:space="preserve">0.104265823960304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102760180830956</t>
+    <t xml:space="preserve">0.102760188281536</t>
   </si>
   <si>
     <t xml:space="preserve">0.101003602147102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104579523205757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885648608208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889420628548</t>
+    <t xml:space="preserve">0.104579515755177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885663509369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889413177967</t>
   </si>
   <si>
     <t xml:space="preserve">0.101254537701607</t>
@@ -587,52 +587,52 @@
     <t xml:space="preserve">0.100564457476139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101066343486309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101630948483944</t>
+    <t xml:space="preserve">0.101066336035728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101630963385105</t>
   </si>
   <si>
     <t xml:space="preserve">0.106524288654327</t>
   </si>
   <si>
-    <t xml:space="preserve">0.109911978244781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110539346933365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110915742814541</t>
+    <t xml:space="preserve">0.109911970794201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110539332032204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11091573536396</t>
   </si>
   <si>
     <t xml:space="preserve">0.10865730047226</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112609602510929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111292161047459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410122036934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108343608677387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108280882239342</t>
+    <t xml:space="preserve">0.11260960996151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11129217594862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410114586353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108343616127968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108280874788761</t>
   </si>
   <si>
     <t xml:space="preserve">0.109033696353436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110351115465164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544345498085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15370112657547</t>
+    <t xml:space="preserve">0.110351137816906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544315695763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153701141476631</t>
   </si>
   <si>
     <t xml:space="preserve">0.144918203353882</t>
@@ -644,28 +644,28 @@
     <t xml:space="preserve">0.132371172308922</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132684856653214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134253233671188</t>
+    <t xml:space="preserve">0.132684841752052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13425324857235</t>
   </si>
   <si>
     <t xml:space="preserve">0.131304666399956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134692370891571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135821610689163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139836668968201</t>
+    <t xml:space="preserve">0.134692385792732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135821595788002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139836683869362</t>
   </si>
   <si>
     <t xml:space="preserve">0.14265975356102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144855469465256</t>
+    <t xml:space="preserve">0.144855454564095</t>
   </si>
   <si>
     <t xml:space="preserve">0.143161624670029</t>
@@ -677,127 +677,127 @@
     <t xml:space="preserve">0.133500412106514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129861772060394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130175441503525</t>
+    <t xml:space="preserve">0.129861786961555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130175456404686</t>
   </si>
   <si>
     <t xml:space="preserve">0.131681084632874</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130112692713737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130740091204643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842964112759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126097664237022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12697596848011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289637923241</t>
+    <t xml:space="preserve">0.130112707614899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130740061402321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12484297901392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126097679138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975953578949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289623022079</t>
   </si>
   <si>
     <t xml:space="preserve">0.127226889133453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126411333680153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125470295548439</t>
+    <t xml:space="preserve">0.126411348581314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125470325350761</t>
   </si>
   <si>
     <t xml:space="preserve">0.126536801457405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124215595424175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12597219645977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130551859736443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182970643044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171684384346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132245719432831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006040334702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133939549326897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127780795097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136260733008385</t>
+    <t xml:space="preserve">0.124215610325336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125972211360931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130551874637604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677342414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182955741882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171699285507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13224570453167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006070137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133939564228058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127750992775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136260762810707</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943321347237</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137766405940056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138017356395721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777707099915</t>
+    <t xml:space="preserve">0.137766391038895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13801734149456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
     <t xml:space="preserve">0.145733758807182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144165381789207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14397719502449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141154080629349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137640923261642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136762619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134629637002945</t>
+    <t xml:space="preserve">0.144165396690369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143977180123329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14115409553051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137640938162804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136762633919716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134629651904106</t>
   </si>
   <si>
     <t xml:space="preserve">0.134002283215523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133437678217888</t>
+    <t xml:space="preserve">0.133437693119049</t>
   </si>
   <si>
     <t xml:space="preserve">0.129673570394516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356143832207</t>
+    <t xml:space="preserve">0.128356128931046</t>
   </si>
   <si>
     <t xml:space="preserve">0.132496640086174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135633423924446</t>
+    <t xml:space="preserve">0.135633409023285</t>
   </si>
   <si>
     <t xml:space="preserve">0.137891873717308</t>
@@ -809,46 +809,46 @@
     <t xml:space="preserve">0.132433906197548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132057502865791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134504184126854</t>
+    <t xml:space="preserve">0.13205748796463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134504169225693</t>
   </si>
   <si>
     <t xml:space="preserve">0.134502410888672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13298973441124</t>
+    <t xml:space="preserve">0.132989719510078</t>
   </si>
   <si>
     <t xml:space="preserve">0.131729155778885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13072070479393</t>
+    <t xml:space="preserve">0.130720719695091</t>
   </si>
   <si>
     <t xml:space="preserve">0.13317883014679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134565427899361</t>
+    <t xml:space="preserve">0.134565442800522</t>
   </si>
   <si>
     <t xml:space="preserve">0.134943619370461</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131792202591896</t>
+    <t xml:space="preserve">0.131792187690735</t>
   </si>
   <si>
     <t xml:space="preserve">0.131477057933807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132359459996223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130909785628319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130468621850014</t>
+    <t xml:space="preserve">0.132359445095062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13090980052948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130468606948853</t>
   </si>
   <si>
     <t xml:space="preserve">0.129964396357536</t>
@@ -860,46 +860,46 @@
     <t xml:space="preserve">0.129586204886436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127002030611038</t>
+    <t xml:space="preserve">0.127002045512199</t>
   </si>
   <si>
     <t xml:space="preserve">0.127947479486465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128199577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128703817725182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371756196022</t>
+    <t xml:space="preserve">0.128199592232704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12870380282402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371771097183</t>
   </si>
   <si>
     <t xml:space="preserve">0.125930562615395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127128109335899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056611537933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12479604780674</t>
+    <t xml:space="preserve">0.127128094434738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056641340256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12479605525732</t>
   </si>
   <si>
     <t xml:space="preserve">0.124669998884201</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124165773391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125174224376678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125237241387367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12901896238327</t>
+    <t xml:space="preserve">0.124165765941143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.12517423927784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125237226486206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129018932580948</t>
   </si>
   <si>
     <t xml:space="preserve">0.127380207180977</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">0.128451690077782</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128136545419693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127884462475777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127443239092827</t>
+    <t xml:space="preserve">0.128136530518532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127884447574615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127443209290504</t>
   </si>
   <si>
     <t xml:space="preserve">0.126939013600349</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">0.128262624144554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126875981688499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126308739185333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133430927991867</t>
+    <t xml:space="preserve">0.126875996589661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126497820019722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126308724284172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133430942893028</t>
   </si>
   <si>
     <t xml:space="preserve">0.135573893785477</t>
@@ -941,25 +941,25 @@
     <t xml:space="preserve">0.135762974619865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136456295847893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135636910796165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134061217308044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132485508918762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133556991815567</t>
+    <t xml:space="preserve">0.136456280946732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135636955499649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134061232209206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132485523819923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133556976914406</t>
   </si>
   <si>
     <t xml:space="preserve">0.135195717215538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136141151189804</t>
+    <t xml:space="preserve">0.136141180992126</t>
   </si>
   <si>
     <t xml:space="preserve">0.134439378976822</t>
@@ -968,31 +968,31 @@
     <t xml:space="preserve">0.137464746832848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137716844677925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138221085071564</t>
+    <t xml:space="preserve">0.137716859579086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138221070170403</t>
   </si>
   <si>
     <t xml:space="preserve">0.137842938303947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136330232024193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13708658516407</t>
+    <t xml:space="preserve">0.136330217123032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137086570262909</t>
   </si>
   <si>
     <t xml:space="preserve">0.13677142560482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136204168200493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135006636381149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134754538536072</t>
+    <t xml:space="preserve">0.136204183101654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135006666183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134754523634911</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
@@ -1001,43 +1001,43 @@
     <t xml:space="preserve">0.137401714920998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151141911745071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153789088129997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152780637145042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151267930865288</t>
+    <t xml:space="preserve">0.15114189684391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153789103031158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152780622243881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151267945766449</t>
   </si>
   <si>
     <t xml:space="preserve">0.145280256867409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14704504609108</t>
+    <t xml:space="preserve">0.147045060992241</t>
   </si>
   <si>
     <t xml:space="preserve">0.157444730401039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159398600459099</t>
+    <t xml:space="preserve">0.159398585557938</t>
   </si>
   <si>
     <t xml:space="preserve">0.156625360250473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157570779323578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15284363925457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152654573321342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151898235082626</t>
+    <t xml:space="preserve">0.157570794224739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152843654155731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152654558420181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151898249983788</t>
   </si>
   <si>
     <t xml:space="preserve">0.15309576690197</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">0.148746818304062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153347864747047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805990099907</t>
+    <t xml:space="preserve">0.15334789454937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805975198746</t>
   </si>
   <si>
     <t xml:space="preserve">0.154419377446175</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156940490007401</t>
+    <t xml:space="preserve">0.156940504908562</t>
   </si>
   <si>
     <t xml:space="preserve">0.159146502614021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167655304074287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170050397515297</t>
+    <t xml:space="preserve">0.16765533387661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170050382614136</t>
   </si>
   <si>
     <t xml:space="preserve">0.16721411049366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.172067284584045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.179945811629295</t>
+    <t xml:space="preserve">0.172067299485207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.179945826530457</t>
   </si>
   <si>
     <t xml:space="preserve">0.178811296820641</t>
@@ -1085,37 +1085,37 @@
     <t xml:space="preserve">0.17521870136261</t>
   </si>
   <si>
-    <t xml:space="preserve">0.174336299300194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170176461338997</t>
+    <t xml:space="preserve">0.174336314201355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170176446437836</t>
   </si>
   <si>
     <t xml:space="preserve">0.176479265093803</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173642978072166</t>
+    <t xml:space="preserve">0.173642992973328</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365527272224</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166205674409866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168222576379776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.168600752949715</t>
+    <t xml:space="preserve">0.166205644607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168222591280937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.168600738048553</t>
   </si>
   <si>
     <t xml:space="preserve">0.166520804166794</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166394725441933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161730647087097</t>
+    <t xml:space="preserve">0.166394755244255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161730632185936</t>
   </si>
   <si>
     <t xml:space="preserve">0.160091906785965</t>
@@ -1124,31 +1124,31 @@
     <t xml:space="preserve">0.156688377261162</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161226436495781</t>
+    <t xml:space="preserve">0.16122642159462</t>
   </si>
   <si>
     <t xml:space="preserve">0.162486985325813</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163747549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873612880707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161037340760231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158011958003044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157759860157967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167970433831215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167718350887299</t>
+    <t xml:space="preserve">0.163747534155846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873597979546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16103732585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158011987805367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157759845256805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167970448732376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167718321084976</t>
   </si>
   <si>
     <t xml:space="preserve">0.165260225534439</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">0.163810580968857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159461632370949</t>
+    <t xml:space="preserve">0.159461617469788</t>
   </si>
   <si>
     <t xml:space="preserve">0.147675335407257</t>
@@ -1172,43 +1172,43 @@
     <t xml:space="preserve">0.150007382035255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150448590517044</t>
+    <t xml:space="preserve">0.150448560714722</t>
   </si>
   <si>
     <t xml:space="preserve">0.150511607527733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151078879833221</t>
+    <t xml:space="preserve">0.151078835129738</t>
   </si>
   <si>
     <t xml:space="preserve">0.151646122336388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150322526693344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148494690656662</t>
+    <t xml:space="preserve">0.150322496891022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148494705557823</t>
   </si>
   <si>
     <t xml:space="preserve">0.150826752185822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.151772156357765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149881318211555</t>
+    <t xml:space="preserve">0.151772171258926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149881333112717</t>
   </si>
   <si>
     <t xml:space="preserve">0.151583090424538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149629205465317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151709139347076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151015847921371</t>
+    <t xml:space="preserve">0.149629220366478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151709124445915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15101583302021</t>
   </si>
   <si>
     <t xml:space="preserve">0.148935914039612</t>
@@ -1220,52 +1220,52 @@
     <t xml:space="preserve">0.15076370537281</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150637686252594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151204884052277</t>
+    <t xml:space="preserve">0.150637656450272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151204913854599</t>
   </si>
   <si>
     <t xml:space="preserve">0.149944365024567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152213394641876</t>
+    <t xml:space="preserve">0.152213349938393</t>
   </si>
   <si>
     <t xml:space="preserve">0.152528509497643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149377107620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157255634665489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156310215592384</t>
+    <t xml:space="preserve">0.149377092719078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15725564956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156310200691223</t>
   </si>
   <si>
     <t xml:space="preserve">0.164503887295723</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163243323564529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162613034248352</t>
+    <t xml:space="preserve">0.163243353366852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162613049149513</t>
   </si>
   <si>
     <t xml:space="preserve">0.161982759833336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163558468222618</t>
+    <t xml:space="preserve">0.163558483123779</t>
   </si>
   <si>
     <t xml:space="preserve">0.165764465928078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165449306368828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079595685005</t>
+    <t xml:space="preserve">0.165449321269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079610586166</t>
   </si>
   <si>
     <t xml:space="preserve">0.160722196102142</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">0.149061962962151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147171124815941</t>
+    <t xml:space="preserve">0.147171095013618</t>
   </si>
   <si>
     <t xml:space="preserve">0.146540805697441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146225675940514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142759129405022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144334837794304</t>
+    <t xml:space="preserve">0.146225661039352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14275911450386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144334822893143</t>
   </si>
   <si>
     <t xml:space="preserve">0.140238001942635</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">0.139607712626457</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138032004237175</t>
+    <t xml:space="preserve">0.138031989336014</t>
   </si>
   <si>
     <t xml:space="preserve">0.139922857284546</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">0.138347148895264</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141498565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813710331917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140553131699562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141183406114578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138662293553352</t>
+    <t xml:space="preserve">0.141498550772667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813695430756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140553146600723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141183421015739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138662278652191</t>
   </si>
   <si>
     <t xml:space="preserve">0.135510876774788</t>
@@ -1331,79 +1331,82 @@
     <t xml:space="preserve">0.134250313043594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133935153484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132674619555473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14307427406311</t>
+    <t xml:space="preserve">0.133935168385506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132674589753151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143074259161949</t>
   </si>
   <si>
     <t xml:space="preserve">0.14496511220932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
+    <t xml:space="preserve">0.143389403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443969845772</t>
   </si>
   <si>
     <t xml:space="preserve">0.146575838327408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147864431142807</t>
+    <t xml:space="preserve">0.147864416241646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144965097308159</t>
   </si>
   <si>
     <t xml:space="preserve">0.146253690123558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14560940861702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140455067157745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142710089683533</t>
+    <t xml:space="preserve">0.145609393715858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140455082058907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142710104584694</t>
   </si>
   <si>
     <t xml:space="preserve">0.141421541571617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13916651904583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
+    <t xml:space="preserve">0.139166533946991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777215361595</t>
   </si>
   <si>
     <t xml:space="preserve">0.139488652348518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135622918605804</t>
+    <t xml:space="preserve">0.135622903704643</t>
   </si>
   <si>
     <t xml:space="preserve">0.133690059185028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132723614573479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13207933306694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129824310541153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125765293836594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124992147088051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126796156167984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129180014133453</t>
+    <t xml:space="preserve">0.132723599672318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132079318165779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129824325442314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125765278935432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124992154538631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126796141266823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129180043935776</t>
   </si>
   <si>
     <t xml:space="preserve">0.133367910981178</t>
@@ -1412,19 +1415,16 @@
     <t xml:space="preserve">0.131757184863091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125894159078598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126925021409988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125378713011742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128600150346756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130468606948853</t>
+    <t xml:space="preserve">0.125894144177437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126925006508827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125378727912903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128600165247917</t>
   </si>
   <si>
     <t xml:space="preserve">0.127440452575684</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">0.127955883741379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127827018499374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126023024320602</t>
+    <t xml:space="preserve">0.127827033400536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126023009419441</t>
   </si>
   <si>
     <t xml:space="preserve">0.124347850680351</t>
@@ -1448,22 +1448,22 @@
     <t xml:space="preserve">0.127311587333679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.127569288015366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12666729092598</t>
+    <t xml:space="preserve">0.127569302916527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126667305827141</t>
   </si>
   <si>
     <t xml:space="preserve">0.126538440585136</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128729030489922</t>
+    <t xml:space="preserve">0.12872901558876</t>
   </si>
   <si>
     <t xml:space="preserve">0.12834244966507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129502177238464</t>
+    <t xml:space="preserve">0.129502192139626</t>
   </si>
   <si>
     <t xml:space="preserve">0.130146458745003</t>
@@ -1472,16 +1472,16 @@
     <t xml:space="preserve">0.134012207388878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134656488895416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138522207736969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13820007443428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135300770401955</t>
+    <t xml:space="preserve">0.134656473994255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138522237539291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138200059533119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135300755500793</t>
   </si>
   <si>
     <t xml:space="preserve">0.130790755152702</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">0.128084734082222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128857880830765</t>
+    <t xml:space="preserve">0.128857895731926</t>
   </si>
   <si>
     <t xml:space="preserve">0.125249862670898</t>
@@ -1499,7 +1499,7 @@
     <t xml:space="preserve">0.122157283127308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12331698089838</t>
+    <t xml:space="preserve">0.123316988348961</t>
   </si>
   <si>
     <t xml:space="preserve">0.125507578253746</t>
@@ -1514,16 +1514,16 @@
     <t xml:space="preserve">0.127182722091675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125636413693428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12048214673996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12228611856699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122414998710155</t>
+    <t xml:space="preserve">0.125636428594589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.120482102036476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122286133468151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122414983808994</t>
   </si>
   <si>
     <t xml:space="preserve">0.117260657250881</t>
@@ -1532,40 +1532,40 @@
     <t xml:space="preserve">0.113266065716743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113394930958748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111848644912243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11210636049509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114425785839558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114683508872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112235210835934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110817775130272</t>
+    <t xml:space="preserve">0.113394938409328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111848630011082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11210635304451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114425800740719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114683516323566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112235218286514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110817797482014</t>
   </si>
   <si>
     <t xml:space="preserve">0.108240611851215</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106565460562706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105921179056168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10192658752203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10501916706562</t>
+    <t xml:space="preserve">0.106565453112125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105921171605587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101926580071449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105019189417362</t>
   </si>
   <si>
     <t xml:space="preserve">0.103086292743683</t>
@@ -1574,46 +1574,46 @@
     <t xml:space="preserve">0.104374893009663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104117169976234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105663456022739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10798291862011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108627177774906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108111754059792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11146205663681</t>
+    <t xml:space="preserve">0.104117162525654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10566346347332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107982903718948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108627192676067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108111761510372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11146204918623</t>
   </si>
   <si>
     <t xml:space="preserve">0.112750649452209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10875603556633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110173501074314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109529189765453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106952041387558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101153433322906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10398830473423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102699726819992</t>
+    <t xml:space="preserve">0.108756050467491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110173508524895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109529197216034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106952033936977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101153440773487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103988312184811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102699719369411</t>
   </si>
   <si>
     <t xml:space="preserve">0.105276882648468</t>
@@ -1622,13 +1622,13 @@
     <t xml:space="preserve">0.111204348504543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.115585513412952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1158432289958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115327797830105</t>
+    <t xml:space="preserve">0.115585535764694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115843214094639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115327812731266</t>
   </si>
   <si>
     <t xml:space="preserve">0.113008365035057</t>
@@ -1640,88 +1640,88 @@
     <t xml:space="preserve">0.11043119430542</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107854045927525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103730596601963</t>
+    <t xml:space="preserve">0.107854031026363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103730604052544</t>
   </si>
   <si>
     <t xml:space="preserve">0.10630775988102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103859454393387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554651081562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109142638742924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109013758599758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108884915709496</t>
+    <t xml:space="preserve">0.103859439492226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554658532143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109142631292343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109013773500919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108884908258915</t>
   </si>
   <si>
     <t xml:space="preserve">0.109271474182606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10733862221241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102442018687725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101411163806915</t>
+    <t xml:space="preserve">0.107338614761829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102442003786564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101411156356335</t>
   </si>
   <si>
     <t xml:space="preserve">0.102055437862873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.100251443684101</t>
+    <t xml:space="preserve">0.100251436233521</t>
   </si>
   <si>
     <t xml:space="preserve">0.0999937206506729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101282298564911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101797737181187</t>
+    <t xml:space="preserve">0.10128229111433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101797744631767</t>
   </si>
   <si>
     <t xml:space="preserve">0.100766867399216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105148024857044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109915778040886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111075513064861</t>
+    <t xml:space="preserve">0.105148039758205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109915763139725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111075475811958</t>
   </si>
   <si>
     <t xml:space="preserve">0.112621784210205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110302336513996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110688909888268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104761444032192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105534598231316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107467480003834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108498342335224</t>
+    <t xml:space="preserve">0.110302366316319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110688924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104761458933353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105534613132477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107467465102673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108498327434063</t>
   </si>
   <si>
     <t xml:space="preserve">0.107080891728401</t>
@@ -1730,58 +1730,58 @@
     <t xml:space="preserve">0.104503735899925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.105792313814163</t>
+    <t xml:space="preserve">0.105792328715324</t>
   </si>
   <si>
     <t xml:space="preserve">0.106436595320702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10534130781889</t>
+    <t xml:space="preserve">0.10534131526947</t>
   </si>
   <si>
     <t xml:space="preserve">0.107596330344677</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108562767505646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109207034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11018505692482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109857141971588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111168846487999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110513001680374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107889540493488</t>
+    <t xml:space="preserve">0.108562760055065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109207041561604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110185071825981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109857134521008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11116885393858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110512994229794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107889547944069</t>
   </si>
   <si>
     <t xml:space="preserve">0.10690575838089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.10592196136713</t>
+    <t xml:space="preserve">0.105921968817711</t>
   </si>
   <si>
     <t xml:space="preserve">0.10395435988903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104282282292843</t>
+    <t xml:space="preserve">0.104282289743423</t>
   </si>
   <si>
     <t xml:space="preserve">0.105594024062157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108217477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105266101658344</t>
+    <t xml:space="preserve">0.108217485249043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105266094207764</t>
   </si>
   <si>
     <t xml:space="preserve">0.10493815690279</t>
@@ -1790,61 +1790,61 @@
     <t xml:space="preserve">0.102970570325851</t>
   </si>
   <si>
-    <t xml:space="preserve">0.103626430034637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103298500180244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101658843457699</t>
+    <t xml:space="preserve">0.103626444935799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103298515081406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101658836007118</t>
   </si>
   <si>
     <t xml:space="preserve">0.100347101688385</t>
   </si>
   <si>
-    <t xml:space="preserve">0.101330906152725</t>
+    <t xml:space="preserve">0.101330913603306</t>
   </si>
   <si>
     <t xml:space="preserve">0.097067803144455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.097723662853241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.097395732998848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0951002091169357</t>
+    <t xml:space="preserve">0.0977236554026604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0973957180976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0951002016663551</t>
   </si>
   <si>
     <t xml:space="preserve">0.0980515852570534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0964119285345078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0987074449658394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0993633270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100019194185734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101002968847752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100675046443939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102642618119717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0983795300126076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0996912345290184</t>
+    <t xml:space="preserve">0.0964119210839272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09870745241642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.099363312125206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100019179284573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101002976298332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100675038993359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102642633020878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0983795151114464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0996912494301796</t>
   </si>
   <si>
     <t xml:space="preserve">0.099035382270813</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">0.104610219597816</t>
   </si>
   <si>
-    <t xml:space="preserve">0.107561618089676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108873330056667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108545415103436</t>
+    <t xml:space="preserve">0.107561610639095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108873337507248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108545407652855</t>
   </si>
   <si>
     <t xml:space="preserve">0.109201274812222</t>
@@ -1871,16 +1871,16 @@
     <t xml:space="preserve">0.106249891221523</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11215265840292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114448174834251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111824721097946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112808518111706</t>
+    <t xml:space="preserve">0.1121526658535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114448182284832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111824728548527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112808525562286</t>
   </si>
   <si>
     <t xml:space="preserve">0.113136447966099</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">0.111496791243553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130516827106476</t>
+    <t xml:space="preserve">0.130516842007637</t>
   </si>
   <si>
     <t xml:space="preserve">0.139698937535286</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">0.160686552524567</t>
   </si>
   <si>
-    <t xml:space="preserve">0.173803821206093</t>
+    <t xml:space="preserve">0.173803806304932</t>
   </si>
   <si>
     <t xml:space="preserve">0.16724519431591</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">0.155439645051956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150848612189293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.154127925634384</t>
+    <t xml:space="preserve">0.150848597288132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.154127910733223</t>
   </si>
   <si>
     <t xml:space="preserve">0.157407239079475</t>
@@ -1928,28 +1928,28 @@
     <t xml:space="preserve">0.156751364469528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152816191315651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.148881003260612</t>
+    <t xml:space="preserve">0.15281617641449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148881018161774</t>
   </si>
   <si>
     <t xml:space="preserve">0.145601689815521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146257549524307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146913409233093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150192752480507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149536892771721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142978221178055</t>
+    <t xml:space="preserve">0.146257564425468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146913424134254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150192737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.14953687787056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142978250980377</t>
   </si>
   <si>
     <t xml:space="preserve">0.147569268941879</t>
@@ -1958,79 +1958,79 @@
     <t xml:space="preserve">0.148225143551826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162654146552086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161342442035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141666531562805</t>
+    <t xml:space="preserve">0.162654131650925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161342427134514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141666516661644</t>
   </si>
   <si>
     <t xml:space="preserve">0.139043062925339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135107859969139</t>
+    <t xml:space="preserve">0.1351078748703</t>
   </si>
   <si>
     <t xml:space="preserve">0.133140295743942</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137731343507767</t>
+    <t xml:space="preserve">0.137731328606606</t>
   </si>
   <si>
     <t xml:space="preserve">0.154783770442009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156095504760742</t>
+    <t xml:space="preserve">0.156095489859581</t>
   </si>
   <si>
     <t xml:space="preserve">0.153472051024437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13182857632637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135763734579086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137075453996658</t>
+    <t xml:space="preserve">0.131828561425209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135763749480247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13707546889782</t>
   </si>
   <si>
     <t xml:space="preserve">0.125597849488258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126581639051437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.123958192765713</t>
+    <t xml:space="preserve">0.126581653952599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123958185315132</t>
   </si>
   <si>
     <t xml:space="preserve">0.118711292743683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110840931534767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0967398583889008</t>
+    <t xml:space="preserve">0.110840924084187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0967398509383202</t>
   </si>
   <si>
     <t xml:space="preserve">0.0826388001441956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.087885707616806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0872298404574394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0885415822267532</t>
+    <t xml:space="preserve">0.0878857150673866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.08722984790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0885415747761726</t>
   </si>
   <si>
     <t xml:space="preserve">0.0911650285124779</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0918208956718445</t>
+    <t xml:space="preserve">0.0918208882212639</t>
   </si>
   <si>
     <t xml:space="preserve">0.0928046852350235</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">0.0931326150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0957560613751411</t>
+    <t xml:space="preserve">0.0957560688257217</t>
   </si>
   <si>
     <t xml:space="preserve">0.0937884822487831</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">0.0969366282224655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0978548228740692</t>
+    <t xml:space="preserve">0.0978548303246498</t>
   </si>
   <si>
     <t xml:space="preserve">0.0971989706158638</t>
@@ -2069,22 +2069,22 @@
     <t xml:space="preserve">0.0940508246421814</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0939196422696114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0941819995641708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0949690341949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0954937115311623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0982483476400375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100740626454353</t>
+    <t xml:space="preserve">0.093919649720192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0941819921135902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0949690192937851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0954937264323235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0982483550906181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100740641355515</t>
   </si>
   <si>
     <t xml:space="preserve">0.0968054458498955</t>
@@ -2093,16 +2093,16 @@
     <t xml:space="preserve">0.0966742783784866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110709749162197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0979859903454781</t>
+    <t xml:space="preserve">0.110709756612778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0979859977960587</t>
   </si>
   <si>
     <t xml:space="preserve">0.0991665571928024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0936573073267937</t>
+    <t xml:space="preserve">0.0936573147773743</t>
   </si>
   <si>
     <t xml:space="preserve">0.0948378592729568</t>
@@ -2111,49 +2111,49 @@
     <t xml:space="preserve">0.100084774196148</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102183520793915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0999535992741585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103232905268669</t>
+    <t xml:space="preserve">0.102183528244495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0999535843729973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10323292016983</t>
   </si>
   <si>
     <t xml:space="preserve">0.104806981980801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140354782342911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125925794243813</t>
+    <t xml:space="preserve">0.14035476744175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125925779342651</t>
   </si>
   <si>
     <t xml:space="preserve">0.138387188315392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14232237637043</t>
+    <t xml:space="preserve">0.142322361469269</t>
   </si>
   <si>
     <t xml:space="preserve">0.137403398752213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135435804724693</t>
+    <t xml:space="preserve">0.135435819625854</t>
   </si>
   <si>
     <t xml:space="preserve">0.136419609189034</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134452015161514</t>
+    <t xml:space="preserve">0.134452000260353</t>
   </si>
   <si>
     <t xml:space="preserve">0.134124085307121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131041526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127893388271332</t>
+    <t xml:space="preserve">0.131041511893272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127893358469009</t>
   </si>
   <si>
     <t xml:space="preserve">0.134779945015907</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">0.131172701716423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130779176950455</t>
+    <t xml:space="preserve">0.130779162049294</t>
   </si>
   <si>
     <t xml:space="preserve">0.130123317241669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129336297512054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130385652184486</t>
+    <t xml:space="preserve">0.129336267709732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130385667085648</t>
   </si>
   <si>
     <t xml:space="preserve">0.131500616669655</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">0.133468225598335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129992142319679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126975163817406</t>
+    <t xml:space="preserve">0.129992127418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126975178718567</t>
   </si>
   <si>
     <t xml:space="preserve">0.127631038427353</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">0.128549247980118</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133796140551567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132156491279602</t>
+    <t xml:space="preserve">0.133796170353889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132156506180763</t>
   </si>
   <si>
     <t xml:space="preserve">0.130648016929626</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">0.129205107688904</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129598632454872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140026852488518</t>
+    <t xml:space="preserve">0.129598617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140026867389679</t>
   </si>
   <si>
     <t xml:space="preserve">0.129729807376862</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">0.12986096739769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130254477262497</t>
+    <t xml:space="preserve">0.130254492163658</t>
   </si>
   <si>
     <t xml:space="preserve">0.129073917865753</t>
@@ -2228,10 +2228,10 @@
     <t xml:space="preserve">0.125138759613037</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124614074826241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143634095788002</t>
+    <t xml:space="preserve">0.12461406737566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143634080886841</t>
   </si>
   <si>
     <t xml:space="preserve">0.143962040543556</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">0.139370992779732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136091664433479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138059258460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136747524142265</t>
+    <t xml:space="preserve">0.136091679334641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13805927336216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136747539043427</t>
   </si>
   <si>
     <t xml:space="preserve">0.140682712197304</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">0.144945830106735</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142650306224823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141994461417198</t>
+    <t xml:space="preserve">0.142650321125984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141994446516037</t>
   </si>
   <si>
     <t xml:space="preserve">0.144289970397949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153799995779991</t>
+    <t xml:space="preserve">0.15379998087883</t>
   </si>
   <si>
     <t xml:space="preserve">0.152488261461258</t>
@@ -2276,19 +2276,19 @@
     <t xml:space="preserve">0.152160316705704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153144136071205</t>
+    <t xml:space="preserve">0.153144121170044</t>
   </si>
   <si>
     <t xml:space="preserve">0.155111715197563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155767574906349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160358622670174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159702762961388</t>
+    <t xml:space="preserve">0.155767560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160358637571335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159702748060226</t>
   </si>
   <si>
     <t xml:space="preserve">0.16298209130764</t>
@@ -2297,19 +2297,19 @@
     <t xml:space="preserve">0.166917249560356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163310006260872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162326201796532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16101448237896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159046903252602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159374818205833</t>
+    <t xml:space="preserve">0.163310021162033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162326216697693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161014497280121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15904688835144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159374833106995</t>
   </si>
   <si>
     <t xml:space="preserve">0.158718958497047</t>
@@ -2321,64 +2321,64 @@
     <t xml:space="preserve">0.160030692815781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1580630838871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165341451764107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163571193814278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162863090634346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.16250903904438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161092832684517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158614471554756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157198280096054</t>
+    <t xml:space="preserve">0.158063098788261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165341436862946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163571178913116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162863075733185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162509024143219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161092847585678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158614486455917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157198294997215</t>
   </si>
   <si>
     <t xml:space="preserve">0.158260434865952</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162155002355576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158968523144722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160384729504585</t>
+    <t xml:space="preserve">0.162154987454414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158968538045883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160384744405746</t>
   </si>
   <si>
     <t xml:space="preserve">0.159322574734688</t>
   </si>
   <si>
-    <t xml:space="preserve">0.15755233168602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161800935864449</t>
+    <t xml:space="preserve">0.157552346587181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161800920963287</t>
   </si>
   <si>
     <t xml:space="preserve">0.155073970556259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.153303742408752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155782088637352</t>
+    <t xml:space="preserve">0.153303727507591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155782073736191</t>
   </si>
   <si>
     <t xml:space="preserve">0.151533484458923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152595609426498</t>
+    <t xml:space="preserve">0.15259562432766</t>
   </si>
   <si>
     <t xml:space="preserve">0.154719933867455</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">0.155428037047386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156844228506088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156490176916122</t>
+    <t xml:space="preserve">0.156844243407249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156490162014961</t>
   </si>
   <si>
     <t xml:space="preserve">0.153657779097557</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">0.156136125326157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152241587638855</t>
+    <t xml:space="preserve">0.152241572737694</t>
   </si>
   <si>
     <t xml:space="preserve">0.154365867376328</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">0.150825396180153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149763241410255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150471329689026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.149055123329163</t>
+    <t xml:space="preserve">0.149763226509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150471344590187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.149055138230324</t>
   </si>
   <si>
     <t xml:space="preserve">0.146222725510597</t>
@@ -2438,19 +2438,19 @@
     <t xml:space="preserve">0.1426822245121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143390312790871</t>
+    <t xml:space="preserve">0.143390327692032</t>
   </si>
   <si>
     <t xml:space="preserve">0.145514622330666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148347020149231</t>
+    <t xml:space="preserve">0.148347049951553</t>
   </si>
   <si>
     <t xml:space="preserve">0.149409174919128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152949705719948</t>
+    <t xml:space="preserve">0.152949690818787</t>
   </si>
   <si>
     <t xml:space="preserve">0.1451605707407</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">0.148701086640358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146576777100563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144452467560768</t>
+    <t xml:space="preserve">0.146576792001724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144452482461929</t>
   </si>
   <si>
     <t xml:space="preserve">0.143744379281998</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">0.144806534051895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144098430871964</t>
+    <t xml:space="preserve">0.144098445773125</t>
   </si>
   <si>
     <t xml:space="preserve">0.14586865901947</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">0.168527886271477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167111679911613</t>
+    <t xml:space="preserve">0.167111694812775</t>
   </si>
   <si>
     <t xml:space="preserve">0.16746574640274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.16498738527298</t>
+    <t xml:space="preserve">0.164987370371819</t>
   </si>
   <si>
     <t xml:space="preserve">0.163217127323151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.164358541369438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162075772881508</t>
+    <t xml:space="preserve">0.164358526468277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162075757980347</t>
   </si>
   <si>
     <t xml:space="preserve">0.16778264939785</t>
@@ -2513,16 +2513,16 @@
     <t xml:space="preserve">0.167021736502647</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161695301532745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161314830183983</t>
+    <t xml:space="preserve">0.161695286631584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.161314845085144</t>
   </si>
   <si>
     <t xml:space="preserve">0.159793004393578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163978040218353</t>
+    <t xml:space="preserve">0.163978055119514</t>
   </si>
   <si>
     <t xml:space="preserve">0.16055391728878</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">0.160934388637543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162836685776711</t>
+    <t xml:space="preserve">0.162836670875549</t>
   </si>
   <si>
     <t xml:space="preserve">0.165119424462318</t>
@@ -2549,25 +2549,25 @@
     <t xml:space="preserve">0.159032076597214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.159412533044815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160173460841179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.165880337357521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17044585943222</t>
+    <t xml:space="preserve">0.159412547945976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.160173445940018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.165880352258682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170445874333382</t>
   </si>
   <si>
     <t xml:space="preserve">0.169684946537018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.170826315879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.171967700123787</t>
+    <t xml:space="preserve">0.170826330780983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.171967715024948</t>
   </si>
   <si>
     <t xml:space="preserve">0.170065402984619</t>
@@ -2576,10 +2576,10 @@
     <t xml:space="preserve">0.157129779458046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157890692353249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153705656528473</t>
+    <t xml:space="preserve">0.15789070725441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153705641627312</t>
   </si>
   <si>
     <t xml:space="preserve">0.14427025616169</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">0.155227482318878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155988395214081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157510250806808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.164738982915878</t>
+    <t xml:space="preserve">0.155988410115242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157510235905647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.164738968014717</t>
   </si>
   <si>
     <t xml:space="preserve">0.166260808706284</t>
@@ -19186,7 +19186,7 @@
         <v>0.224999994039536</v>
       </c>
       <c r="G596" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -19212,7 +19212,7 @@
         <v>0.226999998092651</v>
       </c>
       <c r="G597" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -19238,7 +19238,7 @@
         <v>0.225999996066093</v>
       </c>
       <c r="G598" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -19264,7 +19264,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G599" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -19290,7 +19290,7 @@
         <v>0.221499994397163</v>
       </c>
       <c r="G600" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -19316,7 +19316,7 @@
         <v>0.217999994754791</v>
       </c>
       <c r="G601" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -19342,7 +19342,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G602" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -19368,7 +19368,7 @@
         <v>0.216000005602837</v>
       </c>
       <c r="G603" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -19394,7 +19394,7 @@
         <v>0.218500003218651</v>
       </c>
       <c r="G604" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -19420,7 +19420,7 @@
         <v>0.219500005245209</v>
       </c>
       <c r="G605" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -19446,7 +19446,7 @@
         <v>0.216499999165535</v>
       </c>
       <c r="G606" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -19472,7 +19472,7 @@
         <v>0.210500001907349</v>
       </c>
       <c r="G607" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -19498,7 +19498,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G608" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19524,7 +19524,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G609" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19550,7 +19550,7 @@
         <v>0.206000000238419</v>
       </c>
       <c r="G610" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19576,7 +19576,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G611" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19602,7 +19602,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G612" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19628,7 +19628,7 @@
         <v>0.195199996232986</v>
       </c>
       <c r="G613" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19654,7 +19654,7 @@
         <v>0.194000005722046</v>
       </c>
       <c r="G614" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19680,7 +19680,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G615" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19706,7 +19706,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G616" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19732,7 +19732,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G617" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19758,7 +19758,7 @@
         <v>0.204500004649162</v>
       </c>
       <c r="G618" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19784,7 +19784,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G619" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19810,7 +19810,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G620" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19836,7 +19836,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G621" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19862,7 +19862,7 @@
         <v>0.194600000977516</v>
       </c>
       <c r="G622" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19888,7 +19888,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G623" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19914,7 +19914,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G624" t="s">
-        <v>470</v>
+        <v>278</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19940,7 +19940,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G625" t="s">
-        <v>470</v>
+        <v>278</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19966,7 +19966,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G626" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19992,7 +19992,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G627" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -20044,7 +20044,7 @@
         <v>0.196799993515015</v>
       </c>
       <c r="G629" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -20096,7 +20096,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G631" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -20330,7 +20330,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G640" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20460,7 +20460,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G645" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20642,7 +20642,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G652" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20694,7 +20694,7 @@
         <v>0.202500000596046</v>
       </c>
       <c r="G654" t="s">
-        <v>470</v>
+        <v>278</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20746,7 +20746,7 @@
         <v>0.207499995827675</v>
       </c>
       <c r="G656" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20902,7 +20902,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G662" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20954,7 +20954,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G664" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20980,7 +20980,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G665" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -21006,7 +21006,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G666" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -21188,7 +21188,7 @@
         <v>0.200499996542931</v>
       </c>
       <c r="G673" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -21240,7 +21240,7 @@
         <v>0.207000002264977</v>
       </c>
       <c r="G675" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -21266,7 +21266,7 @@
         <v>0.204999998211861</v>
       </c>
       <c r="G676" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -21552,7 +21552,7 @@
         <v>0.201499998569489</v>
       </c>
       <c r="G687" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21604,7 +21604,7 @@
         <v>0.196999996900558</v>
       </c>
       <c r="G689" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21708,7 +21708,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G693" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21734,7 +21734,7 @@
         <v>0.199599996209145</v>
       </c>
       <c r="G694" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21838,7 +21838,7 @@
         <v>0.19539999961853</v>
       </c>
       <c r="G698" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -70518,7 +70518,7 @@
     </row>
     <row r="2571">
       <c r="A2571" s="1" t="n">
-        <v>46065.6912731481</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2571" t="n">
         <v>250089</v>
@@ -70527,7 +70527,7 @@
         <v>0.172499999403954</v>
       </c>
       <c r="D2571" t="n">
-        <v>0.171000003814697</v>
+        <v>0.170000001788139</v>
       </c>
       <c r="E2571" t="n">
         <v>0.171000003814697</v>
@@ -70539,6 +70539,32 @@
         <v>1074</v>
       </c>
       <c r="H2571" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2572">
+      <c r="A2572" s="1" t="n">
+        <v>46066.6909837963</v>
+      </c>
+      <c r="B2572" t="n">
+        <v>355198</v>
+      </c>
+      <c r="C2572" t="n">
+        <v>0.171499997377396</v>
+      </c>
+      <c r="D2572" t="n">
+        <v>0.16949999332428</v>
+      </c>
+      <c r="E2572" t="n">
+        <v>0.171000003814697</v>
+      </c>
+      <c r="F2572" t="n">
+        <v>0.170000001788139</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>1074</v>
+      </c>
+      <c r="H2572" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PRO.MI.xlsx
+++ b/data/PRO.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.158481404185295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.155000299215317</t>
+    <t xml:space="preserve">0.155000314116478</t>
   </si>
   <si>
     <t xml:space="preserve">0.153229221701622</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">0.150542065501213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148099184036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15029776096344</t>
+    <t xml:space="preserve">0.148099198937416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150297775864601</t>
   </si>
   <si>
     <t xml:space="preserve">0.151580274105072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.14736633002758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142358407378197</t>
+    <t xml:space="preserve">0.147366315126419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142358437180519</t>
   </si>
   <si>
     <t xml:space="preserve">0.132831215858459</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">0.125319391489029</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131121203303337</t>
+    <t xml:space="preserve">0.131121218204498</t>
   </si>
   <si>
     <t xml:space="preserve">0.134358018636703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134419113397598</t>
+    <t xml:space="preserve">0.134419098496437</t>
   </si>
   <si>
     <t xml:space="preserve">0.143335580825806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138022318482399</t>
+    <t xml:space="preserve">0.13802233338356</t>
   </si>
   <si>
     <t xml:space="preserve">0.137778043746948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140465185046196</t>
+    <t xml:space="preserve">0.140465199947357</t>
   </si>
   <si>
     <t xml:space="preserve">0.139854490756989</t>
@@ -107,49 +107,49 @@
     <t xml:space="preserve">0.136190176010132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131793007254601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129166930913925</t>
+    <t xml:space="preserve">0.131792992353439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129166916012764</t>
   </si>
   <si>
     <t xml:space="preserve">0.129289075732231</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118967920541763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.122754387557507</t>
+    <t xml:space="preserve">0.118967935442924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.122754365205765</t>
   </si>
   <si>
     <t xml:space="preserve">0.116158619523048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.11847934871912</t>
+    <t xml:space="preserve">0.118479333817959</t>
   </si>
   <si>
     <t xml:space="preserve">0.125807970762253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125197231769562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129960834980011</t>
+    <t xml:space="preserve">0.125197261571884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129960849881172</t>
   </si>
   <si>
     <t xml:space="preserve">0.127029404044151</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125014036893845</t>
+    <t xml:space="preserve">0.125014021992683</t>
   </si>
   <si>
     <t xml:space="preserve">0.130999073386192</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12910583615303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128617286682129</t>
+    <t xml:space="preserve">0.129105851054192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128617271780968</t>
   </si>
   <si>
     <t xml:space="preserve">0.130205139517784</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">0.13051050901413</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129533335566521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133808389306068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138755187392235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139671266078949</t>
+    <t xml:space="preserve">0.129533365368843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133808374404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138755172491074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139671251177788</t>
   </si>
   <si>
     <t xml:space="preserve">0.136739820241928</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">0.136495545506477</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140159830451012</t>
+    <t xml:space="preserve">0.140159860253334</t>
   </si>
   <si>
     <t xml:space="preserve">0.141747713088989</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">0.149015262722969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.146572396159172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14571738243103</t>
+    <t xml:space="preserve">0.146572381258011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.145717367529869</t>
   </si>
   <si>
     <t xml:space="preserve">0.1432134360075</t>
@@ -200,22 +200,22 @@
     <t xml:space="preserve">0.144129514694214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140892699360847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139793410897255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134968772530556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136068046092987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13594588637352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135823741555214</t>
+    <t xml:space="preserve">0.140892714262009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139793425798416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134968742728233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136068031191826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135945871472359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135823756456375</t>
   </si>
   <si>
     <t xml:space="preserve">0.133136585354805</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">0.130693718791008</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128861546516418</t>
+    <t xml:space="preserve">0.128861576318741</t>
   </si>
   <si>
     <t xml:space="preserve">0.125258311629295</t>
@@ -236,79 +236,79 @@
     <t xml:space="preserve">0.137472674250603</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142480581998825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142114162445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141320198774338</t>
+    <t xml:space="preserve">0.142480567097664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142114147543907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141320213675499</t>
   </si>
   <si>
     <t xml:space="preserve">0.142175227403641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138327687978745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142236292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1382055580616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140526741743088</t>
+    <t xml:space="preserve">0.138327702879906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142236277461052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138205543160439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140526756644249</t>
   </si>
   <si>
     <t xml:space="preserve">0.139899402856827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136135280132294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136637166142464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133876815438271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133814081549644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132998511195183</t>
+    <t xml:space="preserve">0.136135295033455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136637181043625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133876830339432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133814096450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132998526096344</t>
   </si>
   <si>
     <t xml:space="preserve">0.129234418272972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128732576966286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12515664100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126662284135818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126725003123283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127352356910706</t>
+    <t xml:space="preserve">0.128732517361641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125156626105309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126662269234657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126725032925606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127352371811867</t>
   </si>
   <si>
     <t xml:space="preserve">0.127979710698128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126599535346031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127916976809502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130489125847816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131743833422661</t>
+    <t xml:space="preserve">0.126599565148354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127916991710663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130489140748978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1317438185215</t>
   </si>
   <si>
     <t xml:space="preserve">0.131116464734077</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">0.13155560195446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13406503200531</t>
+    <t xml:space="preserve">0.134065046906471</t>
   </si>
   <si>
     <t xml:space="preserve">0.131179198622704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.133688598871231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134880587458611</t>
+    <t xml:space="preserve">0.133688628673553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134880572557449</t>
   </si>
   <si>
     <t xml:space="preserve">0.134190484881401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130614593625069</t>
+    <t xml:space="preserve">0.130614578723907</t>
   </si>
   <si>
     <t xml:space="preserve">0.132873058319092</t>
@@ -341,112 +341,112 @@
     <t xml:space="preserve">0.128481581807137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121078841388226</t>
+    <t xml:space="preserve">0.121078863739967</t>
   </si>
   <si>
     <t xml:space="preserve">0.120200552046299</t>
   </si>
   <si>
-    <t xml:space="preserve">0.121831655502319</t>
+    <t xml:space="preserve">0.121831670403481</t>
   </si>
   <si>
     <t xml:space="preserve">0.110413856804371</t>
   </si>
   <si>
-    <t xml:space="preserve">0.112233206629753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114366203546524</t>
+    <t xml:space="preserve">0.112233184278011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114366196095943</t>
   </si>
   <si>
     <t xml:space="preserve">0.111794054508209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114052511751652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105395048856735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104893185198307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111041232943535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107904464006424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111354902386665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110727533698082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107277110219002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102822937071323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100501723587513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107716247439384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110790267586708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.114554390311241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112923294305801</t>
+    <t xml:space="preserve">0.114052496850491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105395056307316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104893177747726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111041218042374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107904478907585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111354887485504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110727548599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107277132570744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102822907269001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.100501708686352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107716254889965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11079028993845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.114554397761822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112923286855221</t>
   </si>
   <si>
     <t xml:space="preserve">0.114303447306156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118632167577744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11656192690134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11637369543314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11574637144804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115432687103748</t>
+    <t xml:space="preserve">0.118632182478905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116561912000179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.116373710334301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115746356546879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115432679653168</t>
   </si>
   <si>
     <t xml:space="preserve">0.114805333316326</t>
   </si>
   <si>
-    <t xml:space="preserve">0.116185523569584</t>
+    <t xml:space="preserve">0.116185508668423</t>
   </si>
   <si>
     <t xml:space="preserve">0.118569433689117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.118820391595364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.115934558212757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109159171581268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107088901102543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10614787787199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104140356183052</t>
+    <t xml:space="preserve">0.118820376694202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.115934580564499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109159179031849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107088908553123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10614787042141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104140348732471</t>
   </si>
   <si>
     <t xml:space="preserve">0.105646006762981</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">0.10746531188488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108531802892685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107590794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109535582363605</t>
+    <t xml:space="preserve">0.108531817793846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107590779662132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109535589814186</t>
   </si>
   <si>
     <t xml:space="preserve">0.10483043640852</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108092658221722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108029924333096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107653506100178</t>
+    <t xml:space="preserve">0.108092673122883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108029931783676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1076535359025</t>
   </si>
   <si>
     <t xml:space="preserve">0.109849266707897</t>
@@ -485,115 +485,115 @@
     <t xml:space="preserve">0.11160583794117</t>
   </si>
   <si>
-    <t xml:space="preserve">0.113738819956779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.113864302635193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11028840392828</t>
+    <t xml:space="preserve">0.113738849759102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113864287734032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110288389027119</t>
   </si>
   <si>
     <t xml:space="preserve">0.110225662589073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108845494687557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109723798930645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107339859008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108406335115433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10451677441597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105018645524979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106649748980999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105834193527699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106085166335106</t>
+    <t xml:space="preserve">0.108845509588718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109723791480064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107339851558208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108406342566013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104516766965389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105018652975559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10664976388216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10583420842886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106085158884525</t>
   </si>
   <si>
     <t xml:space="preserve">0.109786532819271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104391284286976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107778988778591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.107214391231537</t>
+    <t xml:space="preserve">0.104391299188137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107778981328011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.107214383780956</t>
   </si>
   <si>
     <t xml:space="preserve">0.11606003344059</t>
   </si>
   <si>
-    <t xml:space="preserve">0.114742577075958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112421400845051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11342515796423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112295925617218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106022424995899</t>
+    <t xml:space="preserve">0.114742606878281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112421408295631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.113425172865391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.112295918166637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106022410094738</t>
   </si>
   <si>
     <t xml:space="preserve">0.106712512671947</t>
   </si>
   <si>
-    <t xml:space="preserve">0.106837965548038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.105520531535149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.104265816509724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102760188281536</t>
+    <t xml:space="preserve">0.106837972998619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.105520538985729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.104265831410885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102760180830956</t>
   </si>
   <si>
     <t xml:space="preserve">0.101003594696522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.104579515755177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.102885641157627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.103889413177967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101254537701607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.100564450025558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101066336035728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.101630955934525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.106524281203747</t>
+    <t xml:space="preserve">0.104579508304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.102885663509369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.103889428079128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101254545152187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10056446492672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101066321134567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.101630948483944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.106524296104908</t>
   </si>
   <si>
     <t xml:space="preserve">0.109911993145943</t>
@@ -602,58 +602,58 @@
     <t xml:space="preserve">0.110539354383945</t>
   </si>
   <si>
-    <t xml:space="preserve">0.110915757715702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.108657293021679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.112609602510929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.111292146146297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109410114586353</t>
+    <t xml:space="preserve">0.110915742814541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.108657278120518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11260960996151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.111292161047459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109410099685192</t>
   </si>
   <si>
     <t xml:space="preserve">0.108343623578548</t>
   </si>
   <si>
-    <t xml:space="preserve">0.108280874788761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.109033711254597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.110351122915745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128544315695763</t>
+    <t xml:space="preserve">0.108280897140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.109033703804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.110351137816906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128544330596924</t>
   </si>
   <si>
     <t xml:space="preserve">0.15370112657547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144918218255043</t>
+    <t xml:space="preserve">0.144918203353882</t>
   </si>
   <si>
     <t xml:space="preserve">0.142408803105354</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132371157407761</t>
+    <t xml:space="preserve">0.132371187210083</t>
   </si>
   <si>
     <t xml:space="preserve">0.132684856653214</t>
   </si>
   <si>
-    <t xml:space="preserve">0.13425324857235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131304681301117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134692385792732</t>
+    <t xml:space="preserve">0.134253233671188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131304666399956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134692370891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.135821610689163</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">0.139836654067039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.142659738659859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.144855484366417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143161609768867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141781434416771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133500382304192</t>
+    <t xml:space="preserve">0.14265975356102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.144855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143161624670029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141781464219093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133500412106514</t>
   </si>
   <si>
     <t xml:space="preserve">0.129861786961555</t>
@@ -683,82 +683,82 @@
     <t xml:space="preserve">0.130175441503525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131681114435196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130112707614899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130740061402321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124842971563339</t>
+    <t xml:space="preserve">0.131681084632874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13011272251606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13074004650116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124842956662178</t>
   </si>
   <si>
     <t xml:space="preserve">0.126097664237022</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126975938677788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127289637923241</t>
+    <t xml:space="preserve">0.12697596848011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127289623022079</t>
   </si>
   <si>
     <t xml:space="preserve">0.127226904034615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126411318778992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1254703104496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126536816358566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124215587973595</t>
+    <t xml:space="preserve">0.126411333680153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125470295548439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126536801457405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124215602874756</t>
   </si>
   <si>
     <t xml:space="preserve">0.12597219645977</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130551844835281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.130677327513695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132182985544205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129171684384346</t>
+    <t xml:space="preserve">0.130551859736443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130677312612534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132182970643044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129171699285507</t>
   </si>
   <si>
     <t xml:space="preserve">0.132245719432831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135006040334702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133939549326897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134127765893936</t>
+    <t xml:space="preserve">0.135006070137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133939519524574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134127750992775</t>
   </si>
   <si>
     <t xml:space="preserve">0.136260747909546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134943321347237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.137766420841217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13801734149456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777707099915</t>
+    <t xml:space="preserve">0.134943306446075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.137766391038895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138017326593399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777692198753</t>
   </si>
   <si>
     <t xml:space="preserve">0.145733758807182</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.144165381789207</t>
   </si>
   <si>
-    <t xml:space="preserve">0.143977165222168</t>
+    <t xml:space="preserve">0.143977180123329</t>
   </si>
   <si>
     <t xml:space="preserve">0.14115409553051</t>
@@ -791,49 +791,49 @@
     <t xml:space="preserve">0.129673570394516</t>
   </si>
   <si>
-    <t xml:space="preserve">0.128356143832207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132496640086174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135633409023285</t>
+    <t xml:space="preserve">0.128356128931046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132496654987335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135633423924446</t>
   </si>
   <si>
     <t xml:space="preserve">0.137891873717308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137703686952591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132433891296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13205748796463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134504169225693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134502395987511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132989749312401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.131729185581207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13072070479393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13317883014679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134565457701683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134943619370461</t>
+    <t xml:space="preserve">0.13770367205143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132433921098709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132057502865791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134504154324532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134502425789833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.13298973441124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.131729170680046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.130720734596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133178815245628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134565427899361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134943634271622</t>
   </si>
   <si>
     <t xml:space="preserve">0.131792202591896</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">0.131477057933807</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132359445095062</t>
+    <t xml:space="preserve">0.132359459996223</t>
   </si>
   <si>
     <t xml:space="preserve">0.13090980052948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.130468606948853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129964381456375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127506285905838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.129586189985275</t>
+    <t xml:space="preserve">0.13046857714653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129964396357536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127506256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.129586204886436</t>
   </si>
   <si>
     <t xml:space="preserve">0.127002045512199</t>
@@ -869,46 +869,46 @@
     <t xml:space="preserve">0.128199592232704</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12870380282402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126371756196022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125930562615395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.127128124237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126056626439095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124796032905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.12466999143362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.124165780842304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125174224376678</t>
+    <t xml:space="preserve">0.128703817725182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126371771097183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125930547714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.127128109335899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126056611537933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124796062707901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124670013785362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.124165765941143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125174209475517</t>
   </si>
   <si>
     <t xml:space="preserve">0.125237256288528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129018932580948</t>
+    <t xml:space="preserve">0.129018947482109</t>
   </si>
   <si>
     <t xml:space="preserve">0.127380222082138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.12845167517662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128136545419693</t>
+    <t xml:space="preserve">0.128451690077782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128136560320854</t>
   </si>
   <si>
     <t xml:space="preserve">0.127884447574615</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">0.127443239092827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126939013600349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.128262624144554</t>
+    <t xml:space="preserve">0.126938998699188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.128262609243393</t>
   </si>
   <si>
     <t xml:space="preserve">0.126875981688499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.126497805118561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126308724284172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133430927991867</t>
+    <t xml:space="preserve">0.126497820019722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126308739185333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133430942893028</t>
   </si>
   <si>
     <t xml:space="preserve">0.135573893785477</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">0.136456280946732</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135636910796165</t>
+    <t xml:space="preserve">0.135636940598488</t>
   </si>
   <si>
     <t xml:space="preserve">0.134061217308044</t>
   </si>
   <si>
-    <t xml:space="preserve">0.132485494017601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133557006716728</t>
+    <t xml:space="preserve">0.132485508918762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133556976914406</t>
   </si>
   <si>
     <t xml:space="preserve">0.135195717215538</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">0.136141166090965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134439393877983</t>
+    <t xml:space="preserve">0.134439378976822</t>
   </si>
   <si>
     <t xml:space="preserve">0.137464731931686</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">0.138221085071564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137842908501625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.136330232024193</t>
+    <t xml:space="preserve">0.137842923402786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.136330217123032</t>
   </si>
   <si>
     <t xml:space="preserve">0.13708658516407</t>
   </si>
   <si>
-    <t xml:space="preserve">0.136771410703659</t>
+    <t xml:space="preserve">0.136771440505981</t>
   </si>
   <si>
     <t xml:space="preserve">0.136204183101654</t>
@@ -992,22 +992,22 @@
     <t xml:space="preserve">0.135006636381149</t>
   </si>
   <si>
-    <t xml:space="preserve">0.134754538536072</t>
+    <t xml:space="preserve">0.134754523634911</t>
   </si>
   <si>
     <t xml:space="preserve">0.13506968319416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.137401714920998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151141911745071</t>
+    <t xml:space="preserve">0.137401729822159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151141881942749</t>
   </si>
   <si>
     <t xml:space="preserve">0.153789088129997</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152780622243881</t>
+    <t xml:space="preserve">0.152780637145042</t>
   </si>
   <si>
     <t xml:space="preserve">0.151267930865288</t>
@@ -1019,52 +1019,52 @@
     <t xml:space="preserve">0.14704504609108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.157444715499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.159398585557938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.156625360250473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.157570764422417</t>
+    <t xml:space="preserve">0.157444700598717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159398600459099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.156625375151634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157570779323578</t>
   </si>
   <si>
     <t xml:space="preserve">0.152843654155731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.152654558420181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151898235082626</t>
+    <t xml:space="preserve">0.152654573321342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151898220181465</t>
   </si>
   <si>
     <t xml:space="preserve">0.15309576690197</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150259494781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14874678850174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153347879648209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.155805975198746</t>
+    <t xml:space="preserve">0.150259479880333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.148746803402901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.15334789454937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.155805990099907</t>
   </si>
   <si>
     <t xml:space="preserve">0.154419362545013</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156940490007401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15914648771286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.167655318975449</t>
+    <t xml:space="preserve">0.156940504908562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.159146472811699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.167655304074287</t>
   </si>
   <si>
     <t xml:space="preserve">0.170050382614136</t>
@@ -1079,10 +1079,10 @@
     <t xml:space="preserve">0.179945811629295</t>
   </si>
   <si>
-    <t xml:space="preserve">0.178811311721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.17521870136261</t>
+    <t xml:space="preserve">0.178811296820641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.175218716263771</t>
   </si>
   <si>
     <t xml:space="preserve">0.174336314201355</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">0.170176446437836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.176479294896126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.173642992973328</t>
+    <t xml:space="preserve">0.176479265093803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.173642978072166</t>
   </si>
   <si>
     <t xml:space="preserve">0.170365512371063</t>
@@ -1109,43 +1109,43 @@
     <t xml:space="preserve">0.168600738048553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.166520819067955</t>
+    <t xml:space="preserve">0.166520789265633</t>
   </si>
   <si>
     <t xml:space="preserve">0.166394740343094</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161730661988258</t>
+    <t xml:space="preserve">0.161730647087097</t>
   </si>
   <si>
     <t xml:space="preserve">0.160091906785965</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156688407063484</t>
+    <t xml:space="preserve">0.156688392162323</t>
   </si>
   <si>
     <t xml:space="preserve">0.16122642159462</t>
   </si>
   <si>
-    <t xml:space="preserve">0.162486985325813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163747549057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.163873597979546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.161037340760231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.158011958003044</t>
+    <t xml:space="preserve">0.162487000226974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163747534155846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163873612880707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16103732585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.158011987805367</t>
   </si>
   <si>
     <t xml:space="preserve">0.157759860157967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.167970463633537</t>
+    <t xml:space="preserve">0.167970448732376</t>
   </si>
   <si>
     <t xml:space="preserve">0.167718321084976</t>
@@ -1157,31 +1157,31 @@
     <t xml:space="preserve">0.163117274641991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163810580968857</t>
+    <t xml:space="preserve">0.163810566067696</t>
   </si>
   <si>
     <t xml:space="preserve">0.159461632370949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.147675350308418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.14748626947403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150007382035255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150448605418205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.150511607527733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.15107886493206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151646107435226</t>
+    <t xml:space="preserve">0.147675335407257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147486239671707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150007367134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150448575615883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.150511622428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151078850030899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151646122336388</t>
   </si>
   <si>
     <t xml:space="preserve">0.150322526693344</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">0.151772171258926</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149881318211555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.151583105325699</t>
+    <t xml:space="preserve">0.149881333112717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.151583075523376</t>
   </si>
   <si>
     <t xml:space="preserve">0.149629205465317</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">0.15101583302021</t>
   </si>
   <si>
-    <t xml:space="preserve">0.148935899138451</t>
+    <t xml:space="preserve">0.148935928940773</t>
   </si>
   <si>
     <t xml:space="preserve">0.148116528987885</t>
   </si>
   <si>
-    <t xml:space="preserve">0.150763720273972</t>
+    <t xml:space="preserve">0.15076370537281</t>
   </si>
   <si>
     <t xml:space="preserve">0.150637671351433</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">0.151204913854599</t>
   </si>
   <si>
-    <t xml:space="preserve">0.149944365024567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152213379740715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.152528509497643</t>
+    <t xml:space="preserve">0.149944335222244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152213364839554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.152528524398804</t>
   </si>
   <si>
     <t xml:space="preserve">0.149377107620239</t>
@@ -1241,19 +1241,19 @@
     <t xml:space="preserve">0.157255634665489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.156310230493546</t>
+    <t xml:space="preserve">0.156310200691223</t>
   </si>
   <si>
     <t xml:space="preserve">0.164503902196884</t>
   </si>
   <si>
-    <t xml:space="preserve">0.163243323564529</t>
+    <t xml:space="preserve">0.163243308663368</t>
   </si>
   <si>
     <t xml:space="preserve">0.162613034248352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.161982774734497</t>
+    <t xml:space="preserve">0.161982759833336</t>
   </si>
   <si>
     <t xml:space="preserve">0.163558468222618</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">0.165764465928078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.165449306368828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.166079610586166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.160722196102142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.162297904491425</t>
+    <t xml:space="preserve">0.165449321269989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.166079595685005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.16072216629982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.162297889590263</t>
   </si>
   <si>
     <t xml:space="preserve">0.149061962962151</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">0.139607697725296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.138032004237175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.139922842383385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135826006531715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.138347163796425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141498550772667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.141813695430756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140553146600723</t>
+    <t xml:space="preserve">0.138031989336014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139922857284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135826021432877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.138347148895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141498565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.141813710331917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140553131699562</t>
   </si>
   <si>
     <t xml:space="preserve">0.141183421015739</t>
@@ -1325,34 +1325,34 @@
     <t xml:space="preserve">0.138662293553352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.135510876774788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.134250298142433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.133935153484344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13267457485199</t>
+    <t xml:space="preserve">0.135510861873627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.134250313043594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.133935168385506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132674604654312</t>
   </si>
   <si>
     <t xml:space="preserve">0.143074259161949</t>
   </si>
   <si>
-    <t xml:space="preserve">0.144965127110481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.143389418721199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.142443984746933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.146575853228569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.147864401340485</t>
+    <t xml:space="preserve">0.14496511220932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.143389403820038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.142443969845772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.146575838327408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.147864416241646</t>
   </si>
   <si>
     <t xml:space="preserve">0.146253690123558</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">0.145609393715858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.140455082058907</t>
+    <t xml:space="preserve">0.140455096960068</t>
   </si>
   <si>
     <t xml:space="preserve">0.142710089683533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.141421541571617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13916651904583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.140777230262756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.13948866724968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.135622903704643</t>
+    <t xml:space="preserve">0.141421526670456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139166504144669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.140777245163918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.139488652348518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.135622918605804</t>
   </si>
   <si>
     <t xml:space="preserve">0.133690044283867</t>
@@ -1397,43 +1397,40 @@
     <t xml:space="preserve">0.125765293836594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.124992154538631</t>
+    <t xml:space="preserve">0.12499213218689</t>
   </si>
   <si>
     <t xml:space="preserve">0.126796156167984</t>
   </si>
   <si>
-    <t xml:space="preserve">0.129180029034615</t>
+    <t xml:space="preserve">0.129180014133453</t>
   </si>
   <si>
     <t xml:space="preserve">0.133367910981178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.131757184863091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.125894159078598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.126925021409988</t>
+    <t xml:space="preserve">0.131757199764252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.125894144177437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.126925006508827</t>
   </si>
   <si>
   